--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M266"/>
+  <dimension ref="A1:M269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9494,6 +9494,108 @@
       </c>
       <c r="M266" t="n">
         <v>1.264947</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>03/02</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>2.9106</v>
+      </c>
+      <c r="D267" t="n">
+        <v>2.9106</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.668666</v>
+      </c>
+      <c r="F267" t="n">
+        <v>-0.8265</v>
+      </c>
+      <c r="H267" t="n">
+        <v>-0.8265</v>
+      </c>
+      <c r="I267" t="n">
+        <v>1.103546</v>
+      </c>
+      <c r="J267" t="n">
+        <v>-2.0512</v>
+      </c>
+      <c r="L267" t="n">
+        <v>-2.0512</v>
+      </c>
+      <c r="M267" t="n">
+        <v>1.239</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>03/03</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>6.0064</v>
+      </c>
+      <c r="D268" t="n">
+        <v>6.0064</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.708829</v>
+      </c>
+      <c r="F268" t="n">
+        <v>-1.2305</v>
+      </c>
+      <c r="H268" t="n">
+        <v>-1.2305</v>
+      </c>
+      <c r="I268" t="n">
+        <v>1.089967</v>
+      </c>
+      <c r="J268" t="n">
+        <v>-2.6202</v>
+      </c>
+      <c r="L268" t="n">
+        <v>-2.6202</v>
+      </c>
+      <c r="M268" t="n">
+        <v>1.206536</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>03/04</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>-1.1185</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-1.1185</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1.093537</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1.0806</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1.0806</v>
+      </c>
+      <c r="M269" t="n">
+        <v>1.219574</v>
       </c>
     </row>
   </sheetData>
@@ -9507,7 +9609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E266"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14570,6 +14672,63 @@
       </c>
       <c r="E266" t="n">
         <v>1.577578</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>03/02</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>-0.4877</v>
+      </c>
+      <c r="C267" t="n">
+        <v>-1.5626</v>
+      </c>
+      <c r="D267" t="n">
+        <v>-1.0252</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.561405</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>03/03</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-2.5706</v>
+      </c>
+      <c r="C268" t="n">
+        <v>-5.2132</v>
+      </c>
+      <c r="D268" t="n">
+        <v>-3.8919</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1.500637</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>03/04</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>-1.4055</v>
+      </c>
+      <c r="C269" t="n">
+        <v>-0.4934</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-0.9495</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1.486389</v>
       </c>
     </row>
   </sheetData>
@@ -14583,7 +14742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E266"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19646,6 +19805,63 @@
       </c>
       <c r="E266" t="n">
         <v>1.499464</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>03/02</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="C267" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="D267" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.561841</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>03/03</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="C268" t="n">
+        <v>-1.695</v>
+      </c>
+      <c r="D268" t="n">
+        <v>-0.975</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1.546613</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>03/04</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="C269" t="n">
+        <v>-1.475</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1.559218</v>
       </c>
     </row>
   </sheetData>
@@ -19659,7 +19875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26804,6 +27020,93 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>03/02</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>-0.6317</v>
+      </c>
+      <c r="C247" t="n">
+        <v>-0.09669999999999999</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-0.535</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1.025204</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 煤炭, 环保</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>03/03</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>-1.6233</v>
+      </c>
+      <c r="C248" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2.5867</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1.051723</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 煤炭, 环保</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>03/04</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>-0.7267</v>
+      </c>
+      <c r="C249" t="n">
+        <v>-0.5317</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-0.195</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1.049672</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 环保, 煤炭</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M269"/>
+  <dimension ref="A1:M270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9596,6 +9596,40 @@
       </c>
       <c r="M269" t="n">
         <v>1.219574</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>03/05</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>-1.8355</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-1.8355</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.688035</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="I270" t="n">
+        <v>1.095485</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0.6499</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0.6499</v>
+      </c>
+      <c r="M270" t="n">
+        <v>1.2275</v>
       </c>
     </row>
   </sheetData>
@@ -9609,7 +9643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E269"/>
+  <dimension ref="A1:E270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14729,6 +14763,25 @@
       </c>
       <c r="E269" t="n">
         <v>1.486389</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>03/05</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>1.6612</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1.7223</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1.6917</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1.511535</v>
       </c>
     </row>
   </sheetData>
@@ -14742,7 +14795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E269"/>
+  <dimension ref="A1:E270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19862,6 +19915,25 @@
       </c>
       <c r="E269" t="n">
         <v>1.559218</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>03/05</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-0.585</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1.550097</v>
       </c>
     </row>
   </sheetData>
@@ -19875,7 +19947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:G250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27107,6 +27179,35 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>03/05</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1.6883</v>
+      </c>
+      <c r="D250" t="n">
+        <v>-1.1183</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1.037933</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 环保, 钢铁</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M270"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9630,6 +9630,40 @@
       </c>
       <c r="M270" t="n">
         <v>1.2275</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>03/06</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.4555</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-0.4555</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.684901</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1.098988</v>
+      </c>
+      <c r="J271" t="n">
+        <v>1.0687</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1.0687</v>
+      </c>
+      <c r="M271" t="n">
+        <v>1.240618</v>
       </c>
     </row>
   </sheetData>
@@ -9643,7 +9677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E270"/>
+  <dimension ref="A1:E271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14782,6 +14816,25 @@
       </c>
       <c r="E270" t="n">
         <v>1.511535</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>03/06</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.5138</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1.519301</v>
       </c>
     </row>
   </sheetData>
@@ -14795,7 +14848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E270"/>
+  <dimension ref="A1:E271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19934,6 +19987,25 @@
       </c>
       <c r="E270" t="n">
         <v>1.550097</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>03/06</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.6633</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-2.5083</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1.511215</v>
       </c>
     </row>
   </sheetData>
@@ -19947,7 +20019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G250"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27208,6 +27280,35 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>03/06</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1.5167</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1.4167</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1.052637</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 环保, 钢铁</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9664,6 +9664,74 @@
       </c>
       <c r="M271" t="n">
         <v>1.240618</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>03/09</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1.7589</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1.7589</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.696948</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="I272" t="n">
+        <v>1.100305</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="M272" t="n">
+        <v>1.242262</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>03/10</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-2.9122</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-2.9122</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0.676652</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="I273" t="n">
+        <v>1.105468</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0.9009</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0.9009</v>
+      </c>
+      <c r="M273" t="n">
+        <v>1.253454</v>
       </c>
     </row>
   </sheetData>
@@ -9677,7 +9745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E271"/>
+  <dimension ref="A1:E273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14835,6 +14903,44 @@
       </c>
       <c r="E271" t="n">
         <v>1.519301</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>03/09</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>-0.6415999999999999</v>
+      </c>
+      <c r="C272" t="n">
+        <v>-1.6906</v>
+      </c>
+      <c r="D272" t="n">
+        <v>-1.1661</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.501585</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>03/10</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>3.0406</v>
+      </c>
+      <c r="C273" t="n">
+        <v>2.1616</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2.6011</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.540643</v>
       </c>
     </row>
   </sheetData>
@@ -14848,7 +14954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E271"/>
+  <dimension ref="A1:E273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20006,6 +20112,44 @@
       </c>
       <c r="E271" t="n">
         <v>1.511215</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>03/09</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="C272" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1.1533</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.528645</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>03/10</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-0.8333</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-2.1083</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.496416</v>
       </c>
     </row>
   </sheetData>
@@ -20019,7 +20163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27309,6 +27453,64 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>03/09</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>-0.495</v>
+      </c>
+      <c r="C252" t="n">
+        <v>-0.705</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1.054847</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 房地产, 环保</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>03/10</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C253" t="n">
+        <v>2.4783</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-1.8583</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1.035245</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 房地产, 钢铁</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M273"/>
+  <dimension ref="A1:M276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9732,6 +9732,108 @@
       </c>
       <c r="M273" t="n">
         <v>1.253454</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>03/11</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>2.8246</v>
+      </c>
+      <c r="D274" t="n">
+        <v>2.8246</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.695764</v>
+      </c>
+      <c r="F274" t="n">
+        <v>-0.3685</v>
+      </c>
+      <c r="H274" t="n">
+        <v>-0.3685</v>
+      </c>
+      <c r="I274" t="n">
+        <v>1.101394</v>
+      </c>
+      <c r="J274" t="n">
+        <v>-0.9084</v>
+      </c>
+      <c r="L274" t="n">
+        <v>-0.9084</v>
+      </c>
+      <c r="M274" t="n">
+        <v>1.242067</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>03/12</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>2.4525</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2.4525</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.712828</v>
+      </c>
+      <c r="F275" t="n">
+        <v>-0.214</v>
+      </c>
+      <c r="H275" t="n">
+        <v>-0.214</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1.099037</v>
+      </c>
+      <c r="J275" t="n">
+        <v>-0.799</v>
+      </c>
+      <c r="L275" t="n">
+        <v>-0.799</v>
+      </c>
+      <c r="M275" t="n">
+        <v>1.232143</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>03/13</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.715356</v>
+      </c>
+      <c r="F276" t="n">
+        <v>-0.6158</v>
+      </c>
+      <c r="H276" t="n">
+        <v>-0.6158</v>
+      </c>
+      <c r="I276" t="n">
+        <v>1.09227</v>
+      </c>
+      <c r="J276" t="n">
+        <v>-0.9287</v>
+      </c>
+      <c r="L276" t="n">
+        <v>-0.9287</v>
+      </c>
+      <c r="M276" t="n">
+        <v>1.2207</v>
       </c>
     </row>
   </sheetData>
@@ -9745,7 +9847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14941,6 +15043,63 @@
       </c>
       <c r="E273" t="n">
         <v>1.540643</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>03/11</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1.3123</v>
+      </c>
+      <c r="C274" t="n">
+        <v>-1.3695</v>
+      </c>
+      <c r="D274" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1.540202</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>03/12</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>-0.9555</v>
+      </c>
+      <c r="C275" t="n">
+        <v>-1.2442</v>
+      </c>
+      <c r="D275" t="n">
+        <v>-1.0998</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1.523262</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>03/13</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>-0.2184</v>
+      </c>
+      <c r="C276" t="n">
+        <v>-0.7239</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-0.4712</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1.516085</v>
       </c>
     </row>
   </sheetData>
@@ -14954,7 +15113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20150,6 +20309,63 @@
       </c>
       <c r="E273" t="n">
         <v>1.496416</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>03/11</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="C274" t="n">
+        <v>-0.235</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.8217</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1.508711</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>03/12</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>1.3833</v>
+      </c>
+      <c r="C275" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1.9533</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1.538181</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>03/13</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-1.955</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1.50811</v>
       </c>
     </row>
   </sheetData>
@@ -20163,7 +20379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G253"/>
+  <dimension ref="A1:G256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27511,6 +27727,93 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>03/11</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>-0.4067</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="D254" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1.029551</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 房地产, 钢铁</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>03/12</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>-0.1033</v>
+      </c>
+      <c r="C255" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.8967000000000001</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1.038783</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>综合, 美容护理, 社会服务, 纺织服饰, 房地产, 钢铁</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>03/13</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>-0.9817</v>
+      </c>
+      <c r="C256" t="n">
+        <v>-1.515</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1.044323</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 房地产, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M276"/>
+  <dimension ref="A1:M277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9834,6 +9834,40 @@
       </c>
       <c r="M276" t="n">
         <v>1.2207</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>03/16</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-1.5333</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-1.5333</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.704387</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1.093364</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0.2559</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0.2559</v>
+      </c>
+      <c r="M277" t="n">
+        <v>1.223824</v>
       </c>
     </row>
   </sheetData>
@@ -9847,7 +9881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15100,6 +15134,25 @@
       </c>
       <c r="E276" t="n">
         <v>1.516085</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>03/16</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>1.4121</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.8263</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1.1192</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1.533053</v>
       </c>
     </row>
   </sheetData>
@@ -15113,7 +15166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20366,6 +20419,25 @@
       </c>
       <c r="E276" t="n">
         <v>1.50811</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>03/16</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-2.6033</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-3.8233</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1.45045</v>
       </c>
     </row>
   </sheetData>
@@ -20379,7 +20451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G256"/>
+  <dimension ref="A1:G257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27814,6 +27886,35 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>03/16</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="C257" t="n">
+        <v>-0.1533</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.6516999999999999</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1.051128</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 房地产, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M277"/>
+  <dimension ref="A1:M278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9868,6 +9868,40 @@
       </c>
       <c r="M277" t="n">
         <v>1.223824</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>03/17</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.71484</v>
+      </c>
+      <c r="F278" t="n">
+        <v>-1.0214</v>
+      </c>
+      <c r="H278" t="n">
+        <v>-1.0214</v>
+      </c>
+      <c r="I278" t="n">
+        <v>1.082196</v>
+      </c>
+      <c r="J278" t="n">
+        <v>-1.7678</v>
+      </c>
+      <c r="L278" t="n">
+        <v>-1.7678</v>
+      </c>
+      <c r="M278" t="n">
+        <v>1.202189</v>
       </c>
     </row>
   </sheetData>
@@ -9881,7 +9915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15153,6 +15187,25 @@
       </c>
       <c r="E277" t="n">
         <v>1.533053</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>03/17</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>-2.2926</v>
+      </c>
+      <c r="C278" t="n">
+        <v>-2.2263</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-2.2595</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1.498415</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -15219,7 +15219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20491,6 +20491,25 @@
       </c>
       <c r="E277" t="n">
         <v>1.45045</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>03/17</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>-1.3733</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-1.5233</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1.428355</v>
       </c>
     </row>
   </sheetData>
@@ -20504,7 +20523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27968,6 +27987,35 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>03/17</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-1.0083</v>
+      </c>
+      <c r="C258" t="n">
+        <v>-2.7167</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1.7083</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1.069085</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 房地产, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M278"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9902,6 +9902,108 @@
       </c>
       <c r="M278" t="n">
         <v>1.202189</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>03/18</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>-1.9583</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-1.9583</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.700841</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="I279" t="n">
+        <v>1.087956</v>
+      </c>
+      <c r="J279" t="n">
+        <v>1.1158</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1.1158</v>
+      </c>
+      <c r="M279" t="n">
+        <v>1.215603</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>03/19</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>1.8573</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1.8573</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.713858</v>
+      </c>
+      <c r="F280" t="n">
+        <v>-0.2331</v>
+      </c>
+      <c r="H280" t="n">
+        <v>-0.2331</v>
+      </c>
+      <c r="I280" t="n">
+        <v>1.08542</v>
+      </c>
+      <c r="J280" t="n">
+        <v>-0.9412</v>
+      </c>
+      <c r="L280" t="n">
+        <v>-0.9412</v>
+      </c>
+      <c r="M280" t="n">
+        <v>1.204162</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>03/20</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>1.0902</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1.0902</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.721641</v>
+      </c>
+      <c r="F281" t="n">
+        <v>-0.7534</v>
+      </c>
+      <c r="H281" t="n">
+        <v>-0.7534</v>
+      </c>
+      <c r="I281" t="n">
+        <v>1.077242</v>
+      </c>
+      <c r="J281" t="n">
+        <v>-2.2286</v>
+      </c>
+      <c r="L281" t="n">
+        <v>-2.2286</v>
+      </c>
+      <c r="M281" t="n">
+        <v>1.177326</v>
       </c>
     </row>
   </sheetData>
@@ -9915,7 +10017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15206,6 +15308,63 @@
       </c>
       <c r="E278" t="n">
         <v>1.498415</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>03/18</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>2.0215</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1.3605</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1.691</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1.523753</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>03/19</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-1.1135</v>
+      </c>
+      <c r="C280" t="n">
+        <v>-2.4438</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-1.7786</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1.496651</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>03/20</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>1.2994</v>
+      </c>
+      <c r="C281" t="n">
+        <v>-1.5479</v>
+      </c>
+      <c r="D281" t="n">
+        <v>-0.1242</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1.494791</v>
       </c>
     </row>
   </sheetData>
@@ -15219,7 +15378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20510,6 +20669,63 @@
       </c>
       <c r="E278" t="n">
         <v>1.428355</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>03/18</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>-0.6233</v>
+      </c>
+      <c r="C279" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.4683</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1.421665</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>03/19</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-2.7867</v>
+      </c>
+      <c r="C280" t="n">
+        <v>-1.575</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-1.2117</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1.404439</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>03/20</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>-1.1033</v>
+      </c>
+      <c r="C281" t="n">
+        <v>-1.255</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1.406569</v>
       </c>
     </row>
   </sheetData>
@@ -20523,7 +20739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28016,6 +28232,93 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>03/18</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1.8483</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-1.505</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1.052995</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 房地产, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>03/19</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>-2.435</v>
+      </c>
+      <c r="C260" t="n">
+        <v>-2.565</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1.054364</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 房地产, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>03/20</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-2.6167</v>
+      </c>
+      <c r="C261" t="n">
+        <v>-0.8917</v>
+      </c>
+      <c r="D261" t="n">
+        <v>-1.725</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1.036177</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M281"/>
+  <dimension ref="A1:M285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10004,6 +10004,142 @@
       </c>
       <c r="M281" t="n">
         <v>1.177326</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>03/23</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1.7755</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1.7755</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.734453</v>
+      </c>
+      <c r="F282" t="n">
+        <v>-0.9802</v>
+      </c>
+      <c r="H282" t="n">
+        <v>-0.9802</v>
+      </c>
+      <c r="I282" t="n">
+        <v>1.066683</v>
+      </c>
+      <c r="J282" t="n">
+        <v>-2.1259</v>
+      </c>
+      <c r="L282" t="n">
+        <v>-2.1259</v>
+      </c>
+      <c r="M282" t="n">
+        <v>1.152297</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>03/24</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>-0.7865</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-0.7865</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.728677</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.8482</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0.8482</v>
+      </c>
+      <c r="I283" t="n">
+        <v>1.075731</v>
+      </c>
+      <c r="J283" t="n">
+        <v>2.4572</v>
+      </c>
+      <c r="L283" t="n">
+        <v>2.4572</v>
+      </c>
+      <c r="M283" t="n">
+        <v>1.180612</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>03/25</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>-1.6624</v>
+      </c>
+      <c r="D284" t="n">
+        <v>-1.6624</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.7165629999999999</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="I284" t="n">
+        <v>1.079417</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0.8823</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0.8823</v>
+      </c>
+      <c r="M284" t="n">
+        <v>1.191028</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2.0672</v>
+      </c>
+      <c r="D285" t="n">
+        <v>2.0672</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.731376</v>
+      </c>
+      <c r="F285" t="n">
+        <v>-0.0925</v>
+      </c>
+      <c r="H285" t="n">
+        <v>-0.0925</v>
+      </c>
+      <c r="I285" t="n">
+        <v>1.078419</v>
+      </c>
+      <c r="J285" t="n">
+        <v>-0.2593</v>
+      </c>
+      <c r="L285" t="n">
+        <v>-0.2593</v>
+      </c>
+      <c r="M285" t="n">
+        <v>1.18794</v>
       </c>
     </row>
   </sheetData>
@@ -10017,7 +10153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15365,6 +15501,82 @@
       </c>
       <c r="E281" t="n">
         <v>1.494791</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>03/23</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-3.4868</v>
+      </c>
+      <c r="C282" t="n">
+        <v>-4.3138</v>
+      </c>
+      <c r="D282" t="n">
+        <v>-3.9003</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1.43649</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>03/24</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="C283" t="n">
+        <v>2.327</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1.4158</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1.456827</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>03/25</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>2.0122</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1.9074</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1.9598</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1.485378</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>-1.3411</v>
+      </c>
+      <c r="C285" t="n">
+        <v>-2.0226</v>
+      </c>
+      <c r="D285" t="n">
+        <v>-1.6819</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1.460397</v>
       </c>
     </row>
   </sheetData>
@@ -15378,7 +15590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20726,6 +20938,82 @@
       </c>
       <c r="E281" t="n">
         <v>1.406569</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>03/23</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="C282" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1.422323</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>03/24</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>2.1067</v>
+      </c>
+      <c r="C283" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1.422773</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>03/25</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1.1667</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1.427635</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>-0.9467</v>
+      </c>
+      <c r="C285" t="n">
+        <v>-1.015</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1.42861</v>
       </c>
     </row>
   </sheetData>
@@ -20739,7 +21027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28319,6 +28607,122 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>03/23</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>-5.5467</v>
+      </c>
+      <c r="C262" t="n">
+        <v>-4.4883</v>
+      </c>
+      <c r="D262" t="n">
+        <v>-1.0583</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1.02521</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 有色金属, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>03/24</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2.8433</v>
+      </c>
+      <c r="C263" t="n">
+        <v>2.3183</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1.030593</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 有色金属, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>03/25</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>2.2433</v>
+      </c>
+      <c r="C264" t="n">
+        <v>2.4317</v>
+      </c>
+      <c r="D264" t="n">
+        <v>-0.1883</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1.028652</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 有色金属, 机械设备, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>03/26</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-1.4167</v>
+      </c>
+      <c r="C265" t="n">
+        <v>-1.9533</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1.034172</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 有色金属, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10140,6 +10140,40 @@
       </c>
       <c r="M285" t="n">
         <v>1.18794</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>03/27</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>-0.6981000000000001</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-0.6981000000000001</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.72627</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="I286" t="n">
+        <v>1.083346</v>
+      </c>
+      <c r="J286" t="n">
+        <v>1.0066</v>
+      </c>
+      <c r="L286" t="n">
+        <v>1.0066</v>
+      </c>
+      <c r="M286" t="n">
+        <v>1.199898</v>
       </c>
     </row>
   </sheetData>
@@ -10153,7 +10187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15577,6 +15611,25 @@
       </c>
       <c r="E285" t="n">
         <v>1.460397</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>03/27</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.7148</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.9271</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1.472386</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -15643,7 +15643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21067,6 +21067,25 @@
       </c>
       <c r="E285" t="n">
         <v>1.42861</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>03/27</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="C286" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1.411324</v>
       </c>
     </row>
   </sheetData>
@@ -21080,7 +21099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28776,6 +28795,35 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>03/27</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>1.1133</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1.0433</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1.034896</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 有色金属, 计算机, 通信</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M286"/>
+  <dimension ref="A1:M287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10174,6 +10174,40 @@
       </c>
       <c r="M286" t="n">
         <v>1.199898</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>03/30</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>1.7678</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1.7678</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.739109</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.2332</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0.2332</v>
+      </c>
+      <c r="I287" t="n">
+        <v>1.085872</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0.6026</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0.6026</v>
+      </c>
+      <c r="M287" t="n">
+        <v>1.207128</v>
       </c>
     </row>
   </sheetData>
@@ -10187,7 +10221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E286"/>
+  <dimension ref="A1:E287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15630,6 +15664,25 @@
       </c>
       <c r="E286" t="n">
         <v>1.472386</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>03/30</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>-0.6834</v>
+      </c>
+      <c r="C287" t="n">
+        <v>-0.8438</v>
+      </c>
+      <c r="D287" t="n">
+        <v>-0.7635999999999999</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1.461143</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -15696,7 +15696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E286"/>
+  <dimension ref="A1:E287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21139,6 +21139,25 @@
       </c>
       <c r="E286" t="n">
         <v>1.411324</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>03/30</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0.7867</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1.412194</v>
       </c>
     </row>
   </sheetData>
@@ -21152,7 +21171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G266"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28877,6 +28896,35 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>03/30</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.035396</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 有色金属, 通信, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M287"/>
+  <dimension ref="A1:M288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10208,6 +10208,40 @@
       </c>
       <c r="M287" t="n">
         <v>1.207128</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>03/31</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>1.4262</v>
+      </c>
+      <c r="D288" t="n">
+        <v>1.4262</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.749651</v>
+      </c>
+      <c r="F288" t="n">
+        <v>-0.3548</v>
+      </c>
+      <c r="H288" t="n">
+        <v>-0.3548</v>
+      </c>
+      <c r="I288" t="n">
+        <v>1.08202</v>
+      </c>
+      <c r="J288" t="n">
+        <v>-0.7337</v>
+      </c>
+      <c r="L288" t="n">
+        <v>-0.7337</v>
+      </c>
+      <c r="M288" t="n">
+        <v>1.198271</v>
       </c>
     </row>
   </sheetData>
@@ -10221,7 +10255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E287"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15683,6 +15717,25 @@
       </c>
       <c r="E287" t="n">
         <v>1.461143</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>03/31</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>-2.7007</v>
+      </c>
+      <c r="C288" t="n">
+        <v>-2.5937</v>
+      </c>
+      <c r="D288" t="n">
+        <v>-2.6472</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1.422463</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M288"/>
+  <dimension ref="A1:M289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10242,6 +10242,40 @@
       </c>
       <c r="M288" t="n">
         <v>1.198271</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>04/01</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>-3.2734</v>
+      </c>
+      <c r="D289" t="n">
+        <v>-3.2734</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.725111</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="I289" t="n">
+        <v>1.086265</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="M289" t="n">
+        <v>1.2025</v>
       </c>
     </row>
   </sheetData>
@@ -10255,7 +10289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15736,6 +15770,25 @@
       </c>
       <c r="E288" t="n">
         <v>1.422463</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>04/01</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1.9646</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3.3328</v>
+      </c>
+      <c r="D289" t="n">
+        <v>2.6487</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1.46014</v>
       </c>
     </row>
   </sheetData>
@@ -15749,7 +15802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E287"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21211,6 +21264,25 @@
       </c>
       <c r="E287" t="n">
         <v>1.412194</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>03/31</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>-2.2933</v>
+      </c>
+      <c r="C288" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="D288" t="n">
+        <v>-2.2083</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1.381008</v>
       </c>
     </row>
   </sheetData>
@@ -21224,7 +21296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G267"/>
+  <dimension ref="A1:G268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28978,6 +29050,35 @@
         </is>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>03/31</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="C268" t="n">
+        <v>-1.9967</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1.0367</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1.04613</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 有色金属, 通信, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M289"/>
+  <dimension ref="A1:M290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10276,6 +10276,40 @@
       </c>
       <c r="M289" t="n">
         <v>1.2025</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>04/02</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="D290" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.746923</v>
+      </c>
+      <c r="F290" t="n">
+        <v>-0.3986</v>
+      </c>
+      <c r="H290" t="n">
+        <v>-0.3986</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1.081935</v>
+      </c>
+      <c r="J290" t="n">
+        <v>-0.7107</v>
+      </c>
+      <c r="L290" t="n">
+        <v>-0.7107</v>
+      </c>
+      <c r="M290" t="n">
+        <v>1.193954</v>
       </c>
     </row>
   </sheetData>
@@ -10289,7 +10323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15789,6 +15823,25 @@
       </c>
       <c r="E289" t="n">
         <v>1.46014</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>04/02</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-2.3056</v>
+      </c>
+      <c r="C290" t="n">
+        <v>-2.7744</v>
+      </c>
+      <c r="D290" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1.423052</v>
       </c>
     </row>
   </sheetData>
@@ -15802,7 +15855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21283,6 +21336,25 @@
       </c>
       <c r="E288" t="n">
         <v>1.381008</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>04/01</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1.2367</v>
+      </c>
+      <c r="C289" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D289" t="n">
+        <v>-1.2133</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1.364252</v>
       </c>
     </row>
   </sheetData>
@@ -21296,7 +21368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G268"/>
+  <dimension ref="A1:G269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29079,6 +29151,35 @@
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>04/01</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>1.5167</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-0.7883</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1.037883</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 通信, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M290"/>
+  <dimension ref="A1:M291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10310,6 +10310,40 @@
       </c>
       <c r="M290" t="n">
         <v>1.193954</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>04/03</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-1.1843</v>
+      </c>
+      <c r="D291" t="n">
+        <v>-1.1843</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0.738077</v>
+      </c>
+      <c r="F291" t="n">
+        <v>-0.1428</v>
+      </c>
+      <c r="H291" t="n">
+        <v>-0.1428</v>
+      </c>
+      <c r="I291" t="n">
+        <v>1.08039</v>
+      </c>
+      <c r="J291" t="n">
+        <v>-1.2125</v>
+      </c>
+      <c r="L291" t="n">
+        <v>-1.2125</v>
+      </c>
+      <c r="M291" t="n">
+        <v>1.179477</v>
       </c>
     </row>
   </sheetData>
@@ -10323,7 +10357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15842,6 +15876,25 @@
       </c>
       <c r="E290" t="n">
         <v>1.423052</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>04/03</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-0.7266</v>
+      </c>
+      <c r="C291" t="n">
+        <v>-0.4731</v>
+      </c>
+      <c r="D291" t="n">
+        <v>-0.5998</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1.414516</v>
       </c>
     </row>
   </sheetData>
@@ -15855,7 +15908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21355,6 +21408,25 @@
       </c>
       <c r="E289" t="n">
         <v>1.364252</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>04/02</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D290" t="n">
+        <v>-0.785</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1.353543</v>
       </c>
     </row>
   </sheetData>
@@ -21368,7 +21440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G269"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29180,6 +29252,35 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>04/02</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>-1.7733</v>
+      </c>
+      <c r="C270" t="n">
+        <v>-2.3233</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1.043591</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 通信, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -15908,7 +15908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21427,6 +21427,25 @@
       </c>
       <c r="E290" t="n">
         <v>1.353543</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>04/03</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-1.5033</v>
+      </c>
+      <c r="C291" t="n">
+        <v>-1.605</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1.354919</v>
       </c>
     </row>
   </sheetData>
@@ -21440,7 +21459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29281,6 +29300,35 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>04/03</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-2.0133</v>
+      </c>
+      <c r="C271" t="n">
+        <v>-0.465</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-1.5483</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1.027433</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 机械设备, 通信, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M291"/>
+  <dimension ref="A1:M292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10344,6 +10344,40 @@
       </c>
       <c r="M291" t="n">
         <v>1.179477</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-0.9119</v>
+      </c>
+      <c r="D292" t="n">
+        <v>-0.9119</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0.7313460000000001</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="I292" t="n">
+        <v>1.085475</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1.3748</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1.3748</v>
+      </c>
+      <c r="M292" t="n">
+        <v>1.195693</v>
       </c>
     </row>
   </sheetData>
@@ -10357,7 +10391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E291"/>
+  <dimension ref="A1:E292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15895,6 +15929,25 @@
       </c>
       <c r="E291" t="n">
         <v>1.414516</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1.4173</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1.427059</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -15961,7 +15961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E291"/>
+  <dimension ref="A1:E292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21499,6 +21499,25 @@
       </c>
       <c r="E291" t="n">
         <v>1.354919</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>1.3033</v>
+      </c>
+      <c r="C292" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1.4733</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1.374881</v>
       </c>
     </row>
   </sheetData>
@@ -21512,7 +21531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29382,6 +29401,35 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0.8183</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.030806</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 计算机, 有色金属</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M292"/>
+  <dimension ref="A1:M293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10378,6 +10378,40 @@
       </c>
       <c r="M292" t="n">
         <v>1.195693</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-5.3712</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-5.3712</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0.692064</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="I293" t="n">
+        <v>1.091831</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="M293" t="n">
+        <v>1.206667</v>
       </c>
     </row>
   </sheetData>
@@ -10391,7 +10425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E292"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15948,6 +15982,25 @@
       </c>
       <c r="E292" t="n">
         <v>1.427059</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>5.9097</v>
+      </c>
+      <c r="C293" t="n">
+        <v>6.1754</v>
+      </c>
+      <c r="D293" t="n">
+        <v>6.0426</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1.51329</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M292"/>
+  <dimension ref="A1:M293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10378,6 +10378,40 @@
       </c>
       <c r="M292" t="n">
         <v>1.195693</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-5.3712</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-5.3712</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0.692064</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="I293" t="n">
+        <v>1.091831</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="M293" t="n">
+        <v>1.206667</v>
       </c>
     </row>
   </sheetData>
@@ -10391,7 +10425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E292"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15948,6 +15982,25 @@
       </c>
       <c r="E292" t="n">
         <v>1.427059</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>5.9097</v>
+      </c>
+      <c r="C293" t="n">
+        <v>6.1754</v>
+      </c>
+      <c r="D293" t="n">
+        <v>6.0426</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1.51329</v>
       </c>
     </row>
   </sheetData>
@@ -15961,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E291"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21499,6 +21552,44 @@
       </c>
       <c r="E291" t="n">
         <v>1.354919</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>1.3033</v>
+      </c>
+      <c r="C292" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1.4733</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1.374881</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1.387324</v>
       </c>
     </row>
   </sheetData>
@@ -21512,7 +21603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29382,6 +29473,64 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0.8183</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.030806</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 房地产</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 计算机, 有色金属</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>3.335</v>
+      </c>
+      <c r="C273" t="n">
+        <v>5.1917</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-1.8567</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.011668</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 钢铁</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16014,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E292"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21571,6 +21571,25 @@
       </c>
       <c r="E292" t="n">
         <v>1.374881</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1.387324</v>
       </c>
     </row>
   </sheetData>
@@ -21584,7 +21603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G272"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29483,6 +29502,35 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>3.335</v>
+      </c>
+      <c r="C273" t="n">
+        <v>5.1917</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-1.8567</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.011668</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 钢铁</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M293"/>
+  <dimension ref="A1:M294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10412,6 +10412,40 @@
       </c>
       <c r="M293" t="n">
         <v>1.206667</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.1102</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-0.1102</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.691302</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1.092325</v>
+      </c>
+      <c r="J294" t="n">
+        <v>-0.1089</v>
+      </c>
+      <c r="L294" t="n">
+        <v>-0.1089</v>
+      </c>
+      <c r="M294" t="n">
+        <v>1.205353</v>
       </c>
     </row>
   </sheetData>
@@ -10425,7 +10459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:E294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16001,6 +16035,25 @@
       </c>
       <c r="E293" t="n">
         <v>1.51329</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.7262</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-0.6464</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-0.6863</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1.502905</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M293"/>
+  <dimension ref="A1:M294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10412,6 +10412,40 @@
       </c>
       <c r="M293" t="n">
         <v>1.206667</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.1102</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-0.1102</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.691302</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1.092325</v>
+      </c>
+      <c r="J294" t="n">
+        <v>-0.1089</v>
+      </c>
+      <c r="L294" t="n">
+        <v>-0.1089</v>
+      </c>
+      <c r="M294" t="n">
+        <v>1.205353</v>
       </c>
     </row>
   </sheetData>
@@ -10425,7 +10459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:E294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16001,6 +16035,25 @@
       </c>
       <c r="E293" t="n">
         <v>1.51329</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.7262</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-0.6464</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-0.6863</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1.502905</v>
       </c>
     </row>
   </sheetData>
@@ -16014,7 +16067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E292"/>
+  <dimension ref="A1:E294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21571,6 +21624,44 @@
       </c>
       <c r="E292" t="n">
         <v>1.374881</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1.387324</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.5133</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.7766999999999999</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1.398099</v>
       </c>
     </row>
   </sheetData>
@@ -21584,7 +21675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G272"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29483,6 +29574,64 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>3.335</v>
+      </c>
+      <c r="C273" t="n">
+        <v>5.1917</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-1.8567</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.011668</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 钢铁</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>-1.7383</v>
+      </c>
+      <c r="C274" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D274" t="n">
+        <v>-1.7083</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.994385</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 钢铁</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16067,7 +16067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:E294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21643,6 +21643,25 @@
       </c>
       <c r="E293" t="n">
         <v>1.387324</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.5133</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.7766999999999999</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1.398099</v>
       </c>
     </row>
   </sheetData>
@@ -21656,7 +21675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G273"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29584,6 +29603,35 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>-1.7383</v>
+      </c>
+      <c r="C274" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D274" t="n">
+        <v>-1.7083</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.994385</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 钢铁</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M294"/>
+  <dimension ref="A1:M295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10446,6 +10446,40 @@
       </c>
       <c r="M294" t="n">
         <v>1.205353</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-1.3144</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-1.3144</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.682215</v>
+      </c>
+      <c r="F295" t="n">
+        <v>-0.2552</v>
+      </c>
+      <c r="H295" t="n">
+        <v>-0.2552</v>
+      </c>
+      <c r="I295" t="n">
+        <v>1.089538</v>
+      </c>
+      <c r="J295" t="n">
+        <v>-0.8371</v>
+      </c>
+      <c r="L295" t="n">
+        <v>-0.8371</v>
+      </c>
+      <c r="M295" t="n">
+        <v>1.195263</v>
       </c>
     </row>
   </sheetData>
@@ -10459,7 +10493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E294"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16054,6 +16088,25 @@
       </c>
       <c r="E294" t="n">
         <v>1.502905</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>3.776</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2.6525</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1.542769</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M294"/>
+  <dimension ref="A1:M295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10446,6 +10446,40 @@
       </c>
       <c r="M294" t="n">
         <v>1.205353</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-1.3144</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-1.3144</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.682215</v>
+      </c>
+      <c r="F295" t="n">
+        <v>-0.2552</v>
+      </c>
+      <c r="H295" t="n">
+        <v>-0.2552</v>
+      </c>
+      <c r="I295" t="n">
+        <v>1.089538</v>
+      </c>
+      <c r="J295" t="n">
+        <v>-0.8371</v>
+      </c>
+      <c r="L295" t="n">
+        <v>-0.8371</v>
+      </c>
+      <c r="M295" t="n">
+        <v>1.195263</v>
       </c>
     </row>
   </sheetData>
@@ -10459,7 +10493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E294"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16054,6 +16088,25 @@
       </c>
       <c r="E294" t="n">
         <v>1.502905</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>3.776</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2.6525</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1.542769</v>
       </c>
     </row>
   </sheetData>
@@ -16067,7 +16120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E294"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21662,6 +21715,25 @@
       </c>
       <c r="E294" t="n">
         <v>1.398099</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-0.2033</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-0.4633</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1.391621</v>
       </c>
     </row>
   </sheetData>
@@ -21675,7 +21747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G274"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29632,6 +29704,35 @@
         </is>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1.4767</v>
+      </c>
+      <c r="D275" t="n">
+        <v>-0.9417</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.985021</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 钢铁</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16120,7 +16120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E294"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21715,6 +21715,25 @@
       </c>
       <c r="E294" t="n">
         <v>1.398099</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-0.2033</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-0.4633</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1.391621</v>
       </c>
     </row>
   </sheetData>
@@ -21728,7 +21747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G274"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29685,6 +29704,35 @@
         </is>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="C275" t="n">
+        <v>1.4767</v>
+      </c>
+      <c r="D275" t="n">
+        <v>-0.9417</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.985021</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 商贸零售, 钢铁</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M295"/>
+  <dimension ref="A1:M296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,6 +10480,40 @@
       </c>
       <c r="M295" t="n">
         <v>1.195263</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>04/13</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.869</v>
+      </c>
+      <c r="D296" t="n">
+        <v>-0.869</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.676287</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1.090283</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="L296" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="M296" t="n">
+        <v>1.196426</v>
       </c>
     </row>
   </sheetData>
@@ -10493,7 +10527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E295"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16107,6 +16141,25 @@
       </c>
       <c r="E295" t="n">
         <v>1.542769</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>04/13</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.7964</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1.555056</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M295"/>
+  <dimension ref="A1:M296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,6 +10480,40 @@
       </c>
       <c r="M295" t="n">
         <v>1.195263</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>04/13</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.869</v>
+      </c>
+      <c r="D296" t="n">
+        <v>-0.869</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.676287</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1.090283</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="L296" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="M296" t="n">
+        <v>1.196426</v>
       </c>
     </row>
   </sheetData>
@@ -10493,7 +10527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E295"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16107,6 +16141,25 @@
       </c>
       <c r="E295" t="n">
         <v>1.542769</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>04/13</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.7964</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1.555056</v>
       </c>
     </row>
   </sheetData>
@@ -16120,7 +16173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E295"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21734,6 +21787,25 @@
       </c>
       <c r="E295" t="n">
         <v>1.391621</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>04/13</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0.6933</v>
+      </c>
+      <c r="C296" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="D296" t="n">
+        <v>1.4133</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1.411289</v>
       </c>
     </row>
   </sheetData>
@@ -21747,7 +21819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G275"/>
+  <dimension ref="A1:G276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29733,6 +29805,35 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>04/13</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-0.3567</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.981508</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 钢铁, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 基础化工</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M296"/>
+  <dimension ref="A1:M297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10514,6 +10514,40 @@
       </c>
       <c r="M296" t="n">
         <v>1.196426</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>04/14</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-1.9522</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-1.9522</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0.663084</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0.0886</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0.0886</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1.091249</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="L297" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M297" t="n">
+        <v>1.197514</v>
       </c>
     </row>
   </sheetData>
@@ -10527,7 +10561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E296"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16160,6 +16194,25 @@
       </c>
       <c r="E296" t="n">
         <v>1.555056</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>04/14</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2.3613</v>
+      </c>
+      <c r="C297" t="n">
+        <v>2.1657</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2.2635</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1.590254</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16226,7 +16226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E296"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21859,6 +21859,25 @@
       </c>
       <c r="E296" t="n">
         <v>1.411289</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>04/14</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0.1733</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-0.3167</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1.40682</v>
       </c>
     </row>
   </sheetData>
@@ -21872,7 +21891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G276"/>
+  <dimension ref="A1:G277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29887,6 +29906,35 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>04/14</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0.8117</v>
+      </c>
+      <c r="C277" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-1.0433</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.971268</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 钢铁, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M297"/>
+  <dimension ref="A1:M298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10548,6 +10548,40 @@
       </c>
       <c r="M297" t="n">
         <v>1.197514</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>04/15</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0.664862</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I298" t="n">
+        <v>1.092395</v>
+      </c>
+      <c r="J298" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="L298" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="M298" t="n">
+        <v>1.19597</v>
       </c>
     </row>
   </sheetData>
@@ -10561,7 +10595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16213,6 +16247,25 @@
       </c>
       <c r="E297" t="n">
         <v>1.590254</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>04/15</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-1.2243</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-0.5676</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1.581227</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16279,7 +16279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21931,6 +21931,25 @@
       </c>
       <c r="E297" t="n">
         <v>1.40682</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>04/15</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-1.715</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1.382693</v>
       </c>
     </row>
   </sheetData>
@@ -21944,7 +21963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G277"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29988,6 +30007,35 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>04/15</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>-0.355</v>
+      </c>
+      <c r="C278" t="n">
+        <v>-1.0283</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.977808</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 钢铁, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M298"/>
+  <dimension ref="A1:M299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10582,6 +10582,40 @@
       </c>
       <c r="M298" t="n">
         <v>1.19597</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>04/16</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>-0.8877</v>
+      </c>
+      <c r="D299" t="n">
+        <v>-0.8877</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0.65896</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="I299" t="n">
+        <v>1.096459</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0.7784</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0.7784</v>
+      </c>
+      <c r="M299" t="n">
+        <v>1.205279</v>
       </c>
     </row>
   </sheetData>
@@ -10595,7 +10629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E298"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16266,6 +16300,25 @@
       </c>
       <c r="E298" t="n">
         <v>1.581227</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>04/16</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>3.1668</v>
+      </c>
+      <c r="C299" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="D299" t="n">
+        <v>2.1489</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1.615206</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16332,7 +16332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E298"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22003,6 +22003,25 @@
       </c>
       <c r="E298" t="n">
         <v>1.382693</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>04/16</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>1.7433</v>
+      </c>
+      <c r="C299" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1.7783</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1.407282</v>
       </c>
     </row>
   </sheetData>
@@ -22016,7 +22035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:G279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30089,6 +30108,35 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>04/16</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="C279" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.695</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.971012</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 钢铁, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10616,6 +10616,40 @@
       </c>
       <c r="M299" t="n">
         <v>1.205279</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>04/17</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>-0.7623</v>
+      </c>
+      <c r="D300" t="n">
+        <v>-0.7623</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.653937</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="I300" t="n">
+        <v>1.102668</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="M300" t="n">
+        <v>1.213394</v>
       </c>
     </row>
   </sheetData>
@@ -10629,7 +10663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16319,6 +16353,25 @@
       </c>
       <c r="E299" t="n">
         <v>1.615206</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>04/17</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1.4346</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.7568</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1.62743</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16385,7 +16385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22075,6 +22075,25 @@
       </c>
       <c r="E299" t="n">
         <v>1.407282</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>04/17</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="C300" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1.429376</v>
       </c>
     </row>
   </sheetData>
@@ -22088,7 +22107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G279"/>
+  <dimension ref="A1:G280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30190,6 +30209,35 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>04/17</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-0.5367</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1.1033</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.955087</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M300"/>
+  <dimension ref="A1:M301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10650,6 +10650,40 @@
       </c>
       <c r="M300" t="n">
         <v>1.213394</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>04/20</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>-1.7827</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-1.7827</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0.642279</v>
+      </c>
+      <c r="F301" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="H301" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="I301" t="n">
+        <v>1.102545</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="M301" t="n">
+        <v>1.217451</v>
       </c>
     </row>
   </sheetData>
@@ -10663,7 +10697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16372,6 +16406,25 @@
       </c>
       <c r="E300" t="n">
         <v>1.62743</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>04/20</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1.9089</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.9447</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1.642804</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16438,7 +16438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22147,6 +22147,25 @@
       </c>
       <c r="E300" t="n">
         <v>1.429376</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>04/20</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-0.1817</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1.42678</v>
       </c>
     </row>
   </sheetData>
@@ -22160,7 +22179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G280"/>
+  <dimension ref="A1:G281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30291,6 +30310,35 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>04/20</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="D281" t="n">
+        <v>-0.5033</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.95028</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M301"/>
+  <dimension ref="A1:M302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10684,6 +10684,40 @@
       </c>
       <c r="M301" t="n">
         <v>1.217451</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>04/21</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>2.5263</v>
+      </c>
+      <c r="D302" t="n">
+        <v>2.5263</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.658505</v>
+      </c>
+      <c r="F302" t="n">
+        <v>-0.06560000000000001</v>
+      </c>
+      <c r="H302" t="n">
+        <v>-0.06560000000000001</v>
+      </c>
+      <c r="I302" t="n">
+        <v>1.101822</v>
+      </c>
+      <c r="J302" t="n">
+        <v>-0.4025</v>
+      </c>
+      <c r="L302" t="n">
+        <v>-0.4025</v>
+      </c>
+      <c r="M302" t="n">
+        <v>1.21255</v>
       </c>
     </row>
   </sheetData>
@@ -10697,7 +10731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16425,6 +16459,25 @@
       </c>
       <c r="E301" t="n">
         <v>1.642804</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>04/21</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="C302" t="n">
+        <v>-1.6438</v>
+      </c>
+      <c r="D302" t="n">
+        <v>-0.6674</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1.63184</v>
       </c>
     </row>
   </sheetData>
@@ -16438,7 +16491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22166,6 +22219,25 @@
       </c>
       <c r="E301" t="n">
         <v>1.42678</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>04/21</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C302" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1.442403</v>
       </c>
     </row>
   </sheetData>
@@ -22179,7 +22251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G281"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30339,6 +30411,35 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>04/21</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-0.5417</v>
+      </c>
+      <c r="C282" t="n">
+        <v>-0.1983</v>
+      </c>
+      <c r="D282" t="n">
+        <v>-0.3433</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.947017</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 商贸零售</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M302"/>
+  <dimension ref="A1:M303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10718,6 +10718,40 @@
       </c>
       <c r="M302" t="n">
         <v>1.21255</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>04/22</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>-1.7227</v>
+      </c>
+      <c r="D303" t="n">
+        <v>-1.7227</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0.647161</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="I303" t="n">
+        <v>1.106411</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="M303" t="n">
+        <v>1.214324</v>
       </c>
     </row>
   </sheetData>
@@ -10731,7 +10765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E302"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16478,6 +16512,25 @@
       </c>
       <c r="E302" t="n">
         <v>1.63184</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>04/22</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1.7301</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1.7146</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1.7224</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1.659946</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16544,7 +16544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E302"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22291,6 +22291,25 @@
       </c>
       <c r="E302" t="n">
         <v>1.442403</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>04/22</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1.446129</v>
       </c>
     </row>
   </sheetData>
@@ -22304,7 +22323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30493,6 +30512,35 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>04/22</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="C283" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-1.4183</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.933585</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 煤炭</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M303"/>
+  <dimension ref="A1:M304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10752,6 +10752,40 @@
       </c>
       <c r="M303" t="n">
         <v>1.214324</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>04/23</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1.7812</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1.7812</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.6586880000000001</v>
+      </c>
+      <c r="F304" t="n">
+        <v>-0.6365</v>
+      </c>
+      <c r="H304" t="n">
+        <v>-0.6365</v>
+      </c>
+      <c r="I304" t="n">
+        <v>1.099369</v>
+      </c>
+      <c r="J304" t="n">
+        <v>-1.3177</v>
+      </c>
+      <c r="L304" t="n">
+        <v>-1.3177</v>
+      </c>
+      <c r="M304" t="n">
+        <v>1.198323</v>
       </c>
     </row>
   </sheetData>
@@ -10765,7 +10799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16531,6 +16565,25 @@
       </c>
       <c r="E303" t="n">
         <v>1.659946</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>04/23</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>-0.8663</v>
+      </c>
+      <c r="C304" t="n">
+        <v>-1.278</v>
+      </c>
+      <c r="D304" t="n">
+        <v>-1.0721</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1.642148</v>
       </c>
     </row>
   </sheetData>
@@ -16544,7 +16597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22310,6 +22363,25 @@
       </c>
       <c r="E303" t="n">
         <v>1.446129</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>04/23</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>-1.0833</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D304" t="n">
+        <v>-1.1083</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1.430101</v>
       </c>
     </row>
   </sheetData>
@@ -22323,7 +22395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G283"/>
+  <dimension ref="A1:G284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30541,6 +30613,35 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>04/23</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>-0.3833</v>
+      </c>
+      <c r="C284" t="n">
+        <v>-1.615</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1.2317</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.945084</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 煤炭</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M304"/>
+  <dimension ref="A1:M305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10786,6 +10786,40 @@
       </c>
       <c r="M304" t="n">
         <v>1.198323</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>04/24</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>-1.5586</v>
+      </c>
+      <c r="D305" t="n">
+        <v>-1.5586</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.6484220000000001</v>
+      </c>
+      <c r="F305" t="n">
+        <v>-0.3093</v>
+      </c>
+      <c r="H305" t="n">
+        <v>-0.3093</v>
+      </c>
+      <c r="I305" t="n">
+        <v>1.095968</v>
+      </c>
+      <c r="J305" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="L305" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1.193469</v>
       </c>
     </row>
   </sheetData>
@@ -10799,7 +10833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16584,6 +16618,25 @@
       </c>
       <c r="E304" t="n">
         <v>1.642148</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>04/24</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>-1.4102</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1.4724</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1.642659</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16650,7 +16650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22435,6 +22435,25 @@
       </c>
       <c r="E304" t="n">
         <v>1.430101</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>04/24</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D305" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1.427241</v>
       </c>
     </row>
   </sheetData>
@@ -22448,7 +22467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G284"/>
+  <dimension ref="A1:G285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30695,6 +30714,35 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>04/24</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>-0.3233</v>
+      </c>
+      <c r="C285" t="n">
+        <v>-0.655</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.948219</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 煤炭</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M305"/>
+  <dimension ref="A1:M306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10820,6 +10820,40 @@
       </c>
       <c r="M305" t="n">
         <v>1.193469</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-3.9786</v>
+      </c>
+      <c r="D306" t="n">
+        <v>-3.9786</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0.622624</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="I306" t="n">
+        <v>1.096841</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="M306" t="n">
+        <v>1.205106</v>
       </c>
     </row>
   </sheetData>
@@ -10833,7 +10867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16637,6 +16671,25 @@
       </c>
       <c r="E305" t="n">
         <v>1.642659</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-0.5179</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3.7628</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1.6224</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1.66931</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16703,7 +16703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22507,6 +22507,25 @@
       </c>
       <c r="E305" t="n">
         <v>1.427241</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="C306" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1.431523</v>
       </c>
     </row>
   </sheetData>
@@ -22520,7 +22539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G285"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30796,6 +30815,35 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-0.1433</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.946859</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 煤炭</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M305"/>
+  <dimension ref="A1:M306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10820,6 +10820,40 @@
       </c>
       <c r="M305" t="n">
         <v>1.193469</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-3.9786</v>
+      </c>
+      <c r="D306" t="n">
+        <v>-3.9786</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0.622624</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="I306" t="n">
+        <v>1.096841</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="M306" t="n">
+        <v>1.205106</v>
       </c>
     </row>
   </sheetData>
@@ -10833,7 +10867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16637,6 +16671,25 @@
       </c>
       <c r="E305" t="n">
         <v>1.642659</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-0.5179</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3.7628</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1.6224</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1.66931</v>
       </c>
     </row>
   </sheetData>
@@ -16650,7 +16703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22454,6 +22507,25 @@
       </c>
       <c r="E305" t="n">
         <v>1.427241</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="C306" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1.431523</v>
       </c>
     </row>
   </sheetData>
@@ -22467,7 +22539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G285"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30743,6 +30815,35 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>04/27</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-0.1433</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.946859</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 煤炭</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M306"/>
+  <dimension ref="A1:M307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10854,6 +10854,40 @@
       </c>
       <c r="M306" t="n">
         <v>1.205106</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>04/28</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>2.4354</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2.4354</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0.637787</v>
+      </c>
+      <c r="F307" t="n">
+        <v>-0.5570000000000001</v>
+      </c>
+      <c r="H307" t="n">
+        <v>-0.5570000000000001</v>
+      </c>
+      <c r="I307" t="n">
+        <v>1.090731</v>
+      </c>
+      <c r="J307" t="n">
+        <v>-0.8967000000000001</v>
+      </c>
+      <c r="L307" t="n">
+        <v>-0.8967000000000001</v>
+      </c>
+      <c r="M307" t="n">
+        <v>1.1943</v>
       </c>
     </row>
   </sheetData>
@@ -10867,7 +10901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E306"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16690,6 +16724,25 @@
       </c>
       <c r="E306" t="n">
         <v>1.66931</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>04/28</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>-1.4272</v>
+      </c>
+      <c r="C307" t="n">
+        <v>-1.3076</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1.646484</v>
       </c>
     </row>
   </sheetData>
@@ -16703,7 +16756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E306"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22526,6 +22579,25 @@
       </c>
       <c r="E306" t="n">
         <v>1.431523</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>04/28</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-0.1217</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1.429781</v>
       </c>
     </row>
   </sheetData>
@@ -22539,7 +22611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G286"/>
+  <dimension ref="A1:G287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30844,6 +30916,35 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>04/28</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="C287" t="n">
+        <v>-1.765</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1.9167</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.965008</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 钢铁, 煤炭</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M307"/>
+  <dimension ref="A1:M308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10888,6 +10888,40 @@
       </c>
       <c r="M307" t="n">
         <v>1.1943</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>04/29</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.641773</v>
+      </c>
+      <c r="F308" t="n">
+        <v>-0.0658</v>
+      </c>
+      <c r="H308" t="n">
+        <v>-0.0658</v>
+      </c>
+      <c r="I308" t="n">
+        <v>1.090014</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="M308" t="n">
+        <v>1.195482</v>
       </c>
     </row>
   </sheetData>
@@ -10901,7 +10935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16743,6 +16777,25 @@
       </c>
       <c r="E307" t="n">
         <v>1.646484</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>04/29</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1.669868</v>
       </c>
     </row>
   </sheetData>
@@ -16756,7 +16809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22598,6 +22651,25 @@
       </c>
       <c r="E307" t="n">
         <v>1.429781</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>04/29</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>2.5167</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1.8617</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1.456399</v>
       </c>
     </row>
   </sheetData>
@@ -22611,7 +22683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G287"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30945,6 +31017,35 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>04/29</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="C288" t="n">
+        <v>1.8283</v>
+      </c>
+      <c r="D288" t="n">
+        <v>-0.4133</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.961019</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 煤炭, 钢铁</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M308"/>
+  <dimension ref="A1:M309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10922,6 +10922,40 @@
       </c>
       <c r="M308" t="n">
         <v>1.195482</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>04/30</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>-5.5195</v>
+      </c>
+      <c r="D309" t="n">
+        <v>-5.5195</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.606351</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="I309" t="n">
+        <v>1.093595</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L309" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="M309" t="n">
+        <v>1.202452</v>
       </c>
     </row>
   </sheetData>
@@ -10935,7 +10969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16796,6 +16830,25 @@
       </c>
       <c r="E308" t="n">
         <v>1.669868</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>04/30</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>-0.2717</v>
+      </c>
+      <c r="C309" t="n">
+        <v>5.1932</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2.4607</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1.710959</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -16862,7 +16862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22723,6 +22723,25 @@
       </c>
       <c r="E308" t="n">
         <v>1.456399</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>04/30</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>-0.7267</v>
+      </c>
+      <c r="C309" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="D309" t="n">
+        <v>-0.3467</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1.45135</v>
       </c>
     </row>
   </sheetData>
@@ -22736,7 +22755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31099,6 +31118,35 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>04/30</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="D289" t="n">
+        <v>-0.0633</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.96041</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 纺织服饰, 社会服务, 煤炭, 钢铁</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M309"/>
+  <dimension ref="A1:M310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10956,6 +10956,40 @@
       </c>
       <c r="M309" t="n">
         <v>1.202452</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>-5.1806</v>
+      </c>
+      <c r="D310" t="n">
+        <v>-5.1806</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0.5749379999999999</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="I310" t="n">
+        <v>1.097828</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="M310" t="n">
+        <v>1.209428</v>
       </c>
     </row>
   </sheetData>
@@ -10969,7 +11003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E309"/>
+  <dimension ref="A1:E310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16849,6 +16883,25 @@
       </c>
       <c r="E309" t="n">
         <v>1.710959</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>2.747</v>
+      </c>
+      <c r="C310" t="n">
+        <v>5.4664</v>
+      </c>
+      <c r="D310" t="n">
+        <v>4.1067</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1.781223</v>
       </c>
     </row>
   </sheetData>
@@ -16862,7 +16915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E309"/>
+  <dimension ref="A1:E310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22742,6 +22795,25 @@
       </c>
       <c r="E309" t="n">
         <v>1.45135</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C310" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1.480595</v>
       </c>
     </row>
   </sheetData>
@@ -22755,7 +22827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G289"/>
+  <dimension ref="A1:G290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31147,6 +31219,35 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>1.0583</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="D290" t="n">
+        <v>-2.0467</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.940754</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 煤炭, 钢铁</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10990,6 +10990,40 @@
       </c>
       <c r="M310" t="n">
         <v>1.209428</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>-2.9332</v>
+      </c>
+      <c r="D311" t="n">
+        <v>-2.9332</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.558074</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0.8957000000000001</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0.8957000000000001</v>
+      </c>
+      <c r="I311" t="n">
+        <v>1.107661</v>
+      </c>
+      <c r="J311" t="n">
+        <v>1.4505</v>
+      </c>
+      <c r="L311" t="n">
+        <v>1.4505</v>
+      </c>
+      <c r="M311" t="n">
+        <v>1.22697</v>
       </c>
     </row>
   </sheetData>
@@ -11003,7 +11037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E310"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16902,6 +16936,25 @@
       </c>
       <c r="E310" t="n">
         <v>1.781223</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1.3242</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1.3886</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1.805957</v>
       </c>
     </row>
   </sheetData>
@@ -16915,7 +16968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E310"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22814,6 +22867,25 @@
       </c>
       <c r="E310" t="n">
         <v>1.480595</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>-1.5467</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="D311" t="n">
+        <v>-1.6517</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1.45614</v>
       </c>
     </row>
   </sheetData>
@@ -22827,7 +22899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G290"/>
+  <dimension ref="A1:G291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31248,6 +31320,35 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="C291" t="n">
+        <v>2.0083</v>
+      </c>
+      <c r="D291" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0.922127</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 煤炭, 钢铁</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M311"/>
+  <dimension ref="A1:M312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11024,6 +11024,40 @@
       </c>
       <c r="M311" t="n">
         <v>1.22697</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1.9514</v>
+      </c>
+      <c r="D312" t="n">
+        <v>1.9514</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0.568964</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="I312" t="n">
+        <v>1.11519</v>
+      </c>
+      <c r="J312" t="n">
+        <v>1.5809</v>
+      </c>
+      <c r="L312" t="n">
+        <v>1.5809</v>
+      </c>
+      <c r="M312" t="n">
+        <v>1.246367</v>
       </c>
     </row>
   </sheetData>
@@ -11037,7 +11071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16955,6 +16989,25 @@
       </c>
       <c r="E311" t="n">
         <v>1.805957</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>-0.9634</v>
+      </c>
+      <c r="C312" t="n">
+        <v>-2.2888</v>
+      </c>
+      <c r="D312" t="n">
+        <v>-1.6261</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1.77659</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M312"/>
+  <dimension ref="A1:M313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11058,6 +11058,40 @@
       </c>
       <c r="M312" t="n">
         <v>1.246367</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>-4.3731</v>
+      </c>
+      <c r="D313" t="n">
+        <v>-4.3731</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0.544083</v>
+      </c>
+      <c r="F313" t="n">
+        <v>-0.2302</v>
+      </c>
+      <c r="H313" t="n">
+        <v>-0.2302</v>
+      </c>
+      <c r="I313" t="n">
+        <v>1.112622</v>
+      </c>
+      <c r="J313" t="n">
+        <v>-0.5006</v>
+      </c>
+      <c r="L313" t="n">
+        <v>-0.5006</v>
+      </c>
+      <c r="M313" t="n">
+        <v>1.240128</v>
       </c>
     </row>
   </sheetData>
@@ -11071,7 +11105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E312"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17008,6 +17042,25 @@
       </c>
       <c r="E312" t="n">
         <v>1.77659</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>3.4995</v>
+      </c>
+      <c r="C313" t="n">
+        <v>4.6469</v>
+      </c>
+      <c r="D313" t="n">
+        <v>4.0732</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1.848954</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -17074,7 +17074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E312"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23011,6 +23011,25 @@
       </c>
       <c r="E312" t="n">
         <v>1.458154</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D313" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1.45028</v>
       </c>
     </row>
   </sheetData>
@@ -23024,7 +23043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G292"/>
+  <dimension ref="A1:G293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31503,6 +31522,35 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-0.1033</v>
+      </c>
+      <c r="C293" t="n">
+        <v>2.0583</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-2.1617</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0.898465</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 纺织服饰, 煤炭, 钢铁</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M313"/>
+  <dimension ref="A1:M314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11092,6 +11092,40 @@
       </c>
       <c r="M313" t="n">
         <v>1.240128</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>-0.5642</v>
+      </c>
+      <c r="D314" t="n">
+        <v>-0.5642</v>
+      </c>
+      <c r="E314" t="n">
+        <v>0.541013</v>
+      </c>
+      <c r="F314" t="n">
+        <v>-0.1726</v>
+      </c>
+      <c r="H314" t="n">
+        <v>-0.1726</v>
+      </c>
+      <c r="I314" t="n">
+        <v>1.110702</v>
+      </c>
+      <c r="J314" t="n">
+        <v>-0.8008999999999999</v>
+      </c>
+      <c r="L314" t="n">
+        <v>-0.8008999999999999</v>
+      </c>
+      <c r="M314" t="n">
+        <v>1.230196</v>
       </c>
     </row>
   </sheetData>
@@ -11105,7 +11139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17061,6 +17095,25 @@
       </c>
       <c r="E313" t="n">
         <v>1.848954</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1.854164</v>
       </c>
     </row>
   </sheetData>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -17127,7 +17127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23083,6 +23083,25 @@
       </c>
       <c r="E313" t="n">
         <v>1.45028</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>-0.9933</v>
+      </c>
+      <c r="C314" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="D314" t="n">
+        <v>-0.09329999999999999</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1.448927</v>
       </c>
     </row>
   </sheetData>
@@ -23096,7 +23115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G293"/>
+  <dimension ref="A1:G294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31604,6 +31623,35 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-1.5233</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-1.2633</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.887114</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 煤炭, 纺织服饰, 钢铁</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M314"/>
+  <dimension ref="A1:M315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11126,6 +11126,40 @@
       </c>
       <c r="M314" t="n">
         <v>1.230196</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>-3.151</v>
+      </c>
+      <c r="D315" t="n">
+        <v>-3.151</v>
+      </c>
+      <c r="E315" t="n">
+        <v>0.523966</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="I315" t="n">
+        <v>1.114282</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="M315" t="n">
+        <v>1.235777</v>
       </c>
     </row>
   </sheetData>
@@ -11139,7 +11173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E314"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17114,6 +17148,25 @@
       </c>
       <c r="E314" t="n">
         <v>1.854164</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>2.6291</v>
+      </c>
+      <c r="C315" t="n">
+        <v>2.6896</v>
+      </c>
+      <c r="D315" t="n">
+        <v>2.6593</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1.903473</v>
       </c>
     </row>
   </sheetData>
@@ -17127,7 +17180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E314"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23102,6 +23155,25 @@
       </c>
       <c r="E314" t="n">
         <v>1.448927</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="C315" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1.455012</v>
       </c>
     </row>
   </sheetData>
@@ -23115,7 +23187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G294"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31652,6 +31724,35 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C295" t="n">
+        <v>2.0767</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-1.5267</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.873571</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 煤炭, 钢铁, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M315"/>
+  <dimension ref="A1:M316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11160,6 +11160,40 @@
       </c>
       <c r="M315" t="n">
         <v>1.235777</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>1.6097</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1.6097</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0.5324</v>
+      </c>
+      <c r="F316" t="n">
+        <v>-0.0584</v>
+      </c>
+      <c r="H316" t="n">
+        <v>-0.0584</v>
+      </c>
+      <c r="I316" t="n">
+        <v>1.113631</v>
+      </c>
+      <c r="J316" t="n">
+        <v>-0.2948</v>
+      </c>
+      <c r="L316" t="n">
+        <v>-0.2948</v>
+      </c>
+      <c r="M316" t="n">
+        <v>1.232134</v>
       </c>
     </row>
   </sheetData>
@@ -11173,7 +11207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17167,6 +17201,25 @@
       </c>
       <c r="E315" t="n">
         <v>1.903473</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>-2.1591</v>
+      </c>
+      <c r="C316" t="n">
+        <v>-2.5452</v>
+      </c>
+      <c r="D316" t="n">
+        <v>-2.3521</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1.8587</v>
       </c>
     </row>
   </sheetData>
@@ -17180,7 +17233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23174,6 +23227,25 @@
       </c>
       <c r="E315" t="n">
         <v>1.455012</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>-2.2633</v>
+      </c>
+      <c r="C316" t="n">
+        <v>-1.125</v>
+      </c>
+      <c r="D316" t="n">
+        <v>-1.1383</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1.438449</v>
       </c>
     </row>
   </sheetData>
@@ -23187,7 +23259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G295"/>
+  <dimension ref="A1:G296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31753,6 +31825,35 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-1.9017</v>
+      </c>
+      <c r="C296" t="n">
+        <v>-2.4133</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.87804</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 煤炭, 钢铁, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M316"/>
+  <dimension ref="A1:M317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11194,6 +11194,40 @@
       </c>
       <c r="M316" t="n">
         <v>1.232134</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>1.4266</v>
+      </c>
+      <c r="D317" t="n">
+        <v>1.4266</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0.539995</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="I317" t="n">
+        <v>1.118036</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="M317" t="n">
+        <v>1.240744</v>
       </c>
     </row>
   </sheetData>
@@ -11207,7 +11241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17220,6 +17254,25 @@
       </c>
       <c r="E316" t="n">
         <v>1.8587</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="C317" t="n">
+        <v>-1.6713</v>
+      </c>
+      <c r="D317" t="n">
+        <v>-1.115</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1.837976</v>
       </c>
     </row>
   </sheetData>
@@ -17233,7 +17286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23246,6 +23299,25 @@
       </c>
       <c r="E316" t="n">
         <v>1.438449</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>-1.7167</v>
+      </c>
+      <c r="C317" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="D317" t="n">
+        <v>-0.6167</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1.429579</v>
       </c>
     </row>
   </sheetData>
@@ -23259,7 +23331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G296"/>
+  <dimension ref="A1:G297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31854,6 +31926,35 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.9983</v>
+      </c>
+      <c r="C297" t="n">
+        <v>-1.4233</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0.881772</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M317"/>
+  <dimension ref="A1:M318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11228,6 +11228,40 @@
       </c>
       <c r="M317" t="n">
         <v>1.240744</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>-1.2684</v>
+      </c>
+      <c r="D318" t="n">
+        <v>-1.2684</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0.533146</v>
+      </c>
+      <c r="F318" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="I318" t="n">
+        <v>1.122328</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M318" t="n">
+        <v>1.25108</v>
       </c>
     </row>
   </sheetData>
@@ -11241,7 +11275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E317"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17273,6 +17307,25 @@
       </c>
       <c r="E317" t="n">
         <v>1.837976</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>-0.3611</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.8077</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.2233</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1.84208</v>
       </c>
     </row>
   </sheetData>
@@ -17286,7 +17339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E317"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23318,6 +23371,25 @@
       </c>
       <c r="E317" t="n">
         <v>1.429579</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>-0.2733</v>
+      </c>
+      <c r="C318" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.7567</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1.440396</v>
       </c>
     </row>
   </sheetData>
@@ -23331,7 +23403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G297"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31955,6 +32027,35 @@
         </is>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.5783</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-1.0117</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0.872852</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M318"/>
+  <dimension ref="A1:M319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,13 +502,13 @@
         <v>0.995383</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2723</v>
+        <v>0.6197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2723</v>
+        <v>0.6197</v>
       </c>
       <c r="I2" t="n">
-        <v>1.002723</v>
+        <v>1.006197</v>
       </c>
       <c r="J2" t="n">
         <v>0.7503</v>
@@ -536,13 +536,13 @@
         <v>0.980968</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3</v>
+        <v>-0.9925</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>-0.9925</v>
       </c>
       <c r="I3" t="n">
-        <v>1.005731</v>
+        <v>0.996211</v>
       </c>
       <c r="J3" t="n">
         <v>0.1271</v>
@@ -570,13 +570,13 @@
         <v>0.972106</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1246</v>
+        <v>0.1357</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1246</v>
+        <v>0.1357</v>
       </c>
       <c r="I4" t="n">
-        <v>1.004478</v>
+        <v>0.997563</v>
       </c>
       <c r="J4" t="n">
         <v>-0.3906</v>
@@ -604,13 +604,13 @@
         <v>0.991196</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2565</v>
+        <v>-0.1346</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2565</v>
+        <v>-0.1346</v>
       </c>
       <c r="I5" t="n">
-        <v>1.001902</v>
+        <v>0.99622</v>
       </c>
       <c r="J5" t="n">
         <v>-0.4329</v>
@@ -638,13 +638,13 @@
         <v>0.988644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7377</v>
+        <v>-0.9865</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7377</v>
+        <v>-0.9865</v>
       </c>
       <c r="I6" t="n">
-        <v>1.009293</v>
+        <v>0.986392</v>
       </c>
       <c r="J6" t="n">
         <v>0.6863</v>
@@ -672,13 +672,13 @@
         <v>1.021181</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7437</v>
+        <v>1.044</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7437</v>
+        <v>1.044</v>
       </c>
       <c r="I7" t="n">
-        <v>1.001786</v>
+        <v>0.99669</v>
       </c>
       <c r="J7" t="n">
         <v>-1.2552</v>
@@ -706,13 +706,13 @@
         <v>0.971398</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8234</v>
+        <v>0.8501</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8234</v>
+        <v>0.8501</v>
       </c>
       <c r="I8" t="n">
-        <v>1.010035</v>
+        <v>1.005163</v>
       </c>
       <c r="J8" t="n">
         <v>1.9645</v>
@@ -740,13 +740,13 @@
         <v>0.944133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8965</v>
+        <v>-0.5903</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8965</v>
+        <v>-0.5903</v>
       </c>
       <c r="I9" t="n">
-        <v>1.01909</v>
+        <v>0.999229</v>
       </c>
       <c r="J9" t="n">
         <v>1.5683</v>
@@ -774,13 +774,13 @@
         <v>0.943408</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0738</v>
+        <v>0.1705</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0738</v>
+        <v>0.1705</v>
       </c>
       <c r="I10" t="n">
-        <v>1.019842</v>
+        <v>1.000932</v>
       </c>
       <c r="J10" t="n">
         <v>0.2246</v>
@@ -808,13 +808,13 @@
         <v>0.925696</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7608</v>
+        <v>2.039</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7608</v>
+        <v>2.039</v>
       </c>
       <c r="I11" t="n">
-        <v>1.027601</v>
+        <v>1.021342</v>
       </c>
       <c r="J11" t="n">
         <v>1.9943</v>
@@ -842,13 +842,13 @@
         <v>0.940234</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1001</v>
+        <v>-0.1929</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1001</v>
+        <v>-0.1929</v>
       </c>
       <c r="I12" t="n">
-        <v>1.02863</v>
+        <v>1.019371</v>
       </c>
       <c r="J12" t="n">
         <v>0.1747</v>
@@ -876,13 +876,13 @@
         <v>0.925096</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2697</v>
+        <v>-1.1467</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2697</v>
+        <v>-1.1467</v>
       </c>
       <c r="I13" t="n">
-        <v>1.031404</v>
+        <v>1.007683</v>
       </c>
       <c r="J13" t="n">
         <v>0.3633</v>
@@ -910,13 +910,13 @@
         <v>0.946805</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5316</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5316</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.025921</v>
+        <v>1.000984</v>
       </c>
       <c r="J14" t="n">
         <v>-0.7197</v>
@@ -944,13 +944,13 @@
         <v>0.943644</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2635</v>
+        <v>1.8557</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2635</v>
+        <v>1.8557</v>
       </c>
       <c r="I15" t="n">
-        <v>1.023218</v>
+        <v>1.019559</v>
       </c>
       <c r="J15" t="n">
         <v>-1.0265</v>
@@ -978,13 +978,13 @@
         <v>0.925975</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5894</v>
+        <v>0.2391</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5894</v>
+        <v>0.2391</v>
       </c>
       <c r="I16" t="n">
-        <v>1.029249</v>
+        <v>1.021997</v>
       </c>
       <c r="J16" t="n">
         <v>1.5712</v>
@@ -1012,13 +1012,13 @@
         <v>0.946196</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7889</v>
+        <v>-1.2117</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7889</v>
+        <v>-1.2117</v>
       </c>
       <c r="I17" t="n">
-        <v>1.021129</v>
+        <v>1.009613</v>
       </c>
       <c r="J17" t="n">
         <v>-1.9458</v>
@@ -1046,13 +1046,13 @@
         <v>0.921641</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2027</v>
+        <v>-0.1661</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2027</v>
+        <v>-0.1661</v>
       </c>
       <c r="I18" t="n">
-        <v>1.03341</v>
+        <v>1.007936</v>
       </c>
       <c r="J18" t="n">
         <v>2.2605</v>
@@ -1080,13 +1080,13 @@
         <v>0.920763</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6863</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6863</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.040502</v>
+        <v>1.017512</v>
       </c>
       <c r="J19" t="n">
         <v>1.5282</v>
@@ -1114,13 +1114,13 @@
         <v>0.859859</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3804</v>
+        <v>-1.0693</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3804</v>
+        <v>-1.0693</v>
       </c>
       <c r="I20" t="n">
-        <v>1.04446</v>
+        <v>1.006632</v>
       </c>
       <c r="J20" t="n">
         <v>0.0236</v>
@@ -1148,13 +1148,13 @@
         <v>0.856441</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1449</v>
+        <v>0.8156</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1449</v>
+        <v>0.8156</v>
       </c>
       <c r="I21" t="n">
-        <v>1.045974</v>
+        <v>1.014843</v>
       </c>
       <c r="J21" t="n">
         <v>0.3994</v>
@@ -1182,13 +1182,13 @@
         <v>0.848554</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3983</v>
+        <v>-0.0603</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3983</v>
+        <v>-0.0603</v>
       </c>
       <c r="I22" t="n">
-        <v>1.05014</v>
+        <v>1.01423</v>
       </c>
       <c r="J22" t="n">
         <v>1.007</v>
@@ -1216,13 +1216,13 @@
         <v>0.840793</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3669</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3669</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.053993</v>
+        <v>1.021371</v>
       </c>
       <c r="J23" t="n">
         <v>0.7095</v>
@@ -1250,13 +1250,13 @@
         <v>0.850485</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3212</v>
+        <v>1.2079</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3212</v>
+        <v>1.2079</v>
       </c>
       <c r="I24" t="n">
-        <v>1.050607</v>
+        <v>1.033708</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5014999999999999</v>
@@ -1284,13 +1284,13 @@
         <v>0.880144</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1553</v>
+        <v>0.2249</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1553</v>
+        <v>0.2249</v>
       </c>
       <c r="I25" t="n">
-        <v>1.03847</v>
+        <v>1.036034</v>
       </c>
       <c r="J25" t="n">
         <v>-2.1951</v>
@@ -1318,13 +1318,13 @@
         <v>0.892473</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0326</v>
+        <v>1.0706</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0326</v>
+        <v>1.0706</v>
       </c>
       <c r="I26" t="n">
-        <v>1.038808</v>
+        <v>1.047126</v>
       </c>
       <c r="J26" t="n">
         <v>0.2214</v>
@@ -1352,13 +1352,13 @@
         <v>0.877175</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7863</v>
+        <v>0.8154</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7863</v>
+        <v>0.8154</v>
       </c>
       <c r="I27" t="n">
-        <v>1.046976</v>
+        <v>1.055664</v>
       </c>
       <c r="J27" t="n">
         <v>1.6365</v>
@@ -1386,13 +1386,13 @@
         <v>0.8787740000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2953</v>
+        <v>-0.7909</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2953</v>
+        <v>-0.7909</v>
       </c>
       <c r="I28" t="n">
-        <v>1.050068</v>
+        <v>1.047315</v>
       </c>
       <c r="J28" t="n">
         <v>0.286</v>
@@ -1420,13 +1420,13 @@
         <v>0.847943</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5468</v>
+        <v>-0.6515</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5468</v>
+        <v>-0.6515</v>
       </c>
       <c r="I29" t="n">
-        <v>1.05581</v>
+        <v>1.040492</v>
       </c>
       <c r="J29" t="n">
         <v>0.6859</v>
@@ -1454,13 +1454,13 @@
         <v>0.859646</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1085</v>
+        <v>-0.3477</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1085</v>
+        <v>-0.3477</v>
       </c>
       <c r="I30" t="n">
-        <v>1.054664</v>
+        <v>1.036874</v>
       </c>
       <c r="J30" t="n">
         <v>-0.2693</v>
@@ -1488,13 +1488,13 @@
         <v>0.864075</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2432</v>
+        <v>1.7556</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2432</v>
+        <v>1.7556</v>
       </c>
       <c r="I31" t="n">
-        <v>1.057229</v>
+        <v>1.055077</v>
       </c>
       <c r="J31" t="n">
         <v>0.7772</v>
@@ -1522,13 +1522,13 @@
         <v>0.873036</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0609</v>
+        <v>-0.5659</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0609</v>
+        <v>-0.5659</v>
       </c>
       <c r="I32" t="n">
-        <v>1.056585</v>
+        <v>1.049105</v>
       </c>
       <c r="J32" t="n">
         <v>-0.0308</v>
@@ -1556,13 +1556,13 @@
         <v>0.875897</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4737</v>
+        <v>-0.4005</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4737</v>
+        <v>-0.4005</v>
       </c>
       <c r="I33" t="n">
-        <v>1.061591</v>
+        <v>1.044904</v>
       </c>
       <c r="J33" t="n">
         <v>1.0936</v>
@@ -1590,13 +1590,13 @@
         <v>0.900463</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8057</v>
+        <v>0.2526</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8057</v>
+        <v>0.2526</v>
       </c>
       <c r="I34" t="n">
-        <v>1.053037</v>
+        <v>1.047543</v>
       </c>
       <c r="J34" t="n">
         <v>-1.4404</v>
@@ -1624,13 +1624,13 @@
         <v>0.8918160000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2873</v>
+        <v>0.71</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2873</v>
+        <v>0.71</v>
       </c>
       <c r="I35" t="n">
-        <v>1.050012</v>
+        <v>1.054981</v>
       </c>
       <c r="J35" t="n">
         <v>-0.633</v>
@@ -1658,13 +1658,13 @@
         <v>0.899124</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3903</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3903</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>1.05411</v>
+        <v>1.05597</v>
       </c>
       <c r="J36" t="n">
         <v>1.0237</v>
@@ -1692,13 +1692,13 @@
         <v>0.892093</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1267</v>
+        <v>0.0449</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1267</v>
+        <v>0.0449</v>
       </c>
       <c r="I37" t="n">
-        <v>1.055446</v>
+        <v>1.056444</v>
       </c>
       <c r="J37" t="n">
         <v>0.3254</v>
@@ -1726,13 +1726,13 @@
         <v>0.903988</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3316</v>
+        <v>-0.5393</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3316</v>
+        <v>-0.5393</v>
       </c>
       <c r="I38" t="n">
-        <v>1.051946</v>
+        <v>1.050747</v>
       </c>
       <c r="J38" t="n">
         <v>-0.6055</v>
@@ -1760,13 +1760,13 @@
         <v>0.911693</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4226</v>
+        <v>-0.5429</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4226</v>
+        <v>-0.5429</v>
       </c>
       <c r="I39" t="n">
-        <v>1.056391</v>
+        <v>1.045043</v>
       </c>
       <c r="J39" t="n">
         <v>1.0131</v>
@@ -1794,13 +1794,13 @@
         <v>0.926563</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.3927</v>
+        <v>-0.0319</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.3927</v>
+        <v>-0.0319</v>
       </c>
       <c r="I40" t="n">
-        <v>1.052243</v>
+        <v>1.044709</v>
       </c>
       <c r="J40" t="n">
         <v>-0.5977</v>
@@ -1828,13 +1828,13 @@
         <v>0.929041</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8778</v>
+        <v>-1.0619</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8778</v>
+        <v>-1.0619</v>
       </c>
       <c r="I41" t="n">
-        <v>1.043006</v>
+        <v>1.033616</v>
       </c>
       <c r="J41" t="n">
         <v>-2.4099</v>
@@ -1862,13 +1862,13 @@
         <v>0.947582</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.5643</v>
+        <v>1.086</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.5643</v>
+        <v>1.086</v>
       </c>
       <c r="I42" t="n">
-        <v>1.037121</v>
+        <v>1.044841</v>
       </c>
       <c r="J42" t="n">
         <v>-0.9184</v>
@@ -1896,13 +1896,13 @@
         <v>0.948689</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5851</v>
+        <v>0.9058</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5851</v>
+        <v>0.9058</v>
       </c>
       <c r="I43" t="n">
-        <v>1.043189</v>
+        <v>1.054305</v>
       </c>
       <c r="J43" t="n">
         <v>1.508</v>
@@ -1930,13 +1930,13 @@
         <v>0.937182</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3974</v>
+        <v>2.288</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3974</v>
+        <v>2.288</v>
       </c>
       <c r="I44" t="n">
-        <v>1.039043</v>
+        <v>1.078427</v>
       </c>
       <c r="J44" t="n">
         <v>-1.0604</v>
@@ -1964,13 +1964,13 @@
         <v>0.940368</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4672</v>
+        <v>-0.0449</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4672</v>
+        <v>-0.0449</v>
       </c>
       <c r="I45" t="n">
-        <v>1.034189</v>
+        <v>1.077942</v>
       </c>
       <c r="J45" t="n">
         <v>-1.0699</v>
@@ -1998,13 +1998,13 @@
         <v>0.941619</v>
       </c>
       <c r="F46" t="n">
-        <v>0.021</v>
+        <v>-1.1426</v>
       </c>
       <c r="H46" t="n">
-        <v>0.021</v>
+        <v>-1.1426</v>
       </c>
       <c r="I46" t="n">
-        <v>1.034406</v>
+        <v>1.065625</v>
       </c>
       <c r="J46" t="n">
         <v>-0.5024</v>
@@ -2032,13 +2032,13 @@
         <v>0.949234</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3371</v>
+        <v>4.482</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3371</v>
+        <v>4.482</v>
       </c>
       <c r="I47" t="n">
-        <v>1.037893</v>
+        <v>1.113387</v>
       </c>
       <c r="J47" t="n">
         <v>0.8784999999999999</v>
@@ -2066,13 +2066,13 @@
         <v>0.954188</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2337</v>
+        <v>-0.3019</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2337</v>
+        <v>-0.3019</v>
       </c>
       <c r="I48" t="n">
-        <v>1.040318</v>
+        <v>1.110025</v>
       </c>
       <c r="J48" t="n">
         <v>0.3573</v>
@@ -2100,13 +2100,13 @@
         <v>0.9598410000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4273</v>
+        <v>1.115</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.4273</v>
+        <v>1.115</v>
       </c>
       <c r="I49" t="n">
-        <v>1.035873</v>
+        <v>1.122402</v>
       </c>
       <c r="J49" t="n">
         <v>-0.4359</v>
@@ -2134,13 +2134,13 @@
         <v>0.984331</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.1676</v>
+        <v>-4.387</v>
       </c>
       <c r="H50" t="n">
-        <v>-3.1676</v>
+        <v>-4.387</v>
       </c>
       <c r="I50" t="n">
-        <v>1.003061</v>
+        <v>1.073162</v>
       </c>
       <c r="J50" t="n">
         <v>-5.786</v>
@@ -2168,13 +2168,13 @@
         <v>0.992529</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.7203000000000001</v>
+        <v>1.6142</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.7203000000000001</v>
+        <v>1.6142</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9958360000000001</v>
+        <v>1.090485</v>
       </c>
       <c r="J51" t="n">
         <v>-2.226</v>
@@ -2202,13 +2202,13 @@
         <v>0.95275</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8143</v>
+        <v>-0.5926</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8143</v>
+        <v>-0.5926</v>
       </c>
       <c r="I52" t="n">
-        <v>1.003945</v>
+        <v>1.084023</v>
       </c>
       <c r="J52" t="n">
         <v>2.0004</v>
@@ -2236,13 +2236,13 @@
         <v>0.9514049999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8391</v>
+        <v>1.8016</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8391</v>
+        <v>1.8016</v>
       </c>
       <c r="I53" t="n">
-        <v>1.012369</v>
+        <v>1.103553</v>
       </c>
       <c r="J53" t="n">
         <v>1.8126</v>
@@ -2270,13 +2270,13 @@
         <v>0.92746</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5538</v>
+        <v>-0.5557</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5538</v>
+        <v>-0.5557</v>
       </c>
       <c r="I54" t="n">
-        <v>1.017976</v>
+        <v>1.09742</v>
       </c>
       <c r="J54" t="n">
         <v>0.5581</v>
@@ -2304,13 +2304,13 @@
         <v>0.933406</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8097</v>
+        <v>0.7169</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8097</v>
+        <v>0.7169</v>
       </c>
       <c r="I55" t="n">
-        <v>1.026218</v>
+        <v>1.105287</v>
       </c>
       <c r="J55" t="n">
         <v>1.952</v>
@@ -2338,13 +2338,13 @@
         <v>0.945194</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.129</v>
+        <v>0.7604</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.129</v>
+        <v>0.7604</v>
       </c>
       <c r="I56" t="n">
-        <v>1.024894</v>
+        <v>1.113692</v>
       </c>
       <c r="J56" t="n">
         <v>-0.1054</v>
@@ -2372,13 +2372,13 @@
         <v>0.941817</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.0581</v>
+        <v>-1.8668</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.0581</v>
+        <v>-1.8668</v>
       </c>
       <c r="I57" t="n">
-        <v>1.01405</v>
+        <v>1.092901</v>
       </c>
       <c r="J57" t="n">
         <v>-2.0165</v>
@@ -2406,13 +2406,13 @@
         <v>0.937733</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2013</v>
+        <v>0.8413</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2013</v>
+        <v>0.8413</v>
       </c>
       <c r="I58" t="n">
-        <v>1.016091</v>
+        <v>1.102096</v>
       </c>
       <c r="J58" t="n">
         <v>0.5756</v>
@@ -2440,13 +2440,13 @@
         <v>0.9456639999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0527</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.0527</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>1.015556</v>
+        <v>1.103054</v>
       </c>
       <c r="J59" t="n">
         <v>-0.2037</v>
@@ -2474,13 +2474,13 @@
         <v>0.93424</v>
       </c>
       <c r="F60" t="n">
-        <v>1.1481</v>
+        <v>1.2856</v>
       </c>
       <c r="H60" t="n">
-        <v>1.1481</v>
+        <v>1.2856</v>
       </c>
       <c r="I60" t="n">
-        <v>1.027215</v>
+        <v>1.117235</v>
       </c>
       <c r="J60" t="n">
         <v>1.9633</v>
@@ -2508,13 +2508,13 @@
         <v>0.94079</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1.8792</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1.8792</v>
       </c>
       <c r="I61" t="n">
-        <v>1.027215</v>
+        <v>1.13823</v>
       </c>
       <c r="J61" t="n">
         <v>0.0094</v>
@@ -2542,13 +2542,13 @@
         <v>0.939905</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5617</v>
+        <v>0.1634</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5617</v>
+        <v>0.1634</v>
       </c>
       <c r="I62" t="n">
-        <v>1.032985</v>
+        <v>1.14009</v>
       </c>
       <c r="J62" t="n">
         <v>1.0961</v>
@@ -2576,13 +2576,13 @@
         <v>0.953615</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5570000000000001</v>
+        <v>2.2595</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5570000000000001</v>
+        <v>2.2595</v>
       </c>
       <c r="I63" t="n">
-        <v>1.027231</v>
+        <v>1.165851</v>
       </c>
       <c r="J63" t="n">
         <v>-0.9599</v>
@@ -2610,13 +2610,13 @@
         <v>0.950933</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1368</v>
+        <v>-2.0949</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1368</v>
+        <v>-2.0949</v>
       </c>
       <c r="I64" t="n">
-        <v>1.028637</v>
+        <v>1.141427</v>
       </c>
       <c r="J64" t="n">
         <v>0.2174</v>
@@ -2644,13 +2644,13 @@
         <v>0.952421</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6647</v>
+        <v>-0.7179</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6647</v>
+        <v>-0.7179</v>
       </c>
       <c r="I65" t="n">
-        <v>1.021799</v>
+        <v>1.133232</v>
       </c>
       <c r="J65" t="n">
         <v>-1.2807</v>
@@ -2678,13 +2678,13 @@
         <v>0.948939</v>
       </c>
       <c r="F66" t="n">
-        <v>0.488</v>
+        <v>-0.1499</v>
       </c>
       <c r="H66" t="n">
-        <v>0.488</v>
+        <v>-0.1499</v>
       </c>
       <c r="I66" t="n">
-        <v>1.026786</v>
+        <v>1.131534</v>
       </c>
       <c r="J66" t="n">
         <v>1.1635</v>
@@ -2712,13 +2712,13 @@
         <v>0.934599</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6592</v>
+        <v>-0.105</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6592</v>
+        <v>-0.105</v>
       </c>
       <c r="I67" t="n">
-        <v>1.033554</v>
+        <v>1.130345</v>
       </c>
       <c r="J67" t="n">
         <v>1.4137</v>
@@ -2746,13 +2746,13 @@
         <v>0.92394</v>
       </c>
       <c r="F68" t="n">
-        <v>1.077</v>
+        <v>0.2366</v>
       </c>
       <c r="H68" t="n">
-        <v>1.077</v>
+        <v>0.2366</v>
       </c>
       <c r="I68" t="n">
-        <v>1.044686</v>
+        <v>1.13302</v>
       </c>
       <c r="J68" t="n">
         <v>2.2439</v>
@@ -2780,13 +2780,13 @@
         <v>0.926893</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.2508</v>
+        <v>-0.5456</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.2508</v>
+        <v>-0.5456</v>
       </c>
       <c r="I69" t="n">
-        <v>1.042066</v>
+        <v>1.126839</v>
       </c>
       <c r="J69" t="n">
         <v>0.1342</v>
@@ -2814,13 +2814,13 @@
         <v>0.930716</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2635</v>
+        <v>-0.0331</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2635</v>
+        <v>-0.0331</v>
       </c>
       <c r="I70" t="n">
-        <v>1.044811</v>
+        <v>1.126466</v>
       </c>
       <c r="J70" t="n">
         <v>0.5344</v>
@@ -2848,13 +2848,13 @@
         <v>0.953742</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6509</v>
+        <v>-0.059</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6509</v>
+        <v>-0.059</v>
       </c>
       <c r="I71" t="n">
-        <v>1.038011</v>
+        <v>1.125801</v>
       </c>
       <c r="J71" t="n">
         <v>-1.317</v>
@@ -2882,13 +2882,13 @@
         <v>0.952387</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2327</v>
+        <v>-1.0044</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2327</v>
+        <v>-1.0044</v>
       </c>
       <c r="I72" t="n">
-        <v>1.040426</v>
+        <v>1.114494</v>
       </c>
       <c r="J72" t="n">
         <v>0.4404</v>
@@ -2916,13 +2916,13 @@
         <v>0.960504</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.2593</v>
+        <v>0.7241</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.2593</v>
+        <v>0.7241</v>
       </c>
       <c r="I73" t="n">
-        <v>1.037728</v>
+        <v>1.122563</v>
       </c>
       <c r="J73" t="n">
         <v>-0.4494</v>
@@ -2950,13 +2950,13 @@
         <v>0.9620339999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.6073</v>
+        <v>-0.6825</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6073</v>
+        <v>-0.6825</v>
       </c>
       <c r="I74" t="n">
-        <v>1.031426</v>
+        <v>1.114901</v>
       </c>
       <c r="J74" t="n">
         <v>-1.096</v>
@@ -2984,13 +2984,13 @@
         <v>0.970234</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.4133</v>
+        <v>3.8527</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.4133</v>
+        <v>3.8527</v>
       </c>
       <c r="I75" t="n">
-        <v>1.027163</v>
+        <v>1.157855</v>
       </c>
       <c r="J75" t="n">
         <v>-0.402</v>
@@ -3018,13 +3018,13 @@
         <v>0.970401</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5416</v>
+        <v>2.7165</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5416</v>
+        <v>2.7165</v>
       </c>
       <c r="I76" t="n">
-        <v>1.032726</v>
+        <v>1.189308</v>
       </c>
       <c r="J76" t="n">
         <v>1.3647</v>
@@ -3052,13 +3052,13 @@
         <v>0.972963</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4127</v>
+        <v>-0.8666</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4127</v>
+        <v>-0.8666</v>
       </c>
       <c r="I77" t="n">
-        <v>1.036989</v>
+        <v>1.179001</v>
       </c>
       <c r="J77" t="n">
         <v>1.1661</v>
@@ -3086,13 +3086,13 @@
         <v>0.973422</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1761</v>
+        <v>1.0501</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1761</v>
+        <v>1.0501</v>
       </c>
       <c r="I78" t="n">
-        <v>1.038815</v>
+        <v>1.191382</v>
       </c>
       <c r="J78" t="n">
         <v>0.2972</v>
@@ -3120,13 +3120,13 @@
         <v>0.983</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.517</v>
+        <v>0.5142</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.517</v>
+        <v>0.5142</v>
       </c>
       <c r="I79" t="n">
-        <v>1.033444</v>
+        <v>1.197508</v>
       </c>
       <c r="J79" t="n">
         <v>-1.2673</v>
@@ -3154,13 +3154,13 @@
         <v>0.9859830000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.5848</v>
+        <v>-0.389</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.5848</v>
+        <v>-0.389</v>
       </c>
       <c r="I80" t="n">
-        <v>1.0274</v>
+        <v>1.19285</v>
       </c>
       <c r="J80" t="n">
         <v>-1.1669</v>
@@ -3188,13 +3188,13 @@
         <v>0.986371</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.19</v>
+        <v>3.5006</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.19</v>
+        <v>3.5006</v>
       </c>
       <c r="I81" t="n">
-        <v>1.025448</v>
+        <v>1.234607</v>
       </c>
       <c r="J81" t="n">
         <v>-0.3692</v>
@@ -3222,13 +3222,13 @@
         <v>0.978015</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7475000000000001</v>
+        <v>-1.3811</v>
       </c>
       <c r="H82" t="n">
-        <v>0.7475000000000001</v>
+        <v>-1.3811</v>
       </c>
       <c r="I82" t="n">
-        <v>1.033114</v>
+        <v>1.217556</v>
       </c>
       <c r="J82" t="n">
         <v>1.826</v>
@@ -3256,13 +3256,13 @@
         <v>0.984773</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1664</v>
+        <v>1.9706</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1664</v>
+        <v>1.9706</v>
       </c>
       <c r="I83" t="n">
-        <v>1.034833</v>
+        <v>1.241549</v>
       </c>
       <c r="J83" t="n">
         <v>0.7407</v>
@@ -3290,13 +3290,13 @@
         <v>0.990221</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.0945</v>
+        <v>-1.1403</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.0945</v>
+        <v>-1.1403</v>
       </c>
       <c r="I84" t="n">
-        <v>1.033855</v>
+        <v>1.227392</v>
       </c>
       <c r="J84" t="n">
         <v>-0.2581</v>
@@ -3324,13 +3324,13 @@
         <v>0.976</v>
       </c>
       <c r="F85" t="n">
-        <v>0.742</v>
+        <v>1.0271</v>
       </c>
       <c r="H85" t="n">
-        <v>0.742</v>
+        <v>1.0271</v>
       </c>
       <c r="I85" t="n">
-        <v>1.041526</v>
+        <v>1.239998</v>
       </c>
       <c r="J85" t="n">
         <v>1.1667</v>
@@ -3358,13 +3358,13 @@
         <v>0.9861</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.4598</v>
+        <v>0.2559</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.4598</v>
+        <v>0.2559</v>
       </c>
       <c r="I86" t="n">
-        <v>1.036737</v>
+        <v>1.243172</v>
       </c>
       <c r="J86" t="n">
         <v>-1.2733</v>
@@ -3392,13 +3392,13 @@
         <v>0.984975</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3095</v>
+        <v>2.7437</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3095</v>
+        <v>2.7437</v>
       </c>
       <c r="I87" t="n">
-        <v>1.039946</v>
+        <v>1.277281</v>
       </c>
       <c r="J87" t="n">
         <v>0.5158</v>
@@ -3426,13 +3426,13 @@
         <v>0.9832959999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2784</v>
+        <v>-1.3537</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2784</v>
+        <v>-1.3537</v>
       </c>
       <c r="I88" t="n">
-        <v>1.042841</v>
+        <v>1.25999</v>
       </c>
       <c r="J88" t="n">
         <v>0.6211</v>
@@ -3460,13 +3460,13 @@
         <v>0.9674</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3053</v>
+        <v>-2.1865</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3053</v>
+        <v>-2.1865</v>
       </c>
       <c r="I89" t="n">
-        <v>1.046025</v>
+        <v>1.23244</v>
       </c>
       <c r="J89" t="n">
         <v>0.3641</v>
@@ -3494,13 +3494,13 @@
         <v>0.971815</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.081</v>
+        <v>0.4585</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.081</v>
+        <v>0.4585</v>
       </c>
       <c r="I90" t="n">
-        <v>1.045177</v>
+        <v>1.238091</v>
       </c>
       <c r="J90" t="n">
         <v>-0.1005</v>
@@ -3528,13 +3528,13 @@
         <v>0.967851</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6133999999999999</v>
+        <v>2.3691</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6133999999999999</v>
+        <v>2.3691</v>
       </c>
       <c r="I91" t="n">
-        <v>1.051589</v>
+        <v>1.267422</v>
       </c>
       <c r="J91" t="n">
         <v>1.1466</v>
@@ -3562,13 +3562,13 @@
         <v>0.981356</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.1745</v>
+        <v>0.9951</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.1745</v>
+        <v>0.9951</v>
       </c>
       <c r="I92" t="n">
-        <v>1.049754</v>
+        <v>1.280034</v>
       </c>
       <c r="J92" t="n">
         <v>-0.3078</v>
@@ -3596,13 +3596,13 @@
         <v>0.986367</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.2274</v>
+        <v>-1.3122</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.2274</v>
+        <v>-1.3122</v>
       </c>
       <c r="I93" t="n">
-        <v>1.047366</v>
+        <v>1.263238</v>
       </c>
       <c r="J93" t="n">
         <v>-0.3135</v>
@@ -3630,13 +3630,13 @@
         <v>0.989364</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1524</v>
+        <v>0.4938</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1524</v>
+        <v>0.4938</v>
       </c>
       <c r="I94" t="n">
-        <v>1.048963</v>
+        <v>1.269476</v>
       </c>
       <c r="J94" t="n">
         <v>0.3177</v>
@@ -3664,13 +3664,13 @@
         <v>0.984457</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.6387</v>
+        <v>-1.5669</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.6387</v>
+        <v>-1.5669</v>
       </c>
       <c r="I95" t="n">
-        <v>1.042263</v>
+        <v>1.249585</v>
       </c>
       <c r="J95" t="n">
         <v>-1.3119</v>
@@ -3698,13 +3698,13 @@
         <v>0.988765</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4124</v>
+        <v>-0.2825</v>
       </c>
       <c r="H96" t="n">
-        <v>0.4124</v>
+        <v>-0.2825</v>
       </c>
       <c r="I96" t="n">
-        <v>1.046561</v>
+        <v>1.246055</v>
       </c>
       <c r="J96" t="n">
         <v>0.8215</v>
@@ -3732,13 +3732,13 @@
         <v>0.996247</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.0276</v>
+        <v>-1.3502</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.0276</v>
+        <v>-1.3502</v>
       </c>
       <c r="I97" t="n">
-        <v>1.046272</v>
+        <v>1.229232</v>
       </c>
       <c r="J97" t="n">
         <v>-0.0535</v>
@@ -3766,13 +3766,13 @@
         <v>0.989861</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.0256</v>
+        <v>-1.0533</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.0256</v>
+        <v>-1.0533</v>
       </c>
       <c r="I98" t="n">
-        <v>1.046004</v>
+        <v>1.216284</v>
       </c>
       <c r="J98" t="n">
         <v>-0.3982</v>
@@ -3800,13 +3800,13 @@
         <v>0.988784</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.511</v>
+        <v>-1.4814</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.511</v>
+        <v>-1.4814</v>
       </c>
       <c r="I99" t="n">
-        <v>1.040659</v>
+        <v>1.198266</v>
       </c>
       <c r="J99" t="n">
         <v>-1.1281</v>
@@ -3834,13 +3834,13 @@
         <v>0.995638</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.4667</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.4667</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>1.035803</v>
+        <v>1.206039</v>
       </c>
       <c r="J100" t="n">
         <v>-1.0024</v>
@@ -3868,13 +3868,13 @@
         <v>0.994412</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7181</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7181</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>1.043241</v>
+        <v>1.215588</v>
       </c>
       <c r="J101" t="n">
         <v>1.6494</v>
@@ -3902,13 +3902,13 @@
         <v>0.979781</v>
       </c>
       <c r="F102" t="n">
-        <v>0.5194</v>
+        <v>0.0616</v>
       </c>
       <c r="H102" t="n">
-        <v>0.5194</v>
+        <v>0.0616</v>
       </c>
       <c r="I102" t="n">
-        <v>1.048659</v>
+        <v>1.216337</v>
       </c>
       <c r="J102" t="n">
         <v>1.0267</v>
@@ -3936,13 +3936,13 @@
         <v>0.966199</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.144</v>
+        <v>-1.6626</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.144</v>
+        <v>-1.6626</v>
       </c>
       <c r="I103" t="n">
-        <v>1.047149</v>
+        <v>1.196114</v>
       </c>
       <c r="J103" t="n">
         <v>-0.4332</v>
@@ -3970,13 +3970,13 @@
         <v>0.9719370000000001</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.0183</v>
+        <v>-0.4257</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.0183</v>
+        <v>-0.4257</v>
       </c>
       <c r="I104" t="n">
-        <v>1.046958</v>
+        <v>1.191023</v>
       </c>
       <c r="J104" t="n">
         <v>0.1714</v>
@@ -4004,13 +4004,13 @@
         <v>0.9685780000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4736</v>
+        <v>0.6433</v>
       </c>
       <c r="H105" t="n">
-        <v>0.4736</v>
+        <v>0.6433</v>
       </c>
       <c r="I105" t="n">
-        <v>1.051916</v>
+        <v>1.198684</v>
       </c>
       <c r="J105" t="n">
         <v>1.0836</v>
@@ -4038,13 +4038,13 @@
         <v>0.952616</v>
       </c>
       <c r="F106" t="n">
-        <v>0.5218</v>
+        <v>0.1281</v>
       </c>
       <c r="H106" t="n">
-        <v>0.5218</v>
+        <v>0.1281</v>
       </c>
       <c r="I106" t="n">
-        <v>1.057405</v>
+        <v>1.20022</v>
       </c>
       <c r="J106" t="n">
         <v>1.1737</v>
@@ -4072,13 +4072,13 @@
         <v>0.968557</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0179</v>
+        <v>2.8914</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0179</v>
+        <v>2.8914</v>
       </c>
       <c r="I107" t="n">
-        <v>1.057594</v>
+        <v>1.234922</v>
       </c>
       <c r="J107" t="n">
         <v>0.1143</v>
@@ -4106,13 +4106,13 @@
         <v>0.9873459999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.6146</v>
+        <v>-0.2144</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.6146</v>
+        <v>-0.2144</v>
       </c>
       <c r="I108" t="n">
-        <v>1.051094</v>
+        <v>1.232275</v>
       </c>
       <c r="J108" t="n">
         <v>-0.8706</v>
@@ -4140,13 +4140,13 @@
         <v>0.984961</v>
       </c>
       <c r="F109" t="n">
-        <v>0.095</v>
+        <v>1.5642</v>
       </c>
       <c r="H109" t="n">
-        <v>0.095</v>
+        <v>1.5642</v>
       </c>
       <c r="I109" t="n">
-        <v>1.052093</v>
+        <v>1.25155</v>
       </c>
       <c r="J109" t="n">
         <v>0.0955</v>
@@ -4174,13 +4174,13 @@
         <v>0.990094</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.5999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.5999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>1.045781</v>
+        <v>1.250667</v>
       </c>
       <c r="J110" t="n">
         <v>-1.4338</v>
@@ -4208,13 +4208,13 @@
         <v>1.000967</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3921</v>
+        <v>-0.6533</v>
       </c>
       <c r="H111" t="n">
-        <v>0.3921</v>
+        <v>-0.6533</v>
       </c>
       <c r="I111" t="n">
-        <v>1.049882</v>
+        <v>1.242497</v>
       </c>
       <c r="J111" t="n">
         <v>1.0995</v>
@@ -4242,13 +4242,13 @@
         <v>0.986503</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2334</v>
+        <v>-0.3359</v>
       </c>
       <c r="H112" t="n">
-        <v>0.2334</v>
+        <v>-0.3359</v>
       </c>
       <c r="I112" t="n">
-        <v>1.052332</v>
+        <v>1.238323</v>
       </c>
       <c r="J112" t="n">
         <v>0.4481</v>
@@ -4276,13 +4276,13 @@
         <v>0.99849</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.0562</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.0562</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>1.051741</v>
+        <v>1.22928</v>
       </c>
       <c r="J113" t="n">
         <v>0.0948</v>
@@ -4310,13 +4310,13 @@
         <v>1.007874</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.2669</v>
+        <v>0.2895</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.2669</v>
+        <v>0.2895</v>
       </c>
       <c r="I114" t="n">
-        <v>1.048934</v>
+        <v>1.232839</v>
       </c>
       <c r="J114" t="n">
         <v>-0.5128</v>
@@ -4344,13 +4344,13 @@
         <v>0.9856279999999999</v>
       </c>
       <c r="F115" t="n">
-        <v>0.436</v>
+        <v>0.5243</v>
       </c>
       <c r="H115" t="n">
-        <v>0.436</v>
+        <v>0.5243</v>
       </c>
       <c r="I115" t="n">
-        <v>1.053507</v>
+        <v>1.239302</v>
       </c>
       <c r="J115" t="n">
         <v>0.3578</v>
@@ -4378,13 +4378,13 @@
         <v>0.992503</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2089</v>
+        <v>0.96</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2089</v>
+        <v>0.96</v>
       </c>
       <c r="I116" t="n">
-        <v>1.055708</v>
+        <v>1.251199</v>
       </c>
       <c r="J116" t="n">
         <v>0.5653</v>
@@ -4412,13 +4412,13 @@
         <v>0.97711</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.1295</v>
+        <v>-0.9019</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.1295</v>
+        <v>-0.9019</v>
       </c>
       <c r="I117" t="n">
-        <v>1.054341</v>
+        <v>1.239914</v>
       </c>
       <c r="J117" t="n">
         <v>-0.7213000000000001</v>
@@ -4446,13 +4446,13 @@
         <v>0.971547</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4867</v>
+        <v>1.5676</v>
       </c>
       <c r="H118" t="n">
-        <v>0.4867</v>
+        <v>1.5676</v>
       </c>
       <c r="I118" t="n">
-        <v>1.059472</v>
+        <v>1.259352</v>
       </c>
       <c r="J118" t="n">
         <v>0.9364</v>
@@ -4480,13 +4480,13 @@
         <v>0.962906</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2691</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2691</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>1.062323</v>
+        <v>1.258128</v>
       </c>
       <c r="J119" t="n">
         <v>0.4056</v>
@@ -4514,13 +4514,13 @@
         <v>0.9644160000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.2571</v>
+        <v>0.4319</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.2571</v>
+        <v>0.4319</v>
       </c>
       <c r="I120" t="n">
-        <v>1.059592</v>
+        <v>1.263562</v>
       </c>
       <c r="J120" t="n">
         <v>-0.5344</v>
@@ -4548,13 +4548,13 @@
         <v>0.976169</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1164</v>
+        <v>0.1362</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1164</v>
+        <v>0.1362</v>
       </c>
       <c r="I121" t="n">
-        <v>1.060825</v>
+        <v>1.265282</v>
       </c>
       <c r="J121" t="n">
         <v>0.6062</v>
@@ -4582,13 +4582,13 @@
         <v>0.984123</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.3541</v>
+        <v>-0.9969</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.3541</v>
+        <v>-0.9969</v>
       </c>
       <c r="I122" t="n">
-        <v>1.057069</v>
+        <v>1.252669</v>
       </c>
       <c r="J122" t="n">
         <v>-0.8092</v>
@@ -4616,13 +4616,13 @@
         <v>0.976114</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.3383</v>
+        <v>0.0313</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.3383</v>
+        <v>0.0313</v>
       </c>
       <c r="I123" t="n">
-        <v>1.053493</v>
+        <v>1.253061</v>
       </c>
       <c r="J123" t="n">
         <v>-0.9043</v>
@@ -4650,13 +4650,13 @@
         <v>0.968746</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1567</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1567</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>1.055144</v>
+        <v>1.261771</v>
       </c>
       <c r="J124" t="n">
         <v>0.4097</v>
@@ -4684,13 +4684,13 @@
         <v>0.942407</v>
       </c>
       <c r="F125" t="n">
-        <v>0.3774</v>
+        <v>0.1355</v>
       </c>
       <c r="H125" t="n">
-        <v>0.3774</v>
+        <v>0.1355</v>
       </c>
       <c r="I125" t="n">
-        <v>1.059126</v>
+        <v>1.263482</v>
       </c>
       <c r="J125" t="n">
         <v>0.8246</v>
@@ -4718,13 +4718,13 @@
         <v>0.9313360000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>0.1563</v>
+        <v>0.7469</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1563</v>
+        <v>0.7469</v>
       </c>
       <c r="I126" t="n">
-        <v>1.060781</v>
+        <v>1.272918</v>
       </c>
       <c r="J126" t="n">
         <v>0.5017</v>
@@ -4752,13 +4752,13 @@
         <v>0.91745</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1924</v>
+        <v>1.5227</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1924</v>
+        <v>1.5227</v>
       </c>
       <c r="I127" t="n">
-        <v>1.062822</v>
+        <v>1.292301</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0227</v>
@@ -4786,13 +4786,13 @@
         <v>0.929444</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.5309</v>
+        <v>0.9935</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.5309</v>
+        <v>0.9935</v>
       </c>
       <c r="I128" t="n">
-        <v>1.05718</v>
+        <v>1.30514</v>
       </c>
       <c r="J128" t="n">
         <v>-0.8772</v>
@@ -4820,13 +4820,13 @@
         <v>0.922726</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7745</v>
+        <v>1.7175</v>
       </c>
       <c r="H129" t="n">
-        <v>0.7745</v>
+        <v>1.7175</v>
       </c>
       <c r="I129" t="n">
-        <v>1.065367</v>
+        <v>1.327556</v>
       </c>
       <c r="J129" t="n">
         <v>1.1774</v>
@@ -4854,13 +4854,13 @@
         <v>0.9324750000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>0.3708</v>
+        <v>0.4293</v>
       </c>
       <c r="H130" t="n">
-        <v>0.3708</v>
+        <v>0.4293</v>
       </c>
       <c r="I130" t="n">
-        <v>1.069318</v>
+        <v>1.333255</v>
       </c>
       <c r="J130" t="n">
         <v>0.9656</v>
@@ -4888,13 +4888,13 @@
         <v>0.925492</v>
       </c>
       <c r="F131" t="n">
-        <v>0.5425</v>
+        <v>-0.4146</v>
       </c>
       <c r="H131" t="n">
-        <v>0.5425</v>
+        <v>-0.4146</v>
       </c>
       <c r="I131" t="n">
-        <v>1.075119</v>
+        <v>1.327727</v>
       </c>
       <c r="J131" t="n">
         <v>1.1729</v>
@@ -4922,13 +4922,13 @@
         <v>0.9314170000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.0514</v>
+        <v>-1.186</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.0514</v>
+        <v>-1.186</v>
       </c>
       <c r="I132" t="n">
-        <v>1.074566</v>
+        <v>1.311981</v>
       </c>
       <c r="J132" t="n">
         <v>0.0956</v>
@@ -4956,13 +4956,13 @@
         <v>0.9319190000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4765</v>
+        <v>-1.8894</v>
       </c>
       <c r="H133" t="n">
-        <v>0.4765</v>
+        <v>-1.8894</v>
       </c>
       <c r="I133" t="n">
-        <v>1.079687</v>
+        <v>1.287193</v>
       </c>
       <c r="J133" t="n">
         <v>0.9485</v>
@@ -4990,13 +4990,13 @@
         <v>0.934864</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0408</v>
+        <v>-1.0301</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0408</v>
+        <v>-1.0301</v>
       </c>
       <c r="I134" t="n">
-        <v>1.080127</v>
+        <v>1.273933</v>
       </c>
       <c r="J134" t="n">
         <v>0.0428</v>
@@ -5024,13 +5024,13 @@
         <v>0.948312</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.1745</v>
+        <v>0.9569</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.1745</v>
+        <v>0.9569</v>
       </c>
       <c r="I135" t="n">
-        <v>1.078242</v>
+        <v>1.286123</v>
       </c>
       <c r="J135" t="n">
         <v>0.0098</v>
@@ -5058,13 +5058,13 @@
         <v>0.938645</v>
       </c>
       <c r="F136" t="n">
-        <v>0.6199</v>
+        <v>1.181</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6199</v>
+        <v>1.181</v>
       </c>
       <c r="I136" t="n">
-        <v>1.084926</v>
+        <v>1.301312</v>
       </c>
       <c r="J136" t="n">
         <v>1.2768</v>
@@ -5092,13 +5092,13 @@
         <v>0.925953</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-1.5699</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-1.5699</v>
       </c>
       <c r="I137" t="n">
-        <v>1.084109</v>
+        <v>1.280882</v>
       </c>
       <c r="J137" t="n">
         <v>-0.4595</v>
@@ -5126,13 +5126,13 @@
         <v>0.914293</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4011</v>
+        <v>-0.407</v>
       </c>
       <c r="H138" t="n">
-        <v>0.4011</v>
+        <v>-0.407</v>
       </c>
       <c r="I138" t="n">
-        <v>1.088458</v>
+        <v>1.275669</v>
       </c>
       <c r="J138" t="n">
         <v>0.2489</v>
@@ -5160,13 +5160,13 @@
         <v>0.898718</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.4635</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.4635</v>
       </c>
       <c r="I139" t="n">
-        <v>1.080717</v>
+        <v>1.257</v>
       </c>
       <c r="J139" t="n">
         <v>-1.7899</v>
@@ -5194,13 +5194,13 @@
         <v>0.887995</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7179</v>
+        <v>-0.1366</v>
       </c>
       <c r="H140" t="n">
-        <v>0.7179</v>
+        <v>-0.1366</v>
       </c>
       <c r="I140" t="n">
-        <v>1.088475</v>
+        <v>1.255283</v>
       </c>
       <c r="J140" t="n">
         <v>1.3358</v>
@@ -5228,13 +5228,13 @@
         <v>0.867319</v>
       </c>
       <c r="F141" t="n">
-        <v>0.6685</v>
+        <v>-0.3527</v>
       </c>
       <c r="H141" t="n">
-        <v>0.6685</v>
+        <v>-0.3527</v>
       </c>
       <c r="I141" t="n">
-        <v>1.095752</v>
+        <v>1.250855</v>
       </c>
       <c r="J141" t="n">
         <v>1.2608</v>
@@ -5262,13 +5262,13 @@
         <v>0.87617</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3639</v>
+        <v>0.6294</v>
       </c>
       <c r="H142" t="n">
-        <v>0.3639</v>
+        <v>0.6294</v>
       </c>
       <c r="I142" t="n">
-        <v>1.099739</v>
+        <v>1.258728</v>
       </c>
       <c r="J142" t="n">
         <v>1.0733</v>
@@ -5296,13 +5296,13 @@
         <v>0.854522</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.3266</v>
+        <v>-1.3894</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.3266</v>
+        <v>-1.3894</v>
       </c>
       <c r="I143" t="n">
-        <v>1.096147</v>
+        <v>1.241239</v>
       </c>
       <c r="J143" t="n">
         <v>-0.7135</v>
@@ -5330,13 +5330,13 @@
         <v>0.858359</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.6218</v>
+        <v>-0.1671</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.6218</v>
+        <v>-0.1671</v>
       </c>
       <c r="I144" t="n">
-        <v>1.089331</v>
+        <v>1.239166</v>
       </c>
       <c r="J144" t="n">
         <v>-1.1343</v>
@@ -5364,13 +5364,13 @@
         <v>0.783128</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.4461</v>
+        <v>-2.0089</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.4461</v>
+        <v>-2.0089</v>
       </c>
       <c r="I145" t="n">
-        <v>1.084472</v>
+        <v>1.214272</v>
       </c>
       <c r="J145" t="n">
         <v>-1.4048</v>
@@ -5398,13 +5398,13 @@
         <v>0.76385</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.3031</v>
+        <v>-0.7312</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.3031</v>
+        <v>-0.7312</v>
       </c>
       <c r="I146" t="n">
-        <v>1.081185</v>
+        <v>1.205394</v>
       </c>
       <c r="J146" t="n">
         <v>-0.913</v>
@@ -5432,13 +5432,13 @@
         <v>0.772981</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.0216</v>
+        <v>-0.319</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.0216</v>
+        <v>-0.319</v>
       </c>
       <c r="I147" t="n">
-        <v>1.080951</v>
+        <v>1.201549</v>
       </c>
       <c r="J147" t="n">
         <v>0.3887</v>
@@ -5466,13 +5466,13 @@
         <v>0.758015</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.2534</v>
+        <v>-1.5471</v>
       </c>
       <c r="H148" t="n">
-        <v>-0.2534</v>
+        <v>-1.5471</v>
       </c>
       <c r="I148" t="n">
-        <v>1.078212</v>
+        <v>1.18296</v>
       </c>
       <c r="J148" t="n">
         <v>-0.8247</v>
@@ -5500,13 +5500,13 @@
         <v>0.704797</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.2825</v>
+        <v>-2.4848</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.2825</v>
+        <v>-2.4848</v>
       </c>
       <c r="I149" t="n">
-        <v>1.075166</v>
+        <v>1.153566</v>
       </c>
       <c r="J149" t="n">
         <v>-1.0446</v>
@@ -5534,13 +5534,13 @@
         <v>0.716046</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.6397</v>
+        <v>0.0554</v>
       </c>
       <c r="H150" t="n">
-        <v>-0.6397</v>
+        <v>0.0554</v>
       </c>
       <c r="I150" t="n">
-        <v>1.068288</v>
+        <v>1.154205</v>
       </c>
       <c r="J150" t="n">
         <v>-1.0836</v>
@@ -5568,13 +5568,13 @@
         <v>0.705873</v>
       </c>
       <c r="F151" t="n">
-        <v>0.1704</v>
+        <v>0.6914</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1704</v>
+        <v>0.6914</v>
       </c>
       <c r="I151" t="n">
-        <v>1.070109</v>
+        <v>1.162185</v>
       </c>
       <c r="J151" t="n">
         <v>0.4707</v>
@@ -5602,13 +5602,13 @@
         <v>0.723115</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.0037</v>
+        <v>0.1792</v>
       </c>
       <c r="H152" t="n">
-        <v>-1.0037</v>
+        <v>0.1792</v>
       </c>
       <c r="I152" t="n">
-        <v>1.059368</v>
+        <v>1.164268</v>
       </c>
       <c r="J152" t="n">
         <v>-1.2533</v>
@@ -5636,13 +5636,13 @@
         <v>0.72889</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.4315</v>
+        <v>0.152</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.4315</v>
+        <v>0.152</v>
       </c>
       <c r="I153" t="n">
-        <v>1.054797</v>
+        <v>1.166038</v>
       </c>
       <c r="J153" t="n">
         <v>-1.3454</v>
@@ -5670,13 +5670,13 @@
         <v>0.772922</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.052</v>
+        <v>2.1793</v>
       </c>
       <c r="H154" t="n">
-        <v>-0.052</v>
+        <v>2.1793</v>
       </c>
       <c r="I154" t="n">
-        <v>1.054248</v>
+        <v>1.191449</v>
       </c>
       <c r="J154" t="n">
         <v>0.6763</v>
@@ -5704,13 +5704,13 @@
         <v>0.749125</v>
       </c>
       <c r="F155" t="n">
-        <v>0.3514</v>
+        <v>-0.8462</v>
       </c>
       <c r="H155" t="n">
-        <v>0.3514</v>
+        <v>-0.8462</v>
       </c>
       <c r="I155" t="n">
-        <v>1.057953</v>
+        <v>1.181367</v>
       </c>
       <c r="J155" t="n">
         <v>0.5674</v>
@@ -5738,13 +5738,13 @@
         <v>0.750589</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3346</v>
+        <v>0.4405</v>
       </c>
       <c r="H156" t="n">
-        <v>0.3346</v>
+        <v>0.4405</v>
       </c>
       <c r="I156" t="n">
-        <v>1.061493</v>
+        <v>1.18657</v>
       </c>
       <c r="J156" t="n">
         <v>1.0557</v>
@@ -5772,13 +5772,13 @@
         <v>0.77012</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.4485</v>
+        <v>-0.3065</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.4485</v>
+        <v>-0.3065</v>
       </c>
       <c r="I157" t="n">
-        <v>1.056732</v>
+        <v>1.182933</v>
       </c>
       <c r="J157" t="n">
         <v>-0.5908</v>
@@ -5806,13 +5806,13 @@
         <v>0.757961</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0202</v>
+        <v>-0.7684</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0202</v>
+        <v>-0.7684</v>
       </c>
       <c r="I158" t="n">
-        <v>1.056946</v>
+        <v>1.173843</v>
       </c>
       <c r="J158" t="n">
         <v>0.115</v>
@@ -5840,13 +5840,13 @@
         <v>0.720681</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.0114</v>
+        <v>-1.8021</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.0114</v>
+        <v>-1.8021</v>
       </c>
       <c r="I159" t="n">
-        <v>1.056825</v>
+        <v>1.152689</v>
       </c>
       <c r="J159" t="n">
         <v>-0.3936</v>
@@ -5874,13 +5874,13 @@
         <v>0.710296</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3761</v>
+        <v>-0.0017</v>
       </c>
       <c r="H160" t="n">
-        <v>0.3761</v>
+        <v>-0.0017</v>
       </c>
       <c r="I160" t="n">
-        <v>1.0608</v>
+        <v>1.152669</v>
       </c>
       <c r="J160" t="n">
         <v>0.5817</v>
@@ -5908,13 +5908,13 @@
         <v>0.7066170000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.1711</v>
+        <v>-0.0775</v>
       </c>
       <c r="H161" t="n">
-        <v>-0.1711</v>
+        <v>-0.0775</v>
       </c>
       <c r="I161" t="n">
-        <v>1.058985</v>
+        <v>1.151776</v>
       </c>
       <c r="J161" t="n">
         <v>-0.3514</v>
@@ -5942,13 +5942,13 @@
         <v>0.697034</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7454</v>
+        <v>-0.2897</v>
       </c>
       <c r="H162" t="n">
-        <v>0.7454</v>
+        <v>-0.2897</v>
       </c>
       <c r="I162" t="n">
-        <v>1.066878</v>
+        <v>1.148439</v>
       </c>
       <c r="J162" t="n">
         <v>1.8274</v>
@@ -5976,13 +5976,13 @@
         <v>0.692364</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0452</v>
+        <v>-1.1393</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0452</v>
+        <v>-1.1393</v>
       </c>
       <c r="I163" t="n">
-        <v>1.067361</v>
+        <v>1.135355</v>
       </c>
       <c r="J163" t="n">
         <v>-0.1884</v>
@@ -6010,13 +6010,13 @@
         <v>0.675044</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0238</v>
+        <v>0.1324</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0238</v>
+        <v>0.1324</v>
       </c>
       <c r="I164" t="n">
-        <v>1.067615</v>
+        <v>1.136859</v>
       </c>
       <c r="J164" t="n">
         <v>0.0785</v>
@@ -6044,13 +6044,13 @@
         <v>0.689253</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.4315</v>
+        <v>-1.061</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.4315</v>
+        <v>-1.061</v>
       </c>
       <c r="I165" t="n">
-        <v>1.063008</v>
+        <v>1.124797</v>
       </c>
       <c r="J165" t="n">
         <v>-0.924</v>
@@ -6078,13 +6078,13 @@
         <v>0.661616</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1198</v>
+        <v>-1.8096</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1198</v>
+        <v>-1.8096</v>
       </c>
       <c r="I166" t="n">
-        <v>1.064281</v>
+        <v>1.104443</v>
       </c>
       <c r="J166" t="n">
         <v>-0.0315</v>
@@ -6112,13 +6112,13 @@
         <v>0.664683</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.6879</v>
+        <v>-1.7015</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.6879</v>
+        <v>-1.7015</v>
       </c>
       <c r="I167" t="n">
-        <v>1.05696</v>
+        <v>1.08565</v>
       </c>
       <c r="J167" t="n">
         <v>-1.365</v>
@@ -6146,13 +6146,13 @@
         <v>0.643043</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1444</v>
+        <v>0.1154</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1444</v>
+        <v>0.1154</v>
       </c>
       <c r="I168" t="n">
-        <v>1.058487</v>
+        <v>1.086903</v>
       </c>
       <c r="J168" t="n">
         <v>0.3642</v>
@@ -6180,13 +6180,13 @@
         <v>0.6319669999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.6006</v>
+        <v>-1.3025</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.6006</v>
+        <v>-1.3025</v>
       </c>
       <c r="I169" t="n">
-        <v>1.052129</v>
+        <v>1.072746</v>
       </c>
       <c r="J169" t="n">
         <v>-1.2124</v>
@@ -6214,13 +6214,13 @@
         <v>0.643794</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.4465</v>
+        <v>0.0116</v>
       </c>
       <c r="H170" t="n">
-        <v>-0.4465</v>
+        <v>0.0116</v>
       </c>
       <c r="I170" t="n">
-        <v>1.047432</v>
+        <v>1.072871</v>
       </c>
       <c r="J170" t="n">
         <v>-0.6018</v>
@@ -6248,13 +6248,13 @@
         <v>0.637387</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.264</v>
+        <v>-1.2175</v>
       </c>
       <c r="H171" t="n">
-        <v>-0.264</v>
+        <v>-1.2175</v>
       </c>
       <c r="I171" t="n">
-        <v>1.044666</v>
+        <v>1.059808</v>
       </c>
       <c r="J171" t="n">
         <v>-0.7</v>
@@ -6282,13 +6282,13 @@
         <v>0.6250559999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>0.136</v>
+        <v>-0.1671</v>
       </c>
       <c r="H172" t="n">
-        <v>0.136</v>
+        <v>-0.1671</v>
       </c>
       <c r="I172" t="n">
-        <v>1.046087</v>
+        <v>1.058038</v>
       </c>
       <c r="J172" t="n">
         <v>-0.1233</v>
@@ -6316,13 +6316,13 @@
         <v>0.611476</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.4642</v>
+        <v>-1.3454</v>
       </c>
       <c r="H173" t="n">
-        <v>-0.4642</v>
+        <v>-1.3454</v>
       </c>
       <c r="I173" t="n">
-        <v>1.041231</v>
+        <v>1.043802</v>
       </c>
       <c r="J173" t="n">
         <v>-0.8457</v>
@@ -6350,13 +6350,13 @@
         <v>0.652103</v>
       </c>
       <c r="F174" t="n">
-        <v>0.4571</v>
+        <v>1.8583</v>
       </c>
       <c r="H174" t="n">
-        <v>0.4571</v>
+        <v>1.8583</v>
       </c>
       <c r="I174" t="n">
-        <v>1.045991</v>
+        <v>1.0632</v>
       </c>
       <c r="J174" t="n">
         <v>1.2758</v>
@@ -6384,13 +6384,13 @@
         <v>0.64007</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0376</v>
+        <v>-0.3235</v>
       </c>
       <c r="H175" t="n">
-        <v>0.0376</v>
+        <v>-0.3235</v>
       </c>
       <c r="I175" t="n">
-        <v>1.046384</v>
+        <v>1.05976</v>
       </c>
       <c r="J175" t="n">
         <v>0.3028</v>
@@ -6418,13 +6418,13 @@
         <v>0.67449</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.2907</v>
+        <v>0.8749</v>
       </c>
       <c r="H176" t="n">
-        <v>-0.2907</v>
+        <v>0.8749</v>
       </c>
       <c r="I176" t="n">
-        <v>1.043342</v>
+        <v>1.069032</v>
       </c>
       <c r="J176" t="n">
         <v>-0.3801</v>
@@ -6452,13 +6452,13 @@
         <v>0.667951</v>
       </c>
       <c r="F177" t="n">
-        <v>0.1542</v>
+        <v>0.5389</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1542</v>
+        <v>0.5389</v>
       </c>
       <c r="I177" t="n">
-        <v>1.044951</v>
+        <v>1.074794</v>
       </c>
       <c r="J177" t="n">
         <v>0.2157</v>
@@ -6486,13 +6486,13 @@
         <v>0.676527</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.7147</v>
+        <v>-0.0371</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.7147</v>
+        <v>-0.0371</v>
       </c>
       <c r="I178" t="n">
-        <v>1.037483</v>
+        <v>1.074395</v>
       </c>
       <c r="J178" t="n">
         <v>-1.495</v>
@@ -6520,13 +6520,13 @@
         <v>0.696841</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.435</v>
+        <v>1.0744</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.435</v>
+        <v>1.0744</v>
       </c>
       <c r="I179" t="n">
-        <v>1.03297</v>
+        <v>1.085938</v>
       </c>
       <c r="J179" t="n">
         <v>-0.5991</v>
@@ -6554,13 +6554,13 @@
         <v>0.699605</v>
       </c>
       <c r="F180" t="n">
-        <v>0.3219</v>
+        <v>0.0233</v>
       </c>
       <c r="H180" t="n">
-        <v>0.3219</v>
+        <v>0.0233</v>
       </c>
       <c r="I180" t="n">
-        <v>1.036295</v>
+        <v>1.086191</v>
       </c>
       <c r="J180" t="n">
         <v>0.9002</v>
@@ -6588,13 +6588,13 @@
         <v>0.680256</v>
       </c>
       <c r="F181" t="n">
-        <v>0.0675</v>
+        <v>0.4438</v>
       </c>
       <c r="H181" t="n">
-        <v>0.0675</v>
+        <v>0.4438</v>
       </c>
       <c r="I181" t="n">
-        <v>1.036994</v>
+        <v>1.091011</v>
       </c>
       <c r="J181" t="n">
         <v>0.398</v>
@@ -6622,13 +6622,13 @@
         <v>0.681366</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0145</v>
+        <v>0.9775</v>
       </c>
       <c r="H182" t="n">
-        <v>0.0145</v>
+        <v>0.9775</v>
       </c>
       <c r="I182" t="n">
-        <v>1.037145</v>
+        <v>1.101675</v>
       </c>
       <c r="J182" t="n">
         <v>-0.0399</v>
@@ -6656,13 +6656,13 @@
         <v>0.688929</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.2697</v>
+        <v>-0.6805</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.2697</v>
+        <v>-0.6805</v>
       </c>
       <c r="I183" t="n">
-        <v>1.034347</v>
+        <v>1.094178</v>
       </c>
       <c r="J183" t="n">
         <v>-0.5165</v>
@@ -6690,13 +6690,13 @@
         <v>0.654498</v>
       </c>
       <c r="F184" t="n">
-        <v>0.08160000000000001</v>
+        <v>-1.499</v>
       </c>
       <c r="H184" t="n">
-        <v>0.08160000000000001</v>
+        <v>-1.499</v>
       </c>
       <c r="I184" t="n">
-        <v>1.035191</v>
+        <v>1.077777</v>
       </c>
       <c r="J184" t="n">
         <v>-0.2389</v>
@@ -6724,13 +6724,13 @@
         <v>0.647716</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.1528</v>
+        <v>-1.0835</v>
       </c>
       <c r="H185" t="n">
-        <v>-0.1528</v>
+        <v>-1.0835</v>
       </c>
       <c r="I185" t="n">
-        <v>1.03361</v>
+        <v>1.066099</v>
       </c>
       <c r="J185" t="n">
         <v>-0.243</v>
@@ -6758,13 +6758,13 @@
         <v>0.6497579999999999</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3158</v>
+        <v>0.1113</v>
       </c>
       <c r="H186" t="n">
-        <v>0.3158</v>
+        <v>0.1113</v>
       </c>
       <c r="I186" t="n">
-        <v>1.036874</v>
+        <v>1.067285</v>
       </c>
       <c r="J186" t="n">
         <v>0.6821</v>
@@ -6792,13 +6792,13 @@
         <v>0.642321</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.2417</v>
+        <v>-0.6385</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.2417</v>
+        <v>-0.6385</v>
       </c>
       <c r="I187" t="n">
-        <v>1.034368</v>
+        <v>1.060471</v>
       </c>
       <c r="J187" t="n">
         <v>-0.8863</v>
@@ -6826,13 +6826,13 @@
         <v>0.651686</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.3116</v>
+        <v>0.1729</v>
       </c>
       <c r="H188" t="n">
-        <v>-0.3116</v>
+        <v>0.1729</v>
       </c>
       <c r="I188" t="n">
-        <v>1.031145</v>
+        <v>1.062305</v>
       </c>
       <c r="J188" t="n">
         <v>-0.7066</v>
@@ -6860,13 +6860,13 @@
         <v>0.671766</v>
       </c>
       <c r="F189" t="n">
-        <v>1.1488</v>
+        <v>3.0754</v>
       </c>
       <c r="H189" t="n">
-        <v>1.1488</v>
+        <v>3.0754</v>
       </c>
       <c r="I189" t="n">
-        <v>1.04299</v>
+        <v>1.094975</v>
       </c>
       <c r="J189" t="n">
         <v>2.5236</v>
@@ -6894,13 +6894,13 @@
         <v>0.684786</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2233</v>
+        <v>0.2199</v>
       </c>
       <c r="H190" t="n">
-        <v>0.2233</v>
+        <v>0.2199</v>
       </c>
       <c r="I190" t="n">
-        <v>1.045319</v>
+        <v>1.097382</v>
       </c>
       <c r="J190" t="n">
         <v>0.4996</v>
@@ -6928,13 +6928,13 @@
         <v>0.693977</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.2814</v>
+        <v>-0.4875</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.2814</v>
+        <v>-0.4875</v>
       </c>
       <c r="I191" t="n">
-        <v>1.042378</v>
+        <v>1.092032</v>
       </c>
       <c r="J191" t="n">
         <v>-0.1114</v>
@@ -6962,13 +6962,13 @@
         <v>0.695314</v>
       </c>
       <c r="F192" t="n">
-        <v>0.1615</v>
+        <v>-0.122</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1615</v>
+        <v>-0.122</v>
       </c>
       <c r="I192" t="n">
-        <v>1.044061</v>
+        <v>1.0907</v>
       </c>
       <c r="J192" t="n">
         <v>0.5881</v>
@@ -6996,13 +6996,13 @@
         <v>0.674813</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.1808</v>
+        <v>-1.4233</v>
       </c>
       <c r="H193" t="n">
-        <v>-0.1808</v>
+        <v>-1.4233</v>
       </c>
       <c r="I193" t="n">
-        <v>1.042174</v>
+        <v>1.075177</v>
       </c>
       <c r="J193" t="n">
         <v>-0.8284</v>
@@ -7030,13 +7030,13 @@
         <v>0.685584</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.0234</v>
+        <v>0.9829</v>
       </c>
       <c r="H194" t="n">
-        <v>-0.0234</v>
+        <v>0.9829</v>
       </c>
       <c r="I194" t="n">
-        <v>1.04193</v>
+        <v>1.085745</v>
       </c>
       <c r="J194" t="n">
         <v>-0.0892</v>
@@ -7064,13 +7064,13 @@
         <v>0.6945789999999999</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0515</v>
+        <v>0.8536</v>
       </c>
       <c r="H195" t="n">
-        <v>0.0515</v>
+        <v>0.8536</v>
       </c>
       <c r="I195" t="n">
-        <v>1.042466</v>
+        <v>1.095012</v>
       </c>
       <c r="J195" t="n">
         <v>0.2666</v>
@@ -7098,13 +7098,13 @@
         <v>0.7029260000000001</v>
       </c>
       <c r="F196" t="n">
-        <v>0.4677</v>
+        <v>1.4725</v>
       </c>
       <c r="H196" t="n">
-        <v>0.4677</v>
+        <v>1.4725</v>
       </c>
       <c r="I196" t="n">
-        <v>1.047342</v>
+        <v>1.111137</v>
       </c>
       <c r="J196" t="n">
         <v>1.3137</v>
@@ -7132,13 +7132,13 @@
         <v>0.7074859999999999</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.3041</v>
+        <v>0.4747</v>
       </c>
       <c r="H197" t="n">
-        <v>-0.3041</v>
+        <v>0.4747</v>
       </c>
       <c r="I197" t="n">
-        <v>1.044157</v>
+        <v>1.116412</v>
       </c>
       <c r="J197" t="n">
         <v>-0.5497</v>
@@ -7166,13 +7166,13 @@
         <v>0.699214</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.0204</v>
+        <v>0.5374</v>
       </c>
       <c r="H198" t="n">
-        <v>-0.0204</v>
+        <v>0.5374</v>
       </c>
       <c r="I198" t="n">
-        <v>1.043944</v>
+        <v>1.122412</v>
       </c>
       <c r="J198" t="n">
         <v>0.0183</v>
@@ -7200,13 +7200,13 @@
         <v>0.714082</v>
       </c>
       <c r="F199" t="n">
-        <v>0.2067</v>
+        <v>1.8728</v>
       </c>
       <c r="H199" t="n">
-        <v>0.2067</v>
+        <v>1.8728</v>
       </c>
       <c r="I199" t="n">
-        <v>1.046102</v>
+        <v>1.143433</v>
       </c>
       <c r="J199" t="n">
         <v>0.9126</v>
@@ -7234,13 +7234,13 @@
         <v>0.71436</v>
       </c>
       <c r="F200" t="n">
-        <v>0.484</v>
+        <v>-0.9936</v>
       </c>
       <c r="H200" t="n">
-        <v>0.484</v>
+        <v>-0.9936</v>
       </c>
       <c r="I200" t="n">
-        <v>1.051165</v>
+        <v>1.132072</v>
       </c>
       <c r="J200" t="n">
         <v>1.2788</v>
@@ -7268,13 +7268,13 @@
         <v>0.702408</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.1906</v>
+        <v>-0.4836</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.1906</v>
+        <v>-0.4836</v>
       </c>
       <c r="I201" t="n">
-        <v>1.049161</v>
+        <v>1.126597</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6694</v>
@@ -7302,13 +7302,13 @@
         <v>0.710303</v>
       </c>
       <c r="F202" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.5978</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.5978</v>
       </c>
       <c r="I202" t="n">
-        <v>1.041129</v>
+        <v>1.108597</v>
       </c>
       <c r="J202" t="n">
         <v>-1.854</v>
@@ -7336,13 +7336,13 @@
         <v>0.717494</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.1164</v>
+        <v>-0.0459</v>
       </c>
       <c r="H203" t="n">
-        <v>-0.1164</v>
+        <v>-0.0459</v>
       </c>
       <c r="I203" t="n">
-        <v>1.039917</v>
+        <v>1.108087</v>
       </c>
       <c r="J203" t="n">
         <v>-0.3221</v>
@@ -7370,13 +7370,13 @@
         <v>0.7274969999999999</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.6399</v>
+        <v>-1.3672</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.6399</v>
+        <v>-1.3672</v>
       </c>
       <c r="I204" t="n">
-        <v>1.033263</v>
+        <v>1.092937</v>
       </c>
       <c r="J204" t="n">
         <v>-1.546</v>
@@ -7404,13 +7404,13 @@
         <v>0.717821</v>
       </c>
       <c r="F205" t="n">
-        <v>1.1346</v>
+        <v>0.7543</v>
       </c>
       <c r="H205" t="n">
-        <v>1.1346</v>
+        <v>0.7543</v>
       </c>
       <c r="I205" t="n">
-        <v>1.044986</v>
+        <v>1.101181</v>
       </c>
       <c r="J205" t="n">
         <v>1.9824</v>
@@ -7438,13 +7438,13 @@
         <v>0.718253</v>
       </c>
       <c r="F206" t="n">
-        <v>0.3778</v>
+        <v>1.2492</v>
       </c>
       <c r="H206" t="n">
-        <v>0.3778</v>
+        <v>1.2492</v>
       </c>
       <c r="I206" t="n">
-        <v>1.048934</v>
+        <v>1.114937</v>
       </c>
       <c r="J206" t="n">
         <v>0.7963</v>
@@ -7472,13 +7472,13 @@
         <v>0.7081229999999999</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.3973</v>
+        <v>0.3283</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.3973</v>
+        <v>0.3283</v>
       </c>
       <c r="I207" t="n">
-        <v>1.044767</v>
+        <v>1.118597</v>
       </c>
       <c r="J207" t="n">
         <v>-0.9435</v>
@@ -7506,13 +7506,13 @@
         <v>0.711639</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1673</v>
+        <v>0.6127</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1673</v>
+        <v>0.6127</v>
       </c>
       <c r="I208" t="n">
-        <v>1.046515</v>
+        <v>1.125452</v>
       </c>
       <c r="J208" t="n">
         <v>0.3618</v>
@@ -7540,13 +7540,13 @@
         <v>0.7034589999999999</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3566</v>
+        <v>-1.4031</v>
       </c>
       <c r="H209" t="n">
-        <v>0.3566</v>
+        <v>-1.4031</v>
       </c>
       <c r="I209" t="n">
-        <v>1.050246</v>
+        <v>1.10966</v>
       </c>
       <c r="J209" t="n">
         <v>1.0767</v>
@@ -7574,13 +7574,13 @@
         <v>0.704199</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.1761</v>
+        <v>-0.6914</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.1761</v>
+        <v>-0.6914</v>
       </c>
       <c r="I210" t="n">
-        <v>1.048397</v>
+        <v>1.101988</v>
       </c>
       <c r="J210" t="n">
         <v>-0.4025</v>
@@ -7608,13 +7608,13 @@
         <v>0.712067</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.1948</v>
+        <v>-0.5955</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.1948</v>
+        <v>-0.5955</v>
       </c>
       <c r="I211" t="n">
-        <v>1.046355</v>
+        <v>1.095426</v>
       </c>
       <c r="J211" t="n">
         <v>0.0112</v>
@@ -7642,13 +7642,13 @@
         <v>0.717028</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.2841</v>
+        <v>-0.133</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.2841</v>
+        <v>-0.133</v>
       </c>
       <c r="I212" t="n">
-        <v>1.043382</v>
+        <v>1.093969</v>
       </c>
       <c r="J212" t="n">
         <v>-0.516</v>
@@ -7676,13 +7676,13 @@
         <v>0.70458</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.3904</v>
+        <v>-1.0956</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.3904</v>
+        <v>-1.0956</v>
       </c>
       <c r="I213" t="n">
-        <v>1.039309</v>
+        <v>1.081983</v>
       </c>
       <c r="J213" t="n">
         <v>-1.0889</v>
@@ -7710,13 +7710,13 @@
         <v>0.70525</v>
       </c>
       <c r="F214" t="n">
-        <v>0.4836</v>
+        <v>-0.924</v>
       </c>
       <c r="H214" t="n">
-        <v>0.4836</v>
+        <v>-0.924</v>
       </c>
       <c r="I214" t="n">
-        <v>1.044335</v>
+        <v>1.071986</v>
       </c>
       <c r="J214" t="n">
         <v>1.0306</v>
@@ -7744,13 +7744,13 @@
         <v>0.688242</v>
       </c>
       <c r="F215" t="n">
-        <v>0.359</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="H215" t="n">
-        <v>0.359</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>1.048084</v>
+        <v>1.062547</v>
       </c>
       <c r="J215" t="n">
         <v>0.6531</v>
@@ -7778,13 +7778,13 @@
         <v>0.683824</v>
       </c>
       <c r="F216" t="n">
-        <v>0.1248</v>
+        <v>-0.4577</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1248</v>
+        <v>-0.4577</v>
       </c>
       <c r="I216" t="n">
-        <v>1.049392</v>
+        <v>1.057684</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0237</v>
@@ -7812,13 +7812,13 @@
         <v>0.68462</v>
       </c>
       <c r="F217" t="n">
-        <v>0.1753</v>
+        <v>-0.238</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1753</v>
+        <v>-0.238</v>
       </c>
       <c r="I217" t="n">
-        <v>1.051231</v>
+        <v>1.055167</v>
       </c>
       <c r="J217" t="n">
         <v>0.3157</v>
@@ -7846,13 +7846,13 @@
         <v>0.689492</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.317</v>
+        <v>0.0286</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.317</v>
+        <v>0.0286</v>
       </c>
       <c r="I218" t="n">
-        <v>1.047899</v>
+        <v>1.055468</v>
       </c>
       <c r="J218" t="n">
         <v>-0.8327</v>
@@ -7880,13 +7880,13 @@
         <v>0.676376</v>
       </c>
       <c r="F219" t="n">
-        <v>0.1635</v>
+        <v>-1.1433</v>
       </c>
       <c r="H219" t="n">
-        <v>0.1635</v>
+        <v>-1.1433</v>
       </c>
       <c r="I219" t="n">
-        <v>1.049612</v>
+        <v>1.043402</v>
       </c>
       <c r="J219" t="n">
         <v>0.0312</v>
@@ -7914,13 +7914,13 @@
         <v>0.695184</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0086</v>
+        <v>0.2847</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0086</v>
+        <v>0.2847</v>
       </c>
       <c r="I220" t="n">
-        <v>1.049703</v>
+        <v>1.046372</v>
       </c>
       <c r="J220" t="n">
         <v>0.3941</v>
@@ -7948,13 +7948,13 @@
         <v>0.703195</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.3417</v>
+        <v>-0.2062</v>
       </c>
       <c r="H221" t="n">
-        <v>-0.3417</v>
+        <v>-0.2062</v>
       </c>
       <c r="I221" t="n">
-        <v>1.046116</v>
+        <v>1.044214</v>
       </c>
       <c r="J221" t="n">
         <v>-0.529</v>
@@ -7982,13 +7982,13 @@
         <v>0.687819</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.336</v>
+        <v>-0.9253</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.336</v>
+        <v>-0.9253</v>
       </c>
       <c r="I222" t="n">
-        <v>1.042601</v>
+        <v>1.034552</v>
       </c>
       <c r="J222" t="n">
         <v>-1.0787</v>
@@ -8016,13 +8016,13 @@
         <v>0.703447</v>
       </c>
       <c r="F223" t="n">
-        <v>0.2169</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="H223" t="n">
-        <v>0.2169</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="I223" t="n">
-        <v>1.044862</v>
+        <v>1.044726</v>
       </c>
       <c r="J223" t="n">
         <v>0.6642</v>
@@ -8050,13 +8050,13 @@
         <v>0.703274</v>
       </c>
       <c r="F224" t="n">
-        <v>0.2616</v>
+        <v>0.782</v>
       </c>
       <c r="H224" t="n">
-        <v>0.2616</v>
+        <v>0.782</v>
       </c>
       <c r="I224" t="n">
-        <v>1.047596</v>
+        <v>1.052896</v>
       </c>
       <c r="J224" t="n">
         <v>1.132</v>
@@ -8084,13 +8084,13 @@
         <v>0.6857259999999999</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0474</v>
+        <v>-1.1642</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0474</v>
+        <v>-1.1642</v>
       </c>
       <c r="I225" t="n">
-        <v>1.048092</v>
+        <v>1.040638</v>
       </c>
       <c r="J225" t="n">
         <v>-0.091</v>
@@ -8118,13 +8118,13 @@
         <v>0.683391</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.2507</v>
+        <v>0.1472</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.2507</v>
+        <v>0.1472</v>
       </c>
       <c r="I226" t="n">
-        <v>1.045465</v>
+        <v>1.04217</v>
       </c>
       <c r="J226" t="n">
         <v>-0.8229</v>
@@ -8152,13 +8152,13 @@
         <v>0.678854</v>
       </c>
       <c r="F227" t="n">
-        <v>0.71</v>
+        <v>-0.454</v>
       </c>
       <c r="H227" t="n">
-        <v>0.71</v>
+        <v>-0.454</v>
       </c>
       <c r="I227" t="n">
-        <v>1.052887</v>
+        <v>1.037438</v>
       </c>
       <c r="J227" t="n">
         <v>1.2651</v>
@@ -8186,13 +8186,13 @@
         <v>0.682157</v>
       </c>
       <c r="F228" t="n">
-        <v>0.5942</v>
+        <v>0.226</v>
       </c>
       <c r="H228" t="n">
-        <v>0.5942</v>
+        <v>0.226</v>
       </c>
       <c r="I228" t="n">
-        <v>1.059144</v>
+        <v>1.039783</v>
       </c>
       <c r="J228" t="n">
         <v>1.1244</v>
@@ -8220,13 +8220,13 @@
         <v>0.687186</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.3407</v>
+        <v>-0.6845</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.3407</v>
+        <v>-0.6845</v>
       </c>
       <c r="I229" t="n">
-        <v>1.055535</v>
+        <v>1.032666</v>
       </c>
       <c r="J229" t="n">
         <v>-0.3675</v>
@@ -8254,13 +8254,13 @@
         <v>0.685437</v>
       </c>
       <c r="F230" t="n">
-        <v>0.2357</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="H230" t="n">
-        <v>0.2357</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>1.058023</v>
+        <v>1.026123</v>
       </c>
       <c r="J230" t="n">
         <v>0.3655</v>
@@ -8288,13 +8288,13 @@
         <v>0.678221</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.1757</v>
+        <v>-0.1646</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.1757</v>
+        <v>-0.1646</v>
       </c>
       <c r="I231" t="n">
-        <v>1.056164</v>
+        <v>1.024434</v>
       </c>
       <c r="J231" t="n">
         <v>-0.4361</v>
@@ -8322,13 +8322,13 @@
         <v>0.686626</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1784</v>
+        <v>0.1321</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1784</v>
+        <v>0.1321</v>
       </c>
       <c r="I232" t="n">
-        <v>1.058048</v>
+        <v>1.025786</v>
       </c>
       <c r="J232" t="n">
         <v>0.5543</v>
@@ -8356,13 +8356,13 @@
         <v>0.659016</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0341</v>
+        <v>0.9327</v>
       </c>
       <c r="H233" t="n">
-        <v>0.0341</v>
+        <v>0.9327</v>
       </c>
       <c r="I233" t="n">
-        <v>1.058409</v>
+        <v>1.035354</v>
       </c>
       <c r="J233" t="n">
         <v>-0.2151</v>
@@ -8390,13 +8390,13 @@
         <v>0.654722</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.2335</v>
+        <v>-1.0546</v>
       </c>
       <c r="H234" t="n">
-        <v>-0.2335</v>
+        <v>-1.0546</v>
       </c>
       <c r="I234" t="n">
-        <v>1.055938</v>
+        <v>1.024435</v>
       </c>
       <c r="J234" t="n">
         <v>-0.3271</v>
@@ -8424,13 +8424,13 @@
         <v>0.648489</v>
       </c>
       <c r="F235" t="n">
-        <v>0.361</v>
+        <v>-0.253</v>
       </c>
       <c r="H235" t="n">
-        <v>0.361</v>
+        <v>-0.253</v>
       </c>
       <c r="I235" t="n">
-        <v>1.05975</v>
+        <v>1.021843</v>
       </c>
       <c r="J235" t="n">
         <v>0.8120000000000001</v>
@@ -8458,13 +8458,13 @@
         <v>0.6410709999999999</v>
       </c>
       <c r="F236" t="n">
-        <v>1.1109</v>
+        <v>1.1155</v>
       </c>
       <c r="H236" t="n">
-        <v>1.1109</v>
+        <v>1.1155</v>
       </c>
       <c r="I236" t="n">
-        <v>1.071522</v>
+        <v>1.033243</v>
       </c>
       <c r="J236" t="n">
         <v>2.1135</v>
@@ -8492,13 +8492,13 @@
         <v>0.633989</v>
       </c>
       <c r="F237" t="n">
-        <v>0.7853</v>
+        <v>0.446</v>
       </c>
       <c r="H237" t="n">
-        <v>0.7853</v>
+        <v>0.446</v>
       </c>
       <c r="I237" t="n">
-        <v>1.079937</v>
+        <v>1.03785</v>
       </c>
       <c r="J237" t="n">
         <v>1.2177</v>
@@ -8526,13 +8526,13 @@
         <v>0.620678</v>
       </c>
       <c r="F238" t="n">
-        <v>1.1813</v>
+        <v>-0.8259</v>
       </c>
       <c r="H238" t="n">
-        <v>1.1813</v>
+        <v>-0.8259</v>
       </c>
       <c r="I238" t="n">
-        <v>1.092694</v>
+        <v>1.029279</v>
       </c>
       <c r="J238" t="n">
         <v>2.1111</v>
@@ -8560,13 +8560,13 @@
         <v>0.635906</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.6902</v>
+        <v>3.6184</v>
       </c>
       <c r="H239" t="n">
-        <v>-0.6902</v>
+        <v>3.6184</v>
       </c>
       <c r="I239" t="n">
-        <v>1.085153</v>
+        <v>1.066523</v>
       </c>
       <c r="J239" t="n">
         <v>-1.1877</v>
@@ -8594,13 +8594,13 @@
         <v>0.617835</v>
       </c>
       <c r="F240" t="n">
-        <v>0.6307</v>
+        <v>-0.6714</v>
       </c>
       <c r="H240" t="n">
-        <v>0.6307</v>
+        <v>-0.6714</v>
       </c>
       <c r="I240" t="n">
-        <v>1.091997</v>
+        <v>1.059362</v>
       </c>
       <c r="J240" t="n">
         <v>1.3608</v>
@@ -8628,13 +8628,13 @@
         <v>0.619522</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.4315</v>
+        <v>-0.6085</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.4315</v>
+        <v>-0.6085</v>
       </c>
       <c r="I241" t="n">
-        <v>1.087285</v>
+        <v>1.052916</v>
       </c>
       <c r="J241" t="n">
         <v>-1.1751</v>
@@ -8662,13 +8662,13 @@
         <v>0.605776</v>
       </c>
       <c r="F242" t="n">
-        <v>0.1867</v>
+        <v>-0.4904</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1867</v>
+        <v>-0.4904</v>
       </c>
       <c r="I242" t="n">
-        <v>1.089315</v>
+        <v>1.047753</v>
       </c>
       <c r="J242" t="n">
         <v>0.4582</v>
@@ -8696,13 +8696,13 @@
         <v>0.613679</v>
       </c>
       <c r="F243" t="n">
-        <v>0.2566</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H243" t="n">
-        <v>0.2566</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="I243" t="n">
-        <v>1.09211</v>
+        <v>1.048701</v>
       </c>
       <c r="J243" t="n">
         <v>1.088</v>
@@ -8730,13 +8730,13 @@
         <v>0.631479</v>
       </c>
       <c r="F244" t="n">
-        <v>-0.5876</v>
+        <v>0.3145</v>
       </c>
       <c r="H244" t="n">
-        <v>-0.5876</v>
+        <v>0.3145</v>
       </c>
       <c r="I244" t="n">
-        <v>1.085693</v>
+        <v>1.051999</v>
       </c>
       <c r="J244" t="n">
         <v>-0.6644</v>
@@ -8764,13 +8764,13 @@
         <v>0.605308</v>
       </c>
       <c r="F245" t="n">
-        <v>0.3888</v>
+        <v>0.0163</v>
       </c>
       <c r="H245" t="n">
-        <v>0.3888</v>
+        <v>0.0163</v>
       </c>
       <c r="I245" t="n">
-        <v>1.089914</v>
+        <v>1.05217</v>
       </c>
       <c r="J245" t="n">
         <v>0.9074</v>
@@ -8798,13 +8798,13 @@
         <v>0.607253</v>
       </c>
       <c r="F246" t="n">
-        <v>0.4431</v>
+        <v>0.1491</v>
       </c>
       <c r="H246" t="n">
-        <v>0.4431</v>
+        <v>0.1491</v>
       </c>
       <c r="I246" t="n">
-        <v>1.094743</v>
+        <v>1.053739</v>
       </c>
       <c r="J246" t="n">
         <v>0.9875</v>
@@ -8832,13 +8832,13 @@
         <v>0.601778</v>
       </c>
       <c r="F247" t="n">
-        <v>1.0541</v>
+        <v>0.3368</v>
       </c>
       <c r="H247" t="n">
-        <v>1.0541</v>
+        <v>0.3368</v>
       </c>
       <c r="I247" t="n">
-        <v>1.106283</v>
+        <v>1.057287</v>
       </c>
       <c r="J247" t="n">
         <v>2.3057</v>
@@ -8866,13 +8866,13 @@
         <v>0.613804</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.6992</v>
+        <v>1.7899</v>
       </c>
       <c r="H248" t="n">
-        <v>-0.6992</v>
+        <v>1.7899</v>
       </c>
       <c r="I248" t="n">
-        <v>1.098548</v>
+        <v>1.076211</v>
       </c>
       <c r="J248" t="n">
         <v>-1.6787</v>
@@ -8900,13 +8900,13 @@
         <v>0.599286</v>
       </c>
       <c r="F249" t="n">
-        <v>0.1961</v>
+        <v>-1.1194</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1961</v>
+        <v>-1.1194</v>
       </c>
       <c r="I249" t="n">
-        <v>1.100702</v>
+        <v>1.064164</v>
       </c>
       <c r="J249" t="n">
         <v>0.2985</v>
@@ -8934,13 +8934,13 @@
         <v>0.609091</v>
       </c>
       <c r="F250" t="n">
-        <v>-0.2054</v>
+        <v>-1.3536</v>
       </c>
       <c r="H250" t="n">
-        <v>-0.2054</v>
+        <v>-1.3536</v>
       </c>
       <c r="I250" t="n">
-        <v>1.098441</v>
+        <v>1.049759</v>
       </c>
       <c r="J250" t="n">
         <v>-0.9918</v>
@@ -8968,13 +8968,13 @@
         <v>0.6350980000000001</v>
       </c>
       <c r="F251" t="n">
-        <v>-0.8972</v>
+        <v>-0.9176</v>
       </c>
       <c r="H251" t="n">
-        <v>-0.8972</v>
+        <v>-0.9176</v>
       </c>
       <c r="I251" t="n">
-        <v>1.088586</v>
+        <v>1.040127</v>
       </c>
       <c r="J251" t="n">
         <v>-1.9725</v>
@@ -9002,13 +9002,13 @@
         <v>0.6279979999999999</v>
       </c>
       <c r="F252" t="n">
-        <v>0.3667</v>
+        <v>-0.0946</v>
       </c>
       <c r="H252" t="n">
-        <v>0.3667</v>
+        <v>-0.0946</v>
       </c>
       <c r="I252" t="n">
-        <v>1.092578</v>
+        <v>1.039142</v>
       </c>
       <c r="J252" t="n">
         <v>0.8808</v>
@@ -9036,13 +9036,13 @@
         <v>0.632714</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.3339</v>
+        <v>0.1289</v>
       </c>
       <c r="H253" t="n">
-        <v>-0.3339</v>
+        <v>0.1289</v>
       </c>
       <c r="I253" t="n">
-        <v>1.08893</v>
+        <v>1.040482</v>
       </c>
       <c r="J253" t="n">
         <v>-0.2726</v>
@@ -9070,13 +9070,13 @@
         <v>0.628722</v>
       </c>
       <c r="F254" t="n">
-        <v>0.9588</v>
+        <v>-0.1876</v>
       </c>
       <c r="H254" t="n">
-        <v>0.9588</v>
+        <v>-0.1876</v>
       </c>
       <c r="I254" t="n">
-        <v>1.09937</v>
+        <v>1.038531</v>
       </c>
       <c r="J254" t="n">
         <v>1.6512</v>
@@ -9104,13 +9104,13 @@
         <v>0.65299</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.4929</v>
+        <v>0.0496</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.4929</v>
+        <v>0.0496</v>
       </c>
       <c r="I255" t="n">
-        <v>1.093951</v>
+        <v>1.039045</v>
       </c>
       <c r="J255" t="n">
         <v>-0.7157</v>
@@ -9138,13 +9138,13 @@
         <v>0.659488</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.5595</v>
+        <v>0.9765</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.5595</v>
+        <v>0.9765</v>
       </c>
       <c r="I256" t="n">
-        <v>1.087831</v>
+        <v>1.049191</v>
       </c>
       <c r="J256" t="n">
         <v>-0.6228</v>
@@ -9172,13 +9172,13 @@
         <v>0.662359</v>
       </c>
       <c r="F257" t="n">
-        <v>0.2888</v>
+        <v>1.6973</v>
       </c>
       <c r="H257" t="n">
-        <v>0.2888</v>
+        <v>1.6973</v>
       </c>
       <c r="I257" t="n">
-        <v>1.090972</v>
+        <v>1.067</v>
       </c>
       <c r="J257" t="n">
         <v>0.9981</v>
@@ -9206,13 +9206,13 @@
         <v>0.650141</v>
       </c>
       <c r="F258" t="n">
-        <v>0.284</v>
+        <v>-1.359</v>
       </c>
       <c r="H258" t="n">
-        <v>0.284</v>
+        <v>-1.359</v>
       </c>
       <c r="I258" t="n">
-        <v>1.094071</v>
+        <v>1.052499</v>
       </c>
       <c r="J258" t="n">
         <v>0.4906</v>
@@ -9240,13 +9240,13 @@
         <v>0.64658</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.0373</v>
+        <v>0.0513</v>
       </c>
       <c r="H259" t="n">
-        <v>-0.0373</v>
+        <v>0.0513</v>
       </c>
       <c r="I259" t="n">
-        <v>1.093663</v>
+        <v>1.053039</v>
       </c>
       <c r="J259" t="n">
         <v>-0.2132</v>
@@ -9274,13 +9274,13 @@
         <v>0.658307</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.1126</v>
+        <v>0.0191</v>
       </c>
       <c r="H260" t="n">
-        <v>-0.1126</v>
+        <v>0.0191</v>
       </c>
       <c r="I260" t="n">
-        <v>1.092431</v>
+        <v>1.05324</v>
       </c>
       <c r="J260" t="n">
         <v>-0.2112</v>
@@ -9308,13 +9308,13 @@
         <v>0.6444879999999999</v>
       </c>
       <c r="F261" t="n">
-        <v>0.3598</v>
+        <v>-1.4046</v>
       </c>
       <c r="H261" t="n">
-        <v>0.3598</v>
+        <v>-1.4046</v>
       </c>
       <c r="I261" t="n">
-        <v>1.096362</v>
+        <v>1.038447</v>
       </c>
       <c r="J261" t="n">
         <v>0.1433</v>
@@ -9342,13 +9342,13 @@
         <v>0.63978</v>
       </c>
       <c r="F262" t="n">
-        <v>0.1305</v>
+        <v>0.4215</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1305</v>
+        <v>0.4215</v>
       </c>
       <c r="I262" t="n">
-        <v>1.097793</v>
+        <v>1.042823</v>
       </c>
       <c r="J262" t="n">
         <v>0.5968</v>
@@ -9376,13 +9376,13 @@
         <v>0.651671</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.0551</v>
+        <v>-0.6079</v>
       </c>
       <c r="H263" t="n">
-        <v>-0.0551</v>
+        <v>-0.6079</v>
       </c>
       <c r="I263" t="n">
-        <v>1.097188</v>
+        <v>1.036484</v>
       </c>
       <c r="J263" t="n">
         <v>0.234</v>
@@ -9410,13 +9410,13 @@
         <v>0.651676</v>
       </c>
       <c r="F264" t="n">
-        <v>0.2694</v>
+        <v>0.1552</v>
       </c>
       <c r="H264" t="n">
-        <v>0.2694</v>
+        <v>0.1552</v>
       </c>
       <c r="I264" t="n">
-        <v>1.100144</v>
+        <v>1.038092</v>
       </c>
       <c r="J264" t="n">
         <v>0.4423</v>
@@ -9444,13 +9444,13 @@
         <v>0.644236</v>
       </c>
       <c r="F265" t="n">
-        <v>0.6693</v>
+        <v>-0.2701</v>
       </c>
       <c r="H265" t="n">
-        <v>0.6693</v>
+        <v>-0.2701</v>
       </c>
       <c r="I265" t="n">
-        <v>1.107507</v>
+        <v>1.035288</v>
       </c>
       <c r="J265" t="n">
         <v>0.9811</v>
@@ -9478,13 +9478,13 @@
         <v>0.6497540000000001</v>
       </c>
       <c r="F266" t="n">
-        <v>0.4728</v>
+        <v>-0.1144</v>
       </c>
       <c r="H266" t="n">
-        <v>0.4728</v>
+        <v>-0.1144</v>
       </c>
       <c r="I266" t="n">
-        <v>1.112743</v>
+        <v>1.034104</v>
       </c>
       <c r="J266" t="n">
         <v>1.1467</v>
@@ -9512,13 +9512,13 @@
         <v>0.668666</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.8265</v>
+        <v>-2.0449</v>
       </c>
       <c r="H267" t="n">
-        <v>-0.8265</v>
+        <v>-2.0449</v>
       </c>
       <c r="I267" t="n">
-        <v>1.103546</v>
+        <v>1.012957</v>
       </c>
       <c r="J267" t="n">
         <v>-2.0512</v>
@@ -9546,13 +9546,13 @@
         <v>0.708829</v>
       </c>
       <c r="F268" t="n">
-        <v>-1.2305</v>
+        <v>0.1044</v>
       </c>
       <c r="H268" t="n">
-        <v>-1.2305</v>
+        <v>0.1044</v>
       </c>
       <c r="I268" t="n">
-        <v>1.089967</v>
+        <v>1.014015</v>
       </c>
       <c r="J268" t="n">
         <v>-2.6202</v>
@@ -9580,13 +9580,13 @@
         <v>0.7009</v>
       </c>
       <c r="F269" t="n">
-        <v>0.3275</v>
+        <v>-0.2045</v>
       </c>
       <c r="H269" t="n">
-        <v>0.3275</v>
+        <v>-0.2045</v>
       </c>
       <c r="I269" t="n">
-        <v>1.093537</v>
+        <v>1.011941</v>
       </c>
       <c r="J269" t="n">
         <v>1.0806</v>
@@ -9614,13 +9614,13 @@
         <v>0.688035</v>
       </c>
       <c r="F270" t="n">
-        <v>0.1782</v>
+        <v>-0.3949</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1782</v>
+        <v>-0.3949</v>
       </c>
       <c r="I270" t="n">
-        <v>1.095485</v>
+        <v>1.007944</v>
       </c>
       <c r="J270" t="n">
         <v>0.6499</v>
@@ -9648,13 +9648,13 @@
         <v>0.684901</v>
       </c>
       <c r="F271" t="n">
-        <v>0.3197</v>
+        <v>2.1916</v>
       </c>
       <c r="H271" t="n">
-        <v>0.3197</v>
+        <v>2.1916</v>
       </c>
       <c r="I271" t="n">
-        <v>1.098988</v>
+        <v>1.030034</v>
       </c>
       <c r="J271" t="n">
         <v>1.0687</v>
@@ -9682,13 +9682,13 @@
         <v>0.696948</v>
       </c>
       <c r="F272" t="n">
-        <v>0.1199</v>
+        <v>-0.0722</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1199</v>
+        <v>-0.0722</v>
       </c>
       <c r="I272" t="n">
-        <v>1.100305</v>
+        <v>1.029291</v>
       </c>
       <c r="J272" t="n">
         <v>0.1325</v>
@@ -9716,13 +9716,13 @@
         <v>0.676652</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4692</v>
+        <v>-0.1551</v>
       </c>
       <c r="H273" t="n">
-        <v>0.4692</v>
+        <v>-0.1551</v>
       </c>
       <c r="I273" t="n">
-        <v>1.105468</v>
+        <v>1.027694</v>
       </c>
       <c r="J273" t="n">
         <v>0.9009</v>
@@ -9750,13 +9750,13 @@
         <v>0.695764</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.3685</v>
+        <v>-0.1177</v>
       </c>
       <c r="H274" t="n">
-        <v>-0.3685</v>
+        <v>-0.1177</v>
       </c>
       <c r="I274" t="n">
-        <v>1.101394</v>
+        <v>1.026485</v>
       </c>
       <c r="J274" t="n">
         <v>-0.9084</v>
@@ -9784,13 +9784,13 @@
         <v>0.712828</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.214</v>
+        <v>0.6857</v>
       </c>
       <c r="H275" t="n">
-        <v>-0.214</v>
+        <v>0.6857</v>
       </c>
       <c r="I275" t="n">
-        <v>1.099037</v>
+        <v>1.033523</v>
       </c>
       <c r="J275" t="n">
         <v>-0.799</v>
@@ -9818,13 +9818,13 @@
         <v>0.715356</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.6158</v>
+        <v>1.0336</v>
       </c>
       <c r="H276" t="n">
-        <v>-0.6158</v>
+        <v>1.0336</v>
       </c>
       <c r="I276" t="n">
-        <v>1.09227</v>
+        <v>1.044205</v>
       </c>
       <c r="J276" t="n">
         <v>-0.9287</v>
@@ -9852,13 +9852,13 @@
         <v>0.704387</v>
       </c>
       <c r="F277" t="n">
-        <v>0.1002</v>
+        <v>0.3774</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1002</v>
+        <v>0.3774</v>
       </c>
       <c r="I277" t="n">
-        <v>1.093364</v>
+        <v>1.048147</v>
       </c>
       <c r="J277" t="n">
         <v>0.2559</v>
@@ -9886,13 +9886,13 @@
         <v>0.71484</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.0214</v>
+        <v>-0.1067</v>
       </c>
       <c r="H278" t="n">
-        <v>-1.0214</v>
+        <v>-0.1067</v>
       </c>
       <c r="I278" t="n">
-        <v>1.082196</v>
+        <v>1.047028</v>
       </c>
       <c r="J278" t="n">
         <v>-1.7678</v>
@@ -9920,13 +9920,13 @@
         <v>0.700841</v>
       </c>
       <c r="F279" t="n">
-        <v>0.5322</v>
+        <v>0.0673</v>
       </c>
       <c r="H279" t="n">
-        <v>0.5322</v>
+        <v>0.0673</v>
       </c>
       <c r="I279" t="n">
-        <v>1.087956</v>
+        <v>1.047732</v>
       </c>
       <c r="J279" t="n">
         <v>1.1158</v>
@@ -9954,13 +9954,13 @@
         <v>0.713858</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.2331</v>
+        <v>-0.9709</v>
       </c>
       <c r="H280" t="n">
-        <v>-0.2331</v>
+        <v>-0.9709</v>
       </c>
       <c r="I280" t="n">
-        <v>1.08542</v>
+        <v>1.03756</v>
       </c>
       <c r="J280" t="n">
         <v>-0.9412</v>
@@ -9988,13 +9988,13 @@
         <v>0.721641</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.7534</v>
+        <v>-1.0701</v>
       </c>
       <c r="H281" t="n">
-        <v>-0.7534</v>
+        <v>-1.0701</v>
       </c>
       <c r="I281" t="n">
-        <v>1.077242</v>
+        <v>1.026457</v>
       </c>
       <c r="J281" t="n">
         <v>-2.2286</v>
@@ -10022,13 +10022,13 @@
         <v>0.734453</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.9802</v>
+        <v>-1.6435</v>
       </c>
       <c r="H282" t="n">
-        <v>-0.9802</v>
+        <v>-1.6435</v>
       </c>
       <c r="I282" t="n">
-        <v>1.066683</v>
+        <v>1.009587</v>
       </c>
       <c r="J282" t="n">
         <v>-2.1259</v>
@@ -10056,13 +10056,13 @@
         <v>0.728677</v>
       </c>
       <c r="F283" t="n">
-        <v>0.8482</v>
+        <v>2.2521</v>
       </c>
       <c r="H283" t="n">
-        <v>0.8482</v>
+        <v>2.2521</v>
       </c>
       <c r="I283" t="n">
-        <v>1.075731</v>
+        <v>1.032324</v>
       </c>
       <c r="J283" t="n">
         <v>2.4572</v>
@@ -10090,13 +10090,13 @@
         <v>0.7165629999999999</v>
       </c>
       <c r="F284" t="n">
-        <v>0.3427</v>
+        <v>-0.7409</v>
       </c>
       <c r="H284" t="n">
-        <v>0.3427</v>
+        <v>-0.7409</v>
       </c>
       <c r="I284" t="n">
-        <v>1.079417</v>
+        <v>1.024675</v>
       </c>
       <c r="J284" t="n">
         <v>0.8823</v>
@@ -10124,13 +10124,13 @@
         <v>0.731376</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.0925</v>
+        <v>1.9122</v>
       </c>
       <c r="H285" t="n">
-        <v>-0.0925</v>
+        <v>1.9122</v>
       </c>
       <c r="I285" t="n">
-        <v>1.078419</v>
+        <v>1.044269</v>
       </c>
       <c r="J285" t="n">
         <v>-0.2593</v>
@@ -10158,13 +10158,13 @@
         <v>0.72627</v>
       </c>
       <c r="F286" t="n">
-        <v>0.4569</v>
+        <v>2.8888</v>
       </c>
       <c r="H286" t="n">
-        <v>0.4569</v>
+        <v>2.8888</v>
       </c>
       <c r="I286" t="n">
-        <v>1.083346</v>
+        <v>1.074436</v>
       </c>
       <c r="J286" t="n">
         <v>1.0066</v>
@@ -10192,13 +10192,13 @@
         <v>0.739109</v>
       </c>
       <c r="F287" t="n">
-        <v>0.2332</v>
+        <v>0.8184</v>
       </c>
       <c r="H287" t="n">
-        <v>0.2332</v>
+        <v>0.8184</v>
       </c>
       <c r="I287" t="n">
-        <v>1.085872</v>
+        <v>1.083229</v>
       </c>
       <c r="J287" t="n">
         <v>0.6026</v>
@@ -10226,13 +10226,13 @@
         <v>0.749651</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.3548</v>
+        <v>0.7115</v>
       </c>
       <c r="H288" t="n">
-        <v>-0.3548</v>
+        <v>0.7115</v>
       </c>
       <c r="I288" t="n">
-        <v>1.08202</v>
+        <v>1.090936</v>
       </c>
       <c r="J288" t="n">
         <v>-0.7337</v>
@@ -10260,13 +10260,13 @@
         <v>0.725111</v>
       </c>
       <c r="F289" t="n">
-        <v>0.3923</v>
+        <v>1.2662</v>
       </c>
       <c r="H289" t="n">
-        <v>0.3923</v>
+        <v>1.2662</v>
       </c>
       <c r="I289" t="n">
-        <v>1.086265</v>
+        <v>1.104749</v>
       </c>
       <c r="J289" t="n">
         <v>0.3529</v>
@@ -10294,13 +10294,13 @@
         <v>0.746923</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.3986</v>
+        <v>2.2475</v>
       </c>
       <c r="H290" t="n">
-        <v>-0.3986</v>
+        <v>2.2475</v>
       </c>
       <c r="I290" t="n">
-        <v>1.081935</v>
+        <v>1.129579</v>
       </c>
       <c r="J290" t="n">
         <v>-0.7107</v>
@@ -10328,13 +10328,13 @@
         <v>0.738077</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.1428</v>
+        <v>-2.1668</v>
       </c>
       <c r="H291" t="n">
-        <v>-0.1428</v>
+        <v>-2.1668</v>
       </c>
       <c r="I291" t="n">
-        <v>1.08039</v>
+        <v>1.105104</v>
       </c>
       <c r="J291" t="n">
         <v>-1.2125</v>
@@ -10362,13 +10362,13 @@
         <v>0.7313460000000001</v>
       </c>
       <c r="F292" t="n">
-        <v>0.4707</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="H292" t="n">
-        <v>0.4707</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I292" t="n">
-        <v>1.085475</v>
+        <v>1.111983</v>
       </c>
       <c r="J292" t="n">
         <v>1.3748</v>
@@ -10396,13 +10396,13 @@
         <v>0.692064</v>
       </c>
       <c r="F293" t="n">
-        <v>0.5855</v>
+        <v>-2.6446</v>
       </c>
       <c r="H293" t="n">
-        <v>0.5855</v>
+        <v>-2.6446</v>
       </c>
       <c r="I293" t="n">
-        <v>1.091831</v>
+        <v>1.082576</v>
       </c>
       <c r="J293" t="n">
         <v>0.9177999999999999</v>
@@ -10430,13 +10430,13 @@
         <v>0.691302</v>
       </c>
       <c r="F294" t="n">
-        <v>0.0453</v>
+        <v>-1.2815</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0453</v>
+        <v>-1.2815</v>
       </c>
       <c r="I294" t="n">
-        <v>1.092325</v>
+        <v>1.068703</v>
       </c>
       <c r="J294" t="n">
         <v>-0.1089</v>
@@ -10464,13 +10464,13 @@
         <v>0.682215</v>
       </c>
       <c r="F295" t="n">
-        <v>-0.2552</v>
+        <v>0.4966</v>
       </c>
       <c r="H295" t="n">
-        <v>-0.2552</v>
+        <v>0.4966</v>
       </c>
       <c r="I295" t="n">
-        <v>1.089538</v>
+        <v>1.074009</v>
       </c>
       <c r="J295" t="n">
         <v>-0.8371</v>
@@ -10498,13 +10498,13 @@
         <v>0.676287</v>
       </c>
       <c r="F296" t="n">
-        <v>0.0684</v>
+        <v>-1.0238</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0684</v>
+        <v>-1.0238</v>
       </c>
       <c r="I296" t="n">
-        <v>1.090283</v>
+        <v>1.063013</v>
       </c>
       <c r="J296" t="n">
         <v>0.0973</v>
@@ -10532,13 +10532,13 @@
         <v>0.663084</v>
       </c>
       <c r="F297" t="n">
-        <v>0.0886</v>
+        <v>-1.0147</v>
       </c>
       <c r="H297" t="n">
-        <v>0.0886</v>
+        <v>-1.0147</v>
       </c>
       <c r="I297" t="n">
-        <v>1.091249</v>
+        <v>1.052227</v>
       </c>
       <c r="J297" t="n">
         <v>0.091</v>
@@ -10566,13 +10566,13 @@
         <v>0.664862</v>
       </c>
       <c r="F298" t="n">
-        <v>0.105</v>
+        <v>2.0477</v>
       </c>
       <c r="H298" t="n">
-        <v>0.105</v>
+        <v>2.0477</v>
       </c>
       <c r="I298" t="n">
-        <v>1.092395</v>
+        <v>1.073773</v>
       </c>
       <c r="J298" t="n">
         <v>-0.129</v>
@@ -10600,13 +10600,13 @@
         <v>0.65896</v>
       </c>
       <c r="F299" t="n">
-        <v>0.3721</v>
+        <v>-1.2467</v>
       </c>
       <c r="H299" t="n">
-        <v>0.3721</v>
+        <v>-1.2467</v>
       </c>
       <c r="I299" t="n">
-        <v>1.096459</v>
+        <v>1.060387</v>
       </c>
       <c r="J299" t="n">
         <v>0.7784</v>
@@ -10634,13 +10634,13 @@
         <v>0.653937</v>
       </c>
       <c r="F300" t="n">
-        <v>0.5662</v>
+        <v>-1.2848</v>
       </c>
       <c r="H300" t="n">
-        <v>0.5662</v>
+        <v>-1.2848</v>
       </c>
       <c r="I300" t="n">
-        <v>1.102668</v>
+        <v>1.046762</v>
       </c>
       <c r="J300" t="n">
         <v>0.6733</v>
@@ -10668,13 +10668,13 @@
         <v>0.642279</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.0111</v>
+        <v>-1.0436</v>
       </c>
       <c r="H301" t="n">
-        <v>-0.0111</v>
+        <v>-1.0436</v>
       </c>
       <c r="I301" t="n">
-        <v>1.102545</v>
+        <v>1.035839</v>
       </c>
       <c r="J301" t="n">
         <v>0.3343</v>
@@ -10702,13 +10702,13 @@
         <v>0.658505</v>
       </c>
       <c r="F302" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.6258</v>
       </c>
       <c r="H302" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.6258</v>
       </c>
       <c r="I302" t="n">
-        <v>1.101822</v>
+        <v>1.029357</v>
       </c>
       <c r="J302" t="n">
         <v>-0.4025</v>
@@ -10736,13 +10736,13 @@
         <v>0.647161</v>
       </c>
       <c r="F303" t="n">
-        <v>0.4165</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="H303" t="n">
-        <v>0.4165</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>1.106411</v>
+        <v>1.022399</v>
       </c>
       <c r="J303" t="n">
         <v>0.1463</v>
@@ -10770,13 +10770,13 @@
         <v>0.6586880000000001</v>
       </c>
       <c r="F304" t="n">
-        <v>-0.6365</v>
+        <v>-0.5154</v>
       </c>
       <c r="H304" t="n">
-        <v>-0.6365</v>
+        <v>-0.5154</v>
       </c>
       <c r="I304" t="n">
-        <v>1.099369</v>
+        <v>1.01713</v>
       </c>
       <c r="J304" t="n">
         <v>-1.3177</v>
@@ -10804,13 +10804,13 @@
         <v>0.6484220000000001</v>
       </c>
       <c r="F305" t="n">
-        <v>-0.3093</v>
+        <v>0.3925</v>
       </c>
       <c r="H305" t="n">
-        <v>-0.3093</v>
+        <v>0.3925</v>
       </c>
       <c r="I305" t="n">
-        <v>1.095968</v>
+        <v>1.021122</v>
       </c>
       <c r="J305" t="n">
         <v>-0.4051</v>
@@ -10838,13 +10838,13 @@
         <v>0.622624</v>
       </c>
       <c r="F306" t="n">
-        <v>0.0796</v>
+        <v>1.1615</v>
       </c>
       <c r="H306" t="n">
-        <v>0.0796</v>
+        <v>1.1615</v>
       </c>
       <c r="I306" t="n">
-        <v>1.096841</v>
+        <v>1.032982</v>
       </c>
       <c r="J306" t="n">
         <v>0.9751</v>
@@ -10872,13 +10872,13 @@
         <v>0.637787</v>
       </c>
       <c r="F307" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.3437</v>
       </c>
       <c r="H307" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.3437</v>
       </c>
       <c r="I307" t="n">
-        <v>1.090731</v>
+        <v>1.036532</v>
       </c>
       <c r="J307" t="n">
         <v>-0.8967000000000001</v>
@@ -10906,13 +10906,13 @@
         <v>0.641773</v>
       </c>
       <c r="F308" t="n">
-        <v>-0.0658</v>
+        <v>-0.8711</v>
       </c>
       <c r="H308" t="n">
-        <v>-0.0658</v>
+        <v>-0.8711</v>
       </c>
       <c r="I308" t="n">
-        <v>1.090014</v>
+        <v>1.027502</v>
       </c>
       <c r="J308" t="n">
         <v>0.099</v>
@@ -10940,13 +10940,13 @@
         <v>0.606351</v>
       </c>
       <c r="F309" t="n">
-        <v>0.3286</v>
+        <v>0.3077</v>
       </c>
       <c r="H309" t="n">
-        <v>0.3286</v>
+        <v>0.3077</v>
       </c>
       <c r="I309" t="n">
-        <v>1.093595</v>
+        <v>1.030664</v>
       </c>
       <c r="J309" t="n">
         <v>0.583</v>
@@ -10974,13 +10974,13 @@
         <v>0.5749379999999999</v>
       </c>
       <c r="F310" t="n">
-        <v>0.387</v>
+        <v>-1.0252</v>
       </c>
       <c r="H310" t="n">
-        <v>0.387</v>
+        <v>-1.0252</v>
       </c>
       <c r="I310" t="n">
-        <v>1.097828</v>
+        <v>1.020098</v>
       </c>
       <c r="J310" t="n">
         <v>0.5800999999999999</v>
@@ -11008,13 +11008,13 @@
         <v>0.558074</v>
       </c>
       <c r="F311" t="n">
-        <v>0.8957000000000001</v>
+        <v>-1.322</v>
       </c>
       <c r="H311" t="n">
-        <v>0.8957000000000001</v>
+        <v>-1.322</v>
       </c>
       <c r="I311" t="n">
-        <v>1.107661</v>
+        <v>1.006613</v>
       </c>
       <c r="J311" t="n">
         <v>1.4505</v>
@@ -11042,13 +11042,13 @@
         <v>0.568964</v>
       </c>
       <c r="F312" t="n">
-        <v>0.6797</v>
+        <v>0.5504</v>
       </c>
       <c r="H312" t="n">
-        <v>0.6797</v>
+        <v>0.5504</v>
       </c>
       <c r="I312" t="n">
-        <v>1.11519</v>
+        <v>1.012153</v>
       </c>
       <c r="J312" t="n">
         <v>1.5809</v>
@@ -11076,13 +11076,13 @@
         <v>0.544083</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.2302</v>
+        <v>-0.1374</v>
       </c>
       <c r="H313" t="n">
-        <v>-0.2302</v>
+        <v>-0.1374</v>
       </c>
       <c r="I313" t="n">
-        <v>1.112622</v>
+        <v>1.010763</v>
       </c>
       <c r="J313" t="n">
         <v>-0.5006</v>
@@ -11110,13 +11110,13 @@
         <v>0.541013</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.1726</v>
+        <v>-0.8341</v>
       </c>
       <c r="H314" t="n">
-        <v>-0.1726</v>
+        <v>-0.8341</v>
       </c>
       <c r="I314" t="n">
-        <v>1.110702</v>
+        <v>1.002332</v>
       </c>
       <c r="J314" t="n">
         <v>-0.8008999999999999</v>
@@ -11144,13 +11144,13 @@
         <v>0.523966</v>
       </c>
       <c r="F315" t="n">
-        <v>0.3223</v>
+        <v>-1.3322</v>
       </c>
       <c r="H315" t="n">
-        <v>0.3223</v>
+        <v>-1.3322</v>
       </c>
       <c r="I315" t="n">
-        <v>1.114282</v>
+        <v>0.988978</v>
       </c>
       <c r="J315" t="n">
         <v>0.4537</v>
@@ -11178,13 +11178,13 @@
         <v>0.5324</v>
       </c>
       <c r="F316" t="n">
-        <v>-0.0584</v>
+        <v>0.3181</v>
       </c>
       <c r="H316" t="n">
-        <v>-0.0584</v>
+        <v>0.3181</v>
       </c>
       <c r="I316" t="n">
-        <v>1.113631</v>
+        <v>0.992124</v>
       </c>
       <c r="J316" t="n">
         <v>-0.2948</v>
@@ -11212,13 +11212,13 @@
         <v>0.539995</v>
       </c>
       <c r="F317" t="n">
-        <v>0.3955</v>
+        <v>0.783</v>
       </c>
       <c r="H317" t="n">
-        <v>0.3955</v>
+        <v>0.783</v>
       </c>
       <c r="I317" t="n">
-        <v>1.118036</v>
+        <v>0.999893</v>
       </c>
       <c r="J317" t="n">
         <v>0.6988</v>
@@ -11246,13 +11246,13 @@
         <v>0.533146</v>
       </c>
       <c r="F318" t="n">
-        <v>0.3839</v>
+        <v>-1.1534</v>
       </c>
       <c r="H318" t="n">
-        <v>0.3839</v>
+        <v>-1.1534</v>
       </c>
       <c r="I318" t="n">
-        <v>1.122328</v>
+        <v>0.988361</v>
       </c>
       <c r="J318" t="n">
         <v>0.833</v>
@@ -11262,6 +11262,40 @@
       </c>
       <c r="M318" t="n">
         <v>1.25108</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-3.667</v>
+      </c>
+      <c r="D319" t="n">
+        <v>-3.667</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0.5135960000000001</v>
+      </c>
+      <c r="F319" t="n">
+        <v>-0.4037</v>
+      </c>
+      <c r="H319" t="n">
+        <v>-0.4037</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0.984371</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="M319" t="n">
+        <v>1.259675</v>
       </c>
     </row>
   </sheetData>
@@ -11275,7 +11309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E318"/>
+  <dimension ref="A1:E319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17326,6 +17360,25 @@
       </c>
       <c r="E318" t="n">
         <v>1.84208</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-0.1644</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3.8113</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1.8235</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1.875669</v>
       </c>
     </row>
   </sheetData>
@@ -17339,7 +17392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E318"/>
+  <dimension ref="A1:E319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23390,6 +23443,25 @@
       </c>
       <c r="E318" t="n">
         <v>1.440396</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-0.3067</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D319" t="n">
+        <v>-0.6317</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1.431298</v>
       </c>
     </row>
   </sheetData>
@@ -23403,7 +23475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G298"/>
+  <dimension ref="A1:G299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32056,6 +32128,35 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D299" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0.869098</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M319"/>
+  <dimension ref="A1:M318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,13 +502,13 @@
         <v>0.995383</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6197</v>
+        <v>0.2723</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6197</v>
+        <v>0.2723</v>
       </c>
       <c r="I2" t="n">
-        <v>1.006197</v>
+        <v>1.002723</v>
       </c>
       <c r="J2" t="n">
         <v>0.7503</v>
@@ -536,13 +536,13 @@
         <v>0.980968</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9925</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9925</v>
+        <v>0.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.996211</v>
+        <v>1.005731</v>
       </c>
       <c r="J3" t="n">
         <v>0.1271</v>
@@ -570,13 +570,13 @@
         <v>0.972106</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1357</v>
+        <v>-0.1246</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1357</v>
+        <v>-0.1246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.997563</v>
+        <v>1.004478</v>
       </c>
       <c r="J4" t="n">
         <v>-0.3906</v>
@@ -604,13 +604,13 @@
         <v>0.991196</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1346</v>
+        <v>-0.2565</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1346</v>
+        <v>-0.2565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.99622</v>
+        <v>1.001902</v>
       </c>
       <c r="J5" t="n">
         <v>-0.4329</v>
@@ -638,13 +638,13 @@
         <v>0.988644</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9865</v>
+        <v>0.7377</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9865</v>
+        <v>0.7377</v>
       </c>
       <c r="I6" t="n">
-        <v>0.986392</v>
+        <v>1.009293</v>
       </c>
       <c r="J6" t="n">
         <v>0.6863</v>
@@ -672,13 +672,13 @@
         <v>1.021181</v>
       </c>
       <c r="F7" t="n">
-        <v>1.044</v>
+        <v>-0.7437</v>
       </c>
       <c r="H7" t="n">
-        <v>1.044</v>
+        <v>-0.7437</v>
       </c>
       <c r="I7" t="n">
-        <v>0.99669</v>
+        <v>1.001786</v>
       </c>
       <c r="J7" t="n">
         <v>-1.2552</v>
@@ -706,13 +706,13 @@
         <v>0.971398</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8501</v>
+        <v>0.8234</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8501</v>
+        <v>0.8234</v>
       </c>
       <c r="I8" t="n">
-        <v>1.005163</v>
+        <v>1.010035</v>
       </c>
       <c r="J8" t="n">
         <v>1.9645</v>
@@ -740,13 +740,13 @@
         <v>0.944133</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5903</v>
+        <v>0.8965</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5903</v>
+        <v>0.8965</v>
       </c>
       <c r="I9" t="n">
-        <v>0.999229</v>
+        <v>1.01909</v>
       </c>
       <c r="J9" t="n">
         <v>1.5683</v>
@@ -774,13 +774,13 @@
         <v>0.943408</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1705</v>
+        <v>0.0738</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1705</v>
+        <v>0.0738</v>
       </c>
       <c r="I10" t="n">
-        <v>1.000932</v>
+        <v>1.019842</v>
       </c>
       <c r="J10" t="n">
         <v>0.2246</v>
@@ -808,13 +808,13 @@
         <v>0.925696</v>
       </c>
       <c r="F11" t="n">
-        <v>2.039</v>
+        <v>0.7608</v>
       </c>
       <c r="H11" t="n">
-        <v>2.039</v>
+        <v>0.7608</v>
       </c>
       <c r="I11" t="n">
-        <v>1.021342</v>
+        <v>1.027601</v>
       </c>
       <c r="J11" t="n">
         <v>1.9943</v>
@@ -842,13 +842,13 @@
         <v>0.940234</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1929</v>
+        <v>0.1001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1929</v>
+        <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>1.019371</v>
+        <v>1.02863</v>
       </c>
       <c r="J12" t="n">
         <v>0.1747</v>
@@ -876,13 +876,13 @@
         <v>0.925096</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1467</v>
+        <v>0.2697</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1467</v>
+        <v>0.2697</v>
       </c>
       <c r="I13" t="n">
-        <v>1.007683</v>
+        <v>1.031404</v>
       </c>
       <c r="J13" t="n">
         <v>0.3633</v>
@@ -910,13 +910,13 @@
         <v>0.946805</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.5316</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.5316</v>
       </c>
       <c r="I14" t="n">
-        <v>1.000984</v>
+        <v>1.025921</v>
       </c>
       <c r="J14" t="n">
         <v>-0.7197</v>
@@ -944,13 +944,13 @@
         <v>0.943644</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8557</v>
+        <v>-0.2635</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8557</v>
+        <v>-0.2635</v>
       </c>
       <c r="I15" t="n">
-        <v>1.019559</v>
+        <v>1.023218</v>
       </c>
       <c r="J15" t="n">
         <v>-1.0265</v>
@@ -978,13 +978,13 @@
         <v>0.925975</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2391</v>
+        <v>0.5894</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2391</v>
+        <v>0.5894</v>
       </c>
       <c r="I16" t="n">
-        <v>1.021997</v>
+        <v>1.029249</v>
       </c>
       <c r="J16" t="n">
         <v>1.5712</v>
@@ -1012,13 +1012,13 @@
         <v>0.946196</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2117</v>
+        <v>-0.7889</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2117</v>
+        <v>-0.7889</v>
       </c>
       <c r="I17" t="n">
-        <v>1.009613</v>
+        <v>1.021129</v>
       </c>
       <c r="J17" t="n">
         <v>-1.9458</v>
@@ -1046,13 +1046,13 @@
         <v>0.921641</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1661</v>
+        <v>1.2027</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1661</v>
+        <v>1.2027</v>
       </c>
       <c r="I18" t="n">
-        <v>1.007936</v>
+        <v>1.03341</v>
       </c>
       <c r="J18" t="n">
         <v>2.2605</v>
@@ -1080,13 +1080,13 @@
         <v>0.920763</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.6863</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.6863</v>
       </c>
       <c r="I19" t="n">
-        <v>1.017512</v>
+        <v>1.040502</v>
       </c>
       <c r="J19" t="n">
         <v>1.5282</v>
@@ -1114,13 +1114,13 @@
         <v>0.859859</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0693</v>
+        <v>0.3804</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0693</v>
+        <v>0.3804</v>
       </c>
       <c r="I20" t="n">
-        <v>1.006632</v>
+        <v>1.04446</v>
       </c>
       <c r="J20" t="n">
         <v>0.0236</v>
@@ -1148,13 +1148,13 @@
         <v>0.856441</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8156</v>
+        <v>0.1449</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8156</v>
+        <v>0.1449</v>
       </c>
       <c r="I21" t="n">
-        <v>1.014843</v>
+        <v>1.045974</v>
       </c>
       <c r="J21" t="n">
         <v>0.3994</v>
@@ -1182,13 +1182,13 @@
         <v>0.848554</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0603</v>
+        <v>0.3983</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0603</v>
+        <v>0.3983</v>
       </c>
       <c r="I22" t="n">
-        <v>1.01423</v>
+        <v>1.05014</v>
       </c>
       <c r="J22" t="n">
         <v>1.007</v>
@@ -1216,13 +1216,13 @@
         <v>0.840793</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.3669</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.3669</v>
       </c>
       <c r="I23" t="n">
-        <v>1.021371</v>
+        <v>1.053993</v>
       </c>
       <c r="J23" t="n">
         <v>0.7095</v>
@@ -1250,13 +1250,13 @@
         <v>0.850485</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2079</v>
+        <v>-0.3212</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2079</v>
+        <v>-0.3212</v>
       </c>
       <c r="I24" t="n">
-        <v>1.033708</v>
+        <v>1.050607</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5014999999999999</v>
@@ -1284,13 +1284,13 @@
         <v>0.880144</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2249</v>
+        <v>-1.1553</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2249</v>
+        <v>-1.1553</v>
       </c>
       <c r="I25" t="n">
-        <v>1.036034</v>
+        <v>1.03847</v>
       </c>
       <c r="J25" t="n">
         <v>-2.1951</v>
@@ -1318,13 +1318,13 @@
         <v>0.892473</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0706</v>
+        <v>0.0326</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0706</v>
+        <v>0.0326</v>
       </c>
       <c r="I26" t="n">
-        <v>1.047126</v>
+        <v>1.038808</v>
       </c>
       <c r="J26" t="n">
         <v>0.2214</v>
@@ -1352,13 +1352,13 @@
         <v>0.877175</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8154</v>
+        <v>0.7863</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8154</v>
+        <v>0.7863</v>
       </c>
       <c r="I27" t="n">
-        <v>1.055664</v>
+        <v>1.046976</v>
       </c>
       <c r="J27" t="n">
         <v>1.6365</v>
@@ -1386,13 +1386,13 @@
         <v>0.8787740000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7909</v>
+        <v>0.2953</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7909</v>
+        <v>0.2953</v>
       </c>
       <c r="I28" t="n">
-        <v>1.047315</v>
+        <v>1.050068</v>
       </c>
       <c r="J28" t="n">
         <v>0.286</v>
@@ -1420,13 +1420,13 @@
         <v>0.847943</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6515</v>
+        <v>0.5468</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6515</v>
+        <v>0.5468</v>
       </c>
       <c r="I29" t="n">
-        <v>1.040492</v>
+        <v>1.05581</v>
       </c>
       <c r="J29" t="n">
         <v>0.6859</v>
@@ -1454,13 +1454,13 @@
         <v>0.859646</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3477</v>
+        <v>-0.1085</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3477</v>
+        <v>-0.1085</v>
       </c>
       <c r="I30" t="n">
-        <v>1.036874</v>
+        <v>1.054664</v>
       </c>
       <c r="J30" t="n">
         <v>-0.2693</v>
@@ -1488,13 +1488,13 @@
         <v>0.864075</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7556</v>
+        <v>0.2432</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7556</v>
+        <v>0.2432</v>
       </c>
       <c r="I31" t="n">
-        <v>1.055077</v>
+        <v>1.057229</v>
       </c>
       <c r="J31" t="n">
         <v>0.7772</v>
@@ -1522,13 +1522,13 @@
         <v>0.873036</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5659</v>
+        <v>-0.0609</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5659</v>
+        <v>-0.0609</v>
       </c>
       <c r="I32" t="n">
-        <v>1.049105</v>
+        <v>1.056585</v>
       </c>
       <c r="J32" t="n">
         <v>-0.0308</v>
@@ -1556,13 +1556,13 @@
         <v>0.875897</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4005</v>
+        <v>0.4737</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4005</v>
+        <v>0.4737</v>
       </c>
       <c r="I33" t="n">
-        <v>1.044904</v>
+        <v>1.061591</v>
       </c>
       <c r="J33" t="n">
         <v>1.0936</v>
@@ -1590,13 +1590,13 @@
         <v>0.900463</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2526</v>
+        <v>-0.8057</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2526</v>
+        <v>-0.8057</v>
       </c>
       <c r="I34" t="n">
-        <v>1.047543</v>
+        <v>1.053037</v>
       </c>
       <c r="J34" t="n">
         <v>-1.4404</v>
@@ -1624,13 +1624,13 @@
         <v>0.8918160000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.71</v>
+        <v>-0.2873</v>
       </c>
       <c r="H35" t="n">
-        <v>0.71</v>
+        <v>-0.2873</v>
       </c>
       <c r="I35" t="n">
-        <v>1.054981</v>
+        <v>1.050012</v>
       </c>
       <c r="J35" t="n">
         <v>-0.633</v>
@@ -1658,13 +1658,13 @@
         <v>0.899124</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.3903</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.3903</v>
       </c>
       <c r="I36" t="n">
-        <v>1.05597</v>
+        <v>1.05411</v>
       </c>
       <c r="J36" t="n">
         <v>1.0237</v>
@@ -1692,13 +1692,13 @@
         <v>0.892093</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0449</v>
+        <v>0.1267</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0449</v>
+        <v>0.1267</v>
       </c>
       <c r="I37" t="n">
-        <v>1.056444</v>
+        <v>1.055446</v>
       </c>
       <c r="J37" t="n">
         <v>0.3254</v>
@@ -1726,13 +1726,13 @@
         <v>0.903988</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5393</v>
+        <v>-0.3316</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5393</v>
+        <v>-0.3316</v>
       </c>
       <c r="I38" t="n">
-        <v>1.050747</v>
+        <v>1.051946</v>
       </c>
       <c r="J38" t="n">
         <v>-0.6055</v>
@@ -1760,13 +1760,13 @@
         <v>0.911693</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.5429</v>
+        <v>0.4226</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5429</v>
+        <v>0.4226</v>
       </c>
       <c r="I39" t="n">
-        <v>1.045043</v>
+        <v>1.056391</v>
       </c>
       <c r="J39" t="n">
         <v>1.0131</v>
@@ -1794,13 +1794,13 @@
         <v>0.926563</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0319</v>
+        <v>-0.3927</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.0319</v>
+        <v>-0.3927</v>
       </c>
       <c r="I40" t="n">
-        <v>1.044709</v>
+        <v>1.052243</v>
       </c>
       <c r="J40" t="n">
         <v>-0.5977</v>
@@ -1828,13 +1828,13 @@
         <v>0.929041</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.0619</v>
+        <v>-0.8778</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.0619</v>
+        <v>-0.8778</v>
       </c>
       <c r="I41" t="n">
-        <v>1.033616</v>
+        <v>1.043006</v>
       </c>
       <c r="J41" t="n">
         <v>-2.4099</v>
@@ -1862,13 +1862,13 @@
         <v>0.947582</v>
       </c>
       <c r="F42" t="n">
-        <v>1.086</v>
+        <v>-0.5643</v>
       </c>
       <c r="H42" t="n">
-        <v>1.086</v>
+        <v>-0.5643</v>
       </c>
       <c r="I42" t="n">
-        <v>1.044841</v>
+        <v>1.037121</v>
       </c>
       <c r="J42" t="n">
         <v>-0.9184</v>
@@ -1896,13 +1896,13 @@
         <v>0.948689</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9058</v>
+        <v>0.5851</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9058</v>
+        <v>0.5851</v>
       </c>
       <c r="I43" t="n">
-        <v>1.054305</v>
+        <v>1.043189</v>
       </c>
       <c r="J43" t="n">
         <v>1.508</v>
@@ -1930,13 +1930,13 @@
         <v>0.937182</v>
       </c>
       <c r="F44" t="n">
-        <v>2.288</v>
+        <v>-0.3974</v>
       </c>
       <c r="H44" t="n">
-        <v>2.288</v>
+        <v>-0.3974</v>
       </c>
       <c r="I44" t="n">
-        <v>1.078427</v>
+        <v>1.039043</v>
       </c>
       <c r="J44" t="n">
         <v>-1.0604</v>
@@ -1964,13 +1964,13 @@
         <v>0.940368</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.0449</v>
+        <v>-0.4672</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.0449</v>
+        <v>-0.4672</v>
       </c>
       <c r="I45" t="n">
-        <v>1.077942</v>
+        <v>1.034189</v>
       </c>
       <c r="J45" t="n">
         <v>-1.0699</v>
@@ -1998,13 +1998,13 @@
         <v>0.941619</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.1426</v>
+        <v>0.021</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.1426</v>
+        <v>0.021</v>
       </c>
       <c r="I46" t="n">
-        <v>1.065625</v>
+        <v>1.034406</v>
       </c>
       <c r="J46" t="n">
         <v>-0.5024</v>
@@ -2032,13 +2032,13 @@
         <v>0.949234</v>
       </c>
       <c r="F47" t="n">
-        <v>4.482</v>
+        <v>0.3371</v>
       </c>
       <c r="H47" t="n">
-        <v>4.482</v>
+        <v>0.3371</v>
       </c>
       <c r="I47" t="n">
-        <v>1.113387</v>
+        <v>1.037893</v>
       </c>
       <c r="J47" t="n">
         <v>0.8784999999999999</v>
@@ -2066,13 +2066,13 @@
         <v>0.954188</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.3019</v>
+        <v>0.2337</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.3019</v>
+        <v>0.2337</v>
       </c>
       <c r="I48" t="n">
-        <v>1.110025</v>
+        <v>1.040318</v>
       </c>
       <c r="J48" t="n">
         <v>0.3573</v>
@@ -2100,13 +2100,13 @@
         <v>0.9598410000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>1.115</v>
+        <v>-0.4273</v>
       </c>
       <c r="H49" t="n">
-        <v>1.115</v>
+        <v>-0.4273</v>
       </c>
       <c r="I49" t="n">
-        <v>1.122402</v>
+        <v>1.035873</v>
       </c>
       <c r="J49" t="n">
         <v>-0.4359</v>
@@ -2134,13 +2134,13 @@
         <v>0.984331</v>
       </c>
       <c r="F50" t="n">
-        <v>-4.387</v>
+        <v>-3.1676</v>
       </c>
       <c r="H50" t="n">
-        <v>-4.387</v>
+        <v>-3.1676</v>
       </c>
       <c r="I50" t="n">
-        <v>1.073162</v>
+        <v>1.003061</v>
       </c>
       <c r="J50" t="n">
         <v>-5.786</v>
@@ -2168,13 +2168,13 @@
         <v>0.992529</v>
       </c>
       <c r="F51" t="n">
-        <v>1.6142</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>1.6142</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>1.090485</v>
+        <v>0.9958360000000001</v>
       </c>
       <c r="J51" t="n">
         <v>-2.226</v>
@@ -2202,13 +2202,13 @@
         <v>0.95275</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.5926</v>
+        <v>0.8143</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5926</v>
+        <v>0.8143</v>
       </c>
       <c r="I52" t="n">
-        <v>1.084023</v>
+        <v>1.003945</v>
       </c>
       <c r="J52" t="n">
         <v>2.0004</v>
@@ -2236,13 +2236,13 @@
         <v>0.9514049999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8016</v>
+        <v>0.8391</v>
       </c>
       <c r="H53" t="n">
-        <v>1.8016</v>
+        <v>0.8391</v>
       </c>
       <c r="I53" t="n">
-        <v>1.103553</v>
+        <v>1.012369</v>
       </c>
       <c r="J53" t="n">
         <v>1.8126</v>
@@ -2270,13 +2270,13 @@
         <v>0.92746</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.5557</v>
+        <v>0.5538</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.5557</v>
+        <v>0.5538</v>
       </c>
       <c r="I54" t="n">
-        <v>1.09742</v>
+        <v>1.017976</v>
       </c>
       <c r="J54" t="n">
         <v>0.5581</v>
@@ -2304,13 +2304,13 @@
         <v>0.933406</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7169</v>
+        <v>0.8097</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7169</v>
+        <v>0.8097</v>
       </c>
       <c r="I55" t="n">
-        <v>1.105287</v>
+        <v>1.026218</v>
       </c>
       <c r="J55" t="n">
         <v>1.952</v>
@@ -2338,13 +2338,13 @@
         <v>0.945194</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7604</v>
+        <v>-0.129</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7604</v>
+        <v>-0.129</v>
       </c>
       <c r="I56" t="n">
-        <v>1.113692</v>
+        <v>1.024894</v>
       </c>
       <c r="J56" t="n">
         <v>-0.1054</v>
@@ -2372,13 +2372,13 @@
         <v>0.941817</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.8668</v>
+        <v>-1.0581</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.8668</v>
+        <v>-1.0581</v>
       </c>
       <c r="I57" t="n">
-        <v>1.092901</v>
+        <v>1.01405</v>
       </c>
       <c r="J57" t="n">
         <v>-2.0165</v>
@@ -2406,13 +2406,13 @@
         <v>0.937733</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8413</v>
+        <v>0.2013</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8413</v>
+        <v>0.2013</v>
       </c>
       <c r="I58" t="n">
-        <v>1.102096</v>
+        <v>1.016091</v>
       </c>
       <c r="J58" t="n">
         <v>0.5756</v>
@@ -2440,13 +2440,13 @@
         <v>0.9456639999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="H59" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="I59" t="n">
-        <v>1.103054</v>
+        <v>1.015556</v>
       </c>
       <c r="J59" t="n">
         <v>-0.2037</v>
@@ -2474,13 +2474,13 @@
         <v>0.93424</v>
       </c>
       <c r="F60" t="n">
-        <v>1.2856</v>
+        <v>1.1481</v>
       </c>
       <c r="H60" t="n">
-        <v>1.2856</v>
+        <v>1.1481</v>
       </c>
       <c r="I60" t="n">
-        <v>1.117235</v>
+        <v>1.027215</v>
       </c>
       <c r="J60" t="n">
         <v>1.9633</v>
@@ -2508,13 +2508,13 @@
         <v>0.94079</v>
       </c>
       <c r="F61" t="n">
-        <v>1.8792</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.8792</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1.13823</v>
+        <v>1.027215</v>
       </c>
       <c r="J61" t="n">
         <v>0.0094</v>
@@ -2542,13 +2542,13 @@
         <v>0.939905</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1634</v>
+        <v>0.5617</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1634</v>
+        <v>0.5617</v>
       </c>
       <c r="I62" t="n">
-        <v>1.14009</v>
+        <v>1.032985</v>
       </c>
       <c r="J62" t="n">
         <v>1.0961</v>
@@ -2576,13 +2576,13 @@
         <v>0.953615</v>
       </c>
       <c r="F63" t="n">
-        <v>2.2595</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>2.2595</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>1.165851</v>
+        <v>1.027231</v>
       </c>
       <c r="J63" t="n">
         <v>-0.9599</v>
@@ -2610,13 +2610,13 @@
         <v>0.950933</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.0949</v>
+        <v>0.1368</v>
       </c>
       <c r="H64" t="n">
-        <v>-2.0949</v>
+        <v>0.1368</v>
       </c>
       <c r="I64" t="n">
-        <v>1.141427</v>
+        <v>1.028637</v>
       </c>
       <c r="J64" t="n">
         <v>0.2174</v>
@@ -2644,13 +2644,13 @@
         <v>0.952421</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7179</v>
+        <v>-0.6647</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7179</v>
+        <v>-0.6647</v>
       </c>
       <c r="I65" t="n">
-        <v>1.133232</v>
+        <v>1.021799</v>
       </c>
       <c r="J65" t="n">
         <v>-1.2807</v>
@@ -2678,13 +2678,13 @@
         <v>0.948939</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1499</v>
+        <v>0.488</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1499</v>
+        <v>0.488</v>
       </c>
       <c r="I66" t="n">
-        <v>1.131534</v>
+        <v>1.026786</v>
       </c>
       <c r="J66" t="n">
         <v>1.1635</v>
@@ -2712,13 +2712,13 @@
         <v>0.934599</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.105</v>
+        <v>0.6592</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.105</v>
+        <v>0.6592</v>
       </c>
       <c r="I67" t="n">
-        <v>1.130345</v>
+        <v>1.033554</v>
       </c>
       <c r="J67" t="n">
         <v>1.4137</v>
@@ -2746,13 +2746,13 @@
         <v>0.92394</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2366</v>
+        <v>1.077</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2366</v>
+        <v>1.077</v>
       </c>
       <c r="I68" t="n">
-        <v>1.13302</v>
+        <v>1.044686</v>
       </c>
       <c r="J68" t="n">
         <v>2.2439</v>
@@ -2780,13 +2780,13 @@
         <v>0.926893</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5456</v>
+        <v>-0.2508</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5456</v>
+        <v>-0.2508</v>
       </c>
       <c r="I69" t="n">
-        <v>1.126839</v>
+        <v>1.042066</v>
       </c>
       <c r="J69" t="n">
         <v>0.1342</v>
@@ -2814,13 +2814,13 @@
         <v>0.930716</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.0331</v>
+        <v>0.2635</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.0331</v>
+        <v>0.2635</v>
       </c>
       <c r="I70" t="n">
-        <v>1.126466</v>
+        <v>1.044811</v>
       </c>
       <c r="J70" t="n">
         <v>0.5344</v>
@@ -2848,13 +2848,13 @@
         <v>0.953742</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.059</v>
+        <v>-0.6509</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.059</v>
+        <v>-0.6509</v>
       </c>
       <c r="I71" t="n">
-        <v>1.125801</v>
+        <v>1.038011</v>
       </c>
       <c r="J71" t="n">
         <v>-1.317</v>
@@ -2882,13 +2882,13 @@
         <v>0.952387</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0044</v>
+        <v>0.2327</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0044</v>
+        <v>0.2327</v>
       </c>
       <c r="I72" t="n">
-        <v>1.114494</v>
+        <v>1.040426</v>
       </c>
       <c r="J72" t="n">
         <v>0.4404</v>
@@ -2916,13 +2916,13 @@
         <v>0.960504</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7241</v>
+        <v>-0.2593</v>
       </c>
       <c r="H73" t="n">
-        <v>0.7241</v>
+        <v>-0.2593</v>
       </c>
       <c r="I73" t="n">
-        <v>1.122563</v>
+        <v>1.037728</v>
       </c>
       <c r="J73" t="n">
         <v>-0.4494</v>
@@ -2950,13 +2950,13 @@
         <v>0.9620339999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.6825</v>
+        <v>-0.6073</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6825</v>
+        <v>-0.6073</v>
       </c>
       <c r="I74" t="n">
-        <v>1.114901</v>
+        <v>1.031426</v>
       </c>
       <c r="J74" t="n">
         <v>-1.096</v>
@@ -2984,13 +2984,13 @@
         <v>0.970234</v>
       </c>
       <c r="F75" t="n">
-        <v>3.8527</v>
+        <v>-0.4133</v>
       </c>
       <c r="H75" t="n">
-        <v>3.8527</v>
+        <v>-0.4133</v>
       </c>
       <c r="I75" t="n">
-        <v>1.157855</v>
+        <v>1.027163</v>
       </c>
       <c r="J75" t="n">
         <v>-0.402</v>
@@ -3018,13 +3018,13 @@
         <v>0.970401</v>
       </c>
       <c r="F76" t="n">
-        <v>2.7165</v>
+        <v>0.5416</v>
       </c>
       <c r="H76" t="n">
-        <v>2.7165</v>
+        <v>0.5416</v>
       </c>
       <c r="I76" t="n">
-        <v>1.189308</v>
+        <v>1.032726</v>
       </c>
       <c r="J76" t="n">
         <v>1.3647</v>
@@ -3052,13 +3052,13 @@
         <v>0.972963</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8666</v>
+        <v>0.4127</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8666</v>
+        <v>0.4127</v>
       </c>
       <c r="I77" t="n">
-        <v>1.179001</v>
+        <v>1.036989</v>
       </c>
       <c r="J77" t="n">
         <v>1.1661</v>
@@ -3086,13 +3086,13 @@
         <v>0.973422</v>
       </c>
       <c r="F78" t="n">
-        <v>1.0501</v>
+        <v>0.1761</v>
       </c>
       <c r="H78" t="n">
-        <v>1.0501</v>
+        <v>0.1761</v>
       </c>
       <c r="I78" t="n">
-        <v>1.191382</v>
+        <v>1.038815</v>
       </c>
       <c r="J78" t="n">
         <v>0.2972</v>
@@ -3120,13 +3120,13 @@
         <v>0.983</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5142</v>
+        <v>-0.517</v>
       </c>
       <c r="H79" t="n">
-        <v>0.5142</v>
+        <v>-0.517</v>
       </c>
       <c r="I79" t="n">
-        <v>1.197508</v>
+        <v>1.033444</v>
       </c>
       <c r="J79" t="n">
         <v>-1.2673</v>
@@ -3154,13 +3154,13 @@
         <v>0.9859830000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.389</v>
+        <v>-0.5848</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.389</v>
+        <v>-0.5848</v>
       </c>
       <c r="I80" t="n">
-        <v>1.19285</v>
+        <v>1.0274</v>
       </c>
       <c r="J80" t="n">
         <v>-1.1669</v>
@@ -3188,13 +3188,13 @@
         <v>0.986371</v>
       </c>
       <c r="F81" t="n">
-        <v>3.5006</v>
+        <v>-0.19</v>
       </c>
       <c r="H81" t="n">
-        <v>3.5006</v>
+        <v>-0.19</v>
       </c>
       <c r="I81" t="n">
-        <v>1.234607</v>
+        <v>1.025448</v>
       </c>
       <c r="J81" t="n">
         <v>-0.3692</v>
@@ -3222,13 +3222,13 @@
         <v>0.978015</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.3811</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.3811</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>1.217556</v>
+        <v>1.033114</v>
       </c>
       <c r="J82" t="n">
         <v>1.826</v>
@@ -3256,13 +3256,13 @@
         <v>0.984773</v>
       </c>
       <c r="F83" t="n">
-        <v>1.9706</v>
+        <v>0.1664</v>
       </c>
       <c r="H83" t="n">
-        <v>1.9706</v>
+        <v>0.1664</v>
       </c>
       <c r="I83" t="n">
-        <v>1.241549</v>
+        <v>1.034833</v>
       </c>
       <c r="J83" t="n">
         <v>0.7407</v>
@@ -3290,13 +3290,13 @@
         <v>0.990221</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.1403</v>
+        <v>-0.0945</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.1403</v>
+        <v>-0.0945</v>
       </c>
       <c r="I84" t="n">
-        <v>1.227392</v>
+        <v>1.033855</v>
       </c>
       <c r="J84" t="n">
         <v>-0.2581</v>
@@ -3324,13 +3324,13 @@
         <v>0.976</v>
       </c>
       <c r="F85" t="n">
-        <v>1.0271</v>
+        <v>0.742</v>
       </c>
       <c r="H85" t="n">
-        <v>1.0271</v>
+        <v>0.742</v>
       </c>
       <c r="I85" t="n">
-        <v>1.239998</v>
+        <v>1.041526</v>
       </c>
       <c r="J85" t="n">
         <v>1.1667</v>
@@ -3358,13 +3358,13 @@
         <v>0.9861</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2559</v>
+        <v>-0.4598</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2559</v>
+        <v>-0.4598</v>
       </c>
       <c r="I86" t="n">
-        <v>1.243172</v>
+        <v>1.036737</v>
       </c>
       <c r="J86" t="n">
         <v>-1.2733</v>
@@ -3392,13 +3392,13 @@
         <v>0.984975</v>
       </c>
       <c r="F87" t="n">
-        <v>2.7437</v>
+        <v>0.3095</v>
       </c>
       <c r="H87" t="n">
-        <v>2.7437</v>
+        <v>0.3095</v>
       </c>
       <c r="I87" t="n">
-        <v>1.277281</v>
+        <v>1.039946</v>
       </c>
       <c r="J87" t="n">
         <v>0.5158</v>
@@ -3426,13 +3426,13 @@
         <v>0.9832959999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>-1.3537</v>
+        <v>0.2784</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.3537</v>
+        <v>0.2784</v>
       </c>
       <c r="I88" t="n">
-        <v>1.25999</v>
+        <v>1.042841</v>
       </c>
       <c r="J88" t="n">
         <v>0.6211</v>
@@ -3460,13 +3460,13 @@
         <v>0.9674</v>
       </c>
       <c r="F89" t="n">
-        <v>-2.1865</v>
+        <v>0.3053</v>
       </c>
       <c r="H89" t="n">
-        <v>-2.1865</v>
+        <v>0.3053</v>
       </c>
       <c r="I89" t="n">
-        <v>1.23244</v>
+        <v>1.046025</v>
       </c>
       <c r="J89" t="n">
         <v>0.3641</v>
@@ -3494,13 +3494,13 @@
         <v>0.971815</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4585</v>
+        <v>-0.081</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4585</v>
+        <v>-0.081</v>
       </c>
       <c r="I90" t="n">
-        <v>1.238091</v>
+        <v>1.045177</v>
       </c>
       <c r="J90" t="n">
         <v>-0.1005</v>
@@ -3528,13 +3528,13 @@
         <v>0.967851</v>
       </c>
       <c r="F91" t="n">
-        <v>2.3691</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>2.3691</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>1.267422</v>
+        <v>1.051589</v>
       </c>
       <c r="J91" t="n">
         <v>1.1466</v>
@@ -3562,13 +3562,13 @@
         <v>0.981356</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9951</v>
+        <v>-0.1745</v>
       </c>
       <c r="H92" t="n">
-        <v>0.9951</v>
+        <v>-0.1745</v>
       </c>
       <c r="I92" t="n">
-        <v>1.280034</v>
+        <v>1.049754</v>
       </c>
       <c r="J92" t="n">
         <v>-0.3078</v>
@@ -3596,13 +3596,13 @@
         <v>0.986367</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.3122</v>
+        <v>-0.2274</v>
       </c>
       <c r="H93" t="n">
-        <v>-1.3122</v>
+        <v>-0.2274</v>
       </c>
       <c r="I93" t="n">
-        <v>1.263238</v>
+        <v>1.047366</v>
       </c>
       <c r="J93" t="n">
         <v>-0.3135</v>
@@ -3630,13 +3630,13 @@
         <v>0.989364</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4938</v>
+        <v>0.1524</v>
       </c>
       <c r="H94" t="n">
-        <v>0.4938</v>
+        <v>0.1524</v>
       </c>
       <c r="I94" t="n">
-        <v>1.269476</v>
+        <v>1.048963</v>
       </c>
       <c r="J94" t="n">
         <v>0.3177</v>
@@ -3664,13 +3664,13 @@
         <v>0.984457</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.5669</v>
+        <v>-0.6387</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.5669</v>
+        <v>-0.6387</v>
       </c>
       <c r="I95" t="n">
-        <v>1.249585</v>
+        <v>1.042263</v>
       </c>
       <c r="J95" t="n">
         <v>-1.3119</v>
@@ -3698,13 +3698,13 @@
         <v>0.988765</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.2825</v>
+        <v>0.4124</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.2825</v>
+        <v>0.4124</v>
       </c>
       <c r="I96" t="n">
-        <v>1.246055</v>
+        <v>1.046561</v>
       </c>
       <c r="J96" t="n">
         <v>0.8215</v>
@@ -3732,13 +3732,13 @@
         <v>0.996247</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.3502</v>
+        <v>-0.0276</v>
       </c>
       <c r="H97" t="n">
-        <v>-1.3502</v>
+        <v>-0.0276</v>
       </c>
       <c r="I97" t="n">
-        <v>1.229232</v>
+        <v>1.046272</v>
       </c>
       <c r="J97" t="n">
         <v>-0.0535</v>
@@ -3766,13 +3766,13 @@
         <v>0.989861</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.0533</v>
+        <v>-0.0256</v>
       </c>
       <c r="H98" t="n">
-        <v>-1.0533</v>
+        <v>-0.0256</v>
       </c>
       <c r="I98" t="n">
-        <v>1.216284</v>
+        <v>1.046004</v>
       </c>
       <c r="J98" t="n">
         <v>-0.3982</v>
@@ -3800,13 +3800,13 @@
         <v>0.988784</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.4814</v>
+        <v>-0.511</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.4814</v>
+        <v>-0.511</v>
       </c>
       <c r="I99" t="n">
-        <v>1.198266</v>
+        <v>1.040659</v>
       </c>
       <c r="J99" t="n">
         <v>-1.1281</v>
@@ -3834,13 +3834,13 @@
         <v>0.995638</v>
       </c>
       <c r="F100" t="n">
-        <v>0.6487000000000001</v>
+        <v>-0.4667</v>
       </c>
       <c r="H100" t="n">
-        <v>0.6487000000000001</v>
+        <v>-0.4667</v>
       </c>
       <c r="I100" t="n">
-        <v>1.206039</v>
+        <v>1.035803</v>
       </c>
       <c r="J100" t="n">
         <v>-1.0024</v>
@@ -3868,13 +3868,13 @@
         <v>0.994412</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7181</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7181</v>
       </c>
       <c r="I101" t="n">
-        <v>1.215588</v>
+        <v>1.043241</v>
       </c>
       <c r="J101" t="n">
         <v>1.6494</v>
@@ -3902,13 +3902,13 @@
         <v>0.979781</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0616</v>
+        <v>0.5194</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0616</v>
+        <v>0.5194</v>
       </c>
       <c r="I102" t="n">
-        <v>1.216337</v>
+        <v>1.048659</v>
       </c>
       <c r="J102" t="n">
         <v>1.0267</v>
@@ -3936,13 +3936,13 @@
         <v>0.966199</v>
       </c>
       <c r="F103" t="n">
-        <v>-1.6626</v>
+        <v>-0.144</v>
       </c>
       <c r="H103" t="n">
-        <v>-1.6626</v>
+        <v>-0.144</v>
       </c>
       <c r="I103" t="n">
-        <v>1.196114</v>
+        <v>1.047149</v>
       </c>
       <c r="J103" t="n">
         <v>-0.4332</v>
@@ -3970,13 +3970,13 @@
         <v>0.9719370000000001</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.4257</v>
+        <v>-0.0183</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.4257</v>
+        <v>-0.0183</v>
       </c>
       <c r="I104" t="n">
-        <v>1.191023</v>
+        <v>1.046958</v>
       </c>
       <c r="J104" t="n">
         <v>0.1714</v>
@@ -4004,13 +4004,13 @@
         <v>0.9685780000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6433</v>
+        <v>0.4736</v>
       </c>
       <c r="H105" t="n">
-        <v>0.6433</v>
+        <v>0.4736</v>
       </c>
       <c r="I105" t="n">
-        <v>1.198684</v>
+        <v>1.051916</v>
       </c>
       <c r="J105" t="n">
         <v>1.0836</v>
@@ -4038,13 +4038,13 @@
         <v>0.952616</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1281</v>
+        <v>0.5218</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1281</v>
+        <v>0.5218</v>
       </c>
       <c r="I106" t="n">
-        <v>1.20022</v>
+        <v>1.057405</v>
       </c>
       <c r="J106" t="n">
         <v>1.1737</v>
@@ -4072,13 +4072,13 @@
         <v>0.968557</v>
       </c>
       <c r="F107" t="n">
-        <v>2.8914</v>
+        <v>0.0179</v>
       </c>
       <c r="H107" t="n">
-        <v>2.8914</v>
+        <v>0.0179</v>
       </c>
       <c r="I107" t="n">
-        <v>1.234922</v>
+        <v>1.057594</v>
       </c>
       <c r="J107" t="n">
         <v>0.1143</v>
@@ -4106,13 +4106,13 @@
         <v>0.9873459999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.2144</v>
+        <v>-0.6146</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.2144</v>
+        <v>-0.6146</v>
       </c>
       <c r="I108" t="n">
-        <v>1.232275</v>
+        <v>1.051094</v>
       </c>
       <c r="J108" t="n">
         <v>-0.8706</v>
@@ -4140,13 +4140,13 @@
         <v>0.984961</v>
       </c>
       <c r="F109" t="n">
-        <v>1.5642</v>
+        <v>0.095</v>
       </c>
       <c r="H109" t="n">
-        <v>1.5642</v>
+        <v>0.095</v>
       </c>
       <c r="I109" t="n">
-        <v>1.25155</v>
+        <v>1.052093</v>
       </c>
       <c r="J109" t="n">
         <v>0.0955</v>
@@ -4174,13 +4174,13 @@
         <v>0.990094</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.5999</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.5999</v>
       </c>
       <c r="I110" t="n">
-        <v>1.250667</v>
+        <v>1.045781</v>
       </c>
       <c r="J110" t="n">
         <v>-1.4338</v>
@@ -4208,13 +4208,13 @@
         <v>1.000967</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.6533</v>
+        <v>0.3921</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.6533</v>
+        <v>0.3921</v>
       </c>
       <c r="I111" t="n">
-        <v>1.242497</v>
+        <v>1.049882</v>
       </c>
       <c r="J111" t="n">
         <v>1.0995</v>
@@ -4242,13 +4242,13 @@
         <v>0.986503</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.3359</v>
+        <v>0.2334</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.3359</v>
+        <v>0.2334</v>
       </c>
       <c r="I112" t="n">
-        <v>1.238323</v>
+        <v>1.052332</v>
       </c>
       <c r="J112" t="n">
         <v>0.4481</v>
@@ -4276,13 +4276,13 @@
         <v>0.99849</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.0562</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.0562</v>
       </c>
       <c r="I113" t="n">
-        <v>1.22928</v>
+        <v>1.051741</v>
       </c>
       <c r="J113" t="n">
         <v>0.0948</v>
@@ -4310,13 +4310,13 @@
         <v>1.007874</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2895</v>
+        <v>-0.2669</v>
       </c>
       <c r="H114" t="n">
-        <v>0.2895</v>
+        <v>-0.2669</v>
       </c>
       <c r="I114" t="n">
-        <v>1.232839</v>
+        <v>1.048934</v>
       </c>
       <c r="J114" t="n">
         <v>-0.5128</v>
@@ -4344,13 +4344,13 @@
         <v>0.9856279999999999</v>
       </c>
       <c r="F115" t="n">
-        <v>0.5243</v>
+        <v>0.436</v>
       </c>
       <c r="H115" t="n">
-        <v>0.5243</v>
+        <v>0.436</v>
       </c>
       <c r="I115" t="n">
-        <v>1.239302</v>
+        <v>1.053507</v>
       </c>
       <c r="J115" t="n">
         <v>0.3578</v>
@@ -4378,13 +4378,13 @@
         <v>0.992503</v>
       </c>
       <c r="F116" t="n">
-        <v>0.96</v>
+        <v>0.2089</v>
       </c>
       <c r="H116" t="n">
-        <v>0.96</v>
+        <v>0.2089</v>
       </c>
       <c r="I116" t="n">
-        <v>1.251199</v>
+        <v>1.055708</v>
       </c>
       <c r="J116" t="n">
         <v>0.5653</v>
@@ -4412,13 +4412,13 @@
         <v>0.97711</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.9019</v>
+        <v>-0.1295</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.9019</v>
+        <v>-0.1295</v>
       </c>
       <c r="I117" t="n">
-        <v>1.239914</v>
+        <v>1.054341</v>
       </c>
       <c r="J117" t="n">
         <v>-0.7213000000000001</v>
@@ -4446,13 +4446,13 @@
         <v>0.971547</v>
       </c>
       <c r="F118" t="n">
-        <v>1.5676</v>
+        <v>0.4867</v>
       </c>
       <c r="H118" t="n">
-        <v>1.5676</v>
+        <v>0.4867</v>
       </c>
       <c r="I118" t="n">
-        <v>1.259352</v>
+        <v>1.059472</v>
       </c>
       <c r="J118" t="n">
         <v>0.9364</v>
@@ -4480,13 +4480,13 @@
         <v>0.962906</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.2691</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.2691</v>
       </c>
       <c r="I119" t="n">
-        <v>1.258128</v>
+        <v>1.062323</v>
       </c>
       <c r="J119" t="n">
         <v>0.4056</v>
@@ -4514,13 +4514,13 @@
         <v>0.9644160000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>0.4319</v>
+        <v>-0.2571</v>
       </c>
       <c r="H120" t="n">
-        <v>0.4319</v>
+        <v>-0.2571</v>
       </c>
       <c r="I120" t="n">
-        <v>1.263562</v>
+        <v>1.059592</v>
       </c>
       <c r="J120" t="n">
         <v>-0.5344</v>
@@ -4548,13 +4548,13 @@
         <v>0.976169</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1362</v>
+        <v>0.1164</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1362</v>
+        <v>0.1164</v>
       </c>
       <c r="I121" t="n">
-        <v>1.265282</v>
+        <v>1.060825</v>
       </c>
       <c r="J121" t="n">
         <v>0.6062</v>
@@ -4582,13 +4582,13 @@
         <v>0.984123</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.9969</v>
+        <v>-0.3541</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.9969</v>
+        <v>-0.3541</v>
       </c>
       <c r="I122" t="n">
-        <v>1.252669</v>
+        <v>1.057069</v>
       </c>
       <c r="J122" t="n">
         <v>-0.8092</v>
@@ -4616,13 +4616,13 @@
         <v>0.976114</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0313</v>
+        <v>-0.3383</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0313</v>
+        <v>-0.3383</v>
       </c>
       <c r="I123" t="n">
-        <v>1.253061</v>
+        <v>1.053493</v>
       </c>
       <c r="J123" t="n">
         <v>-0.9043</v>
@@ -4650,13 +4650,13 @@
         <v>0.968746</v>
       </c>
       <c r="F124" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="I124" t="n">
-        <v>1.261771</v>
+        <v>1.055144</v>
       </c>
       <c r="J124" t="n">
         <v>0.4097</v>
@@ -4684,13 +4684,13 @@
         <v>0.942407</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1355</v>
+        <v>0.3774</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1355</v>
+        <v>0.3774</v>
       </c>
       <c r="I125" t="n">
-        <v>1.263482</v>
+        <v>1.059126</v>
       </c>
       <c r="J125" t="n">
         <v>0.8246</v>
@@ -4718,13 +4718,13 @@
         <v>0.9313360000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7469</v>
+        <v>0.1563</v>
       </c>
       <c r="H126" t="n">
-        <v>0.7469</v>
+        <v>0.1563</v>
       </c>
       <c r="I126" t="n">
-        <v>1.272918</v>
+        <v>1.060781</v>
       </c>
       <c r="J126" t="n">
         <v>0.5017</v>
@@ -4752,13 +4752,13 @@
         <v>0.91745</v>
       </c>
       <c r="F127" t="n">
-        <v>1.5227</v>
+        <v>0.1924</v>
       </c>
       <c r="H127" t="n">
-        <v>1.5227</v>
+        <v>0.1924</v>
       </c>
       <c r="I127" t="n">
-        <v>1.292301</v>
+        <v>1.062822</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0227</v>
@@ -4786,13 +4786,13 @@
         <v>0.929444</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9935</v>
+        <v>-0.5309</v>
       </c>
       <c r="H128" t="n">
-        <v>0.9935</v>
+        <v>-0.5309</v>
       </c>
       <c r="I128" t="n">
-        <v>1.30514</v>
+        <v>1.05718</v>
       </c>
       <c r="J128" t="n">
         <v>-0.8772</v>
@@ -4820,13 +4820,13 @@
         <v>0.922726</v>
       </c>
       <c r="F129" t="n">
-        <v>1.7175</v>
+        <v>0.7745</v>
       </c>
       <c r="H129" t="n">
-        <v>1.7175</v>
+        <v>0.7745</v>
       </c>
       <c r="I129" t="n">
-        <v>1.327556</v>
+        <v>1.065367</v>
       </c>
       <c r="J129" t="n">
         <v>1.1774</v>
@@ -4854,13 +4854,13 @@
         <v>0.9324750000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>0.4293</v>
+        <v>0.3708</v>
       </c>
       <c r="H130" t="n">
-        <v>0.4293</v>
+        <v>0.3708</v>
       </c>
       <c r="I130" t="n">
-        <v>1.333255</v>
+        <v>1.069318</v>
       </c>
       <c r="J130" t="n">
         <v>0.9656</v>
@@ -4888,13 +4888,13 @@
         <v>0.925492</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.4146</v>
+        <v>0.5425</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.4146</v>
+        <v>0.5425</v>
       </c>
       <c r="I131" t="n">
-        <v>1.327727</v>
+        <v>1.075119</v>
       </c>
       <c r="J131" t="n">
         <v>1.1729</v>
@@ -4922,13 +4922,13 @@
         <v>0.9314170000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>-1.186</v>
+        <v>-0.0514</v>
       </c>
       <c r="H132" t="n">
-        <v>-1.186</v>
+        <v>-0.0514</v>
       </c>
       <c r="I132" t="n">
-        <v>1.311981</v>
+        <v>1.074566</v>
       </c>
       <c r="J132" t="n">
         <v>0.0956</v>
@@ -4956,13 +4956,13 @@
         <v>0.9319190000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>-1.8894</v>
+        <v>0.4765</v>
       </c>
       <c r="H133" t="n">
-        <v>-1.8894</v>
+        <v>0.4765</v>
       </c>
       <c r="I133" t="n">
-        <v>1.287193</v>
+        <v>1.079687</v>
       </c>
       <c r="J133" t="n">
         <v>0.9485</v>
@@ -4990,13 +4990,13 @@
         <v>0.934864</v>
       </c>
       <c r="F134" t="n">
-        <v>-1.0301</v>
+        <v>0.0408</v>
       </c>
       <c r="H134" t="n">
-        <v>-1.0301</v>
+        <v>0.0408</v>
       </c>
       <c r="I134" t="n">
-        <v>1.273933</v>
+        <v>1.080127</v>
       </c>
       <c r="J134" t="n">
         <v>0.0428</v>
@@ -5024,13 +5024,13 @@
         <v>0.948312</v>
       </c>
       <c r="F135" t="n">
-        <v>0.9569</v>
+        <v>-0.1745</v>
       </c>
       <c r="H135" t="n">
-        <v>0.9569</v>
+        <v>-0.1745</v>
       </c>
       <c r="I135" t="n">
-        <v>1.286123</v>
+        <v>1.078242</v>
       </c>
       <c r="J135" t="n">
         <v>0.0098</v>
@@ -5058,13 +5058,13 @@
         <v>0.938645</v>
       </c>
       <c r="F136" t="n">
-        <v>1.181</v>
+        <v>0.6199</v>
       </c>
       <c r="H136" t="n">
-        <v>1.181</v>
+        <v>0.6199</v>
       </c>
       <c r="I136" t="n">
-        <v>1.301312</v>
+        <v>1.084926</v>
       </c>
       <c r="J136" t="n">
         <v>1.2768</v>
@@ -5092,13 +5092,13 @@
         <v>0.925953</v>
       </c>
       <c r="F137" t="n">
-        <v>-1.5699</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-1.5699</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="I137" t="n">
-        <v>1.280882</v>
+        <v>1.084109</v>
       </c>
       <c r="J137" t="n">
         <v>-0.4595</v>
@@ -5126,13 +5126,13 @@
         <v>0.914293</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.407</v>
+        <v>0.4011</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.407</v>
+        <v>0.4011</v>
       </c>
       <c r="I138" t="n">
-        <v>1.275669</v>
+        <v>1.088458</v>
       </c>
       <c r="J138" t="n">
         <v>0.2489</v>
@@ -5160,13 +5160,13 @@
         <v>0.898718</v>
       </c>
       <c r="F139" t="n">
-        <v>-1.4635</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="H139" t="n">
-        <v>-1.4635</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>1.257</v>
+        <v>1.080717</v>
       </c>
       <c r="J139" t="n">
         <v>-1.7899</v>
@@ -5194,13 +5194,13 @@
         <v>0.887995</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.1366</v>
+        <v>0.7179</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.1366</v>
+        <v>0.7179</v>
       </c>
       <c r="I140" t="n">
-        <v>1.255283</v>
+        <v>1.088475</v>
       </c>
       <c r="J140" t="n">
         <v>1.3358</v>
@@ -5228,13 +5228,13 @@
         <v>0.867319</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.3527</v>
+        <v>0.6685</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.3527</v>
+        <v>0.6685</v>
       </c>
       <c r="I141" t="n">
-        <v>1.250855</v>
+        <v>1.095752</v>
       </c>
       <c r="J141" t="n">
         <v>1.2608</v>
@@ -5262,13 +5262,13 @@
         <v>0.87617</v>
       </c>
       <c r="F142" t="n">
-        <v>0.6294</v>
+        <v>0.3639</v>
       </c>
       <c r="H142" t="n">
-        <v>0.6294</v>
+        <v>0.3639</v>
       </c>
       <c r="I142" t="n">
-        <v>1.258728</v>
+        <v>1.099739</v>
       </c>
       <c r="J142" t="n">
         <v>1.0733</v>
@@ -5296,13 +5296,13 @@
         <v>0.854522</v>
       </c>
       <c r="F143" t="n">
-        <v>-1.3894</v>
+        <v>-0.3266</v>
       </c>
       <c r="H143" t="n">
-        <v>-1.3894</v>
+        <v>-0.3266</v>
       </c>
       <c r="I143" t="n">
-        <v>1.241239</v>
+        <v>1.096147</v>
       </c>
       <c r="J143" t="n">
         <v>-0.7135</v>
@@ -5330,13 +5330,13 @@
         <v>0.858359</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.1671</v>
+        <v>-0.6218</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.1671</v>
+        <v>-0.6218</v>
       </c>
       <c r="I144" t="n">
-        <v>1.239166</v>
+        <v>1.089331</v>
       </c>
       <c r="J144" t="n">
         <v>-1.1343</v>
@@ -5364,13 +5364,13 @@
         <v>0.783128</v>
       </c>
       <c r="F145" t="n">
-        <v>-2.0089</v>
+        <v>-0.4461</v>
       </c>
       <c r="H145" t="n">
-        <v>-2.0089</v>
+        <v>-0.4461</v>
       </c>
       <c r="I145" t="n">
-        <v>1.214272</v>
+        <v>1.084472</v>
       </c>
       <c r="J145" t="n">
         <v>-1.4048</v>
@@ -5398,13 +5398,13 @@
         <v>0.76385</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.7312</v>
+        <v>-0.3031</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.7312</v>
+        <v>-0.3031</v>
       </c>
       <c r="I146" t="n">
-        <v>1.205394</v>
+        <v>1.081185</v>
       </c>
       <c r="J146" t="n">
         <v>-0.913</v>
@@ -5432,13 +5432,13 @@
         <v>0.772981</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.319</v>
+        <v>-0.0216</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.319</v>
+        <v>-0.0216</v>
       </c>
       <c r="I147" t="n">
-        <v>1.201549</v>
+        <v>1.080951</v>
       </c>
       <c r="J147" t="n">
         <v>0.3887</v>
@@ -5466,13 +5466,13 @@
         <v>0.758015</v>
       </c>
       <c r="F148" t="n">
-        <v>-1.5471</v>
+        <v>-0.2534</v>
       </c>
       <c r="H148" t="n">
-        <v>-1.5471</v>
+        <v>-0.2534</v>
       </c>
       <c r="I148" t="n">
-        <v>1.18296</v>
+        <v>1.078212</v>
       </c>
       <c r="J148" t="n">
         <v>-0.8247</v>
@@ -5500,13 +5500,13 @@
         <v>0.704797</v>
       </c>
       <c r="F149" t="n">
-        <v>-2.4848</v>
+        <v>-0.2825</v>
       </c>
       <c r="H149" t="n">
-        <v>-2.4848</v>
+        <v>-0.2825</v>
       </c>
       <c r="I149" t="n">
-        <v>1.153566</v>
+        <v>1.075166</v>
       </c>
       <c r="J149" t="n">
         <v>-1.0446</v>
@@ -5534,13 +5534,13 @@
         <v>0.716046</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0554</v>
+        <v>-0.6397</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0554</v>
+        <v>-0.6397</v>
       </c>
       <c r="I150" t="n">
-        <v>1.154205</v>
+        <v>1.068288</v>
       </c>
       <c r="J150" t="n">
         <v>-1.0836</v>
@@ -5568,13 +5568,13 @@
         <v>0.705873</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6914</v>
+        <v>0.1704</v>
       </c>
       <c r="H151" t="n">
-        <v>0.6914</v>
+        <v>0.1704</v>
       </c>
       <c r="I151" t="n">
-        <v>1.162185</v>
+        <v>1.070109</v>
       </c>
       <c r="J151" t="n">
         <v>0.4707</v>
@@ -5602,13 +5602,13 @@
         <v>0.723115</v>
       </c>
       <c r="F152" t="n">
-        <v>0.1792</v>
+        <v>-1.0037</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1792</v>
+        <v>-1.0037</v>
       </c>
       <c r="I152" t="n">
-        <v>1.164268</v>
+        <v>1.059368</v>
       </c>
       <c r="J152" t="n">
         <v>-1.2533</v>
@@ -5636,13 +5636,13 @@
         <v>0.72889</v>
       </c>
       <c r="F153" t="n">
-        <v>0.152</v>
+        <v>-0.4315</v>
       </c>
       <c r="H153" t="n">
-        <v>0.152</v>
+        <v>-0.4315</v>
       </c>
       <c r="I153" t="n">
-        <v>1.166038</v>
+        <v>1.054797</v>
       </c>
       <c r="J153" t="n">
         <v>-1.3454</v>
@@ -5670,13 +5670,13 @@
         <v>0.772922</v>
       </c>
       <c r="F154" t="n">
-        <v>2.1793</v>
+        <v>-0.052</v>
       </c>
       <c r="H154" t="n">
-        <v>2.1793</v>
+        <v>-0.052</v>
       </c>
       <c r="I154" t="n">
-        <v>1.191449</v>
+        <v>1.054248</v>
       </c>
       <c r="J154" t="n">
         <v>0.6763</v>
@@ -5704,13 +5704,13 @@
         <v>0.749125</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.8462</v>
+        <v>0.3514</v>
       </c>
       <c r="H155" t="n">
-        <v>-0.8462</v>
+        <v>0.3514</v>
       </c>
       <c r="I155" t="n">
-        <v>1.181367</v>
+        <v>1.057953</v>
       </c>
       <c r="J155" t="n">
         <v>0.5674</v>
@@ -5738,13 +5738,13 @@
         <v>0.750589</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4405</v>
+        <v>0.3346</v>
       </c>
       <c r="H156" t="n">
-        <v>0.4405</v>
+        <v>0.3346</v>
       </c>
       <c r="I156" t="n">
-        <v>1.18657</v>
+        <v>1.061493</v>
       </c>
       <c r="J156" t="n">
         <v>1.0557</v>
@@ -5772,13 +5772,13 @@
         <v>0.77012</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.3065</v>
+        <v>-0.4485</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.3065</v>
+        <v>-0.4485</v>
       </c>
       <c r="I157" t="n">
-        <v>1.182933</v>
+        <v>1.056732</v>
       </c>
       <c r="J157" t="n">
         <v>-0.5908</v>
@@ -5806,13 +5806,13 @@
         <v>0.757961</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.7684</v>
+        <v>0.0202</v>
       </c>
       <c r="H158" t="n">
-        <v>-0.7684</v>
+        <v>0.0202</v>
       </c>
       <c r="I158" t="n">
-        <v>1.173843</v>
+        <v>1.056946</v>
       </c>
       <c r="J158" t="n">
         <v>0.115</v>
@@ -5840,13 +5840,13 @@
         <v>0.720681</v>
       </c>
       <c r="F159" t="n">
-        <v>-1.8021</v>
+        <v>-0.0114</v>
       </c>
       <c r="H159" t="n">
-        <v>-1.8021</v>
+        <v>-0.0114</v>
       </c>
       <c r="I159" t="n">
-        <v>1.152689</v>
+        <v>1.056825</v>
       </c>
       <c r="J159" t="n">
         <v>-0.3936</v>
@@ -5874,13 +5874,13 @@
         <v>0.710296</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.0017</v>
+        <v>0.3761</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.0017</v>
+        <v>0.3761</v>
       </c>
       <c r="I160" t="n">
-        <v>1.152669</v>
+        <v>1.0608</v>
       </c>
       <c r="J160" t="n">
         <v>0.5817</v>
@@ -5908,13 +5908,13 @@
         <v>0.7066170000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.0775</v>
+        <v>-0.1711</v>
       </c>
       <c r="H161" t="n">
-        <v>-0.0775</v>
+        <v>-0.1711</v>
       </c>
       <c r="I161" t="n">
-        <v>1.151776</v>
+        <v>1.058985</v>
       </c>
       <c r="J161" t="n">
         <v>-0.3514</v>
@@ -5942,13 +5942,13 @@
         <v>0.697034</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.2897</v>
+        <v>0.7454</v>
       </c>
       <c r="H162" t="n">
-        <v>-0.2897</v>
+        <v>0.7454</v>
       </c>
       <c r="I162" t="n">
-        <v>1.148439</v>
+        <v>1.066878</v>
       </c>
       <c r="J162" t="n">
         <v>1.8274</v>
@@ -5976,13 +5976,13 @@
         <v>0.692364</v>
       </c>
       <c r="F163" t="n">
-        <v>-1.1393</v>
+        <v>0.0452</v>
       </c>
       <c r="H163" t="n">
-        <v>-1.1393</v>
+        <v>0.0452</v>
       </c>
       <c r="I163" t="n">
-        <v>1.135355</v>
+        <v>1.067361</v>
       </c>
       <c r="J163" t="n">
         <v>-0.1884</v>
@@ -6010,13 +6010,13 @@
         <v>0.675044</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1324</v>
+        <v>0.0238</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1324</v>
+        <v>0.0238</v>
       </c>
       <c r="I164" t="n">
-        <v>1.136859</v>
+        <v>1.067615</v>
       </c>
       <c r="J164" t="n">
         <v>0.0785</v>
@@ -6044,13 +6044,13 @@
         <v>0.689253</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.061</v>
+        <v>-0.4315</v>
       </c>
       <c r="H165" t="n">
-        <v>-1.061</v>
+        <v>-0.4315</v>
       </c>
       <c r="I165" t="n">
-        <v>1.124797</v>
+        <v>1.063008</v>
       </c>
       <c r="J165" t="n">
         <v>-0.924</v>
@@ -6078,13 +6078,13 @@
         <v>0.661616</v>
       </c>
       <c r="F166" t="n">
-        <v>-1.8096</v>
+        <v>0.1198</v>
       </c>
       <c r="H166" t="n">
-        <v>-1.8096</v>
+        <v>0.1198</v>
       </c>
       <c r="I166" t="n">
-        <v>1.104443</v>
+        <v>1.064281</v>
       </c>
       <c r="J166" t="n">
         <v>-0.0315</v>
@@ -6112,13 +6112,13 @@
         <v>0.664683</v>
       </c>
       <c r="F167" t="n">
-        <v>-1.7015</v>
+        <v>-0.6879</v>
       </c>
       <c r="H167" t="n">
-        <v>-1.7015</v>
+        <v>-0.6879</v>
       </c>
       <c r="I167" t="n">
-        <v>1.08565</v>
+        <v>1.05696</v>
       </c>
       <c r="J167" t="n">
         <v>-1.365</v>
@@ -6146,13 +6146,13 @@
         <v>0.643043</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1154</v>
+        <v>0.1444</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1154</v>
+        <v>0.1444</v>
       </c>
       <c r="I168" t="n">
-        <v>1.086903</v>
+        <v>1.058487</v>
       </c>
       <c r="J168" t="n">
         <v>0.3642</v>
@@ -6180,13 +6180,13 @@
         <v>0.6319669999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>-1.3025</v>
+        <v>-0.6006</v>
       </c>
       <c r="H169" t="n">
-        <v>-1.3025</v>
+        <v>-0.6006</v>
       </c>
       <c r="I169" t="n">
-        <v>1.072746</v>
+        <v>1.052129</v>
       </c>
       <c r="J169" t="n">
         <v>-1.2124</v>
@@ -6214,13 +6214,13 @@
         <v>0.643794</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0116</v>
+        <v>-0.4465</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0116</v>
+        <v>-0.4465</v>
       </c>
       <c r="I170" t="n">
-        <v>1.072871</v>
+        <v>1.047432</v>
       </c>
       <c r="J170" t="n">
         <v>-0.6018</v>
@@ -6248,13 +6248,13 @@
         <v>0.637387</v>
       </c>
       <c r="F171" t="n">
-        <v>-1.2175</v>
+        <v>-0.264</v>
       </c>
       <c r="H171" t="n">
-        <v>-1.2175</v>
+        <v>-0.264</v>
       </c>
       <c r="I171" t="n">
-        <v>1.059808</v>
+        <v>1.044666</v>
       </c>
       <c r="J171" t="n">
         <v>-0.7</v>
@@ -6282,13 +6282,13 @@
         <v>0.6250559999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.1671</v>
+        <v>0.136</v>
       </c>
       <c r="H172" t="n">
-        <v>-0.1671</v>
+        <v>0.136</v>
       </c>
       <c r="I172" t="n">
-        <v>1.058038</v>
+        <v>1.046087</v>
       </c>
       <c r="J172" t="n">
         <v>-0.1233</v>
@@ -6316,13 +6316,13 @@
         <v>0.611476</v>
       </c>
       <c r="F173" t="n">
-        <v>-1.3454</v>
+        <v>-0.4642</v>
       </c>
       <c r="H173" t="n">
-        <v>-1.3454</v>
+        <v>-0.4642</v>
       </c>
       <c r="I173" t="n">
-        <v>1.043802</v>
+        <v>1.041231</v>
       </c>
       <c r="J173" t="n">
         <v>-0.8457</v>
@@ -6350,13 +6350,13 @@
         <v>0.652103</v>
       </c>
       <c r="F174" t="n">
-        <v>1.8583</v>
+        <v>0.4571</v>
       </c>
       <c r="H174" t="n">
-        <v>1.8583</v>
+        <v>0.4571</v>
       </c>
       <c r="I174" t="n">
-        <v>1.0632</v>
+        <v>1.045991</v>
       </c>
       <c r="J174" t="n">
         <v>1.2758</v>
@@ -6384,13 +6384,13 @@
         <v>0.64007</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.3235</v>
+        <v>0.0376</v>
       </c>
       <c r="H175" t="n">
-        <v>-0.3235</v>
+        <v>0.0376</v>
       </c>
       <c r="I175" t="n">
-        <v>1.05976</v>
+        <v>1.046384</v>
       </c>
       <c r="J175" t="n">
         <v>0.3028</v>
@@ -6418,13 +6418,13 @@
         <v>0.67449</v>
       </c>
       <c r="F176" t="n">
-        <v>0.8749</v>
+        <v>-0.2907</v>
       </c>
       <c r="H176" t="n">
-        <v>0.8749</v>
+        <v>-0.2907</v>
       </c>
       <c r="I176" t="n">
-        <v>1.069032</v>
+        <v>1.043342</v>
       </c>
       <c r="J176" t="n">
         <v>-0.3801</v>
@@ -6452,13 +6452,13 @@
         <v>0.667951</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5389</v>
+        <v>0.1542</v>
       </c>
       <c r="H177" t="n">
-        <v>0.5389</v>
+        <v>0.1542</v>
       </c>
       <c r="I177" t="n">
-        <v>1.074794</v>
+        <v>1.044951</v>
       </c>
       <c r="J177" t="n">
         <v>0.2157</v>
@@ -6486,13 +6486,13 @@
         <v>0.676527</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.0371</v>
+        <v>-0.7147</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.0371</v>
+        <v>-0.7147</v>
       </c>
       <c r="I178" t="n">
-        <v>1.074395</v>
+        <v>1.037483</v>
       </c>
       <c r="J178" t="n">
         <v>-1.495</v>
@@ -6520,13 +6520,13 @@
         <v>0.696841</v>
       </c>
       <c r="F179" t="n">
-        <v>1.0744</v>
+        <v>-0.435</v>
       </c>
       <c r="H179" t="n">
-        <v>1.0744</v>
+        <v>-0.435</v>
       </c>
       <c r="I179" t="n">
-        <v>1.085938</v>
+        <v>1.03297</v>
       </c>
       <c r="J179" t="n">
         <v>-0.5991</v>
@@ -6554,13 +6554,13 @@
         <v>0.699605</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0233</v>
+        <v>0.3219</v>
       </c>
       <c r="H180" t="n">
-        <v>0.0233</v>
+        <v>0.3219</v>
       </c>
       <c r="I180" t="n">
-        <v>1.086191</v>
+        <v>1.036295</v>
       </c>
       <c r="J180" t="n">
         <v>0.9002</v>
@@ -6588,13 +6588,13 @@
         <v>0.680256</v>
       </c>
       <c r="F181" t="n">
-        <v>0.4438</v>
+        <v>0.0675</v>
       </c>
       <c r="H181" t="n">
-        <v>0.4438</v>
+        <v>0.0675</v>
       </c>
       <c r="I181" t="n">
-        <v>1.091011</v>
+        <v>1.036994</v>
       </c>
       <c r="J181" t="n">
         <v>0.398</v>
@@ -6622,13 +6622,13 @@
         <v>0.681366</v>
       </c>
       <c r="F182" t="n">
-        <v>0.9775</v>
+        <v>0.0145</v>
       </c>
       <c r="H182" t="n">
-        <v>0.9775</v>
+        <v>0.0145</v>
       </c>
       <c r="I182" t="n">
-        <v>1.101675</v>
+        <v>1.037145</v>
       </c>
       <c r="J182" t="n">
         <v>-0.0399</v>
@@ -6656,13 +6656,13 @@
         <v>0.688929</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.6805</v>
+        <v>-0.2697</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.6805</v>
+        <v>-0.2697</v>
       </c>
       <c r="I183" t="n">
-        <v>1.094178</v>
+        <v>1.034347</v>
       </c>
       <c r="J183" t="n">
         <v>-0.5165</v>
@@ -6690,13 +6690,13 @@
         <v>0.654498</v>
       </c>
       <c r="F184" t="n">
-        <v>-1.499</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="H184" t="n">
-        <v>-1.499</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>1.077777</v>
+        <v>1.035191</v>
       </c>
       <c r="J184" t="n">
         <v>-0.2389</v>
@@ -6724,13 +6724,13 @@
         <v>0.647716</v>
       </c>
       <c r="F185" t="n">
-        <v>-1.0835</v>
+        <v>-0.1528</v>
       </c>
       <c r="H185" t="n">
-        <v>-1.0835</v>
+        <v>-0.1528</v>
       </c>
       <c r="I185" t="n">
-        <v>1.066099</v>
+        <v>1.03361</v>
       </c>
       <c r="J185" t="n">
         <v>-0.243</v>
@@ -6758,13 +6758,13 @@
         <v>0.6497579999999999</v>
       </c>
       <c r="F186" t="n">
-        <v>0.1113</v>
+        <v>0.3158</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1113</v>
+        <v>0.3158</v>
       </c>
       <c r="I186" t="n">
-        <v>1.067285</v>
+        <v>1.036874</v>
       </c>
       <c r="J186" t="n">
         <v>0.6821</v>
@@ -6792,13 +6792,13 @@
         <v>0.642321</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.6385</v>
+        <v>-0.2417</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.6385</v>
+        <v>-0.2417</v>
       </c>
       <c r="I187" t="n">
-        <v>1.060471</v>
+        <v>1.034368</v>
       </c>
       <c r="J187" t="n">
         <v>-0.8863</v>
@@ -6826,13 +6826,13 @@
         <v>0.651686</v>
       </c>
       <c r="F188" t="n">
-        <v>0.1729</v>
+        <v>-0.3116</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1729</v>
+        <v>-0.3116</v>
       </c>
       <c r="I188" t="n">
-        <v>1.062305</v>
+        <v>1.031145</v>
       </c>
       <c r="J188" t="n">
         <v>-0.7066</v>
@@ -6860,13 +6860,13 @@
         <v>0.671766</v>
       </c>
       <c r="F189" t="n">
-        <v>3.0754</v>
+        <v>1.1488</v>
       </c>
       <c r="H189" t="n">
-        <v>3.0754</v>
+        <v>1.1488</v>
       </c>
       <c r="I189" t="n">
-        <v>1.094975</v>
+        <v>1.04299</v>
       </c>
       <c r="J189" t="n">
         <v>2.5236</v>
@@ -6894,13 +6894,13 @@
         <v>0.684786</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2199</v>
+        <v>0.2233</v>
       </c>
       <c r="H190" t="n">
-        <v>0.2199</v>
+        <v>0.2233</v>
       </c>
       <c r="I190" t="n">
-        <v>1.097382</v>
+        <v>1.045319</v>
       </c>
       <c r="J190" t="n">
         <v>0.4996</v>
@@ -6928,13 +6928,13 @@
         <v>0.693977</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.4875</v>
+        <v>-0.2814</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.4875</v>
+        <v>-0.2814</v>
       </c>
       <c r="I191" t="n">
-        <v>1.092032</v>
+        <v>1.042378</v>
       </c>
       <c r="J191" t="n">
         <v>-0.1114</v>
@@ -6962,13 +6962,13 @@
         <v>0.695314</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.122</v>
+        <v>0.1615</v>
       </c>
       <c r="H192" t="n">
-        <v>-0.122</v>
+        <v>0.1615</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0907</v>
+        <v>1.044061</v>
       </c>
       <c r="J192" t="n">
         <v>0.5881</v>
@@ -6996,13 +6996,13 @@
         <v>0.674813</v>
       </c>
       <c r="F193" t="n">
-        <v>-1.4233</v>
+        <v>-0.1808</v>
       </c>
       <c r="H193" t="n">
-        <v>-1.4233</v>
+        <v>-0.1808</v>
       </c>
       <c r="I193" t="n">
-        <v>1.075177</v>
+        <v>1.042174</v>
       </c>
       <c r="J193" t="n">
         <v>-0.8284</v>
@@ -7030,13 +7030,13 @@
         <v>0.685584</v>
       </c>
       <c r="F194" t="n">
-        <v>0.9829</v>
+        <v>-0.0234</v>
       </c>
       <c r="H194" t="n">
-        <v>0.9829</v>
+        <v>-0.0234</v>
       </c>
       <c r="I194" t="n">
-        <v>1.085745</v>
+        <v>1.04193</v>
       </c>
       <c r="J194" t="n">
         <v>-0.0892</v>
@@ -7064,13 +7064,13 @@
         <v>0.6945789999999999</v>
       </c>
       <c r="F195" t="n">
-        <v>0.8536</v>
+        <v>0.0515</v>
       </c>
       <c r="H195" t="n">
-        <v>0.8536</v>
+        <v>0.0515</v>
       </c>
       <c r="I195" t="n">
-        <v>1.095012</v>
+        <v>1.042466</v>
       </c>
       <c r="J195" t="n">
         <v>0.2666</v>
@@ -7098,13 +7098,13 @@
         <v>0.7029260000000001</v>
       </c>
       <c r="F196" t="n">
-        <v>1.4725</v>
+        <v>0.4677</v>
       </c>
       <c r="H196" t="n">
-        <v>1.4725</v>
+        <v>0.4677</v>
       </c>
       <c r="I196" t="n">
-        <v>1.111137</v>
+        <v>1.047342</v>
       </c>
       <c r="J196" t="n">
         <v>1.3137</v>
@@ -7132,13 +7132,13 @@
         <v>0.7074859999999999</v>
       </c>
       <c r="F197" t="n">
-        <v>0.4747</v>
+        <v>-0.3041</v>
       </c>
       <c r="H197" t="n">
-        <v>0.4747</v>
+        <v>-0.3041</v>
       </c>
       <c r="I197" t="n">
-        <v>1.116412</v>
+        <v>1.044157</v>
       </c>
       <c r="J197" t="n">
         <v>-0.5497</v>
@@ -7166,13 +7166,13 @@
         <v>0.699214</v>
       </c>
       <c r="F198" t="n">
-        <v>0.5374</v>
+        <v>-0.0204</v>
       </c>
       <c r="H198" t="n">
-        <v>0.5374</v>
+        <v>-0.0204</v>
       </c>
       <c r="I198" t="n">
-        <v>1.122412</v>
+        <v>1.043944</v>
       </c>
       <c r="J198" t="n">
         <v>0.0183</v>
@@ -7200,13 +7200,13 @@
         <v>0.714082</v>
       </c>
       <c r="F199" t="n">
-        <v>1.8728</v>
+        <v>0.2067</v>
       </c>
       <c r="H199" t="n">
-        <v>1.8728</v>
+        <v>0.2067</v>
       </c>
       <c r="I199" t="n">
-        <v>1.143433</v>
+        <v>1.046102</v>
       </c>
       <c r="J199" t="n">
         <v>0.9126</v>
@@ -7234,13 +7234,13 @@
         <v>0.71436</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.9936</v>
+        <v>0.484</v>
       </c>
       <c r="H200" t="n">
-        <v>-0.9936</v>
+        <v>0.484</v>
       </c>
       <c r="I200" t="n">
-        <v>1.132072</v>
+        <v>1.051165</v>
       </c>
       <c r="J200" t="n">
         <v>1.2788</v>
@@ -7268,13 +7268,13 @@
         <v>0.702408</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.4836</v>
+        <v>-0.1906</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.4836</v>
+        <v>-0.1906</v>
       </c>
       <c r="I201" t="n">
-        <v>1.126597</v>
+        <v>1.049161</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6694</v>
@@ -7302,13 +7302,13 @@
         <v>0.710303</v>
       </c>
       <c r="F202" t="n">
-        <v>-1.5978</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.5978</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="I202" t="n">
-        <v>1.108597</v>
+        <v>1.041129</v>
       </c>
       <c r="J202" t="n">
         <v>-1.854</v>
@@ -7336,13 +7336,13 @@
         <v>0.717494</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.0459</v>
+        <v>-0.1164</v>
       </c>
       <c r="H203" t="n">
-        <v>-0.0459</v>
+        <v>-0.1164</v>
       </c>
       <c r="I203" t="n">
-        <v>1.108087</v>
+        <v>1.039917</v>
       </c>
       <c r="J203" t="n">
         <v>-0.3221</v>
@@ -7370,13 +7370,13 @@
         <v>0.7274969999999999</v>
       </c>
       <c r="F204" t="n">
-        <v>-1.3672</v>
+        <v>-0.6399</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.3672</v>
+        <v>-0.6399</v>
       </c>
       <c r="I204" t="n">
-        <v>1.092937</v>
+        <v>1.033263</v>
       </c>
       <c r="J204" t="n">
         <v>-1.546</v>
@@ -7404,13 +7404,13 @@
         <v>0.717821</v>
       </c>
       <c r="F205" t="n">
-        <v>0.7543</v>
+        <v>1.1346</v>
       </c>
       <c r="H205" t="n">
-        <v>0.7543</v>
+        <v>1.1346</v>
       </c>
       <c r="I205" t="n">
-        <v>1.101181</v>
+        <v>1.044986</v>
       </c>
       <c r="J205" t="n">
         <v>1.9824</v>
@@ -7438,13 +7438,13 @@
         <v>0.718253</v>
       </c>
       <c r="F206" t="n">
-        <v>1.2492</v>
+        <v>0.3778</v>
       </c>
       <c r="H206" t="n">
-        <v>1.2492</v>
+        <v>0.3778</v>
       </c>
       <c r="I206" t="n">
-        <v>1.114937</v>
+        <v>1.048934</v>
       </c>
       <c r="J206" t="n">
         <v>0.7963</v>
@@ -7472,13 +7472,13 @@
         <v>0.7081229999999999</v>
       </c>
       <c r="F207" t="n">
-        <v>0.3283</v>
+        <v>-0.3973</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3283</v>
+        <v>-0.3973</v>
       </c>
       <c r="I207" t="n">
-        <v>1.118597</v>
+        <v>1.044767</v>
       </c>
       <c r="J207" t="n">
         <v>-0.9435</v>
@@ -7506,13 +7506,13 @@
         <v>0.711639</v>
       </c>
       <c r="F208" t="n">
-        <v>0.6127</v>
+        <v>0.1673</v>
       </c>
       <c r="H208" t="n">
-        <v>0.6127</v>
+        <v>0.1673</v>
       </c>
       <c r="I208" t="n">
-        <v>1.125452</v>
+        <v>1.046515</v>
       </c>
       <c r="J208" t="n">
         <v>0.3618</v>
@@ -7540,13 +7540,13 @@
         <v>0.7034589999999999</v>
       </c>
       <c r="F209" t="n">
-        <v>-1.4031</v>
+        <v>0.3566</v>
       </c>
       <c r="H209" t="n">
-        <v>-1.4031</v>
+        <v>0.3566</v>
       </c>
       <c r="I209" t="n">
-        <v>1.10966</v>
+        <v>1.050246</v>
       </c>
       <c r="J209" t="n">
         <v>1.0767</v>
@@ -7574,13 +7574,13 @@
         <v>0.704199</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.6914</v>
+        <v>-0.1761</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.6914</v>
+        <v>-0.1761</v>
       </c>
       <c r="I210" t="n">
-        <v>1.101988</v>
+        <v>1.048397</v>
       </c>
       <c r="J210" t="n">
         <v>-0.4025</v>
@@ -7608,13 +7608,13 @@
         <v>0.712067</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.5955</v>
+        <v>-0.1948</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.5955</v>
+        <v>-0.1948</v>
       </c>
       <c r="I211" t="n">
-        <v>1.095426</v>
+        <v>1.046355</v>
       </c>
       <c r="J211" t="n">
         <v>0.0112</v>
@@ -7642,13 +7642,13 @@
         <v>0.717028</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.133</v>
+        <v>-0.2841</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.133</v>
+        <v>-0.2841</v>
       </c>
       <c r="I212" t="n">
-        <v>1.093969</v>
+        <v>1.043382</v>
       </c>
       <c r="J212" t="n">
         <v>-0.516</v>
@@ -7676,13 +7676,13 @@
         <v>0.70458</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.0956</v>
+        <v>-0.3904</v>
       </c>
       <c r="H213" t="n">
-        <v>-1.0956</v>
+        <v>-0.3904</v>
       </c>
       <c r="I213" t="n">
-        <v>1.081983</v>
+        <v>1.039309</v>
       </c>
       <c r="J213" t="n">
         <v>-1.0889</v>
@@ -7710,13 +7710,13 @@
         <v>0.70525</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.924</v>
+        <v>0.4836</v>
       </c>
       <c r="H214" t="n">
-        <v>-0.924</v>
+        <v>0.4836</v>
       </c>
       <c r="I214" t="n">
-        <v>1.071986</v>
+        <v>1.044335</v>
       </c>
       <c r="J214" t="n">
         <v>1.0306</v>
@@ -7744,13 +7744,13 @@
         <v>0.688242</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.8804999999999999</v>
+        <v>0.359</v>
       </c>
       <c r="H215" t="n">
-        <v>-0.8804999999999999</v>
+        <v>0.359</v>
       </c>
       <c r="I215" t="n">
-        <v>1.062547</v>
+        <v>1.048084</v>
       </c>
       <c r="J215" t="n">
         <v>0.6531</v>
@@ -7778,13 +7778,13 @@
         <v>0.683824</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.4577</v>
+        <v>0.1248</v>
       </c>
       <c r="H216" t="n">
-        <v>-0.4577</v>
+        <v>0.1248</v>
       </c>
       <c r="I216" t="n">
-        <v>1.057684</v>
+        <v>1.049392</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0237</v>
@@ -7812,13 +7812,13 @@
         <v>0.68462</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.238</v>
+        <v>0.1753</v>
       </c>
       <c r="H217" t="n">
-        <v>-0.238</v>
+        <v>0.1753</v>
       </c>
       <c r="I217" t="n">
-        <v>1.055167</v>
+        <v>1.051231</v>
       </c>
       <c r="J217" t="n">
         <v>0.3157</v>
@@ -7846,13 +7846,13 @@
         <v>0.689492</v>
       </c>
       <c r="F218" t="n">
-        <v>0.0286</v>
+        <v>-0.317</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0286</v>
+        <v>-0.317</v>
       </c>
       <c r="I218" t="n">
-        <v>1.055468</v>
+        <v>1.047899</v>
       </c>
       <c r="J218" t="n">
         <v>-0.8327</v>
@@ -7880,13 +7880,13 @@
         <v>0.676376</v>
       </c>
       <c r="F219" t="n">
-        <v>-1.1433</v>
+        <v>0.1635</v>
       </c>
       <c r="H219" t="n">
-        <v>-1.1433</v>
+        <v>0.1635</v>
       </c>
       <c r="I219" t="n">
-        <v>1.043402</v>
+        <v>1.049612</v>
       </c>
       <c r="J219" t="n">
         <v>0.0312</v>
@@ -7914,13 +7914,13 @@
         <v>0.695184</v>
       </c>
       <c r="F220" t="n">
-        <v>0.2847</v>
+        <v>0.0086</v>
       </c>
       <c r="H220" t="n">
-        <v>0.2847</v>
+        <v>0.0086</v>
       </c>
       <c r="I220" t="n">
-        <v>1.046372</v>
+        <v>1.049703</v>
       </c>
       <c r="J220" t="n">
         <v>0.3941</v>
@@ -7948,13 +7948,13 @@
         <v>0.703195</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.2062</v>
+        <v>-0.3417</v>
       </c>
       <c r="H221" t="n">
-        <v>-0.2062</v>
+        <v>-0.3417</v>
       </c>
       <c r="I221" t="n">
-        <v>1.044214</v>
+        <v>1.046116</v>
       </c>
       <c r="J221" t="n">
         <v>-0.529</v>
@@ -7982,13 +7982,13 @@
         <v>0.687819</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.9253</v>
+        <v>-0.336</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.9253</v>
+        <v>-0.336</v>
       </c>
       <c r="I222" t="n">
-        <v>1.034552</v>
+        <v>1.042601</v>
       </c>
       <c r="J222" t="n">
         <v>-1.0787</v>
@@ -8016,13 +8016,13 @@
         <v>0.703447</v>
       </c>
       <c r="F223" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.2169</v>
       </c>
       <c r="H223" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.2169</v>
       </c>
       <c r="I223" t="n">
-        <v>1.044726</v>
+        <v>1.044862</v>
       </c>
       <c r="J223" t="n">
         <v>0.6642</v>
@@ -8050,13 +8050,13 @@
         <v>0.703274</v>
       </c>
       <c r="F224" t="n">
-        <v>0.782</v>
+        <v>0.2616</v>
       </c>
       <c r="H224" t="n">
-        <v>0.782</v>
+        <v>0.2616</v>
       </c>
       <c r="I224" t="n">
-        <v>1.052896</v>
+        <v>1.047596</v>
       </c>
       <c r="J224" t="n">
         <v>1.132</v>
@@ -8084,13 +8084,13 @@
         <v>0.6857259999999999</v>
       </c>
       <c r="F225" t="n">
-        <v>-1.1642</v>
+        <v>0.0474</v>
       </c>
       <c r="H225" t="n">
-        <v>-1.1642</v>
+        <v>0.0474</v>
       </c>
       <c r="I225" t="n">
-        <v>1.040638</v>
+        <v>1.048092</v>
       </c>
       <c r="J225" t="n">
         <v>-0.091</v>
@@ -8118,13 +8118,13 @@
         <v>0.683391</v>
       </c>
       <c r="F226" t="n">
-        <v>0.1472</v>
+        <v>-0.2507</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1472</v>
+        <v>-0.2507</v>
       </c>
       <c r="I226" t="n">
-        <v>1.04217</v>
+        <v>1.045465</v>
       </c>
       <c r="J226" t="n">
         <v>-0.8229</v>
@@ -8152,13 +8152,13 @@
         <v>0.678854</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.454</v>
+        <v>0.71</v>
       </c>
       <c r="H227" t="n">
-        <v>-0.454</v>
+        <v>0.71</v>
       </c>
       <c r="I227" t="n">
-        <v>1.037438</v>
+        <v>1.052887</v>
       </c>
       <c r="J227" t="n">
         <v>1.2651</v>
@@ -8186,13 +8186,13 @@
         <v>0.682157</v>
       </c>
       <c r="F228" t="n">
-        <v>0.226</v>
+        <v>0.5942</v>
       </c>
       <c r="H228" t="n">
-        <v>0.226</v>
+        <v>0.5942</v>
       </c>
       <c r="I228" t="n">
-        <v>1.039783</v>
+        <v>1.059144</v>
       </c>
       <c r="J228" t="n">
         <v>1.1244</v>
@@ -8220,13 +8220,13 @@
         <v>0.687186</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.6845</v>
+        <v>-0.3407</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.6845</v>
+        <v>-0.3407</v>
       </c>
       <c r="I229" t="n">
-        <v>1.032666</v>
+        <v>1.055535</v>
       </c>
       <c r="J229" t="n">
         <v>-0.3675</v>
@@ -8254,13 +8254,13 @@
         <v>0.685437</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.2357</v>
       </c>
       <c r="H230" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.2357</v>
       </c>
       <c r="I230" t="n">
-        <v>1.026123</v>
+        <v>1.058023</v>
       </c>
       <c r="J230" t="n">
         <v>0.3655</v>
@@ -8288,13 +8288,13 @@
         <v>0.678221</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.1646</v>
+        <v>-0.1757</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.1646</v>
+        <v>-0.1757</v>
       </c>
       <c r="I231" t="n">
-        <v>1.024434</v>
+        <v>1.056164</v>
       </c>
       <c r="J231" t="n">
         <v>-0.4361</v>
@@ -8322,13 +8322,13 @@
         <v>0.686626</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1321</v>
+        <v>0.1784</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1321</v>
+        <v>0.1784</v>
       </c>
       <c r="I232" t="n">
-        <v>1.025786</v>
+        <v>1.058048</v>
       </c>
       <c r="J232" t="n">
         <v>0.5543</v>
@@ -8356,13 +8356,13 @@
         <v>0.659016</v>
       </c>
       <c r="F233" t="n">
-        <v>0.9327</v>
+        <v>0.0341</v>
       </c>
       <c r="H233" t="n">
-        <v>0.9327</v>
+        <v>0.0341</v>
       </c>
       <c r="I233" t="n">
-        <v>1.035354</v>
+        <v>1.058409</v>
       </c>
       <c r="J233" t="n">
         <v>-0.2151</v>
@@ -8390,13 +8390,13 @@
         <v>0.654722</v>
       </c>
       <c r="F234" t="n">
-        <v>-1.0546</v>
+        <v>-0.2335</v>
       </c>
       <c r="H234" t="n">
-        <v>-1.0546</v>
+        <v>-0.2335</v>
       </c>
       <c r="I234" t="n">
-        <v>1.024435</v>
+        <v>1.055938</v>
       </c>
       <c r="J234" t="n">
         <v>-0.3271</v>
@@ -8424,13 +8424,13 @@
         <v>0.648489</v>
       </c>
       <c r="F235" t="n">
-        <v>-0.253</v>
+        <v>0.361</v>
       </c>
       <c r="H235" t="n">
-        <v>-0.253</v>
+        <v>0.361</v>
       </c>
       <c r="I235" t="n">
-        <v>1.021843</v>
+        <v>1.05975</v>
       </c>
       <c r="J235" t="n">
         <v>0.8120000000000001</v>
@@ -8458,13 +8458,13 @@
         <v>0.6410709999999999</v>
       </c>
       <c r="F236" t="n">
-        <v>1.1155</v>
+        <v>1.1109</v>
       </c>
       <c r="H236" t="n">
-        <v>1.1155</v>
+        <v>1.1109</v>
       </c>
       <c r="I236" t="n">
-        <v>1.033243</v>
+        <v>1.071522</v>
       </c>
       <c r="J236" t="n">
         <v>2.1135</v>
@@ -8492,13 +8492,13 @@
         <v>0.633989</v>
       </c>
       <c r="F237" t="n">
-        <v>0.446</v>
+        <v>0.7853</v>
       </c>
       <c r="H237" t="n">
-        <v>0.446</v>
+        <v>0.7853</v>
       </c>
       <c r="I237" t="n">
-        <v>1.03785</v>
+        <v>1.079937</v>
       </c>
       <c r="J237" t="n">
         <v>1.2177</v>
@@ -8526,13 +8526,13 @@
         <v>0.620678</v>
       </c>
       <c r="F238" t="n">
-        <v>-0.8259</v>
+        <v>1.1813</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.8259</v>
+        <v>1.1813</v>
       </c>
       <c r="I238" t="n">
-        <v>1.029279</v>
+        <v>1.092694</v>
       </c>
       <c r="J238" t="n">
         <v>2.1111</v>
@@ -8560,13 +8560,13 @@
         <v>0.635906</v>
       </c>
       <c r="F239" t="n">
-        <v>3.6184</v>
+        <v>-0.6902</v>
       </c>
       <c r="H239" t="n">
-        <v>3.6184</v>
+        <v>-0.6902</v>
       </c>
       <c r="I239" t="n">
-        <v>1.066523</v>
+        <v>1.085153</v>
       </c>
       <c r="J239" t="n">
         <v>-1.1877</v>
@@ -8594,13 +8594,13 @@
         <v>0.617835</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.6714</v>
+        <v>0.6307</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.6714</v>
+        <v>0.6307</v>
       </c>
       <c r="I240" t="n">
-        <v>1.059362</v>
+        <v>1.091997</v>
       </c>
       <c r="J240" t="n">
         <v>1.3608</v>
@@ -8628,13 +8628,13 @@
         <v>0.619522</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.6085</v>
+        <v>-0.4315</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.6085</v>
+        <v>-0.4315</v>
       </c>
       <c r="I241" t="n">
-        <v>1.052916</v>
+        <v>1.087285</v>
       </c>
       <c r="J241" t="n">
         <v>-1.1751</v>
@@ -8662,13 +8662,13 @@
         <v>0.605776</v>
       </c>
       <c r="F242" t="n">
-        <v>-0.4904</v>
+        <v>0.1867</v>
       </c>
       <c r="H242" t="n">
-        <v>-0.4904</v>
+        <v>0.1867</v>
       </c>
       <c r="I242" t="n">
-        <v>1.047753</v>
+        <v>1.089315</v>
       </c>
       <c r="J242" t="n">
         <v>0.4582</v>
@@ -8696,13 +8696,13 @@
         <v>0.613679</v>
       </c>
       <c r="F243" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.2566</v>
       </c>
       <c r="H243" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.2566</v>
       </c>
       <c r="I243" t="n">
-        <v>1.048701</v>
+        <v>1.09211</v>
       </c>
       <c r="J243" t="n">
         <v>1.088</v>
@@ -8730,13 +8730,13 @@
         <v>0.631479</v>
       </c>
       <c r="F244" t="n">
-        <v>0.3145</v>
+        <v>-0.5876</v>
       </c>
       <c r="H244" t="n">
-        <v>0.3145</v>
+        <v>-0.5876</v>
       </c>
       <c r="I244" t="n">
-        <v>1.051999</v>
+        <v>1.085693</v>
       </c>
       <c r="J244" t="n">
         <v>-0.6644</v>
@@ -8764,13 +8764,13 @@
         <v>0.605308</v>
       </c>
       <c r="F245" t="n">
-        <v>0.0163</v>
+        <v>0.3888</v>
       </c>
       <c r="H245" t="n">
-        <v>0.0163</v>
+        <v>0.3888</v>
       </c>
       <c r="I245" t="n">
-        <v>1.05217</v>
+        <v>1.089914</v>
       </c>
       <c r="J245" t="n">
         <v>0.9074</v>
@@ -8798,13 +8798,13 @@
         <v>0.607253</v>
       </c>
       <c r="F246" t="n">
-        <v>0.1491</v>
+        <v>0.4431</v>
       </c>
       <c r="H246" t="n">
-        <v>0.1491</v>
+        <v>0.4431</v>
       </c>
       <c r="I246" t="n">
-        <v>1.053739</v>
+        <v>1.094743</v>
       </c>
       <c r="J246" t="n">
         <v>0.9875</v>
@@ -8832,13 +8832,13 @@
         <v>0.601778</v>
       </c>
       <c r="F247" t="n">
-        <v>0.3368</v>
+        <v>1.0541</v>
       </c>
       <c r="H247" t="n">
-        <v>0.3368</v>
+        <v>1.0541</v>
       </c>
       <c r="I247" t="n">
-        <v>1.057287</v>
+        <v>1.106283</v>
       </c>
       <c r="J247" t="n">
         <v>2.3057</v>
@@ -8866,13 +8866,13 @@
         <v>0.613804</v>
       </c>
       <c r="F248" t="n">
-        <v>1.7899</v>
+        <v>-0.6992</v>
       </c>
       <c r="H248" t="n">
-        <v>1.7899</v>
+        <v>-0.6992</v>
       </c>
       <c r="I248" t="n">
-        <v>1.076211</v>
+        <v>1.098548</v>
       </c>
       <c r="J248" t="n">
         <v>-1.6787</v>
@@ -8900,13 +8900,13 @@
         <v>0.599286</v>
       </c>
       <c r="F249" t="n">
-        <v>-1.1194</v>
+        <v>0.1961</v>
       </c>
       <c r="H249" t="n">
-        <v>-1.1194</v>
+        <v>0.1961</v>
       </c>
       <c r="I249" t="n">
-        <v>1.064164</v>
+        <v>1.100702</v>
       </c>
       <c r="J249" t="n">
         <v>0.2985</v>
@@ -8934,13 +8934,13 @@
         <v>0.609091</v>
       </c>
       <c r="F250" t="n">
-        <v>-1.3536</v>
+        <v>-0.2054</v>
       </c>
       <c r="H250" t="n">
-        <v>-1.3536</v>
+        <v>-0.2054</v>
       </c>
       <c r="I250" t="n">
-        <v>1.049759</v>
+        <v>1.098441</v>
       </c>
       <c r="J250" t="n">
         <v>-0.9918</v>
@@ -8968,13 +8968,13 @@
         <v>0.6350980000000001</v>
       </c>
       <c r="F251" t="n">
-        <v>-0.9176</v>
+        <v>-0.8972</v>
       </c>
       <c r="H251" t="n">
-        <v>-0.9176</v>
+        <v>-0.8972</v>
       </c>
       <c r="I251" t="n">
-        <v>1.040127</v>
+        <v>1.088586</v>
       </c>
       <c r="J251" t="n">
         <v>-1.9725</v>
@@ -9002,13 +9002,13 @@
         <v>0.6279979999999999</v>
       </c>
       <c r="F252" t="n">
-        <v>-0.0946</v>
+        <v>0.3667</v>
       </c>
       <c r="H252" t="n">
-        <v>-0.0946</v>
+        <v>0.3667</v>
       </c>
       <c r="I252" t="n">
-        <v>1.039142</v>
+        <v>1.092578</v>
       </c>
       <c r="J252" t="n">
         <v>0.8808</v>
@@ -9036,13 +9036,13 @@
         <v>0.632714</v>
       </c>
       <c r="F253" t="n">
-        <v>0.1289</v>
+        <v>-0.3339</v>
       </c>
       <c r="H253" t="n">
-        <v>0.1289</v>
+        <v>-0.3339</v>
       </c>
       <c r="I253" t="n">
-        <v>1.040482</v>
+        <v>1.08893</v>
       </c>
       <c r="J253" t="n">
         <v>-0.2726</v>
@@ -9070,13 +9070,13 @@
         <v>0.628722</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.1876</v>
+        <v>0.9588</v>
       </c>
       <c r="H254" t="n">
-        <v>-0.1876</v>
+        <v>0.9588</v>
       </c>
       <c r="I254" t="n">
-        <v>1.038531</v>
+        <v>1.09937</v>
       </c>
       <c r="J254" t="n">
         <v>1.6512</v>
@@ -9104,13 +9104,13 @@
         <v>0.65299</v>
       </c>
       <c r="F255" t="n">
-        <v>0.0496</v>
+        <v>-0.4929</v>
       </c>
       <c r="H255" t="n">
-        <v>0.0496</v>
+        <v>-0.4929</v>
       </c>
       <c r="I255" t="n">
-        <v>1.039045</v>
+        <v>1.093951</v>
       </c>
       <c r="J255" t="n">
         <v>-0.7157</v>
@@ -9138,13 +9138,13 @@
         <v>0.659488</v>
       </c>
       <c r="F256" t="n">
-        <v>0.9765</v>
+        <v>-0.5595</v>
       </c>
       <c r="H256" t="n">
-        <v>0.9765</v>
+        <v>-0.5595</v>
       </c>
       <c r="I256" t="n">
-        <v>1.049191</v>
+        <v>1.087831</v>
       </c>
       <c r="J256" t="n">
         <v>-0.6228</v>
@@ -9172,13 +9172,13 @@
         <v>0.662359</v>
       </c>
       <c r="F257" t="n">
-        <v>1.6973</v>
+        <v>0.2888</v>
       </c>
       <c r="H257" t="n">
-        <v>1.6973</v>
+        <v>0.2888</v>
       </c>
       <c r="I257" t="n">
-        <v>1.067</v>
+        <v>1.090972</v>
       </c>
       <c r="J257" t="n">
         <v>0.9981</v>
@@ -9206,13 +9206,13 @@
         <v>0.650141</v>
       </c>
       <c r="F258" t="n">
-        <v>-1.359</v>
+        <v>0.284</v>
       </c>
       <c r="H258" t="n">
-        <v>-1.359</v>
+        <v>0.284</v>
       </c>
       <c r="I258" t="n">
-        <v>1.052499</v>
+        <v>1.094071</v>
       </c>
       <c r="J258" t="n">
         <v>0.4906</v>
@@ -9240,13 +9240,13 @@
         <v>0.64658</v>
       </c>
       <c r="F259" t="n">
-        <v>0.0513</v>
+        <v>-0.0373</v>
       </c>
       <c r="H259" t="n">
-        <v>0.0513</v>
+        <v>-0.0373</v>
       </c>
       <c r="I259" t="n">
-        <v>1.053039</v>
+        <v>1.093663</v>
       </c>
       <c r="J259" t="n">
         <v>-0.2132</v>
@@ -9274,13 +9274,13 @@
         <v>0.658307</v>
       </c>
       <c r="F260" t="n">
-        <v>0.0191</v>
+        <v>-0.1126</v>
       </c>
       <c r="H260" t="n">
-        <v>0.0191</v>
+        <v>-0.1126</v>
       </c>
       <c r="I260" t="n">
-        <v>1.05324</v>
+        <v>1.092431</v>
       </c>
       <c r="J260" t="n">
         <v>-0.2112</v>
@@ -9308,13 +9308,13 @@
         <v>0.6444879999999999</v>
       </c>
       <c r="F261" t="n">
-        <v>-1.4046</v>
+        <v>0.3598</v>
       </c>
       <c r="H261" t="n">
-        <v>-1.4046</v>
+        <v>0.3598</v>
       </c>
       <c r="I261" t="n">
-        <v>1.038447</v>
+        <v>1.096362</v>
       </c>
       <c r="J261" t="n">
         <v>0.1433</v>
@@ -9342,13 +9342,13 @@
         <v>0.63978</v>
       </c>
       <c r="F262" t="n">
-        <v>0.4215</v>
+        <v>0.1305</v>
       </c>
       <c r="H262" t="n">
-        <v>0.4215</v>
+        <v>0.1305</v>
       </c>
       <c r="I262" t="n">
-        <v>1.042823</v>
+        <v>1.097793</v>
       </c>
       <c r="J262" t="n">
         <v>0.5968</v>
@@ -9376,13 +9376,13 @@
         <v>0.651671</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.6079</v>
+        <v>-0.0551</v>
       </c>
       <c r="H263" t="n">
-        <v>-0.6079</v>
+        <v>-0.0551</v>
       </c>
       <c r="I263" t="n">
-        <v>1.036484</v>
+        <v>1.097188</v>
       </c>
       <c r="J263" t="n">
         <v>0.234</v>
@@ -9410,13 +9410,13 @@
         <v>0.651676</v>
       </c>
       <c r="F264" t="n">
-        <v>0.1552</v>
+        <v>0.2694</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1552</v>
+        <v>0.2694</v>
       </c>
       <c r="I264" t="n">
-        <v>1.038092</v>
+        <v>1.100144</v>
       </c>
       <c r="J264" t="n">
         <v>0.4423</v>
@@ -9444,13 +9444,13 @@
         <v>0.644236</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.2701</v>
+        <v>0.6693</v>
       </c>
       <c r="H265" t="n">
-        <v>-0.2701</v>
+        <v>0.6693</v>
       </c>
       <c r="I265" t="n">
-        <v>1.035288</v>
+        <v>1.107507</v>
       </c>
       <c r="J265" t="n">
         <v>0.9811</v>
@@ -9478,13 +9478,13 @@
         <v>0.6497540000000001</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.1144</v>
+        <v>0.4728</v>
       </c>
       <c r="H266" t="n">
-        <v>-0.1144</v>
+        <v>0.4728</v>
       </c>
       <c r="I266" t="n">
-        <v>1.034104</v>
+        <v>1.112743</v>
       </c>
       <c r="J266" t="n">
         <v>1.1467</v>
@@ -9512,13 +9512,13 @@
         <v>0.668666</v>
       </c>
       <c r="F267" t="n">
-        <v>-2.0449</v>
+        <v>-0.8265</v>
       </c>
       <c r="H267" t="n">
-        <v>-2.0449</v>
+        <v>-0.8265</v>
       </c>
       <c r="I267" t="n">
-        <v>1.012957</v>
+        <v>1.103546</v>
       </c>
       <c r="J267" t="n">
         <v>-2.0512</v>
@@ -9546,13 +9546,13 @@
         <v>0.708829</v>
       </c>
       <c r="F268" t="n">
-        <v>0.1044</v>
+        <v>-1.2305</v>
       </c>
       <c r="H268" t="n">
-        <v>0.1044</v>
+        <v>-1.2305</v>
       </c>
       <c r="I268" t="n">
-        <v>1.014015</v>
+        <v>1.089967</v>
       </c>
       <c r="J268" t="n">
         <v>-2.6202</v>
@@ -9580,13 +9580,13 @@
         <v>0.7009</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.2045</v>
+        <v>0.3275</v>
       </c>
       <c r="H269" t="n">
-        <v>-0.2045</v>
+        <v>0.3275</v>
       </c>
       <c r="I269" t="n">
-        <v>1.011941</v>
+        <v>1.093537</v>
       </c>
       <c r="J269" t="n">
         <v>1.0806</v>
@@ -9614,13 +9614,13 @@
         <v>0.688035</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.3949</v>
+        <v>0.1782</v>
       </c>
       <c r="H270" t="n">
-        <v>-0.3949</v>
+        <v>0.1782</v>
       </c>
       <c r="I270" t="n">
-        <v>1.007944</v>
+        <v>1.095485</v>
       </c>
       <c r="J270" t="n">
         <v>0.6499</v>
@@ -9648,13 +9648,13 @@
         <v>0.684901</v>
       </c>
       <c r="F271" t="n">
-        <v>2.1916</v>
+        <v>0.3197</v>
       </c>
       <c r="H271" t="n">
-        <v>2.1916</v>
+        <v>0.3197</v>
       </c>
       <c r="I271" t="n">
-        <v>1.030034</v>
+        <v>1.098988</v>
       </c>
       <c r="J271" t="n">
         <v>1.0687</v>
@@ -9682,13 +9682,13 @@
         <v>0.696948</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.0722</v>
+        <v>0.1199</v>
       </c>
       <c r="H272" t="n">
-        <v>-0.0722</v>
+        <v>0.1199</v>
       </c>
       <c r="I272" t="n">
-        <v>1.029291</v>
+        <v>1.100305</v>
       </c>
       <c r="J272" t="n">
         <v>0.1325</v>
@@ -9716,13 +9716,13 @@
         <v>0.676652</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.1551</v>
+        <v>0.4692</v>
       </c>
       <c r="H273" t="n">
-        <v>-0.1551</v>
+        <v>0.4692</v>
       </c>
       <c r="I273" t="n">
-        <v>1.027694</v>
+        <v>1.105468</v>
       </c>
       <c r="J273" t="n">
         <v>0.9009</v>
@@ -9750,13 +9750,13 @@
         <v>0.695764</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.1177</v>
+        <v>-0.3685</v>
       </c>
       <c r="H274" t="n">
-        <v>-0.1177</v>
+        <v>-0.3685</v>
       </c>
       <c r="I274" t="n">
-        <v>1.026485</v>
+        <v>1.101394</v>
       </c>
       <c r="J274" t="n">
         <v>-0.9084</v>
@@ -9784,13 +9784,13 @@
         <v>0.712828</v>
       </c>
       <c r="F275" t="n">
-        <v>0.6857</v>
+        <v>-0.214</v>
       </c>
       <c r="H275" t="n">
-        <v>0.6857</v>
+        <v>-0.214</v>
       </c>
       <c r="I275" t="n">
-        <v>1.033523</v>
+        <v>1.099037</v>
       </c>
       <c r="J275" t="n">
         <v>-0.799</v>
@@ -9818,13 +9818,13 @@
         <v>0.715356</v>
       </c>
       <c r="F276" t="n">
-        <v>1.0336</v>
+        <v>-0.6158</v>
       </c>
       <c r="H276" t="n">
-        <v>1.0336</v>
+        <v>-0.6158</v>
       </c>
       <c r="I276" t="n">
-        <v>1.044205</v>
+        <v>1.09227</v>
       </c>
       <c r="J276" t="n">
         <v>-0.9287</v>
@@ -9852,13 +9852,13 @@
         <v>0.704387</v>
       </c>
       <c r="F277" t="n">
-        <v>0.3774</v>
+        <v>0.1002</v>
       </c>
       <c r="H277" t="n">
-        <v>0.3774</v>
+        <v>0.1002</v>
       </c>
       <c r="I277" t="n">
-        <v>1.048147</v>
+        <v>1.093364</v>
       </c>
       <c r="J277" t="n">
         <v>0.2559</v>
@@ -9886,13 +9886,13 @@
         <v>0.71484</v>
       </c>
       <c r="F278" t="n">
-        <v>-0.1067</v>
+        <v>-1.0214</v>
       </c>
       <c r="H278" t="n">
-        <v>-0.1067</v>
+        <v>-1.0214</v>
       </c>
       <c r="I278" t="n">
-        <v>1.047028</v>
+        <v>1.082196</v>
       </c>
       <c r="J278" t="n">
         <v>-1.7678</v>
@@ -9920,13 +9920,13 @@
         <v>0.700841</v>
       </c>
       <c r="F279" t="n">
-        <v>0.0673</v>
+        <v>0.5322</v>
       </c>
       <c r="H279" t="n">
-        <v>0.0673</v>
+        <v>0.5322</v>
       </c>
       <c r="I279" t="n">
-        <v>1.047732</v>
+        <v>1.087956</v>
       </c>
       <c r="J279" t="n">
         <v>1.1158</v>
@@ -9954,13 +9954,13 @@
         <v>0.713858</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.9709</v>
+        <v>-0.2331</v>
       </c>
       <c r="H280" t="n">
-        <v>-0.9709</v>
+        <v>-0.2331</v>
       </c>
       <c r="I280" t="n">
-        <v>1.03756</v>
+        <v>1.08542</v>
       </c>
       <c r="J280" t="n">
         <v>-0.9412</v>
@@ -9988,13 +9988,13 @@
         <v>0.721641</v>
       </c>
       <c r="F281" t="n">
-        <v>-1.0701</v>
+        <v>-0.7534</v>
       </c>
       <c r="H281" t="n">
-        <v>-1.0701</v>
+        <v>-0.7534</v>
       </c>
       <c r="I281" t="n">
-        <v>1.026457</v>
+        <v>1.077242</v>
       </c>
       <c r="J281" t="n">
         <v>-2.2286</v>
@@ -10022,13 +10022,13 @@
         <v>0.734453</v>
       </c>
       <c r="F282" t="n">
-        <v>-1.6435</v>
+        <v>-0.9802</v>
       </c>
       <c r="H282" t="n">
-        <v>-1.6435</v>
+        <v>-0.9802</v>
       </c>
       <c r="I282" t="n">
-        <v>1.009587</v>
+        <v>1.066683</v>
       </c>
       <c r="J282" t="n">
         <v>-2.1259</v>
@@ -10056,13 +10056,13 @@
         <v>0.728677</v>
       </c>
       <c r="F283" t="n">
-        <v>2.2521</v>
+        <v>0.8482</v>
       </c>
       <c r="H283" t="n">
-        <v>2.2521</v>
+        <v>0.8482</v>
       </c>
       <c r="I283" t="n">
-        <v>1.032324</v>
+        <v>1.075731</v>
       </c>
       <c r="J283" t="n">
         <v>2.4572</v>
@@ -10090,13 +10090,13 @@
         <v>0.7165629999999999</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.7409</v>
+        <v>0.3427</v>
       </c>
       <c r="H284" t="n">
-        <v>-0.7409</v>
+        <v>0.3427</v>
       </c>
       <c r="I284" t="n">
-        <v>1.024675</v>
+        <v>1.079417</v>
       </c>
       <c r="J284" t="n">
         <v>0.8823</v>
@@ -10124,13 +10124,13 @@
         <v>0.731376</v>
       </c>
       <c r="F285" t="n">
-        <v>1.9122</v>
+        <v>-0.0925</v>
       </c>
       <c r="H285" t="n">
-        <v>1.9122</v>
+        <v>-0.0925</v>
       </c>
       <c r="I285" t="n">
-        <v>1.044269</v>
+        <v>1.078419</v>
       </c>
       <c r="J285" t="n">
         <v>-0.2593</v>
@@ -10158,13 +10158,13 @@
         <v>0.72627</v>
       </c>
       <c r="F286" t="n">
-        <v>2.8888</v>
+        <v>0.4569</v>
       </c>
       <c r="H286" t="n">
-        <v>2.8888</v>
+        <v>0.4569</v>
       </c>
       <c r="I286" t="n">
-        <v>1.074436</v>
+        <v>1.083346</v>
       </c>
       <c r="J286" t="n">
         <v>1.0066</v>
@@ -10192,13 +10192,13 @@
         <v>0.739109</v>
       </c>
       <c r="F287" t="n">
-        <v>0.8184</v>
+        <v>0.2332</v>
       </c>
       <c r="H287" t="n">
-        <v>0.8184</v>
+        <v>0.2332</v>
       </c>
       <c r="I287" t="n">
-        <v>1.083229</v>
+        <v>1.085872</v>
       </c>
       <c r="J287" t="n">
         <v>0.6026</v>
@@ -10226,13 +10226,13 @@
         <v>0.749651</v>
       </c>
       <c r="F288" t="n">
-        <v>0.7115</v>
+        <v>-0.3548</v>
       </c>
       <c r="H288" t="n">
-        <v>0.7115</v>
+        <v>-0.3548</v>
       </c>
       <c r="I288" t="n">
-        <v>1.090936</v>
+        <v>1.08202</v>
       </c>
       <c r="J288" t="n">
         <v>-0.7337</v>
@@ -10260,13 +10260,13 @@
         <v>0.725111</v>
       </c>
       <c r="F289" t="n">
-        <v>1.2662</v>
+        <v>0.3923</v>
       </c>
       <c r="H289" t="n">
-        <v>1.2662</v>
+        <v>0.3923</v>
       </c>
       <c r="I289" t="n">
-        <v>1.104749</v>
+        <v>1.086265</v>
       </c>
       <c r="J289" t="n">
         <v>0.3529</v>
@@ -10294,13 +10294,13 @@
         <v>0.746923</v>
       </c>
       <c r="F290" t="n">
-        <v>2.2475</v>
+        <v>-0.3986</v>
       </c>
       <c r="H290" t="n">
-        <v>2.2475</v>
+        <v>-0.3986</v>
       </c>
       <c r="I290" t="n">
-        <v>1.129579</v>
+        <v>1.081935</v>
       </c>
       <c r="J290" t="n">
         <v>-0.7107</v>
@@ -10328,13 +10328,13 @@
         <v>0.738077</v>
       </c>
       <c r="F291" t="n">
-        <v>-2.1668</v>
+        <v>-0.1428</v>
       </c>
       <c r="H291" t="n">
-        <v>-2.1668</v>
+        <v>-0.1428</v>
       </c>
       <c r="I291" t="n">
-        <v>1.105104</v>
+        <v>1.08039</v>
       </c>
       <c r="J291" t="n">
         <v>-1.2125</v>
@@ -10362,13 +10362,13 @@
         <v>0.7313460000000001</v>
       </c>
       <c r="F292" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.4707</v>
       </c>
       <c r="H292" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.4707</v>
       </c>
       <c r="I292" t="n">
-        <v>1.111983</v>
+        <v>1.085475</v>
       </c>
       <c r="J292" t="n">
         <v>1.3748</v>
@@ -10396,13 +10396,13 @@
         <v>0.692064</v>
       </c>
       <c r="F293" t="n">
-        <v>-2.6446</v>
+        <v>0.5855</v>
       </c>
       <c r="H293" t="n">
-        <v>-2.6446</v>
+        <v>0.5855</v>
       </c>
       <c r="I293" t="n">
-        <v>1.082576</v>
+        <v>1.091831</v>
       </c>
       <c r="J293" t="n">
         <v>0.9177999999999999</v>
@@ -10430,13 +10430,13 @@
         <v>0.691302</v>
       </c>
       <c r="F294" t="n">
-        <v>-1.2815</v>
+        <v>0.0453</v>
       </c>
       <c r="H294" t="n">
-        <v>-1.2815</v>
+        <v>0.0453</v>
       </c>
       <c r="I294" t="n">
-        <v>1.068703</v>
+        <v>1.092325</v>
       </c>
       <c r="J294" t="n">
         <v>-0.1089</v>
@@ -10464,13 +10464,13 @@
         <v>0.682215</v>
       </c>
       <c r="F295" t="n">
-        <v>0.4966</v>
+        <v>-0.2552</v>
       </c>
       <c r="H295" t="n">
-        <v>0.4966</v>
+        <v>-0.2552</v>
       </c>
       <c r="I295" t="n">
-        <v>1.074009</v>
+        <v>1.089538</v>
       </c>
       <c r="J295" t="n">
         <v>-0.8371</v>
@@ -10498,13 +10498,13 @@
         <v>0.676287</v>
       </c>
       <c r="F296" t="n">
-        <v>-1.0238</v>
+        <v>0.0684</v>
       </c>
       <c r="H296" t="n">
-        <v>-1.0238</v>
+        <v>0.0684</v>
       </c>
       <c r="I296" t="n">
-        <v>1.063013</v>
+        <v>1.090283</v>
       </c>
       <c r="J296" t="n">
         <v>0.0973</v>
@@ -10532,13 +10532,13 @@
         <v>0.663084</v>
       </c>
       <c r="F297" t="n">
-        <v>-1.0147</v>
+        <v>0.0886</v>
       </c>
       <c r="H297" t="n">
-        <v>-1.0147</v>
+        <v>0.0886</v>
       </c>
       <c r="I297" t="n">
-        <v>1.052227</v>
+        <v>1.091249</v>
       </c>
       <c r="J297" t="n">
         <v>0.091</v>
@@ -10566,13 +10566,13 @@
         <v>0.664862</v>
       </c>
       <c r="F298" t="n">
-        <v>2.0477</v>
+        <v>0.105</v>
       </c>
       <c r="H298" t="n">
-        <v>2.0477</v>
+        <v>0.105</v>
       </c>
       <c r="I298" t="n">
-        <v>1.073773</v>
+        <v>1.092395</v>
       </c>
       <c r="J298" t="n">
         <v>-0.129</v>
@@ -10600,13 +10600,13 @@
         <v>0.65896</v>
       </c>
       <c r="F299" t="n">
-        <v>-1.2467</v>
+        <v>0.3721</v>
       </c>
       <c r="H299" t="n">
-        <v>-1.2467</v>
+        <v>0.3721</v>
       </c>
       <c r="I299" t="n">
-        <v>1.060387</v>
+        <v>1.096459</v>
       </c>
       <c r="J299" t="n">
         <v>0.7784</v>
@@ -10634,13 +10634,13 @@
         <v>0.653937</v>
       </c>
       <c r="F300" t="n">
-        <v>-1.2848</v>
+        <v>0.5662</v>
       </c>
       <c r="H300" t="n">
-        <v>-1.2848</v>
+        <v>0.5662</v>
       </c>
       <c r="I300" t="n">
-        <v>1.046762</v>
+        <v>1.102668</v>
       </c>
       <c r="J300" t="n">
         <v>0.6733</v>
@@ -10668,13 +10668,13 @@
         <v>0.642279</v>
       </c>
       <c r="F301" t="n">
-        <v>-1.0436</v>
+        <v>-0.0111</v>
       </c>
       <c r="H301" t="n">
-        <v>-1.0436</v>
+        <v>-0.0111</v>
       </c>
       <c r="I301" t="n">
-        <v>1.035839</v>
+        <v>1.102545</v>
       </c>
       <c r="J301" t="n">
         <v>0.3343</v>
@@ -10702,13 +10702,13 @@
         <v>0.658505</v>
       </c>
       <c r="F302" t="n">
-        <v>-0.6258</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="H302" t="n">
-        <v>-0.6258</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="I302" t="n">
-        <v>1.029357</v>
+        <v>1.101822</v>
       </c>
       <c r="J302" t="n">
         <v>-0.4025</v>
@@ -10736,13 +10736,13 @@
         <v>0.647161</v>
       </c>
       <c r="F303" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.4165</v>
       </c>
       <c r="H303" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.4165</v>
       </c>
       <c r="I303" t="n">
-        <v>1.022399</v>
+        <v>1.106411</v>
       </c>
       <c r="J303" t="n">
         <v>0.1463</v>
@@ -10770,13 +10770,13 @@
         <v>0.6586880000000001</v>
       </c>
       <c r="F304" t="n">
-        <v>-0.5154</v>
+        <v>-0.6365</v>
       </c>
       <c r="H304" t="n">
-        <v>-0.5154</v>
+        <v>-0.6365</v>
       </c>
       <c r="I304" t="n">
-        <v>1.01713</v>
+        <v>1.099369</v>
       </c>
       <c r="J304" t="n">
         <v>-1.3177</v>
@@ -10804,13 +10804,13 @@
         <v>0.6484220000000001</v>
       </c>
       <c r="F305" t="n">
-        <v>0.3925</v>
+        <v>-0.3093</v>
       </c>
       <c r="H305" t="n">
-        <v>0.3925</v>
+        <v>-0.3093</v>
       </c>
       <c r="I305" t="n">
-        <v>1.021122</v>
+        <v>1.095968</v>
       </c>
       <c r="J305" t="n">
         <v>-0.4051</v>
@@ -10838,13 +10838,13 @@
         <v>0.622624</v>
       </c>
       <c r="F306" t="n">
-        <v>1.1615</v>
+        <v>0.0796</v>
       </c>
       <c r="H306" t="n">
-        <v>1.1615</v>
+        <v>0.0796</v>
       </c>
       <c r="I306" t="n">
-        <v>1.032982</v>
+        <v>1.096841</v>
       </c>
       <c r="J306" t="n">
         <v>0.9751</v>
@@ -10872,13 +10872,13 @@
         <v>0.637787</v>
       </c>
       <c r="F307" t="n">
-        <v>0.3437</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="H307" t="n">
-        <v>0.3437</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="I307" t="n">
-        <v>1.036532</v>
+        <v>1.090731</v>
       </c>
       <c r="J307" t="n">
         <v>-0.8967000000000001</v>
@@ -10906,13 +10906,13 @@
         <v>0.641773</v>
       </c>
       <c r="F308" t="n">
-        <v>-0.8711</v>
+        <v>-0.0658</v>
       </c>
       <c r="H308" t="n">
-        <v>-0.8711</v>
+        <v>-0.0658</v>
       </c>
       <c r="I308" t="n">
-        <v>1.027502</v>
+        <v>1.090014</v>
       </c>
       <c r="J308" t="n">
         <v>0.099</v>
@@ -10940,13 +10940,13 @@
         <v>0.606351</v>
       </c>
       <c r="F309" t="n">
-        <v>0.3077</v>
+        <v>0.3286</v>
       </c>
       <c r="H309" t="n">
-        <v>0.3077</v>
+        <v>0.3286</v>
       </c>
       <c r="I309" t="n">
-        <v>1.030664</v>
+        <v>1.093595</v>
       </c>
       <c r="J309" t="n">
         <v>0.583</v>
@@ -10974,13 +10974,13 @@
         <v>0.5749379999999999</v>
       </c>
       <c r="F310" t="n">
-        <v>-1.0252</v>
+        <v>0.387</v>
       </c>
       <c r="H310" t="n">
-        <v>-1.0252</v>
+        <v>0.387</v>
       </c>
       <c r="I310" t="n">
-        <v>1.020098</v>
+        <v>1.097828</v>
       </c>
       <c r="J310" t="n">
         <v>0.5800999999999999</v>
@@ -11008,13 +11008,13 @@
         <v>0.558074</v>
       </c>
       <c r="F311" t="n">
-        <v>-1.322</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="H311" t="n">
-        <v>-1.322</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>1.006613</v>
+        <v>1.107661</v>
       </c>
       <c r="J311" t="n">
         <v>1.4505</v>
@@ -11042,13 +11042,13 @@
         <v>0.568964</v>
       </c>
       <c r="F312" t="n">
-        <v>0.5504</v>
+        <v>0.6797</v>
       </c>
       <c r="H312" t="n">
-        <v>0.5504</v>
+        <v>0.6797</v>
       </c>
       <c r="I312" t="n">
-        <v>1.012153</v>
+        <v>1.11519</v>
       </c>
       <c r="J312" t="n">
         <v>1.5809</v>
@@ -11076,13 +11076,13 @@
         <v>0.544083</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.1374</v>
+        <v>-0.2302</v>
       </c>
       <c r="H313" t="n">
-        <v>-0.1374</v>
+        <v>-0.2302</v>
       </c>
       <c r="I313" t="n">
-        <v>1.010763</v>
+        <v>1.112622</v>
       </c>
       <c r="J313" t="n">
         <v>-0.5006</v>
@@ -11110,13 +11110,13 @@
         <v>0.541013</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.8341</v>
+        <v>-0.1726</v>
       </c>
       <c r="H314" t="n">
-        <v>-0.8341</v>
+        <v>-0.1726</v>
       </c>
       <c r="I314" t="n">
-        <v>1.002332</v>
+        <v>1.110702</v>
       </c>
       <c r="J314" t="n">
         <v>-0.8008999999999999</v>
@@ -11144,13 +11144,13 @@
         <v>0.523966</v>
       </c>
       <c r="F315" t="n">
-        <v>-1.3322</v>
+        <v>0.3223</v>
       </c>
       <c r="H315" t="n">
-        <v>-1.3322</v>
+        <v>0.3223</v>
       </c>
       <c r="I315" t="n">
-        <v>0.988978</v>
+        <v>1.114282</v>
       </c>
       <c r="J315" t="n">
         <v>0.4537</v>
@@ -11178,13 +11178,13 @@
         <v>0.5324</v>
       </c>
       <c r="F316" t="n">
-        <v>0.3181</v>
+        <v>-0.0584</v>
       </c>
       <c r="H316" t="n">
-        <v>0.3181</v>
+        <v>-0.0584</v>
       </c>
       <c r="I316" t="n">
-        <v>0.992124</v>
+        <v>1.113631</v>
       </c>
       <c r="J316" t="n">
         <v>-0.2948</v>
@@ -11212,13 +11212,13 @@
         <v>0.539995</v>
       </c>
       <c r="F317" t="n">
-        <v>0.783</v>
+        <v>0.3955</v>
       </c>
       <c r="H317" t="n">
-        <v>0.783</v>
+        <v>0.3955</v>
       </c>
       <c r="I317" t="n">
-        <v>0.999893</v>
+        <v>1.118036</v>
       </c>
       <c r="J317" t="n">
         <v>0.6988</v>
@@ -11246,13 +11246,13 @@
         <v>0.533146</v>
       </c>
       <c r="F318" t="n">
-        <v>-1.1534</v>
+        <v>0.3839</v>
       </c>
       <c r="H318" t="n">
-        <v>-1.1534</v>
+        <v>0.3839</v>
       </c>
       <c r="I318" t="n">
-        <v>0.988361</v>
+        <v>1.122328</v>
       </c>
       <c r="J318" t="n">
         <v>0.833</v>
@@ -11262,40 +11262,6 @@
       </c>
       <c r="M318" t="n">
         <v>1.25108</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="B319" t="n">
-        <v>-3.667</v>
-      </c>
-      <c r="D319" t="n">
-        <v>-3.667</v>
-      </c>
-      <c r="E319" t="n">
-        <v>0.5135960000000001</v>
-      </c>
-      <c r="F319" t="n">
-        <v>-0.4037</v>
-      </c>
-      <c r="H319" t="n">
-        <v>-0.4037</v>
-      </c>
-      <c r="I319" t="n">
-        <v>0.984371</v>
-      </c>
-      <c r="J319" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="L319" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="M319" t="n">
-        <v>1.259675</v>
       </c>
     </row>
   </sheetData>
@@ -11309,7 +11275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17360,25 +17326,6 @@
       </c>
       <c r="E318" t="n">
         <v>1.84208</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="B319" t="n">
-        <v>-0.1644</v>
-      </c>
-      <c r="C319" t="n">
-        <v>3.8113</v>
-      </c>
-      <c r="D319" t="n">
-        <v>1.8235</v>
-      </c>
-      <c r="E319" t="n">
-        <v>1.875669</v>
       </c>
     </row>
   </sheetData>
@@ -17392,7 +17339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23443,25 +23390,6 @@
       </c>
       <c r="E318" t="n">
         <v>1.440396</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="B319" t="n">
-        <v>-0.3067</v>
-      </c>
-      <c r="C319" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="D319" t="n">
-        <v>-0.6317</v>
-      </c>
-      <c r="E319" t="n">
-        <v>1.431298</v>
       </c>
     </row>
   </sheetData>
@@ -23475,7 +23403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G299"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32128,35 +32056,6 @@
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="B299" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="C299" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="D299" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="E299" t="n">
-        <v>0.869098</v>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M318"/>
+  <dimension ref="A1:M321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,13 +502,13 @@
         <v>0.995383</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2723</v>
+        <v>0.6197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2723</v>
+        <v>0.6197</v>
       </c>
       <c r="I2" t="n">
-        <v>1.002723</v>
+        <v>1.006197</v>
       </c>
       <c r="J2" t="n">
         <v>0.7503</v>
@@ -536,13 +536,13 @@
         <v>0.980968</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3</v>
+        <v>-0.9925</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>-0.9925</v>
       </c>
       <c r="I3" t="n">
-        <v>1.005731</v>
+        <v>0.996211</v>
       </c>
       <c r="J3" t="n">
         <v>0.1271</v>
@@ -570,13 +570,13 @@
         <v>0.972106</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1246</v>
+        <v>0.1357</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1246</v>
+        <v>0.1357</v>
       </c>
       <c r="I4" t="n">
-        <v>1.004478</v>
+        <v>0.997563</v>
       </c>
       <c r="J4" t="n">
         <v>-0.3906</v>
@@ -604,13 +604,13 @@
         <v>0.991196</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2565</v>
+        <v>-0.1346</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2565</v>
+        <v>-0.1346</v>
       </c>
       <c r="I5" t="n">
-        <v>1.001902</v>
+        <v>0.99622</v>
       </c>
       <c r="J5" t="n">
         <v>-0.4329</v>
@@ -638,13 +638,13 @@
         <v>0.988644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7377</v>
+        <v>-0.9865</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7377</v>
+        <v>-0.9865</v>
       </c>
       <c r="I6" t="n">
-        <v>1.009293</v>
+        <v>0.986392</v>
       </c>
       <c r="J6" t="n">
         <v>0.6863</v>
@@ -672,13 +672,13 @@
         <v>1.021181</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7437</v>
+        <v>1.044</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7437</v>
+        <v>1.044</v>
       </c>
       <c r="I7" t="n">
-        <v>1.001786</v>
+        <v>0.99669</v>
       </c>
       <c r="J7" t="n">
         <v>-1.2552</v>
@@ -706,13 +706,13 @@
         <v>0.971398</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8234</v>
+        <v>0.8501</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8234</v>
+        <v>0.8501</v>
       </c>
       <c r="I8" t="n">
-        <v>1.010035</v>
+        <v>1.005163</v>
       </c>
       <c r="J8" t="n">
         <v>1.9645</v>
@@ -740,13 +740,13 @@
         <v>0.944133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8965</v>
+        <v>-0.5903</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8965</v>
+        <v>-0.5903</v>
       </c>
       <c r="I9" t="n">
-        <v>1.01909</v>
+        <v>0.999229</v>
       </c>
       <c r="J9" t="n">
         <v>1.5683</v>
@@ -774,13 +774,13 @@
         <v>0.943408</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0738</v>
+        <v>0.1705</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0738</v>
+        <v>0.1705</v>
       </c>
       <c r="I10" t="n">
-        <v>1.019842</v>
+        <v>1.000932</v>
       </c>
       <c r="J10" t="n">
         <v>0.2246</v>
@@ -808,13 +808,13 @@
         <v>0.925696</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7608</v>
+        <v>2.039</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7608</v>
+        <v>2.039</v>
       </c>
       <c r="I11" t="n">
-        <v>1.027601</v>
+        <v>1.021342</v>
       </c>
       <c r="J11" t="n">
         <v>1.9943</v>
@@ -842,13 +842,13 @@
         <v>0.940234</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1001</v>
+        <v>-0.1929</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1001</v>
+        <v>-0.1929</v>
       </c>
       <c r="I12" t="n">
-        <v>1.02863</v>
+        <v>1.019371</v>
       </c>
       <c r="J12" t="n">
         <v>0.1747</v>
@@ -876,13 +876,13 @@
         <v>0.925096</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2697</v>
+        <v>-1.1467</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2697</v>
+        <v>-1.1467</v>
       </c>
       <c r="I13" t="n">
-        <v>1.031404</v>
+        <v>1.007683</v>
       </c>
       <c r="J13" t="n">
         <v>0.3633</v>
@@ -910,13 +910,13 @@
         <v>0.946805</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5316</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5316</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.025921</v>
+        <v>1.000984</v>
       </c>
       <c r="J14" t="n">
         <v>-0.7197</v>
@@ -944,13 +944,13 @@
         <v>0.943644</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2635</v>
+        <v>1.8557</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2635</v>
+        <v>1.8557</v>
       </c>
       <c r="I15" t="n">
-        <v>1.023218</v>
+        <v>1.019559</v>
       </c>
       <c r="J15" t="n">
         <v>-1.0265</v>
@@ -978,13 +978,13 @@
         <v>0.925975</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5894</v>
+        <v>0.2391</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5894</v>
+        <v>0.2391</v>
       </c>
       <c r="I16" t="n">
-        <v>1.029249</v>
+        <v>1.021997</v>
       </c>
       <c r="J16" t="n">
         <v>1.5712</v>
@@ -1012,13 +1012,13 @@
         <v>0.946196</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7889</v>
+        <v>-1.2117</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7889</v>
+        <v>-1.2117</v>
       </c>
       <c r="I17" t="n">
-        <v>1.021129</v>
+        <v>1.009613</v>
       </c>
       <c r="J17" t="n">
         <v>-1.9458</v>
@@ -1046,13 +1046,13 @@
         <v>0.921641</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2027</v>
+        <v>-0.1661</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2027</v>
+        <v>-0.1661</v>
       </c>
       <c r="I18" t="n">
-        <v>1.03341</v>
+        <v>1.007936</v>
       </c>
       <c r="J18" t="n">
         <v>2.2605</v>
@@ -1080,13 +1080,13 @@
         <v>0.920763</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6863</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6863</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.040502</v>
+        <v>1.017512</v>
       </c>
       <c r="J19" t="n">
         <v>1.5282</v>
@@ -1114,13 +1114,13 @@
         <v>0.859859</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3804</v>
+        <v>-1.0693</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3804</v>
+        <v>-1.0693</v>
       </c>
       <c r="I20" t="n">
-        <v>1.04446</v>
+        <v>1.006632</v>
       </c>
       <c r="J20" t="n">
         <v>0.0236</v>
@@ -1148,13 +1148,13 @@
         <v>0.856441</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1449</v>
+        <v>0.8156</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1449</v>
+        <v>0.8156</v>
       </c>
       <c r="I21" t="n">
-        <v>1.045974</v>
+        <v>1.014843</v>
       </c>
       <c r="J21" t="n">
         <v>0.3994</v>
@@ -1182,13 +1182,13 @@
         <v>0.848554</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3983</v>
+        <v>-0.0603</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3983</v>
+        <v>-0.0603</v>
       </c>
       <c r="I22" t="n">
-        <v>1.05014</v>
+        <v>1.01423</v>
       </c>
       <c r="J22" t="n">
         <v>1.007</v>
@@ -1216,13 +1216,13 @@
         <v>0.840793</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3669</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3669</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.053993</v>
+        <v>1.021371</v>
       </c>
       <c r="J23" t="n">
         <v>0.7095</v>
@@ -1250,13 +1250,13 @@
         <v>0.850485</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3212</v>
+        <v>1.2079</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3212</v>
+        <v>1.2079</v>
       </c>
       <c r="I24" t="n">
-        <v>1.050607</v>
+        <v>1.033708</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5014999999999999</v>
@@ -1284,13 +1284,13 @@
         <v>0.880144</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1553</v>
+        <v>0.2249</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1553</v>
+        <v>0.2249</v>
       </c>
       <c r="I25" t="n">
-        <v>1.03847</v>
+        <v>1.036034</v>
       </c>
       <c r="J25" t="n">
         <v>-2.1951</v>
@@ -1318,13 +1318,13 @@
         <v>0.892473</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0326</v>
+        <v>1.0706</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0326</v>
+        <v>1.0706</v>
       </c>
       <c r="I26" t="n">
-        <v>1.038808</v>
+        <v>1.047126</v>
       </c>
       <c r="J26" t="n">
         <v>0.2214</v>
@@ -1352,13 +1352,13 @@
         <v>0.877175</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7863</v>
+        <v>0.8154</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7863</v>
+        <v>0.8154</v>
       </c>
       <c r="I27" t="n">
-        <v>1.046976</v>
+        <v>1.055664</v>
       </c>
       <c r="J27" t="n">
         <v>1.6365</v>
@@ -1386,13 +1386,13 @@
         <v>0.8787740000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2953</v>
+        <v>-0.7909</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2953</v>
+        <v>-0.7909</v>
       </c>
       <c r="I28" t="n">
-        <v>1.050068</v>
+        <v>1.047315</v>
       </c>
       <c r="J28" t="n">
         <v>0.286</v>
@@ -1420,13 +1420,13 @@
         <v>0.847943</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5468</v>
+        <v>-0.6515</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5468</v>
+        <v>-0.6515</v>
       </c>
       <c r="I29" t="n">
-        <v>1.05581</v>
+        <v>1.040492</v>
       </c>
       <c r="J29" t="n">
         <v>0.6859</v>
@@ -1454,13 +1454,13 @@
         <v>0.859646</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1085</v>
+        <v>-0.3477</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1085</v>
+        <v>-0.3477</v>
       </c>
       <c r="I30" t="n">
-        <v>1.054664</v>
+        <v>1.036874</v>
       </c>
       <c r="J30" t="n">
         <v>-0.2693</v>
@@ -1488,13 +1488,13 @@
         <v>0.864075</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2432</v>
+        <v>1.7556</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2432</v>
+        <v>1.7556</v>
       </c>
       <c r="I31" t="n">
-        <v>1.057229</v>
+        <v>1.055077</v>
       </c>
       <c r="J31" t="n">
         <v>0.7772</v>
@@ -1522,13 +1522,13 @@
         <v>0.873036</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0609</v>
+        <v>-0.5659</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0609</v>
+        <v>-0.5659</v>
       </c>
       <c r="I32" t="n">
-        <v>1.056585</v>
+        <v>1.049105</v>
       </c>
       <c r="J32" t="n">
         <v>-0.0308</v>
@@ -1556,13 +1556,13 @@
         <v>0.875897</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4737</v>
+        <v>-0.4005</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4737</v>
+        <v>-0.4005</v>
       </c>
       <c r="I33" t="n">
-        <v>1.061591</v>
+        <v>1.044904</v>
       </c>
       <c r="J33" t="n">
         <v>1.0936</v>
@@ -1590,13 +1590,13 @@
         <v>0.900463</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8057</v>
+        <v>0.2526</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8057</v>
+        <v>0.2526</v>
       </c>
       <c r="I34" t="n">
-        <v>1.053037</v>
+        <v>1.047543</v>
       </c>
       <c r="J34" t="n">
         <v>-1.4404</v>
@@ -1624,13 +1624,13 @@
         <v>0.8918160000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2873</v>
+        <v>0.71</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2873</v>
+        <v>0.71</v>
       </c>
       <c r="I35" t="n">
-        <v>1.050012</v>
+        <v>1.054981</v>
       </c>
       <c r="J35" t="n">
         <v>-0.633</v>
@@ -1658,13 +1658,13 @@
         <v>0.899124</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3903</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3903</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>1.05411</v>
+        <v>1.05597</v>
       </c>
       <c r="J36" t="n">
         <v>1.0237</v>
@@ -1692,13 +1692,13 @@
         <v>0.892093</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1267</v>
+        <v>0.0449</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1267</v>
+        <v>0.0449</v>
       </c>
       <c r="I37" t="n">
-        <v>1.055446</v>
+        <v>1.056444</v>
       </c>
       <c r="J37" t="n">
         <v>0.3254</v>
@@ -1726,13 +1726,13 @@
         <v>0.903988</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3316</v>
+        <v>-0.5393</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3316</v>
+        <v>-0.5393</v>
       </c>
       <c r="I38" t="n">
-        <v>1.051946</v>
+        <v>1.050747</v>
       </c>
       <c r="J38" t="n">
         <v>-0.6055</v>
@@ -1760,13 +1760,13 @@
         <v>0.911693</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4226</v>
+        <v>-0.5429</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4226</v>
+        <v>-0.5429</v>
       </c>
       <c r="I39" t="n">
-        <v>1.056391</v>
+        <v>1.045043</v>
       </c>
       <c r="J39" t="n">
         <v>1.0131</v>
@@ -1794,13 +1794,13 @@
         <v>0.926563</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.3927</v>
+        <v>-0.0319</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.3927</v>
+        <v>-0.0319</v>
       </c>
       <c r="I40" t="n">
-        <v>1.052243</v>
+        <v>1.044709</v>
       </c>
       <c r="J40" t="n">
         <v>-0.5977</v>
@@ -1828,13 +1828,13 @@
         <v>0.929041</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.8778</v>
+        <v>-1.0619</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8778</v>
+        <v>-1.0619</v>
       </c>
       <c r="I41" t="n">
-        <v>1.043006</v>
+        <v>1.033616</v>
       </c>
       <c r="J41" t="n">
         <v>-2.4099</v>
@@ -1862,13 +1862,13 @@
         <v>0.947582</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.5643</v>
+        <v>1.086</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.5643</v>
+        <v>1.086</v>
       </c>
       <c r="I42" t="n">
-        <v>1.037121</v>
+        <v>1.044841</v>
       </c>
       <c r="J42" t="n">
         <v>-0.9184</v>
@@ -1896,13 +1896,13 @@
         <v>0.948689</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5851</v>
+        <v>0.9058</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5851</v>
+        <v>0.9058</v>
       </c>
       <c r="I43" t="n">
-        <v>1.043189</v>
+        <v>1.054305</v>
       </c>
       <c r="J43" t="n">
         <v>1.508</v>
@@ -1930,13 +1930,13 @@
         <v>0.937182</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3974</v>
+        <v>2.288</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3974</v>
+        <v>2.288</v>
       </c>
       <c r="I44" t="n">
-        <v>1.039043</v>
+        <v>1.078427</v>
       </c>
       <c r="J44" t="n">
         <v>-1.0604</v>
@@ -1964,13 +1964,13 @@
         <v>0.940368</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4672</v>
+        <v>-0.0449</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4672</v>
+        <v>-0.0449</v>
       </c>
       <c r="I45" t="n">
-        <v>1.034189</v>
+        <v>1.077942</v>
       </c>
       <c r="J45" t="n">
         <v>-1.0699</v>
@@ -1998,13 +1998,13 @@
         <v>0.941619</v>
       </c>
       <c r="F46" t="n">
-        <v>0.021</v>
+        <v>-1.1426</v>
       </c>
       <c r="H46" t="n">
-        <v>0.021</v>
+        <v>-1.1426</v>
       </c>
       <c r="I46" t="n">
-        <v>1.034406</v>
+        <v>1.065625</v>
       </c>
       <c r="J46" t="n">
         <v>-0.5024</v>
@@ -2032,13 +2032,13 @@
         <v>0.949234</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3371</v>
+        <v>4.482</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3371</v>
+        <v>4.482</v>
       </c>
       <c r="I47" t="n">
-        <v>1.037893</v>
+        <v>1.113387</v>
       </c>
       <c r="J47" t="n">
         <v>0.8784999999999999</v>
@@ -2066,13 +2066,13 @@
         <v>0.954188</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2337</v>
+        <v>-0.3019</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2337</v>
+        <v>-0.3019</v>
       </c>
       <c r="I48" t="n">
-        <v>1.040318</v>
+        <v>1.110025</v>
       </c>
       <c r="J48" t="n">
         <v>0.3573</v>
@@ -2100,13 +2100,13 @@
         <v>0.9598410000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4273</v>
+        <v>1.115</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.4273</v>
+        <v>1.115</v>
       </c>
       <c r="I49" t="n">
-        <v>1.035873</v>
+        <v>1.122402</v>
       </c>
       <c r="J49" t="n">
         <v>-0.4359</v>
@@ -2134,13 +2134,13 @@
         <v>0.984331</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.1676</v>
+        <v>-4.387</v>
       </c>
       <c r="H50" t="n">
-        <v>-3.1676</v>
+        <v>-4.387</v>
       </c>
       <c r="I50" t="n">
-        <v>1.003061</v>
+        <v>1.073162</v>
       </c>
       <c r="J50" t="n">
         <v>-5.786</v>
@@ -2168,13 +2168,13 @@
         <v>0.992529</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.7203000000000001</v>
+        <v>1.6142</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.7203000000000001</v>
+        <v>1.6142</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9958360000000001</v>
+        <v>1.090485</v>
       </c>
       <c r="J51" t="n">
         <v>-2.226</v>
@@ -2202,13 +2202,13 @@
         <v>0.95275</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8143</v>
+        <v>-0.5926</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8143</v>
+        <v>-0.5926</v>
       </c>
       <c r="I52" t="n">
-        <v>1.003945</v>
+        <v>1.084023</v>
       </c>
       <c r="J52" t="n">
         <v>2.0004</v>
@@ -2236,13 +2236,13 @@
         <v>0.9514049999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8391</v>
+        <v>1.8016</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8391</v>
+        <v>1.8016</v>
       </c>
       <c r="I53" t="n">
-        <v>1.012369</v>
+        <v>1.103553</v>
       </c>
       <c r="J53" t="n">
         <v>1.8126</v>
@@ -2270,13 +2270,13 @@
         <v>0.92746</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5538</v>
+        <v>-0.5557</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5538</v>
+        <v>-0.5557</v>
       </c>
       <c r="I54" t="n">
-        <v>1.017976</v>
+        <v>1.09742</v>
       </c>
       <c r="J54" t="n">
         <v>0.5581</v>
@@ -2304,13 +2304,13 @@
         <v>0.933406</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8097</v>
+        <v>0.7169</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8097</v>
+        <v>0.7169</v>
       </c>
       <c r="I55" t="n">
-        <v>1.026218</v>
+        <v>1.105287</v>
       </c>
       <c r="J55" t="n">
         <v>1.952</v>
@@ -2338,13 +2338,13 @@
         <v>0.945194</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.129</v>
+        <v>0.7604</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.129</v>
+        <v>0.7604</v>
       </c>
       <c r="I56" t="n">
-        <v>1.024894</v>
+        <v>1.113692</v>
       </c>
       <c r="J56" t="n">
         <v>-0.1054</v>
@@ -2372,13 +2372,13 @@
         <v>0.941817</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.0581</v>
+        <v>-1.8668</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.0581</v>
+        <v>-1.8668</v>
       </c>
       <c r="I57" t="n">
-        <v>1.01405</v>
+        <v>1.092901</v>
       </c>
       <c r="J57" t="n">
         <v>-2.0165</v>
@@ -2406,13 +2406,13 @@
         <v>0.937733</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2013</v>
+        <v>0.8413</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2013</v>
+        <v>0.8413</v>
       </c>
       <c r="I58" t="n">
-        <v>1.016091</v>
+        <v>1.102096</v>
       </c>
       <c r="J58" t="n">
         <v>0.5756</v>
@@ -2440,13 +2440,13 @@
         <v>0.9456639999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0527</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.0527</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>1.015556</v>
+        <v>1.103054</v>
       </c>
       <c r="J59" t="n">
         <v>-0.2037</v>
@@ -2474,13 +2474,13 @@
         <v>0.93424</v>
       </c>
       <c r="F60" t="n">
-        <v>1.1481</v>
+        <v>1.2856</v>
       </c>
       <c r="H60" t="n">
-        <v>1.1481</v>
+        <v>1.2856</v>
       </c>
       <c r="I60" t="n">
-        <v>1.027215</v>
+        <v>1.117235</v>
       </c>
       <c r="J60" t="n">
         <v>1.9633</v>
@@ -2508,13 +2508,13 @@
         <v>0.94079</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1.8792</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1.8792</v>
       </c>
       <c r="I61" t="n">
-        <v>1.027215</v>
+        <v>1.13823</v>
       </c>
       <c r="J61" t="n">
         <v>0.0094</v>
@@ -2542,13 +2542,13 @@
         <v>0.939905</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5617</v>
+        <v>0.1634</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5617</v>
+        <v>0.1634</v>
       </c>
       <c r="I62" t="n">
-        <v>1.032985</v>
+        <v>1.14009</v>
       </c>
       <c r="J62" t="n">
         <v>1.0961</v>
@@ -2576,13 +2576,13 @@
         <v>0.953615</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5570000000000001</v>
+        <v>2.2595</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5570000000000001</v>
+        <v>2.2595</v>
       </c>
       <c r="I63" t="n">
-        <v>1.027231</v>
+        <v>1.165851</v>
       </c>
       <c r="J63" t="n">
         <v>-0.9599</v>
@@ -2610,13 +2610,13 @@
         <v>0.950933</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1368</v>
+        <v>-2.0949</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1368</v>
+        <v>-2.0949</v>
       </c>
       <c r="I64" t="n">
-        <v>1.028637</v>
+        <v>1.141427</v>
       </c>
       <c r="J64" t="n">
         <v>0.2174</v>
@@ -2644,13 +2644,13 @@
         <v>0.952421</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6647</v>
+        <v>-0.7179</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6647</v>
+        <v>-0.7179</v>
       </c>
       <c r="I65" t="n">
-        <v>1.021799</v>
+        <v>1.133232</v>
       </c>
       <c r="J65" t="n">
         <v>-1.2807</v>
@@ -2678,13 +2678,13 @@
         <v>0.948939</v>
       </c>
       <c r="F66" t="n">
-        <v>0.488</v>
+        <v>-0.1499</v>
       </c>
       <c r="H66" t="n">
-        <v>0.488</v>
+        <v>-0.1499</v>
       </c>
       <c r="I66" t="n">
-        <v>1.026786</v>
+        <v>1.131534</v>
       </c>
       <c r="J66" t="n">
         <v>1.1635</v>
@@ -2712,13 +2712,13 @@
         <v>0.934599</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6592</v>
+        <v>-0.105</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6592</v>
+        <v>-0.105</v>
       </c>
       <c r="I67" t="n">
-        <v>1.033554</v>
+        <v>1.130345</v>
       </c>
       <c r="J67" t="n">
         <v>1.4137</v>
@@ -2746,13 +2746,13 @@
         <v>0.92394</v>
       </c>
       <c r="F68" t="n">
-        <v>1.077</v>
+        <v>0.2366</v>
       </c>
       <c r="H68" t="n">
-        <v>1.077</v>
+        <v>0.2366</v>
       </c>
       <c r="I68" t="n">
-        <v>1.044686</v>
+        <v>1.13302</v>
       </c>
       <c r="J68" t="n">
         <v>2.2439</v>
@@ -2780,13 +2780,13 @@
         <v>0.926893</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.2508</v>
+        <v>-0.5456</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.2508</v>
+        <v>-0.5456</v>
       </c>
       <c r="I69" t="n">
-        <v>1.042066</v>
+        <v>1.126839</v>
       </c>
       <c r="J69" t="n">
         <v>0.1342</v>
@@ -2814,13 +2814,13 @@
         <v>0.930716</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2635</v>
+        <v>-0.0331</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2635</v>
+        <v>-0.0331</v>
       </c>
       <c r="I70" t="n">
-        <v>1.044811</v>
+        <v>1.126466</v>
       </c>
       <c r="J70" t="n">
         <v>0.5344</v>
@@ -2848,13 +2848,13 @@
         <v>0.953742</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6509</v>
+        <v>-0.059</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6509</v>
+        <v>-0.059</v>
       </c>
       <c r="I71" t="n">
-        <v>1.038011</v>
+        <v>1.125801</v>
       </c>
       <c r="J71" t="n">
         <v>-1.317</v>
@@ -2882,13 +2882,13 @@
         <v>0.952387</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2327</v>
+        <v>-1.0044</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2327</v>
+        <v>-1.0044</v>
       </c>
       <c r="I72" t="n">
-        <v>1.040426</v>
+        <v>1.114494</v>
       </c>
       <c r="J72" t="n">
         <v>0.4404</v>
@@ -2916,13 +2916,13 @@
         <v>0.960504</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.2593</v>
+        <v>0.7241</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.2593</v>
+        <v>0.7241</v>
       </c>
       <c r="I73" t="n">
-        <v>1.037728</v>
+        <v>1.122563</v>
       </c>
       <c r="J73" t="n">
         <v>-0.4494</v>
@@ -2950,13 +2950,13 @@
         <v>0.9620339999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.6073</v>
+        <v>-0.6825</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.6073</v>
+        <v>-0.6825</v>
       </c>
       <c r="I74" t="n">
-        <v>1.031426</v>
+        <v>1.114901</v>
       </c>
       <c r="J74" t="n">
         <v>-1.096</v>
@@ -2984,13 +2984,13 @@
         <v>0.970234</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.4133</v>
+        <v>3.8527</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.4133</v>
+        <v>3.8527</v>
       </c>
       <c r="I75" t="n">
-        <v>1.027163</v>
+        <v>1.157855</v>
       </c>
       <c r="J75" t="n">
         <v>-0.402</v>
@@ -3018,13 +3018,13 @@
         <v>0.970401</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5416</v>
+        <v>2.7165</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5416</v>
+        <v>2.7165</v>
       </c>
       <c r="I76" t="n">
-        <v>1.032726</v>
+        <v>1.189308</v>
       </c>
       <c r="J76" t="n">
         <v>1.3647</v>
@@ -3052,13 +3052,13 @@
         <v>0.972963</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4127</v>
+        <v>-0.8666</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4127</v>
+        <v>-0.8666</v>
       </c>
       <c r="I77" t="n">
-        <v>1.036989</v>
+        <v>1.179001</v>
       </c>
       <c r="J77" t="n">
         <v>1.1661</v>
@@ -3086,13 +3086,13 @@
         <v>0.973422</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1761</v>
+        <v>1.0501</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1761</v>
+        <v>1.0501</v>
       </c>
       <c r="I78" t="n">
-        <v>1.038815</v>
+        <v>1.191382</v>
       </c>
       <c r="J78" t="n">
         <v>0.2972</v>
@@ -3120,13 +3120,13 @@
         <v>0.983</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.517</v>
+        <v>0.5142</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.517</v>
+        <v>0.5142</v>
       </c>
       <c r="I79" t="n">
-        <v>1.033444</v>
+        <v>1.197508</v>
       </c>
       <c r="J79" t="n">
         <v>-1.2673</v>
@@ -3154,13 +3154,13 @@
         <v>0.9859830000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.5848</v>
+        <v>-0.389</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.5848</v>
+        <v>-0.389</v>
       </c>
       <c r="I80" t="n">
-        <v>1.0274</v>
+        <v>1.19285</v>
       </c>
       <c r="J80" t="n">
         <v>-1.1669</v>
@@ -3188,13 +3188,13 @@
         <v>0.986371</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.19</v>
+        <v>3.5006</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.19</v>
+        <v>3.5006</v>
       </c>
       <c r="I81" t="n">
-        <v>1.025448</v>
+        <v>1.234607</v>
       </c>
       <c r="J81" t="n">
         <v>-0.3692</v>
@@ -3222,13 +3222,13 @@
         <v>0.978015</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7475000000000001</v>
+        <v>-1.3811</v>
       </c>
       <c r="H82" t="n">
-        <v>0.7475000000000001</v>
+        <v>-1.3811</v>
       </c>
       <c r="I82" t="n">
-        <v>1.033114</v>
+        <v>1.217556</v>
       </c>
       <c r="J82" t="n">
         <v>1.826</v>
@@ -3256,13 +3256,13 @@
         <v>0.984773</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1664</v>
+        <v>1.9706</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1664</v>
+        <v>1.9706</v>
       </c>
       <c r="I83" t="n">
-        <v>1.034833</v>
+        <v>1.241549</v>
       </c>
       <c r="J83" t="n">
         <v>0.7407</v>
@@ -3290,13 +3290,13 @@
         <v>0.990221</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.0945</v>
+        <v>-1.1403</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.0945</v>
+        <v>-1.1403</v>
       </c>
       <c r="I84" t="n">
-        <v>1.033855</v>
+        <v>1.227392</v>
       </c>
       <c r="J84" t="n">
         <v>-0.2581</v>
@@ -3324,13 +3324,13 @@
         <v>0.976</v>
       </c>
       <c r="F85" t="n">
-        <v>0.742</v>
+        <v>1.0271</v>
       </c>
       <c r="H85" t="n">
-        <v>0.742</v>
+        <v>1.0271</v>
       </c>
       <c r="I85" t="n">
-        <v>1.041526</v>
+        <v>1.239998</v>
       </c>
       <c r="J85" t="n">
         <v>1.1667</v>
@@ -3358,13 +3358,13 @@
         <v>0.9861</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.4598</v>
+        <v>0.2559</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.4598</v>
+        <v>0.2559</v>
       </c>
       <c r="I86" t="n">
-        <v>1.036737</v>
+        <v>1.243172</v>
       </c>
       <c r="J86" t="n">
         <v>-1.2733</v>
@@ -3392,13 +3392,13 @@
         <v>0.984975</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3095</v>
+        <v>2.7437</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3095</v>
+        <v>2.7437</v>
       </c>
       <c r="I87" t="n">
-        <v>1.039946</v>
+        <v>1.277281</v>
       </c>
       <c r="J87" t="n">
         <v>0.5158</v>
@@ -3426,13 +3426,13 @@
         <v>0.9832959999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2784</v>
+        <v>-1.3537</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2784</v>
+        <v>-1.3537</v>
       </c>
       <c r="I88" t="n">
-        <v>1.042841</v>
+        <v>1.25999</v>
       </c>
       <c r="J88" t="n">
         <v>0.6211</v>
@@ -3460,13 +3460,13 @@
         <v>0.9674</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3053</v>
+        <v>-2.1865</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3053</v>
+        <v>-2.1865</v>
       </c>
       <c r="I89" t="n">
-        <v>1.046025</v>
+        <v>1.23244</v>
       </c>
       <c r="J89" t="n">
         <v>0.3641</v>
@@ -3494,13 +3494,13 @@
         <v>0.971815</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.081</v>
+        <v>0.4585</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.081</v>
+        <v>0.4585</v>
       </c>
       <c r="I90" t="n">
-        <v>1.045177</v>
+        <v>1.238091</v>
       </c>
       <c r="J90" t="n">
         <v>-0.1005</v>
@@ -3528,13 +3528,13 @@
         <v>0.967851</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6133999999999999</v>
+        <v>2.3691</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6133999999999999</v>
+        <v>2.3691</v>
       </c>
       <c r="I91" t="n">
-        <v>1.051589</v>
+        <v>1.267422</v>
       </c>
       <c r="J91" t="n">
         <v>1.1466</v>
@@ -3562,13 +3562,13 @@
         <v>0.981356</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.1745</v>
+        <v>0.9951</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.1745</v>
+        <v>0.9951</v>
       </c>
       <c r="I92" t="n">
-        <v>1.049754</v>
+        <v>1.280034</v>
       </c>
       <c r="J92" t="n">
         <v>-0.3078</v>
@@ -3596,13 +3596,13 @@
         <v>0.986367</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.2274</v>
+        <v>-1.3122</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.2274</v>
+        <v>-1.3122</v>
       </c>
       <c r="I93" t="n">
-        <v>1.047366</v>
+        <v>1.263238</v>
       </c>
       <c r="J93" t="n">
         <v>-0.3135</v>
@@ -3630,13 +3630,13 @@
         <v>0.989364</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1524</v>
+        <v>0.4938</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1524</v>
+        <v>0.4938</v>
       </c>
       <c r="I94" t="n">
-        <v>1.048963</v>
+        <v>1.269476</v>
       </c>
       <c r="J94" t="n">
         <v>0.3177</v>
@@ -3664,13 +3664,13 @@
         <v>0.984457</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.6387</v>
+        <v>-1.5669</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.6387</v>
+        <v>-1.5669</v>
       </c>
       <c r="I95" t="n">
-        <v>1.042263</v>
+        <v>1.249585</v>
       </c>
       <c r="J95" t="n">
         <v>-1.3119</v>
@@ -3698,13 +3698,13 @@
         <v>0.988765</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4124</v>
+        <v>-0.2825</v>
       </c>
       <c r="H96" t="n">
-        <v>0.4124</v>
+        <v>-0.2825</v>
       </c>
       <c r="I96" t="n">
-        <v>1.046561</v>
+        <v>1.246055</v>
       </c>
       <c r="J96" t="n">
         <v>0.8215</v>
@@ -3732,13 +3732,13 @@
         <v>0.996247</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.0276</v>
+        <v>-1.3502</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.0276</v>
+        <v>-1.3502</v>
       </c>
       <c r="I97" t="n">
-        <v>1.046272</v>
+        <v>1.229232</v>
       </c>
       <c r="J97" t="n">
         <v>-0.0535</v>
@@ -3766,13 +3766,13 @@
         <v>0.989861</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.0256</v>
+        <v>-1.0533</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.0256</v>
+        <v>-1.0533</v>
       </c>
       <c r="I98" t="n">
-        <v>1.046004</v>
+        <v>1.216284</v>
       </c>
       <c r="J98" t="n">
         <v>-0.3982</v>
@@ -3800,13 +3800,13 @@
         <v>0.988784</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.511</v>
+        <v>-1.4814</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.511</v>
+        <v>-1.4814</v>
       </c>
       <c r="I99" t="n">
-        <v>1.040659</v>
+        <v>1.198266</v>
       </c>
       <c r="J99" t="n">
         <v>-1.1281</v>
@@ -3834,13 +3834,13 @@
         <v>0.995638</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.4667</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.4667</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>1.035803</v>
+        <v>1.206039</v>
       </c>
       <c r="J100" t="n">
         <v>-1.0024</v>
@@ -3868,13 +3868,13 @@
         <v>0.994412</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7181</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7181</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>1.043241</v>
+        <v>1.215588</v>
       </c>
       <c r="J101" t="n">
         <v>1.6494</v>
@@ -3902,13 +3902,13 @@
         <v>0.979781</v>
       </c>
       <c r="F102" t="n">
-        <v>0.5194</v>
+        <v>0.0616</v>
       </c>
       <c r="H102" t="n">
-        <v>0.5194</v>
+        <v>0.0616</v>
       </c>
       <c r="I102" t="n">
-        <v>1.048659</v>
+        <v>1.216337</v>
       </c>
       <c r="J102" t="n">
         <v>1.0267</v>
@@ -3936,13 +3936,13 @@
         <v>0.966199</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.144</v>
+        <v>-1.6626</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.144</v>
+        <v>-1.6626</v>
       </c>
       <c r="I103" t="n">
-        <v>1.047149</v>
+        <v>1.196114</v>
       </c>
       <c r="J103" t="n">
         <v>-0.4332</v>
@@ -3970,13 +3970,13 @@
         <v>0.9719370000000001</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.0183</v>
+        <v>-0.4257</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.0183</v>
+        <v>-0.4257</v>
       </c>
       <c r="I104" t="n">
-        <v>1.046958</v>
+        <v>1.191023</v>
       </c>
       <c r="J104" t="n">
         <v>0.1714</v>
@@ -4004,13 +4004,13 @@
         <v>0.9685780000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4736</v>
+        <v>0.6433</v>
       </c>
       <c r="H105" t="n">
-        <v>0.4736</v>
+        <v>0.6433</v>
       </c>
       <c r="I105" t="n">
-        <v>1.051916</v>
+        <v>1.198684</v>
       </c>
       <c r="J105" t="n">
         <v>1.0836</v>
@@ -4038,13 +4038,13 @@
         <v>0.952616</v>
       </c>
       <c r="F106" t="n">
-        <v>0.5218</v>
+        <v>0.1281</v>
       </c>
       <c r="H106" t="n">
-        <v>0.5218</v>
+        <v>0.1281</v>
       </c>
       <c r="I106" t="n">
-        <v>1.057405</v>
+        <v>1.20022</v>
       </c>
       <c r="J106" t="n">
         <v>1.1737</v>
@@ -4072,13 +4072,13 @@
         <v>0.968557</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0179</v>
+        <v>2.8914</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0179</v>
+        <v>2.8914</v>
       </c>
       <c r="I107" t="n">
-        <v>1.057594</v>
+        <v>1.234922</v>
       </c>
       <c r="J107" t="n">
         <v>0.1143</v>
@@ -4106,13 +4106,13 @@
         <v>0.9873459999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.6146</v>
+        <v>-0.2144</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.6146</v>
+        <v>-0.2144</v>
       </c>
       <c r="I108" t="n">
-        <v>1.051094</v>
+        <v>1.232275</v>
       </c>
       <c r="J108" t="n">
         <v>-0.8706</v>
@@ -4140,13 +4140,13 @@
         <v>0.984961</v>
       </c>
       <c r="F109" t="n">
-        <v>0.095</v>
+        <v>1.5642</v>
       </c>
       <c r="H109" t="n">
-        <v>0.095</v>
+        <v>1.5642</v>
       </c>
       <c r="I109" t="n">
-        <v>1.052093</v>
+        <v>1.25155</v>
       </c>
       <c r="J109" t="n">
         <v>0.0955</v>
@@ -4174,13 +4174,13 @@
         <v>0.990094</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.5999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.5999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>1.045781</v>
+        <v>1.250667</v>
       </c>
       <c r="J110" t="n">
         <v>-1.4338</v>
@@ -4208,13 +4208,13 @@
         <v>1.000967</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3921</v>
+        <v>-0.6533</v>
       </c>
       <c r="H111" t="n">
-        <v>0.3921</v>
+        <v>-0.6533</v>
       </c>
       <c r="I111" t="n">
-        <v>1.049882</v>
+        <v>1.242497</v>
       </c>
       <c r="J111" t="n">
         <v>1.0995</v>
@@ -4242,13 +4242,13 @@
         <v>0.986503</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2334</v>
+        <v>-0.3359</v>
       </c>
       <c r="H112" t="n">
-        <v>0.2334</v>
+        <v>-0.3359</v>
       </c>
       <c r="I112" t="n">
-        <v>1.052332</v>
+        <v>1.238323</v>
       </c>
       <c r="J112" t="n">
         <v>0.4481</v>
@@ -4276,13 +4276,13 @@
         <v>0.99849</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.0562</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.0562</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>1.051741</v>
+        <v>1.22928</v>
       </c>
       <c r="J113" t="n">
         <v>0.0948</v>
@@ -4310,13 +4310,13 @@
         <v>1.007874</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.2669</v>
+        <v>0.2895</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.2669</v>
+        <v>0.2895</v>
       </c>
       <c r="I114" t="n">
-        <v>1.048934</v>
+        <v>1.232839</v>
       </c>
       <c r="J114" t="n">
         <v>-0.5128</v>
@@ -4344,13 +4344,13 @@
         <v>0.9856279999999999</v>
       </c>
       <c r="F115" t="n">
-        <v>0.436</v>
+        <v>0.5243</v>
       </c>
       <c r="H115" t="n">
-        <v>0.436</v>
+        <v>0.5243</v>
       </c>
       <c r="I115" t="n">
-        <v>1.053507</v>
+        <v>1.239302</v>
       </c>
       <c r="J115" t="n">
         <v>0.3578</v>
@@ -4378,13 +4378,13 @@
         <v>0.992503</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2089</v>
+        <v>0.96</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2089</v>
+        <v>0.96</v>
       </c>
       <c r="I116" t="n">
-        <v>1.055708</v>
+        <v>1.251199</v>
       </c>
       <c r="J116" t="n">
         <v>0.5653</v>
@@ -4412,13 +4412,13 @@
         <v>0.97711</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.1295</v>
+        <v>-0.9019</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.1295</v>
+        <v>-0.9019</v>
       </c>
       <c r="I117" t="n">
-        <v>1.054341</v>
+        <v>1.239914</v>
       </c>
       <c r="J117" t="n">
         <v>-0.7213000000000001</v>
@@ -4446,13 +4446,13 @@
         <v>0.971547</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4867</v>
+        <v>1.5676</v>
       </c>
       <c r="H118" t="n">
-        <v>0.4867</v>
+        <v>1.5676</v>
       </c>
       <c r="I118" t="n">
-        <v>1.059472</v>
+        <v>1.259352</v>
       </c>
       <c r="J118" t="n">
         <v>0.9364</v>
@@ -4480,13 +4480,13 @@
         <v>0.962906</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2691</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2691</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>1.062323</v>
+        <v>1.258128</v>
       </c>
       <c r="J119" t="n">
         <v>0.4056</v>
@@ -4514,13 +4514,13 @@
         <v>0.9644160000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.2571</v>
+        <v>0.4319</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.2571</v>
+        <v>0.4319</v>
       </c>
       <c r="I120" t="n">
-        <v>1.059592</v>
+        <v>1.263562</v>
       </c>
       <c r="J120" t="n">
         <v>-0.5344</v>
@@ -4548,13 +4548,13 @@
         <v>0.976169</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1164</v>
+        <v>0.1362</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1164</v>
+        <v>0.1362</v>
       </c>
       <c r="I121" t="n">
-        <v>1.060825</v>
+        <v>1.265282</v>
       </c>
       <c r="J121" t="n">
         <v>0.6062</v>
@@ -4582,13 +4582,13 @@
         <v>0.984123</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.3541</v>
+        <v>-0.9969</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.3541</v>
+        <v>-0.9969</v>
       </c>
       <c r="I122" t="n">
-        <v>1.057069</v>
+        <v>1.252669</v>
       </c>
       <c r="J122" t="n">
         <v>-0.8092</v>
@@ -4616,13 +4616,13 @@
         <v>0.976114</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.3383</v>
+        <v>0.0313</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.3383</v>
+        <v>0.0313</v>
       </c>
       <c r="I123" t="n">
-        <v>1.053493</v>
+        <v>1.253061</v>
       </c>
       <c r="J123" t="n">
         <v>-0.9043</v>
@@ -4650,13 +4650,13 @@
         <v>0.968746</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1567</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1567</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>1.055144</v>
+        <v>1.261771</v>
       </c>
       <c r="J124" t="n">
         <v>0.4097</v>
@@ -4684,13 +4684,13 @@
         <v>0.942407</v>
       </c>
       <c r="F125" t="n">
-        <v>0.3774</v>
+        <v>0.1355</v>
       </c>
       <c r="H125" t="n">
-        <v>0.3774</v>
+        <v>0.1355</v>
       </c>
       <c r="I125" t="n">
-        <v>1.059126</v>
+        <v>1.263482</v>
       </c>
       <c r="J125" t="n">
         <v>0.8246</v>
@@ -4718,13 +4718,13 @@
         <v>0.9313360000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>0.1563</v>
+        <v>0.7469</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1563</v>
+        <v>0.7469</v>
       </c>
       <c r="I126" t="n">
-        <v>1.060781</v>
+        <v>1.272918</v>
       </c>
       <c r="J126" t="n">
         <v>0.5017</v>
@@ -4752,13 +4752,13 @@
         <v>0.91745</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1924</v>
+        <v>1.5227</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1924</v>
+        <v>1.5227</v>
       </c>
       <c r="I127" t="n">
-        <v>1.062822</v>
+        <v>1.292301</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0227</v>
@@ -4786,13 +4786,13 @@
         <v>0.929444</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.5309</v>
+        <v>0.9935</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.5309</v>
+        <v>0.9935</v>
       </c>
       <c r="I128" t="n">
-        <v>1.05718</v>
+        <v>1.30514</v>
       </c>
       <c r="J128" t="n">
         <v>-0.8772</v>
@@ -4820,13 +4820,13 @@
         <v>0.922726</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7745</v>
+        <v>1.7175</v>
       </c>
       <c r="H129" t="n">
-        <v>0.7745</v>
+        <v>1.7175</v>
       </c>
       <c r="I129" t="n">
-        <v>1.065367</v>
+        <v>1.327556</v>
       </c>
       <c r="J129" t="n">
         <v>1.1774</v>
@@ -4854,13 +4854,13 @@
         <v>0.9324750000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>0.3708</v>
+        <v>0.4293</v>
       </c>
       <c r="H130" t="n">
-        <v>0.3708</v>
+        <v>0.4293</v>
       </c>
       <c r="I130" t="n">
-        <v>1.069318</v>
+        <v>1.333255</v>
       </c>
       <c r="J130" t="n">
         <v>0.9656</v>
@@ -4888,13 +4888,13 @@
         <v>0.925492</v>
       </c>
       <c r="F131" t="n">
-        <v>0.5425</v>
+        <v>-0.4146</v>
       </c>
       <c r="H131" t="n">
-        <v>0.5425</v>
+        <v>-0.4146</v>
       </c>
       <c r="I131" t="n">
-        <v>1.075119</v>
+        <v>1.327727</v>
       </c>
       <c r="J131" t="n">
         <v>1.1729</v>
@@ -4922,13 +4922,13 @@
         <v>0.9314170000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.0514</v>
+        <v>-1.186</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.0514</v>
+        <v>-1.186</v>
       </c>
       <c r="I132" t="n">
-        <v>1.074566</v>
+        <v>1.311981</v>
       </c>
       <c r="J132" t="n">
         <v>0.0956</v>
@@ -4956,13 +4956,13 @@
         <v>0.9319190000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4765</v>
+        <v>-1.8894</v>
       </c>
       <c r="H133" t="n">
-        <v>0.4765</v>
+        <v>-1.8894</v>
       </c>
       <c r="I133" t="n">
-        <v>1.079687</v>
+        <v>1.287193</v>
       </c>
       <c r="J133" t="n">
         <v>0.9485</v>
@@ -4990,13 +4990,13 @@
         <v>0.934864</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0408</v>
+        <v>-1.0301</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0408</v>
+        <v>-1.0301</v>
       </c>
       <c r="I134" t="n">
-        <v>1.080127</v>
+        <v>1.273933</v>
       </c>
       <c r="J134" t="n">
         <v>0.0428</v>
@@ -5024,13 +5024,13 @@
         <v>0.948312</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.1745</v>
+        <v>0.9569</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.1745</v>
+        <v>0.9569</v>
       </c>
       <c r="I135" t="n">
-        <v>1.078242</v>
+        <v>1.286123</v>
       </c>
       <c r="J135" t="n">
         <v>0.0098</v>
@@ -5058,13 +5058,13 @@
         <v>0.938645</v>
       </c>
       <c r="F136" t="n">
-        <v>0.6199</v>
+        <v>1.181</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6199</v>
+        <v>1.181</v>
       </c>
       <c r="I136" t="n">
-        <v>1.084926</v>
+        <v>1.301312</v>
       </c>
       <c r="J136" t="n">
         <v>1.2768</v>
@@ -5092,13 +5092,13 @@
         <v>0.925953</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-1.5699</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-1.5699</v>
       </c>
       <c r="I137" t="n">
-        <v>1.084109</v>
+        <v>1.280882</v>
       </c>
       <c r="J137" t="n">
         <v>-0.4595</v>
@@ -5126,13 +5126,13 @@
         <v>0.914293</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4011</v>
+        <v>-0.407</v>
       </c>
       <c r="H138" t="n">
-        <v>0.4011</v>
+        <v>-0.407</v>
       </c>
       <c r="I138" t="n">
-        <v>1.088458</v>
+        <v>1.275669</v>
       </c>
       <c r="J138" t="n">
         <v>0.2489</v>
@@ -5160,13 +5160,13 @@
         <v>0.898718</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.4635</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-1.4635</v>
       </c>
       <c r="I139" t="n">
-        <v>1.080717</v>
+        <v>1.257</v>
       </c>
       <c r="J139" t="n">
         <v>-1.7899</v>
@@ -5194,13 +5194,13 @@
         <v>0.887995</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7179</v>
+        <v>-0.1366</v>
       </c>
       <c r="H140" t="n">
-        <v>0.7179</v>
+        <v>-0.1366</v>
       </c>
       <c r="I140" t="n">
-        <v>1.088475</v>
+        <v>1.255283</v>
       </c>
       <c r="J140" t="n">
         <v>1.3358</v>
@@ -5228,13 +5228,13 @@
         <v>0.867319</v>
       </c>
       <c r="F141" t="n">
-        <v>0.6685</v>
+        <v>-0.3527</v>
       </c>
       <c r="H141" t="n">
-        <v>0.6685</v>
+        <v>-0.3527</v>
       </c>
       <c r="I141" t="n">
-        <v>1.095752</v>
+        <v>1.250855</v>
       </c>
       <c r="J141" t="n">
         <v>1.2608</v>
@@ -5262,13 +5262,13 @@
         <v>0.87617</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3639</v>
+        <v>0.6294</v>
       </c>
       <c r="H142" t="n">
-        <v>0.3639</v>
+        <v>0.6294</v>
       </c>
       <c r="I142" t="n">
-        <v>1.099739</v>
+        <v>1.258728</v>
       </c>
       <c r="J142" t="n">
         <v>1.0733</v>
@@ -5296,13 +5296,13 @@
         <v>0.854522</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.3266</v>
+        <v>-1.3894</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.3266</v>
+        <v>-1.3894</v>
       </c>
       <c r="I143" t="n">
-        <v>1.096147</v>
+        <v>1.241239</v>
       </c>
       <c r="J143" t="n">
         <v>-0.7135</v>
@@ -5330,13 +5330,13 @@
         <v>0.858359</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.6218</v>
+        <v>-0.1671</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.6218</v>
+        <v>-0.1671</v>
       </c>
       <c r="I144" t="n">
-        <v>1.089331</v>
+        <v>1.239166</v>
       </c>
       <c r="J144" t="n">
         <v>-1.1343</v>
@@ -5364,13 +5364,13 @@
         <v>0.783128</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.4461</v>
+        <v>-2.0089</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.4461</v>
+        <v>-2.0089</v>
       </c>
       <c r="I145" t="n">
-        <v>1.084472</v>
+        <v>1.214272</v>
       </c>
       <c r="J145" t="n">
         <v>-1.4048</v>
@@ -5398,13 +5398,13 @@
         <v>0.76385</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.3031</v>
+        <v>-0.7312</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.3031</v>
+        <v>-0.7312</v>
       </c>
       <c r="I146" t="n">
-        <v>1.081185</v>
+        <v>1.205394</v>
       </c>
       <c r="J146" t="n">
         <v>-0.913</v>
@@ -5432,13 +5432,13 @@
         <v>0.772981</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.0216</v>
+        <v>-0.319</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.0216</v>
+        <v>-0.319</v>
       </c>
       <c r="I147" t="n">
-        <v>1.080951</v>
+        <v>1.201549</v>
       </c>
       <c r="J147" t="n">
         <v>0.3887</v>
@@ -5466,13 +5466,13 @@
         <v>0.758015</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.2534</v>
+        <v>-1.5471</v>
       </c>
       <c r="H148" t="n">
-        <v>-0.2534</v>
+        <v>-1.5471</v>
       </c>
       <c r="I148" t="n">
-        <v>1.078212</v>
+        <v>1.18296</v>
       </c>
       <c r="J148" t="n">
         <v>-0.8247</v>
@@ -5500,13 +5500,13 @@
         <v>0.704797</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.2825</v>
+        <v>-2.4848</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.2825</v>
+        <v>-2.4848</v>
       </c>
       <c r="I149" t="n">
-        <v>1.075166</v>
+        <v>1.153566</v>
       </c>
       <c r="J149" t="n">
         <v>-1.0446</v>
@@ -5534,13 +5534,13 @@
         <v>0.716046</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.6397</v>
+        <v>0.0554</v>
       </c>
       <c r="H150" t="n">
-        <v>-0.6397</v>
+        <v>0.0554</v>
       </c>
       <c r="I150" t="n">
-        <v>1.068288</v>
+        <v>1.154205</v>
       </c>
       <c r="J150" t="n">
         <v>-1.0836</v>
@@ -5568,13 +5568,13 @@
         <v>0.705873</v>
       </c>
       <c r="F151" t="n">
-        <v>0.1704</v>
+        <v>0.6914</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1704</v>
+        <v>0.6914</v>
       </c>
       <c r="I151" t="n">
-        <v>1.070109</v>
+        <v>1.162185</v>
       </c>
       <c r="J151" t="n">
         <v>0.4707</v>
@@ -5602,13 +5602,13 @@
         <v>0.723115</v>
       </c>
       <c r="F152" t="n">
-        <v>-1.0037</v>
+        <v>0.1792</v>
       </c>
       <c r="H152" t="n">
-        <v>-1.0037</v>
+        <v>0.1792</v>
       </c>
       <c r="I152" t="n">
-        <v>1.059368</v>
+        <v>1.164268</v>
       </c>
       <c r="J152" t="n">
         <v>-1.2533</v>
@@ -5636,13 +5636,13 @@
         <v>0.72889</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.4315</v>
+        <v>0.152</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.4315</v>
+        <v>0.152</v>
       </c>
       <c r="I153" t="n">
-        <v>1.054797</v>
+        <v>1.166038</v>
       </c>
       <c r="J153" t="n">
         <v>-1.3454</v>
@@ -5670,13 +5670,13 @@
         <v>0.772922</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.052</v>
+        <v>2.1793</v>
       </c>
       <c r="H154" t="n">
-        <v>-0.052</v>
+        <v>2.1793</v>
       </c>
       <c r="I154" t="n">
-        <v>1.054248</v>
+        <v>1.191449</v>
       </c>
       <c r="J154" t="n">
         <v>0.6763</v>
@@ -5704,13 +5704,13 @@
         <v>0.749125</v>
       </c>
       <c r="F155" t="n">
-        <v>0.3514</v>
+        <v>-0.8462</v>
       </c>
       <c r="H155" t="n">
-        <v>0.3514</v>
+        <v>-0.8462</v>
       </c>
       <c r="I155" t="n">
-        <v>1.057953</v>
+        <v>1.181367</v>
       </c>
       <c r="J155" t="n">
         <v>0.5674</v>
@@ -5738,13 +5738,13 @@
         <v>0.750589</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3346</v>
+        <v>0.4405</v>
       </c>
       <c r="H156" t="n">
-        <v>0.3346</v>
+        <v>0.4405</v>
       </c>
       <c r="I156" t="n">
-        <v>1.061493</v>
+        <v>1.18657</v>
       </c>
       <c r="J156" t="n">
         <v>1.0557</v>
@@ -5772,13 +5772,13 @@
         <v>0.77012</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.4485</v>
+        <v>-0.3065</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.4485</v>
+        <v>-0.3065</v>
       </c>
       <c r="I157" t="n">
-        <v>1.056732</v>
+        <v>1.182933</v>
       </c>
       <c r="J157" t="n">
         <v>-0.5908</v>
@@ -5806,13 +5806,13 @@
         <v>0.757961</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0202</v>
+        <v>-0.7684</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0202</v>
+        <v>-0.7684</v>
       </c>
       <c r="I158" t="n">
-        <v>1.056946</v>
+        <v>1.173843</v>
       </c>
       <c r="J158" t="n">
         <v>0.115</v>
@@ -5840,13 +5840,13 @@
         <v>0.720681</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.0114</v>
+        <v>-1.8021</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.0114</v>
+        <v>-1.8021</v>
       </c>
       <c r="I159" t="n">
-        <v>1.056825</v>
+        <v>1.152689</v>
       </c>
       <c r="J159" t="n">
         <v>-0.3936</v>
@@ -5874,13 +5874,13 @@
         <v>0.710296</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3761</v>
+        <v>-0.0017</v>
       </c>
       <c r="H160" t="n">
-        <v>0.3761</v>
+        <v>-0.0017</v>
       </c>
       <c r="I160" t="n">
-        <v>1.0608</v>
+        <v>1.152669</v>
       </c>
       <c r="J160" t="n">
         <v>0.5817</v>
@@ -5908,13 +5908,13 @@
         <v>0.7066170000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.1711</v>
+        <v>-0.0775</v>
       </c>
       <c r="H161" t="n">
-        <v>-0.1711</v>
+        <v>-0.0775</v>
       </c>
       <c r="I161" t="n">
-        <v>1.058985</v>
+        <v>1.151776</v>
       </c>
       <c r="J161" t="n">
         <v>-0.3514</v>
@@ -5942,13 +5942,13 @@
         <v>0.697034</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7454</v>
+        <v>-0.2897</v>
       </c>
       <c r="H162" t="n">
-        <v>0.7454</v>
+        <v>-0.2897</v>
       </c>
       <c r="I162" t="n">
-        <v>1.066878</v>
+        <v>1.148439</v>
       </c>
       <c r="J162" t="n">
         <v>1.8274</v>
@@ -5976,13 +5976,13 @@
         <v>0.692364</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0452</v>
+        <v>-1.1393</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0452</v>
+        <v>-1.1393</v>
       </c>
       <c r="I163" t="n">
-        <v>1.067361</v>
+        <v>1.135355</v>
       </c>
       <c r="J163" t="n">
         <v>-0.1884</v>
@@ -6010,13 +6010,13 @@
         <v>0.675044</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0238</v>
+        <v>0.1324</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0238</v>
+        <v>0.1324</v>
       </c>
       <c r="I164" t="n">
-        <v>1.067615</v>
+        <v>1.136859</v>
       </c>
       <c r="J164" t="n">
         <v>0.0785</v>
@@ -6044,13 +6044,13 @@
         <v>0.689253</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.4315</v>
+        <v>-1.061</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.4315</v>
+        <v>-1.061</v>
       </c>
       <c r="I165" t="n">
-        <v>1.063008</v>
+        <v>1.124797</v>
       </c>
       <c r="J165" t="n">
         <v>-0.924</v>
@@ -6078,13 +6078,13 @@
         <v>0.661616</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1198</v>
+        <v>-1.8096</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1198</v>
+        <v>-1.8096</v>
       </c>
       <c r="I166" t="n">
-        <v>1.064281</v>
+        <v>1.104443</v>
       </c>
       <c r="J166" t="n">
         <v>-0.0315</v>
@@ -6112,13 +6112,13 @@
         <v>0.664683</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.6879</v>
+        <v>-1.7015</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.6879</v>
+        <v>-1.7015</v>
       </c>
       <c r="I167" t="n">
-        <v>1.05696</v>
+        <v>1.08565</v>
       </c>
       <c r="J167" t="n">
         <v>-1.365</v>
@@ -6146,13 +6146,13 @@
         <v>0.643043</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1444</v>
+        <v>0.1154</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1444</v>
+        <v>0.1154</v>
       </c>
       <c r="I168" t="n">
-        <v>1.058487</v>
+        <v>1.086903</v>
       </c>
       <c r="J168" t="n">
         <v>0.3642</v>
@@ -6180,13 +6180,13 @@
         <v>0.6319669999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.6006</v>
+        <v>-1.3025</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.6006</v>
+        <v>-1.3025</v>
       </c>
       <c r="I169" t="n">
-        <v>1.052129</v>
+        <v>1.072746</v>
       </c>
       <c r="J169" t="n">
         <v>-1.2124</v>
@@ -6214,13 +6214,13 @@
         <v>0.643794</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.4465</v>
+        <v>0.0116</v>
       </c>
       <c r="H170" t="n">
-        <v>-0.4465</v>
+        <v>0.0116</v>
       </c>
       <c r="I170" t="n">
-        <v>1.047432</v>
+        <v>1.072871</v>
       </c>
       <c r="J170" t="n">
         <v>-0.6018</v>
@@ -6248,13 +6248,13 @@
         <v>0.637387</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.264</v>
+        <v>-1.2175</v>
       </c>
       <c r="H171" t="n">
-        <v>-0.264</v>
+        <v>-1.2175</v>
       </c>
       <c r="I171" t="n">
-        <v>1.044666</v>
+        <v>1.059808</v>
       </c>
       <c r="J171" t="n">
         <v>-0.7</v>
@@ -6282,13 +6282,13 @@
         <v>0.6250559999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>0.136</v>
+        <v>-0.1671</v>
       </c>
       <c r="H172" t="n">
-        <v>0.136</v>
+        <v>-0.1671</v>
       </c>
       <c r="I172" t="n">
-        <v>1.046087</v>
+        <v>1.058038</v>
       </c>
       <c r="J172" t="n">
         <v>-0.1233</v>
@@ -6316,13 +6316,13 @@
         <v>0.611476</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.4642</v>
+        <v>-1.3454</v>
       </c>
       <c r="H173" t="n">
-        <v>-0.4642</v>
+        <v>-1.3454</v>
       </c>
       <c r="I173" t="n">
-        <v>1.041231</v>
+        <v>1.043802</v>
       </c>
       <c r="J173" t="n">
         <v>-0.8457</v>
@@ -6350,13 +6350,13 @@
         <v>0.652103</v>
       </c>
       <c r="F174" t="n">
-        <v>0.4571</v>
+        <v>1.8583</v>
       </c>
       <c r="H174" t="n">
-        <v>0.4571</v>
+        <v>1.8583</v>
       </c>
       <c r="I174" t="n">
-        <v>1.045991</v>
+        <v>1.0632</v>
       </c>
       <c r="J174" t="n">
         <v>1.2758</v>
@@ -6384,13 +6384,13 @@
         <v>0.64007</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0376</v>
+        <v>-0.3235</v>
       </c>
       <c r="H175" t="n">
-        <v>0.0376</v>
+        <v>-0.3235</v>
       </c>
       <c r="I175" t="n">
-        <v>1.046384</v>
+        <v>1.05976</v>
       </c>
       <c r="J175" t="n">
         <v>0.3028</v>
@@ -6418,13 +6418,13 @@
         <v>0.67449</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.2907</v>
+        <v>0.8749</v>
       </c>
       <c r="H176" t="n">
-        <v>-0.2907</v>
+        <v>0.8749</v>
       </c>
       <c r="I176" t="n">
-        <v>1.043342</v>
+        <v>1.069032</v>
       </c>
       <c r="J176" t="n">
         <v>-0.3801</v>
@@ -6452,13 +6452,13 @@
         <v>0.667951</v>
       </c>
       <c r="F177" t="n">
-        <v>0.1542</v>
+        <v>0.5389</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1542</v>
+        <v>0.5389</v>
       </c>
       <c r="I177" t="n">
-        <v>1.044951</v>
+        <v>1.074794</v>
       </c>
       <c r="J177" t="n">
         <v>0.2157</v>
@@ -6486,13 +6486,13 @@
         <v>0.676527</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.7147</v>
+        <v>-0.0371</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.7147</v>
+        <v>-0.0371</v>
       </c>
       <c r="I178" t="n">
-        <v>1.037483</v>
+        <v>1.074395</v>
       </c>
       <c r="J178" t="n">
         <v>-1.495</v>
@@ -6520,13 +6520,13 @@
         <v>0.696841</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.435</v>
+        <v>1.0744</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.435</v>
+        <v>1.0744</v>
       </c>
       <c r="I179" t="n">
-        <v>1.03297</v>
+        <v>1.085938</v>
       </c>
       <c r="J179" t="n">
         <v>-0.5991</v>
@@ -6554,13 +6554,13 @@
         <v>0.699605</v>
       </c>
       <c r="F180" t="n">
-        <v>0.3219</v>
+        <v>0.0233</v>
       </c>
       <c r="H180" t="n">
-        <v>0.3219</v>
+        <v>0.0233</v>
       </c>
       <c r="I180" t="n">
-        <v>1.036295</v>
+        <v>1.086191</v>
       </c>
       <c r="J180" t="n">
         <v>0.9002</v>
@@ -6588,13 +6588,13 @@
         <v>0.680256</v>
       </c>
       <c r="F181" t="n">
-        <v>0.0675</v>
+        <v>0.4438</v>
       </c>
       <c r="H181" t="n">
-        <v>0.0675</v>
+        <v>0.4438</v>
       </c>
       <c r="I181" t="n">
-        <v>1.036994</v>
+        <v>1.091011</v>
       </c>
       <c r="J181" t="n">
         <v>0.398</v>
@@ -6622,13 +6622,13 @@
         <v>0.681366</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0145</v>
+        <v>0.9775</v>
       </c>
       <c r="H182" t="n">
-        <v>0.0145</v>
+        <v>0.9775</v>
       </c>
       <c r="I182" t="n">
-        <v>1.037145</v>
+        <v>1.101675</v>
       </c>
       <c r="J182" t="n">
         <v>-0.0399</v>
@@ -6656,13 +6656,13 @@
         <v>0.688929</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.2697</v>
+        <v>-0.6805</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.2697</v>
+        <v>-0.6805</v>
       </c>
       <c r="I183" t="n">
-        <v>1.034347</v>
+        <v>1.094178</v>
       </c>
       <c r="J183" t="n">
         <v>-0.5165</v>
@@ -6690,13 +6690,13 @@
         <v>0.654498</v>
       </c>
       <c r="F184" t="n">
-        <v>0.08160000000000001</v>
+        <v>-1.499</v>
       </c>
       <c r="H184" t="n">
-        <v>0.08160000000000001</v>
+        <v>-1.499</v>
       </c>
       <c r="I184" t="n">
-        <v>1.035191</v>
+        <v>1.077777</v>
       </c>
       <c r="J184" t="n">
         <v>-0.2389</v>
@@ -6724,13 +6724,13 @@
         <v>0.647716</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.1528</v>
+        <v>-1.0835</v>
       </c>
       <c r="H185" t="n">
-        <v>-0.1528</v>
+        <v>-1.0835</v>
       </c>
       <c r="I185" t="n">
-        <v>1.03361</v>
+        <v>1.066099</v>
       </c>
       <c r="J185" t="n">
         <v>-0.243</v>
@@ -6758,13 +6758,13 @@
         <v>0.6497579999999999</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3158</v>
+        <v>0.1113</v>
       </c>
       <c r="H186" t="n">
-        <v>0.3158</v>
+        <v>0.1113</v>
       </c>
       <c r="I186" t="n">
-        <v>1.036874</v>
+        <v>1.067285</v>
       </c>
       <c r="J186" t="n">
         <v>0.6821</v>
@@ -6792,13 +6792,13 @@
         <v>0.642321</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.2417</v>
+        <v>-0.6385</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.2417</v>
+        <v>-0.6385</v>
       </c>
       <c r="I187" t="n">
-        <v>1.034368</v>
+        <v>1.060471</v>
       </c>
       <c r="J187" t="n">
         <v>-0.8863</v>
@@ -6826,13 +6826,13 @@
         <v>0.651686</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.3116</v>
+        <v>0.1729</v>
       </c>
       <c r="H188" t="n">
-        <v>-0.3116</v>
+        <v>0.1729</v>
       </c>
       <c r="I188" t="n">
-        <v>1.031145</v>
+        <v>1.062305</v>
       </c>
       <c r="J188" t="n">
         <v>-0.7066</v>
@@ -6860,13 +6860,13 @@
         <v>0.671766</v>
       </c>
       <c r="F189" t="n">
-        <v>1.1488</v>
+        <v>3.0754</v>
       </c>
       <c r="H189" t="n">
-        <v>1.1488</v>
+        <v>3.0754</v>
       </c>
       <c r="I189" t="n">
-        <v>1.04299</v>
+        <v>1.094975</v>
       </c>
       <c r="J189" t="n">
         <v>2.5236</v>
@@ -6894,13 +6894,13 @@
         <v>0.684786</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2233</v>
+        <v>0.2199</v>
       </c>
       <c r="H190" t="n">
-        <v>0.2233</v>
+        <v>0.2199</v>
       </c>
       <c r="I190" t="n">
-        <v>1.045319</v>
+        <v>1.097382</v>
       </c>
       <c r="J190" t="n">
         <v>0.4996</v>
@@ -6928,13 +6928,13 @@
         <v>0.693977</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.2814</v>
+        <v>-0.4875</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.2814</v>
+        <v>-0.4875</v>
       </c>
       <c r="I191" t="n">
-        <v>1.042378</v>
+        <v>1.092032</v>
       </c>
       <c r="J191" t="n">
         <v>-0.1114</v>
@@ -6962,13 +6962,13 @@
         <v>0.695314</v>
       </c>
       <c r="F192" t="n">
-        <v>0.1615</v>
+        <v>-0.122</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1615</v>
+        <v>-0.122</v>
       </c>
       <c r="I192" t="n">
-        <v>1.044061</v>
+        <v>1.0907</v>
       </c>
       <c r="J192" t="n">
         <v>0.5881</v>
@@ -6996,13 +6996,13 @@
         <v>0.674813</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.1808</v>
+        <v>-1.4233</v>
       </c>
       <c r="H193" t="n">
-        <v>-0.1808</v>
+        <v>-1.4233</v>
       </c>
       <c r="I193" t="n">
-        <v>1.042174</v>
+        <v>1.075177</v>
       </c>
       <c r="J193" t="n">
         <v>-0.8284</v>
@@ -7030,13 +7030,13 @@
         <v>0.685584</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.0234</v>
+        <v>0.9829</v>
       </c>
       <c r="H194" t="n">
-        <v>-0.0234</v>
+        <v>0.9829</v>
       </c>
       <c r="I194" t="n">
-        <v>1.04193</v>
+        <v>1.085745</v>
       </c>
       <c r="J194" t="n">
         <v>-0.0892</v>
@@ -7064,13 +7064,13 @@
         <v>0.6945789999999999</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0515</v>
+        <v>0.8536</v>
       </c>
       <c r="H195" t="n">
-        <v>0.0515</v>
+        <v>0.8536</v>
       </c>
       <c r="I195" t="n">
-        <v>1.042466</v>
+        <v>1.095012</v>
       </c>
       <c r="J195" t="n">
         <v>0.2666</v>
@@ -7098,13 +7098,13 @@
         <v>0.7029260000000001</v>
       </c>
       <c r="F196" t="n">
-        <v>0.4677</v>
+        <v>1.4725</v>
       </c>
       <c r="H196" t="n">
-        <v>0.4677</v>
+        <v>1.4725</v>
       </c>
       <c r="I196" t="n">
-        <v>1.047342</v>
+        <v>1.111137</v>
       </c>
       <c r="J196" t="n">
         <v>1.3137</v>
@@ -7132,13 +7132,13 @@
         <v>0.7074859999999999</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.3041</v>
+        <v>0.4747</v>
       </c>
       <c r="H197" t="n">
-        <v>-0.3041</v>
+        <v>0.4747</v>
       </c>
       <c r="I197" t="n">
-        <v>1.044157</v>
+        <v>1.116412</v>
       </c>
       <c r="J197" t="n">
         <v>-0.5497</v>
@@ -7166,13 +7166,13 @@
         <v>0.699214</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.0204</v>
+        <v>0.5374</v>
       </c>
       <c r="H198" t="n">
-        <v>-0.0204</v>
+        <v>0.5374</v>
       </c>
       <c r="I198" t="n">
-        <v>1.043944</v>
+        <v>1.122412</v>
       </c>
       <c r="J198" t="n">
         <v>0.0183</v>
@@ -7200,13 +7200,13 @@
         <v>0.714082</v>
       </c>
       <c r="F199" t="n">
-        <v>0.2067</v>
+        <v>1.8728</v>
       </c>
       <c r="H199" t="n">
-        <v>0.2067</v>
+        <v>1.8728</v>
       </c>
       <c r="I199" t="n">
-        <v>1.046102</v>
+        <v>1.143433</v>
       </c>
       <c r="J199" t="n">
         <v>0.9126</v>
@@ -7234,13 +7234,13 @@
         <v>0.71436</v>
       </c>
       <c r="F200" t="n">
-        <v>0.484</v>
+        <v>-0.9936</v>
       </c>
       <c r="H200" t="n">
-        <v>0.484</v>
+        <v>-0.9936</v>
       </c>
       <c r="I200" t="n">
-        <v>1.051165</v>
+        <v>1.132072</v>
       </c>
       <c r="J200" t="n">
         <v>1.2788</v>
@@ -7268,13 +7268,13 @@
         <v>0.702408</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.1906</v>
+        <v>-0.4836</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.1906</v>
+        <v>-0.4836</v>
       </c>
       <c r="I201" t="n">
-        <v>1.049161</v>
+        <v>1.126597</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6694</v>
@@ -7302,13 +7302,13 @@
         <v>0.710303</v>
       </c>
       <c r="F202" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.5978</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.5978</v>
       </c>
       <c r="I202" t="n">
-        <v>1.041129</v>
+        <v>1.108597</v>
       </c>
       <c r="J202" t="n">
         <v>-1.854</v>
@@ -7336,13 +7336,13 @@
         <v>0.717494</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.1164</v>
+        <v>-0.0459</v>
       </c>
       <c r="H203" t="n">
-        <v>-0.1164</v>
+        <v>-0.0459</v>
       </c>
       <c r="I203" t="n">
-        <v>1.039917</v>
+        <v>1.108087</v>
       </c>
       <c r="J203" t="n">
         <v>-0.3221</v>
@@ -7370,13 +7370,13 @@
         <v>0.7274969999999999</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.6399</v>
+        <v>-1.3672</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.6399</v>
+        <v>-1.3672</v>
       </c>
       <c r="I204" t="n">
-        <v>1.033263</v>
+        <v>1.092937</v>
       </c>
       <c r="J204" t="n">
         <v>-1.546</v>
@@ -7404,13 +7404,13 @@
         <v>0.717821</v>
       </c>
       <c r="F205" t="n">
-        <v>1.1346</v>
+        <v>0.7543</v>
       </c>
       <c r="H205" t="n">
-        <v>1.1346</v>
+        <v>0.7543</v>
       </c>
       <c r="I205" t="n">
-        <v>1.044986</v>
+        <v>1.101181</v>
       </c>
       <c r="J205" t="n">
         <v>1.9824</v>
@@ -7438,13 +7438,13 @@
         <v>0.718253</v>
       </c>
       <c r="F206" t="n">
-        <v>0.3778</v>
+        <v>1.2492</v>
       </c>
       <c r="H206" t="n">
-        <v>0.3778</v>
+        <v>1.2492</v>
       </c>
       <c r="I206" t="n">
-        <v>1.048934</v>
+        <v>1.114937</v>
       </c>
       <c r="J206" t="n">
         <v>0.7963</v>
@@ -7472,13 +7472,13 @@
         <v>0.7081229999999999</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.3973</v>
+        <v>0.3283</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.3973</v>
+        <v>0.3283</v>
       </c>
       <c r="I207" t="n">
-        <v>1.044767</v>
+        <v>1.118597</v>
       </c>
       <c r="J207" t="n">
         <v>-0.9435</v>
@@ -7506,13 +7506,13 @@
         <v>0.711639</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1673</v>
+        <v>0.6127</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1673</v>
+        <v>0.6127</v>
       </c>
       <c r="I208" t="n">
-        <v>1.046515</v>
+        <v>1.125452</v>
       </c>
       <c r="J208" t="n">
         <v>0.3618</v>
@@ -7540,13 +7540,13 @@
         <v>0.7034589999999999</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3566</v>
+        <v>-1.4031</v>
       </c>
       <c r="H209" t="n">
-        <v>0.3566</v>
+        <v>-1.4031</v>
       </c>
       <c r="I209" t="n">
-        <v>1.050246</v>
+        <v>1.10966</v>
       </c>
       <c r="J209" t="n">
         <v>1.0767</v>
@@ -7574,13 +7574,13 @@
         <v>0.704199</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.1761</v>
+        <v>-0.6914</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.1761</v>
+        <v>-0.6914</v>
       </c>
       <c r="I210" t="n">
-        <v>1.048397</v>
+        <v>1.101988</v>
       </c>
       <c r="J210" t="n">
         <v>-0.4025</v>
@@ -7608,13 +7608,13 @@
         <v>0.712067</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.1948</v>
+        <v>-0.5955</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.1948</v>
+        <v>-0.5955</v>
       </c>
       <c r="I211" t="n">
-        <v>1.046355</v>
+        <v>1.095426</v>
       </c>
       <c r="J211" t="n">
         <v>0.0112</v>
@@ -7642,13 +7642,13 @@
         <v>0.717028</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.2841</v>
+        <v>-0.133</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.2841</v>
+        <v>-0.133</v>
       </c>
       <c r="I212" t="n">
-        <v>1.043382</v>
+        <v>1.093969</v>
       </c>
       <c r="J212" t="n">
         <v>-0.516</v>
@@ -7676,13 +7676,13 @@
         <v>0.70458</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.3904</v>
+        <v>-1.0956</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.3904</v>
+        <v>-1.0956</v>
       </c>
       <c r="I213" t="n">
-        <v>1.039309</v>
+        <v>1.081983</v>
       </c>
       <c r="J213" t="n">
         <v>-1.0889</v>
@@ -7710,13 +7710,13 @@
         <v>0.70525</v>
       </c>
       <c r="F214" t="n">
-        <v>0.4836</v>
+        <v>-0.924</v>
       </c>
       <c r="H214" t="n">
-        <v>0.4836</v>
+        <v>-0.924</v>
       </c>
       <c r="I214" t="n">
-        <v>1.044335</v>
+        <v>1.071986</v>
       </c>
       <c r="J214" t="n">
         <v>1.0306</v>
@@ -7744,13 +7744,13 @@
         <v>0.688242</v>
       </c>
       <c r="F215" t="n">
-        <v>0.359</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="H215" t="n">
-        <v>0.359</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>1.048084</v>
+        <v>1.062547</v>
       </c>
       <c r="J215" t="n">
         <v>0.6531</v>
@@ -7778,13 +7778,13 @@
         <v>0.683824</v>
       </c>
       <c r="F216" t="n">
-        <v>0.1248</v>
+        <v>-0.4577</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1248</v>
+        <v>-0.4577</v>
       </c>
       <c r="I216" t="n">
-        <v>1.049392</v>
+        <v>1.057684</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0237</v>
@@ -7812,13 +7812,13 @@
         <v>0.68462</v>
       </c>
       <c r="F217" t="n">
-        <v>0.1753</v>
+        <v>-0.238</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1753</v>
+        <v>-0.238</v>
       </c>
       <c r="I217" t="n">
-        <v>1.051231</v>
+        <v>1.055167</v>
       </c>
       <c r="J217" t="n">
         <v>0.3157</v>
@@ -7846,13 +7846,13 @@
         <v>0.689492</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.317</v>
+        <v>0.0286</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.317</v>
+        <v>0.0286</v>
       </c>
       <c r="I218" t="n">
-        <v>1.047899</v>
+        <v>1.055468</v>
       </c>
       <c r="J218" t="n">
         <v>-0.8327</v>
@@ -7880,13 +7880,13 @@
         <v>0.676376</v>
       </c>
       <c r="F219" t="n">
-        <v>0.1635</v>
+        <v>-1.1433</v>
       </c>
       <c r="H219" t="n">
-        <v>0.1635</v>
+        <v>-1.1433</v>
       </c>
       <c r="I219" t="n">
-        <v>1.049612</v>
+        <v>1.043402</v>
       </c>
       <c r="J219" t="n">
         <v>0.0312</v>
@@ -7914,13 +7914,13 @@
         <v>0.695184</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0086</v>
+        <v>0.2847</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0086</v>
+        <v>0.2847</v>
       </c>
       <c r="I220" t="n">
-        <v>1.049703</v>
+        <v>1.046372</v>
       </c>
       <c r="J220" t="n">
         <v>0.3941</v>
@@ -7948,13 +7948,13 @@
         <v>0.703195</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.3417</v>
+        <v>-0.2062</v>
       </c>
       <c r="H221" t="n">
-        <v>-0.3417</v>
+        <v>-0.2062</v>
       </c>
       <c r="I221" t="n">
-        <v>1.046116</v>
+        <v>1.044214</v>
       </c>
       <c r="J221" t="n">
         <v>-0.529</v>
@@ -7982,13 +7982,13 @@
         <v>0.687819</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.336</v>
+        <v>-0.9253</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.336</v>
+        <v>-0.9253</v>
       </c>
       <c r="I222" t="n">
-        <v>1.042601</v>
+        <v>1.034552</v>
       </c>
       <c r="J222" t="n">
         <v>-1.0787</v>
@@ -8016,13 +8016,13 @@
         <v>0.703447</v>
       </c>
       <c r="F223" t="n">
-        <v>0.2169</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="H223" t="n">
-        <v>0.2169</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="I223" t="n">
-        <v>1.044862</v>
+        <v>1.044726</v>
       </c>
       <c r="J223" t="n">
         <v>0.6642</v>
@@ -8050,13 +8050,13 @@
         <v>0.703274</v>
       </c>
       <c r="F224" t="n">
-        <v>0.2616</v>
+        <v>0.782</v>
       </c>
       <c r="H224" t="n">
-        <v>0.2616</v>
+        <v>0.782</v>
       </c>
       <c r="I224" t="n">
-        <v>1.047596</v>
+        <v>1.052896</v>
       </c>
       <c r="J224" t="n">
         <v>1.132</v>
@@ -8084,13 +8084,13 @@
         <v>0.6857259999999999</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0474</v>
+        <v>-1.1642</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0474</v>
+        <v>-1.1642</v>
       </c>
       <c r="I225" t="n">
-        <v>1.048092</v>
+        <v>1.040638</v>
       </c>
       <c r="J225" t="n">
         <v>-0.091</v>
@@ -8118,13 +8118,13 @@
         <v>0.683391</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.2507</v>
+        <v>0.1472</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.2507</v>
+        <v>0.1472</v>
       </c>
       <c r="I226" t="n">
-        <v>1.045465</v>
+        <v>1.04217</v>
       </c>
       <c r="J226" t="n">
         <v>-0.8229</v>
@@ -8152,13 +8152,13 @@
         <v>0.678854</v>
       </c>
       <c r="F227" t="n">
-        <v>0.71</v>
+        <v>-0.454</v>
       </c>
       <c r="H227" t="n">
-        <v>0.71</v>
+        <v>-0.454</v>
       </c>
       <c r="I227" t="n">
-        <v>1.052887</v>
+        <v>1.037438</v>
       </c>
       <c r="J227" t="n">
         <v>1.2651</v>
@@ -8186,13 +8186,13 @@
         <v>0.682157</v>
       </c>
       <c r="F228" t="n">
-        <v>0.5942</v>
+        <v>0.226</v>
       </c>
       <c r="H228" t="n">
-        <v>0.5942</v>
+        <v>0.226</v>
       </c>
       <c r="I228" t="n">
-        <v>1.059144</v>
+        <v>1.039783</v>
       </c>
       <c r="J228" t="n">
         <v>1.1244</v>
@@ -8220,13 +8220,13 @@
         <v>0.687186</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.3407</v>
+        <v>-0.6845</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.3407</v>
+        <v>-0.6845</v>
       </c>
       <c r="I229" t="n">
-        <v>1.055535</v>
+        <v>1.032666</v>
       </c>
       <c r="J229" t="n">
         <v>-0.3675</v>
@@ -8254,13 +8254,13 @@
         <v>0.685437</v>
       </c>
       <c r="F230" t="n">
-        <v>0.2357</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="H230" t="n">
-        <v>0.2357</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>1.058023</v>
+        <v>1.026123</v>
       </c>
       <c r="J230" t="n">
         <v>0.3655</v>
@@ -8288,13 +8288,13 @@
         <v>0.678221</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.1757</v>
+        <v>-0.1646</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.1757</v>
+        <v>-0.1646</v>
       </c>
       <c r="I231" t="n">
-        <v>1.056164</v>
+        <v>1.024434</v>
       </c>
       <c r="J231" t="n">
         <v>-0.4361</v>
@@ -8322,13 +8322,13 @@
         <v>0.686626</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1784</v>
+        <v>0.1321</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1784</v>
+        <v>0.1321</v>
       </c>
       <c r="I232" t="n">
-        <v>1.058048</v>
+        <v>1.025786</v>
       </c>
       <c r="J232" t="n">
         <v>0.5543</v>
@@ -8356,13 +8356,13 @@
         <v>0.659016</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0341</v>
+        <v>0.9327</v>
       </c>
       <c r="H233" t="n">
-        <v>0.0341</v>
+        <v>0.9327</v>
       </c>
       <c r="I233" t="n">
-        <v>1.058409</v>
+        <v>1.035354</v>
       </c>
       <c r="J233" t="n">
         <v>-0.2151</v>
@@ -8390,13 +8390,13 @@
         <v>0.654722</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.2335</v>
+        <v>-1.0546</v>
       </c>
       <c r="H234" t="n">
-        <v>-0.2335</v>
+        <v>-1.0546</v>
       </c>
       <c r="I234" t="n">
-        <v>1.055938</v>
+        <v>1.024435</v>
       </c>
       <c r="J234" t="n">
         <v>-0.3271</v>
@@ -8424,13 +8424,13 @@
         <v>0.648489</v>
       </c>
       <c r="F235" t="n">
-        <v>0.361</v>
+        <v>-0.253</v>
       </c>
       <c r="H235" t="n">
-        <v>0.361</v>
+        <v>-0.253</v>
       </c>
       <c r="I235" t="n">
-        <v>1.05975</v>
+        <v>1.021843</v>
       </c>
       <c r="J235" t="n">
         <v>0.8120000000000001</v>
@@ -8458,13 +8458,13 @@
         <v>0.6410709999999999</v>
       </c>
       <c r="F236" t="n">
-        <v>1.1109</v>
+        <v>1.1155</v>
       </c>
       <c r="H236" t="n">
-        <v>1.1109</v>
+        <v>1.1155</v>
       </c>
       <c r="I236" t="n">
-        <v>1.071522</v>
+        <v>1.033243</v>
       </c>
       <c r="J236" t="n">
         <v>2.1135</v>
@@ -8492,13 +8492,13 @@
         <v>0.633989</v>
       </c>
       <c r="F237" t="n">
-        <v>0.7853</v>
+        <v>0.446</v>
       </c>
       <c r="H237" t="n">
-        <v>0.7853</v>
+        <v>0.446</v>
       </c>
       <c r="I237" t="n">
-        <v>1.079937</v>
+        <v>1.03785</v>
       </c>
       <c r="J237" t="n">
         <v>1.2177</v>
@@ -8526,13 +8526,13 @@
         <v>0.620678</v>
       </c>
       <c r="F238" t="n">
-        <v>1.1813</v>
+        <v>-0.8259</v>
       </c>
       <c r="H238" t="n">
-        <v>1.1813</v>
+        <v>-0.8259</v>
       </c>
       <c r="I238" t="n">
-        <v>1.092694</v>
+        <v>1.029279</v>
       </c>
       <c r="J238" t="n">
         <v>2.1111</v>
@@ -8560,13 +8560,13 @@
         <v>0.635906</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.6902</v>
+        <v>3.6184</v>
       </c>
       <c r="H239" t="n">
-        <v>-0.6902</v>
+        <v>3.6184</v>
       </c>
       <c r="I239" t="n">
-        <v>1.085153</v>
+        <v>1.066523</v>
       </c>
       <c r="J239" t="n">
         <v>-1.1877</v>
@@ -8594,13 +8594,13 @@
         <v>0.617835</v>
       </c>
       <c r="F240" t="n">
-        <v>0.6307</v>
+        <v>-0.6714</v>
       </c>
       <c r="H240" t="n">
-        <v>0.6307</v>
+        <v>-0.6714</v>
       </c>
       <c r="I240" t="n">
-        <v>1.091997</v>
+        <v>1.059362</v>
       </c>
       <c r="J240" t="n">
         <v>1.3608</v>
@@ -8628,13 +8628,13 @@
         <v>0.619522</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.4315</v>
+        <v>-0.6085</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.4315</v>
+        <v>-0.6085</v>
       </c>
       <c r="I241" t="n">
-        <v>1.087285</v>
+        <v>1.052916</v>
       </c>
       <c r="J241" t="n">
         <v>-1.1751</v>
@@ -8662,13 +8662,13 @@
         <v>0.605776</v>
       </c>
       <c r="F242" t="n">
-        <v>0.1867</v>
+        <v>-0.4904</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1867</v>
+        <v>-0.4904</v>
       </c>
       <c r="I242" t="n">
-        <v>1.089315</v>
+        <v>1.047753</v>
       </c>
       <c r="J242" t="n">
         <v>0.4582</v>
@@ -8696,13 +8696,13 @@
         <v>0.613679</v>
       </c>
       <c r="F243" t="n">
-        <v>0.2566</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H243" t="n">
-        <v>0.2566</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="I243" t="n">
-        <v>1.09211</v>
+        <v>1.048701</v>
       </c>
       <c r="J243" t="n">
         <v>1.088</v>
@@ -8730,13 +8730,13 @@
         <v>0.631479</v>
       </c>
       <c r="F244" t="n">
-        <v>-0.5876</v>
+        <v>0.3145</v>
       </c>
       <c r="H244" t="n">
-        <v>-0.5876</v>
+        <v>0.3145</v>
       </c>
       <c r="I244" t="n">
-        <v>1.085693</v>
+        <v>1.051999</v>
       </c>
       <c r="J244" t="n">
         <v>-0.6644</v>
@@ -8764,13 +8764,13 @@
         <v>0.605308</v>
       </c>
       <c r="F245" t="n">
-        <v>0.3888</v>
+        <v>0.0163</v>
       </c>
       <c r="H245" t="n">
-        <v>0.3888</v>
+        <v>0.0163</v>
       </c>
       <c r="I245" t="n">
-        <v>1.089914</v>
+        <v>1.05217</v>
       </c>
       <c r="J245" t="n">
         <v>0.9074</v>
@@ -8798,13 +8798,13 @@
         <v>0.607253</v>
       </c>
       <c r="F246" t="n">
-        <v>0.4431</v>
+        <v>0.1491</v>
       </c>
       <c r="H246" t="n">
-        <v>0.4431</v>
+        <v>0.1491</v>
       </c>
       <c r="I246" t="n">
-        <v>1.094743</v>
+        <v>1.053739</v>
       </c>
       <c r="J246" t="n">
         <v>0.9875</v>
@@ -8832,13 +8832,13 @@
         <v>0.601778</v>
       </c>
       <c r="F247" t="n">
-        <v>1.0541</v>
+        <v>0.3368</v>
       </c>
       <c r="H247" t="n">
-        <v>1.0541</v>
+        <v>0.3368</v>
       </c>
       <c r="I247" t="n">
-        <v>1.106283</v>
+        <v>1.057287</v>
       </c>
       <c r="J247" t="n">
         <v>2.3057</v>
@@ -8866,13 +8866,13 @@
         <v>0.613804</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.6992</v>
+        <v>1.7899</v>
       </c>
       <c r="H248" t="n">
-        <v>-0.6992</v>
+        <v>1.7899</v>
       </c>
       <c r="I248" t="n">
-        <v>1.098548</v>
+        <v>1.076211</v>
       </c>
       <c r="J248" t="n">
         <v>-1.6787</v>
@@ -8900,13 +8900,13 @@
         <v>0.599286</v>
       </c>
       <c r="F249" t="n">
-        <v>0.1961</v>
+        <v>-1.1194</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1961</v>
+        <v>-1.1194</v>
       </c>
       <c r="I249" t="n">
-        <v>1.100702</v>
+        <v>1.064164</v>
       </c>
       <c r="J249" t="n">
         <v>0.2985</v>
@@ -8934,13 +8934,13 @@
         <v>0.609091</v>
       </c>
       <c r="F250" t="n">
-        <v>-0.2054</v>
+        <v>-1.3536</v>
       </c>
       <c r="H250" t="n">
-        <v>-0.2054</v>
+        <v>-1.3536</v>
       </c>
       <c r="I250" t="n">
-        <v>1.098441</v>
+        <v>1.049759</v>
       </c>
       <c r="J250" t="n">
         <v>-0.9918</v>
@@ -8968,13 +8968,13 @@
         <v>0.6350980000000001</v>
       </c>
       <c r="F251" t="n">
-        <v>-0.8972</v>
+        <v>-0.9176</v>
       </c>
       <c r="H251" t="n">
-        <v>-0.8972</v>
+        <v>-0.9176</v>
       </c>
       <c r="I251" t="n">
-        <v>1.088586</v>
+        <v>1.040127</v>
       </c>
       <c r="J251" t="n">
         <v>-1.9725</v>
@@ -9002,13 +9002,13 @@
         <v>0.6279979999999999</v>
       </c>
       <c r="F252" t="n">
-        <v>0.3667</v>
+        <v>-0.0946</v>
       </c>
       <c r="H252" t="n">
-        <v>0.3667</v>
+        <v>-0.0946</v>
       </c>
       <c r="I252" t="n">
-        <v>1.092578</v>
+        <v>1.039142</v>
       </c>
       <c r="J252" t="n">
         <v>0.8808</v>
@@ -9036,13 +9036,13 @@
         <v>0.632714</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.3339</v>
+        <v>0.1289</v>
       </c>
       <c r="H253" t="n">
-        <v>-0.3339</v>
+        <v>0.1289</v>
       </c>
       <c r="I253" t="n">
-        <v>1.08893</v>
+        <v>1.040482</v>
       </c>
       <c r="J253" t="n">
         <v>-0.2726</v>
@@ -9070,13 +9070,13 @@
         <v>0.628722</v>
       </c>
       <c r="F254" t="n">
-        <v>0.9588</v>
+        <v>-0.1876</v>
       </c>
       <c r="H254" t="n">
-        <v>0.9588</v>
+        <v>-0.1876</v>
       </c>
       <c r="I254" t="n">
-        <v>1.09937</v>
+        <v>1.038531</v>
       </c>
       <c r="J254" t="n">
         <v>1.6512</v>
@@ -9104,13 +9104,13 @@
         <v>0.65299</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.4929</v>
+        <v>0.0496</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.4929</v>
+        <v>0.0496</v>
       </c>
       <c r="I255" t="n">
-        <v>1.093951</v>
+        <v>1.039045</v>
       </c>
       <c r="J255" t="n">
         <v>-0.7157</v>
@@ -9138,13 +9138,13 @@
         <v>0.659488</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.5595</v>
+        <v>0.9765</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.5595</v>
+        <v>0.9765</v>
       </c>
       <c r="I256" t="n">
-        <v>1.087831</v>
+        <v>1.049191</v>
       </c>
       <c r="J256" t="n">
         <v>-0.6228</v>
@@ -9172,13 +9172,13 @@
         <v>0.662359</v>
       </c>
       <c r="F257" t="n">
-        <v>0.2888</v>
+        <v>1.6973</v>
       </c>
       <c r="H257" t="n">
-        <v>0.2888</v>
+        <v>1.6973</v>
       </c>
       <c r="I257" t="n">
-        <v>1.090972</v>
+        <v>1.067</v>
       </c>
       <c r="J257" t="n">
         <v>0.9981</v>
@@ -9206,13 +9206,13 @@
         <v>0.650141</v>
       </c>
       <c r="F258" t="n">
-        <v>0.284</v>
+        <v>-1.359</v>
       </c>
       <c r="H258" t="n">
-        <v>0.284</v>
+        <v>-1.359</v>
       </c>
       <c r="I258" t="n">
-        <v>1.094071</v>
+        <v>1.052499</v>
       </c>
       <c r="J258" t="n">
         <v>0.4906</v>
@@ -9240,13 +9240,13 @@
         <v>0.64658</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.0373</v>
+        <v>0.0513</v>
       </c>
       <c r="H259" t="n">
-        <v>-0.0373</v>
+        <v>0.0513</v>
       </c>
       <c r="I259" t="n">
-        <v>1.093663</v>
+        <v>1.053039</v>
       </c>
       <c r="J259" t="n">
         <v>-0.2132</v>
@@ -9274,13 +9274,13 @@
         <v>0.658307</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.1126</v>
+        <v>0.0191</v>
       </c>
       <c r="H260" t="n">
-        <v>-0.1126</v>
+        <v>0.0191</v>
       </c>
       <c r="I260" t="n">
-        <v>1.092431</v>
+        <v>1.05324</v>
       </c>
       <c r="J260" t="n">
         <v>-0.2112</v>
@@ -9308,13 +9308,13 @@
         <v>0.6444879999999999</v>
       </c>
       <c r="F261" t="n">
-        <v>0.3598</v>
+        <v>-1.4046</v>
       </c>
       <c r="H261" t="n">
-        <v>0.3598</v>
+        <v>-1.4046</v>
       </c>
       <c r="I261" t="n">
-        <v>1.096362</v>
+        <v>1.038447</v>
       </c>
       <c r="J261" t="n">
         <v>0.1433</v>
@@ -9342,13 +9342,13 @@
         <v>0.63978</v>
       </c>
       <c r="F262" t="n">
-        <v>0.1305</v>
+        <v>0.4215</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1305</v>
+        <v>0.4215</v>
       </c>
       <c r="I262" t="n">
-        <v>1.097793</v>
+        <v>1.042823</v>
       </c>
       <c r="J262" t="n">
         <v>0.5968</v>
@@ -9376,13 +9376,13 @@
         <v>0.651671</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.0551</v>
+        <v>-0.6079</v>
       </c>
       <c r="H263" t="n">
-        <v>-0.0551</v>
+        <v>-0.6079</v>
       </c>
       <c r="I263" t="n">
-        <v>1.097188</v>
+        <v>1.036484</v>
       </c>
       <c r="J263" t="n">
         <v>0.234</v>
@@ -9410,13 +9410,13 @@
         <v>0.651676</v>
       </c>
       <c r="F264" t="n">
-        <v>0.2694</v>
+        <v>0.1552</v>
       </c>
       <c r="H264" t="n">
-        <v>0.2694</v>
+        <v>0.1552</v>
       </c>
       <c r="I264" t="n">
-        <v>1.100144</v>
+        <v>1.038092</v>
       </c>
       <c r="J264" t="n">
         <v>0.4423</v>
@@ -9444,13 +9444,13 @@
         <v>0.644236</v>
       </c>
       <c r="F265" t="n">
-        <v>0.6693</v>
+        <v>-0.2701</v>
       </c>
       <c r="H265" t="n">
-        <v>0.6693</v>
+        <v>-0.2701</v>
       </c>
       <c r="I265" t="n">
-        <v>1.107507</v>
+        <v>1.035288</v>
       </c>
       <c r="J265" t="n">
         <v>0.9811</v>
@@ -9478,13 +9478,13 @@
         <v>0.6497540000000001</v>
       </c>
       <c r="F266" t="n">
-        <v>0.4728</v>
+        <v>-0.1144</v>
       </c>
       <c r="H266" t="n">
-        <v>0.4728</v>
+        <v>-0.1144</v>
       </c>
       <c r="I266" t="n">
-        <v>1.112743</v>
+        <v>1.034104</v>
       </c>
       <c r="J266" t="n">
         <v>1.1467</v>
@@ -9512,13 +9512,13 @@
         <v>0.668666</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.8265</v>
+        <v>-2.0449</v>
       </c>
       <c r="H267" t="n">
-        <v>-0.8265</v>
+        <v>-2.0449</v>
       </c>
       <c r="I267" t="n">
-        <v>1.103546</v>
+        <v>1.012957</v>
       </c>
       <c r="J267" t="n">
         <v>-2.0512</v>
@@ -9546,13 +9546,13 @@
         <v>0.708829</v>
       </c>
       <c r="F268" t="n">
-        <v>-1.2305</v>
+        <v>0.1044</v>
       </c>
       <c r="H268" t="n">
-        <v>-1.2305</v>
+        <v>0.1044</v>
       </c>
       <c r="I268" t="n">
-        <v>1.089967</v>
+        <v>1.014015</v>
       </c>
       <c r="J268" t="n">
         <v>-2.6202</v>
@@ -9580,13 +9580,13 @@
         <v>0.7009</v>
       </c>
       <c r="F269" t="n">
-        <v>0.3275</v>
+        <v>-0.2045</v>
       </c>
       <c r="H269" t="n">
-        <v>0.3275</v>
+        <v>-0.2045</v>
       </c>
       <c r="I269" t="n">
-        <v>1.093537</v>
+        <v>1.011941</v>
       </c>
       <c r="J269" t="n">
         <v>1.0806</v>
@@ -9614,13 +9614,13 @@
         <v>0.688035</v>
       </c>
       <c r="F270" t="n">
-        <v>0.1782</v>
+        <v>-0.3949</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1782</v>
+        <v>-0.3949</v>
       </c>
       <c r="I270" t="n">
-        <v>1.095485</v>
+        <v>1.007944</v>
       </c>
       <c r="J270" t="n">
         <v>0.6499</v>
@@ -9648,13 +9648,13 @@
         <v>0.684901</v>
       </c>
       <c r="F271" t="n">
-        <v>0.3197</v>
+        <v>2.1916</v>
       </c>
       <c r="H271" t="n">
-        <v>0.3197</v>
+        <v>2.1916</v>
       </c>
       <c r="I271" t="n">
-        <v>1.098988</v>
+        <v>1.030034</v>
       </c>
       <c r="J271" t="n">
         <v>1.0687</v>
@@ -9682,13 +9682,13 @@
         <v>0.696948</v>
       </c>
       <c r="F272" t="n">
-        <v>0.1199</v>
+        <v>-0.0722</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1199</v>
+        <v>-0.0722</v>
       </c>
       <c r="I272" t="n">
-        <v>1.100305</v>
+        <v>1.029291</v>
       </c>
       <c r="J272" t="n">
         <v>0.1325</v>
@@ -9716,13 +9716,13 @@
         <v>0.676652</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4692</v>
+        <v>-0.1551</v>
       </c>
       <c r="H273" t="n">
-        <v>0.4692</v>
+        <v>-0.1551</v>
       </c>
       <c r="I273" t="n">
-        <v>1.105468</v>
+        <v>1.027694</v>
       </c>
       <c r="J273" t="n">
         <v>0.9009</v>
@@ -9750,13 +9750,13 @@
         <v>0.695764</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.3685</v>
+        <v>-0.1177</v>
       </c>
       <c r="H274" t="n">
-        <v>-0.3685</v>
+        <v>-0.1177</v>
       </c>
       <c r="I274" t="n">
-        <v>1.101394</v>
+        <v>1.026485</v>
       </c>
       <c r="J274" t="n">
         <v>-0.9084</v>
@@ -9784,13 +9784,13 @@
         <v>0.712828</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.214</v>
+        <v>0.6857</v>
       </c>
       <c r="H275" t="n">
-        <v>-0.214</v>
+        <v>0.6857</v>
       </c>
       <c r="I275" t="n">
-        <v>1.099037</v>
+        <v>1.033523</v>
       </c>
       <c r="J275" t="n">
         <v>-0.799</v>
@@ -9818,13 +9818,13 @@
         <v>0.715356</v>
       </c>
       <c r="F276" t="n">
-        <v>-0.6158</v>
+        <v>1.0336</v>
       </c>
       <c r="H276" t="n">
-        <v>-0.6158</v>
+        <v>1.0336</v>
       </c>
       <c r="I276" t="n">
-        <v>1.09227</v>
+        <v>1.044205</v>
       </c>
       <c r="J276" t="n">
         <v>-0.9287</v>
@@ -9852,13 +9852,13 @@
         <v>0.704387</v>
       </c>
       <c r="F277" t="n">
-        <v>0.1002</v>
+        <v>0.3774</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1002</v>
+        <v>0.3774</v>
       </c>
       <c r="I277" t="n">
-        <v>1.093364</v>
+        <v>1.048147</v>
       </c>
       <c r="J277" t="n">
         <v>0.2559</v>
@@ -9886,13 +9886,13 @@
         <v>0.71484</v>
       </c>
       <c r="F278" t="n">
-        <v>-1.0214</v>
+        <v>-0.1067</v>
       </c>
       <c r="H278" t="n">
-        <v>-1.0214</v>
+        <v>-0.1067</v>
       </c>
       <c r="I278" t="n">
-        <v>1.082196</v>
+        <v>1.047028</v>
       </c>
       <c r="J278" t="n">
         <v>-1.7678</v>
@@ -9920,13 +9920,13 @@
         <v>0.700841</v>
       </c>
       <c r="F279" t="n">
-        <v>0.5322</v>
+        <v>0.0673</v>
       </c>
       <c r="H279" t="n">
-        <v>0.5322</v>
+        <v>0.0673</v>
       </c>
       <c r="I279" t="n">
-        <v>1.087956</v>
+        <v>1.047732</v>
       </c>
       <c r="J279" t="n">
         <v>1.1158</v>
@@ -9954,13 +9954,13 @@
         <v>0.713858</v>
       </c>
       <c r="F280" t="n">
-        <v>-0.2331</v>
+        <v>-0.9709</v>
       </c>
       <c r="H280" t="n">
-        <v>-0.2331</v>
+        <v>-0.9709</v>
       </c>
       <c r="I280" t="n">
-        <v>1.08542</v>
+        <v>1.03756</v>
       </c>
       <c r="J280" t="n">
         <v>-0.9412</v>
@@ -9988,13 +9988,13 @@
         <v>0.721641</v>
       </c>
       <c r="F281" t="n">
-        <v>-0.7534</v>
+        <v>-1.0701</v>
       </c>
       <c r="H281" t="n">
-        <v>-0.7534</v>
+        <v>-1.0701</v>
       </c>
       <c r="I281" t="n">
-        <v>1.077242</v>
+        <v>1.026457</v>
       </c>
       <c r="J281" t="n">
         <v>-2.2286</v>
@@ -10022,13 +10022,13 @@
         <v>0.734453</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.9802</v>
+        <v>-1.6435</v>
       </c>
       <c r="H282" t="n">
-        <v>-0.9802</v>
+        <v>-1.6435</v>
       </c>
       <c r="I282" t="n">
-        <v>1.066683</v>
+        <v>1.009587</v>
       </c>
       <c r="J282" t="n">
         <v>-2.1259</v>
@@ -10056,13 +10056,13 @@
         <v>0.728677</v>
       </c>
       <c r="F283" t="n">
-        <v>0.8482</v>
+        <v>2.2521</v>
       </c>
       <c r="H283" t="n">
-        <v>0.8482</v>
+        <v>2.2521</v>
       </c>
       <c r="I283" t="n">
-        <v>1.075731</v>
+        <v>1.032324</v>
       </c>
       <c r="J283" t="n">
         <v>2.4572</v>
@@ -10090,13 +10090,13 @@
         <v>0.7165629999999999</v>
       </c>
       <c r="F284" t="n">
-        <v>0.3427</v>
+        <v>-0.7409</v>
       </c>
       <c r="H284" t="n">
-        <v>0.3427</v>
+        <v>-0.7409</v>
       </c>
       <c r="I284" t="n">
-        <v>1.079417</v>
+        <v>1.024675</v>
       </c>
       <c r="J284" t="n">
         <v>0.8823</v>
@@ -10124,13 +10124,13 @@
         <v>0.731376</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.0925</v>
+        <v>1.9122</v>
       </c>
       <c r="H285" t="n">
-        <v>-0.0925</v>
+        <v>1.9122</v>
       </c>
       <c r="I285" t="n">
-        <v>1.078419</v>
+        <v>1.044269</v>
       </c>
       <c r="J285" t="n">
         <v>-0.2593</v>
@@ -10158,13 +10158,13 @@
         <v>0.72627</v>
       </c>
       <c r="F286" t="n">
-        <v>0.4569</v>
+        <v>2.8888</v>
       </c>
       <c r="H286" t="n">
-        <v>0.4569</v>
+        <v>2.8888</v>
       </c>
       <c r="I286" t="n">
-        <v>1.083346</v>
+        <v>1.074436</v>
       </c>
       <c r="J286" t="n">
         <v>1.0066</v>
@@ -10192,13 +10192,13 @@
         <v>0.739109</v>
       </c>
       <c r="F287" t="n">
-        <v>0.2332</v>
+        <v>0.8184</v>
       </c>
       <c r="H287" t="n">
-        <v>0.2332</v>
+        <v>0.8184</v>
       </c>
       <c r="I287" t="n">
-        <v>1.085872</v>
+        <v>1.083229</v>
       </c>
       <c r="J287" t="n">
         <v>0.6026</v>
@@ -10226,13 +10226,13 @@
         <v>0.749651</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.3548</v>
+        <v>0.7115</v>
       </c>
       <c r="H288" t="n">
-        <v>-0.3548</v>
+        <v>0.7115</v>
       </c>
       <c r="I288" t="n">
-        <v>1.08202</v>
+        <v>1.090936</v>
       </c>
       <c r="J288" t="n">
         <v>-0.7337</v>
@@ -10260,13 +10260,13 @@
         <v>0.725111</v>
       </c>
       <c r="F289" t="n">
-        <v>0.3923</v>
+        <v>1.2662</v>
       </c>
       <c r="H289" t="n">
-        <v>0.3923</v>
+        <v>1.2662</v>
       </c>
       <c r="I289" t="n">
-        <v>1.086265</v>
+        <v>1.104749</v>
       </c>
       <c r="J289" t="n">
         <v>0.3529</v>
@@ -10294,13 +10294,13 @@
         <v>0.746923</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.3986</v>
+        <v>2.2475</v>
       </c>
       <c r="H290" t="n">
-        <v>-0.3986</v>
+        <v>2.2475</v>
       </c>
       <c r="I290" t="n">
-        <v>1.081935</v>
+        <v>1.129579</v>
       </c>
       <c r="J290" t="n">
         <v>-0.7107</v>
@@ -10328,13 +10328,13 @@
         <v>0.738077</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.1428</v>
+        <v>-2.1668</v>
       </c>
       <c r="H291" t="n">
-        <v>-0.1428</v>
+        <v>-2.1668</v>
       </c>
       <c r="I291" t="n">
-        <v>1.08039</v>
+        <v>1.105104</v>
       </c>
       <c r="J291" t="n">
         <v>-1.2125</v>
@@ -10362,13 +10362,13 @@
         <v>0.7313460000000001</v>
       </c>
       <c r="F292" t="n">
-        <v>0.4707</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="H292" t="n">
-        <v>0.4707</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="I292" t="n">
-        <v>1.085475</v>
+        <v>1.111983</v>
       </c>
       <c r="J292" t="n">
         <v>1.3748</v>
@@ -10396,13 +10396,13 @@
         <v>0.692064</v>
       </c>
       <c r="F293" t="n">
-        <v>0.5855</v>
+        <v>-2.6446</v>
       </c>
       <c r="H293" t="n">
-        <v>0.5855</v>
+        <v>-2.6446</v>
       </c>
       <c r="I293" t="n">
-        <v>1.091831</v>
+        <v>1.082576</v>
       </c>
       <c r="J293" t="n">
         <v>0.9177999999999999</v>
@@ -10430,13 +10430,13 @@
         <v>0.691302</v>
       </c>
       <c r="F294" t="n">
-        <v>0.0453</v>
+        <v>-1.2815</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0453</v>
+        <v>-1.2815</v>
       </c>
       <c r="I294" t="n">
-        <v>1.092325</v>
+        <v>1.068703</v>
       </c>
       <c r="J294" t="n">
         <v>-0.1089</v>
@@ -10464,13 +10464,13 @@
         <v>0.682215</v>
       </c>
       <c r="F295" t="n">
-        <v>-0.2552</v>
+        <v>0.4966</v>
       </c>
       <c r="H295" t="n">
-        <v>-0.2552</v>
+        <v>0.4966</v>
       </c>
       <c r="I295" t="n">
-        <v>1.089538</v>
+        <v>1.074009</v>
       </c>
       <c r="J295" t="n">
         <v>-0.8371</v>
@@ -10498,13 +10498,13 @@
         <v>0.676287</v>
       </c>
       <c r="F296" t="n">
-        <v>0.0684</v>
+        <v>-1.0238</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0684</v>
+        <v>-1.0238</v>
       </c>
       <c r="I296" t="n">
-        <v>1.090283</v>
+        <v>1.063013</v>
       </c>
       <c r="J296" t="n">
         <v>0.0973</v>
@@ -10532,13 +10532,13 @@
         <v>0.663084</v>
       </c>
       <c r="F297" t="n">
-        <v>0.0886</v>
+        <v>-1.0147</v>
       </c>
       <c r="H297" t="n">
-        <v>0.0886</v>
+        <v>-1.0147</v>
       </c>
       <c r="I297" t="n">
-        <v>1.091249</v>
+        <v>1.052227</v>
       </c>
       <c r="J297" t="n">
         <v>0.091</v>
@@ -10566,13 +10566,13 @@
         <v>0.664862</v>
       </c>
       <c r="F298" t="n">
-        <v>0.105</v>
+        <v>2.0477</v>
       </c>
       <c r="H298" t="n">
-        <v>0.105</v>
+        <v>2.0477</v>
       </c>
       <c r="I298" t="n">
-        <v>1.092395</v>
+        <v>1.073773</v>
       </c>
       <c r="J298" t="n">
         <v>-0.129</v>
@@ -10600,13 +10600,13 @@
         <v>0.65896</v>
       </c>
       <c r="F299" t="n">
-        <v>0.3721</v>
+        <v>-1.2467</v>
       </c>
       <c r="H299" t="n">
-        <v>0.3721</v>
+        <v>-1.2467</v>
       </c>
       <c r="I299" t="n">
-        <v>1.096459</v>
+        <v>1.060387</v>
       </c>
       <c r="J299" t="n">
         <v>0.7784</v>
@@ -10634,13 +10634,13 @@
         <v>0.653937</v>
       </c>
       <c r="F300" t="n">
-        <v>0.5662</v>
+        <v>-1.2848</v>
       </c>
       <c r="H300" t="n">
-        <v>0.5662</v>
+        <v>-1.2848</v>
       </c>
       <c r="I300" t="n">
-        <v>1.102668</v>
+        <v>1.046762</v>
       </c>
       <c r="J300" t="n">
         <v>0.6733</v>
@@ -10668,13 +10668,13 @@
         <v>0.642279</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.0111</v>
+        <v>-1.0436</v>
       </c>
       <c r="H301" t="n">
-        <v>-0.0111</v>
+        <v>-1.0436</v>
       </c>
       <c r="I301" t="n">
-        <v>1.102545</v>
+        <v>1.035839</v>
       </c>
       <c r="J301" t="n">
         <v>0.3343</v>
@@ -10702,13 +10702,13 @@
         <v>0.658505</v>
       </c>
       <c r="F302" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.6258</v>
       </c>
       <c r="H302" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.6258</v>
       </c>
       <c r="I302" t="n">
-        <v>1.101822</v>
+        <v>1.029357</v>
       </c>
       <c r="J302" t="n">
         <v>-0.4025</v>
@@ -10736,13 +10736,13 @@
         <v>0.647161</v>
       </c>
       <c r="F303" t="n">
-        <v>0.4165</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="H303" t="n">
-        <v>0.4165</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>1.106411</v>
+        <v>1.022399</v>
       </c>
       <c r="J303" t="n">
         <v>0.1463</v>
@@ -10770,13 +10770,13 @@
         <v>0.6586880000000001</v>
       </c>
       <c r="F304" t="n">
-        <v>-0.6365</v>
+        <v>-0.5154</v>
       </c>
       <c r="H304" t="n">
-        <v>-0.6365</v>
+        <v>-0.5154</v>
       </c>
       <c r="I304" t="n">
-        <v>1.099369</v>
+        <v>1.01713</v>
       </c>
       <c r="J304" t="n">
         <v>-1.3177</v>
@@ -10804,13 +10804,13 @@
         <v>0.6484220000000001</v>
       </c>
       <c r="F305" t="n">
-        <v>-0.3093</v>
+        <v>0.3925</v>
       </c>
       <c r="H305" t="n">
-        <v>-0.3093</v>
+        <v>0.3925</v>
       </c>
       <c r="I305" t="n">
-        <v>1.095968</v>
+        <v>1.021122</v>
       </c>
       <c r="J305" t="n">
         <v>-0.4051</v>
@@ -10838,13 +10838,13 @@
         <v>0.622624</v>
       </c>
       <c r="F306" t="n">
-        <v>0.0796</v>
+        <v>1.1615</v>
       </c>
       <c r="H306" t="n">
-        <v>0.0796</v>
+        <v>1.1615</v>
       </c>
       <c r="I306" t="n">
-        <v>1.096841</v>
+        <v>1.032982</v>
       </c>
       <c r="J306" t="n">
         <v>0.9751</v>
@@ -10872,13 +10872,13 @@
         <v>0.637787</v>
       </c>
       <c r="F307" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.3437</v>
       </c>
       <c r="H307" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.3437</v>
       </c>
       <c r="I307" t="n">
-        <v>1.090731</v>
+        <v>1.036532</v>
       </c>
       <c r="J307" t="n">
         <v>-0.8967000000000001</v>
@@ -10906,13 +10906,13 @@
         <v>0.641773</v>
       </c>
       <c r="F308" t="n">
-        <v>-0.0658</v>
+        <v>-0.8711</v>
       </c>
       <c r="H308" t="n">
-        <v>-0.0658</v>
+        <v>-0.8711</v>
       </c>
       <c r="I308" t="n">
-        <v>1.090014</v>
+        <v>1.027502</v>
       </c>
       <c r="J308" t="n">
         <v>0.099</v>
@@ -10940,13 +10940,13 @@
         <v>0.606351</v>
       </c>
       <c r="F309" t="n">
-        <v>0.3286</v>
+        <v>0.3077</v>
       </c>
       <c r="H309" t="n">
-        <v>0.3286</v>
+        <v>0.3077</v>
       </c>
       <c r="I309" t="n">
-        <v>1.093595</v>
+        <v>1.030664</v>
       </c>
       <c r="J309" t="n">
         <v>0.583</v>
@@ -10974,13 +10974,13 @@
         <v>0.5749379999999999</v>
       </c>
       <c r="F310" t="n">
-        <v>0.387</v>
+        <v>-1.0252</v>
       </c>
       <c r="H310" t="n">
-        <v>0.387</v>
+        <v>-1.0252</v>
       </c>
       <c r="I310" t="n">
-        <v>1.097828</v>
+        <v>1.020098</v>
       </c>
       <c r="J310" t="n">
         <v>0.5800999999999999</v>
@@ -11008,13 +11008,13 @@
         <v>0.558074</v>
       </c>
       <c r="F311" t="n">
-        <v>0.8957000000000001</v>
+        <v>-1.322</v>
       </c>
       <c r="H311" t="n">
-        <v>0.8957000000000001</v>
+        <v>-1.322</v>
       </c>
       <c r="I311" t="n">
-        <v>1.107661</v>
+        <v>1.006613</v>
       </c>
       <c r="J311" t="n">
         <v>1.4505</v>
@@ -11042,13 +11042,13 @@
         <v>0.568964</v>
       </c>
       <c r="F312" t="n">
-        <v>0.6797</v>
+        <v>0.5504</v>
       </c>
       <c r="H312" t="n">
-        <v>0.6797</v>
+        <v>0.5504</v>
       </c>
       <c r="I312" t="n">
-        <v>1.11519</v>
+        <v>1.012153</v>
       </c>
       <c r="J312" t="n">
         <v>1.5809</v>
@@ -11076,13 +11076,13 @@
         <v>0.544083</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.2302</v>
+        <v>-0.1374</v>
       </c>
       <c r="H313" t="n">
-        <v>-0.2302</v>
+        <v>-0.1374</v>
       </c>
       <c r="I313" t="n">
-        <v>1.112622</v>
+        <v>1.010763</v>
       </c>
       <c r="J313" t="n">
         <v>-0.5006</v>
@@ -11110,13 +11110,13 @@
         <v>0.541013</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.1726</v>
+        <v>-0.8341</v>
       </c>
       <c r="H314" t="n">
-        <v>-0.1726</v>
+        <v>-0.8341</v>
       </c>
       <c r="I314" t="n">
-        <v>1.110702</v>
+        <v>1.002332</v>
       </c>
       <c r="J314" t="n">
         <v>-0.8008999999999999</v>
@@ -11144,13 +11144,13 @@
         <v>0.523966</v>
       </c>
       <c r="F315" t="n">
-        <v>0.3223</v>
+        <v>-1.3322</v>
       </c>
       <c r="H315" t="n">
-        <v>0.3223</v>
+        <v>-1.3322</v>
       </c>
       <c r="I315" t="n">
-        <v>1.114282</v>
+        <v>0.988978</v>
       </c>
       <c r="J315" t="n">
         <v>0.4537</v>
@@ -11178,13 +11178,13 @@
         <v>0.5324</v>
       </c>
       <c r="F316" t="n">
-        <v>-0.0584</v>
+        <v>0.3181</v>
       </c>
       <c r="H316" t="n">
-        <v>-0.0584</v>
+        <v>0.3181</v>
       </c>
       <c r="I316" t="n">
-        <v>1.113631</v>
+        <v>0.992124</v>
       </c>
       <c r="J316" t="n">
         <v>-0.2948</v>
@@ -11212,13 +11212,13 @@
         <v>0.539995</v>
       </c>
       <c r="F317" t="n">
-        <v>0.3955</v>
+        <v>0.783</v>
       </c>
       <c r="H317" t="n">
-        <v>0.3955</v>
+        <v>0.783</v>
       </c>
       <c r="I317" t="n">
-        <v>1.118036</v>
+        <v>0.999893</v>
       </c>
       <c r="J317" t="n">
         <v>0.6988</v>
@@ -11246,13 +11246,13 @@
         <v>0.533146</v>
       </c>
       <c r="F318" t="n">
-        <v>0.3839</v>
+        <v>-1.1534</v>
       </c>
       <c r="H318" t="n">
-        <v>0.3839</v>
+        <v>-1.1534</v>
       </c>
       <c r="I318" t="n">
-        <v>1.122328</v>
+        <v>0.988361</v>
       </c>
       <c r="J318" t="n">
         <v>0.833</v>
@@ -11262,6 +11262,108 @@
       </c>
       <c r="M318" t="n">
         <v>1.25108</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-3.667</v>
+      </c>
+      <c r="D319" t="n">
+        <v>-3.667</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0.5135960000000001</v>
+      </c>
+      <c r="F319" t="n">
+        <v>-0.4037</v>
+      </c>
+      <c r="H319" t="n">
+        <v>-0.4037</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0.984371</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="M319" t="n">
+        <v>1.259675</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>-3.5365</v>
+      </c>
+      <c r="D320" t="n">
+        <v>-3.5365</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0.495432</v>
+      </c>
+      <c r="F320" t="n">
+        <v>-0.6613</v>
+      </c>
+      <c r="H320" t="n">
+        <v>-0.6613</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0.977862</v>
+      </c>
+      <c r="J320" t="n">
+        <v>-0.3326</v>
+      </c>
+      <c r="L320" t="n">
+        <v>-0.3326</v>
+      </c>
+      <c r="M320" t="n">
+        <v>1.255485</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>2.1281</v>
+      </c>
+      <c r="D321" t="n">
+        <v>2.1281</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0.505976</v>
+      </c>
+      <c r="F321" t="n">
+        <v>-0.0961</v>
+      </c>
+      <c r="H321" t="n">
+        <v>-0.0961</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0.976922</v>
+      </c>
+      <c r="J321" t="n">
+        <v>-2.1222</v>
+      </c>
+      <c r="L321" t="n">
+        <v>-2.1222</v>
+      </c>
+      <c r="M321" t="n">
+        <v>1.228841</v>
       </c>
     </row>
   </sheetData>
@@ -11275,7 +11377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E318"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17326,6 +17428,63 @@
       </c>
       <c r="E318" t="n">
         <v>1.84208</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-0.1644</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3.8113</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1.8235</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1.875669</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="C320" t="n">
+        <v>3.2047</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1.7732</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1.908928</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>-2.3461</v>
+      </c>
+      <c r="C321" t="n">
+        <v>-3.7034</v>
+      </c>
+      <c r="D321" t="n">
+        <v>-3.0248</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1.851187</v>
       </c>
     </row>
   </sheetData>
@@ -17339,7 +17498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E318"/>
+  <dimension ref="A1:E320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23390,6 +23549,44 @@
       </c>
       <c r="E318" t="n">
         <v>1.440396</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>-0.3067</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="D319" t="n">
+        <v>-0.6317</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1.431298</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>-0.8367</v>
+      </c>
+      <c r="C320" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="D320" t="n">
+        <v>-0.4167</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1.425334</v>
       </c>
     </row>
   </sheetData>
@@ -23403,7 +23600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G298"/>
+  <dimension ref="A1:G300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32056,6 +32253,64 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D299" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0.869098</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>-0.9016999999999999</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="D300" t="n">
+        <v>-1.1933</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.858727</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M321"/>
+  <dimension ref="A1:M322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11364,6 +11364,40 @@
       </c>
       <c r="M321" t="n">
         <v>1.228841</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>-1.6793</v>
+      </c>
+      <c r="D322" t="n">
+        <v>-1.6793</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0.497479</v>
+      </c>
+      <c r="F322" t="n">
+        <v>-1.0597</v>
+      </c>
+      <c r="H322" t="n">
+        <v>-1.0597</v>
+      </c>
+      <c r="I322" t="n">
+        <v>0.966569</v>
+      </c>
+      <c r="J322" t="n">
+        <v>1.3364</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1.3364</v>
+      </c>
+      <c r="M322" t="n">
+        <v>1.245263</v>
       </c>
     </row>
   </sheetData>
@@ -11377,7 +11411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17485,6 +17519,25 @@
       </c>
       <c r="E321" t="n">
         <v>1.851187</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>2.8389</v>
+      </c>
+      <c r="C322" t="n">
+        <v>1.5076</v>
+      </c>
+      <c r="D322" t="n">
+        <v>2.1733</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1.891418</v>
       </c>
     </row>
   </sheetData>
@@ -17498,7 +17551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E320"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23587,6 +23640,25 @@
       </c>
       <c r="E320" t="n">
         <v>1.425334</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>-2.4367</v>
+      </c>
+      <c r="C321" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="D321" t="n">
+        <v>-1.7967</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1.399725</v>
       </c>
     </row>
   </sheetData>
@@ -23600,7 +23672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G300"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32311,6 +32383,35 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026/05/21</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>-2.7083</v>
+      </c>
+      <c r="C301" t="n">
+        <v>-3.405</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.6967</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0.86471</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M322"/>
+  <dimension ref="A1:M323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11398,6 +11398,40 @@
       </c>
       <c r="M322" t="n">
         <v>1.245263</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>-5.3897</v>
+      </c>
+      <c r="D323" t="n">
+        <v>-5.3897</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0.470666</v>
+      </c>
+      <c r="F323" t="n">
+        <v>-2.5827</v>
+      </c>
+      <c r="H323" t="n">
+        <v>-2.5827</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0.9416060000000001</v>
+      </c>
+      <c r="J323" t="n">
+        <v>-1.298</v>
+      </c>
+      <c r="L323" t="n">
+        <v>-1.298</v>
+      </c>
+      <c r="M323" t="n">
+        <v>1.2291</v>
       </c>
     </row>
   </sheetData>
@@ -11411,7 +11445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E322"/>
+  <dimension ref="A1:E323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17538,6 +17572,25 @@
       </c>
       <c r="E322" t="n">
         <v>1.891418</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>2.0987</v>
+      </c>
+      <c r="C323" t="n">
+        <v>5.8782</v>
+      </c>
+      <c r="D323" t="n">
+        <v>3.9884</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1.966856</v>
       </c>
     </row>
   </sheetData>
@@ -17551,7 +17604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23659,6 +23712,25 @@
       </c>
       <c r="E321" t="n">
         <v>1.399725</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1.2767</v>
+      </c>
+      <c r="C322" t="n">
+        <v>-0.905</v>
+      </c>
+      <c r="D322" t="n">
+        <v>2.1817</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1.430263</v>
       </c>
     </row>
   </sheetData>
@@ -23672,7 +23744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32412,6 +32484,35 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C302" t="n">
+        <v>2.9783</v>
+      </c>
+      <c r="D302" t="n">
+        <v>-1.8083</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.849073</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M323"/>
+  <dimension ref="A1:M324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11432,6 +11432,40 @@
       </c>
       <c r="M323" t="n">
         <v>1.2291</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>1.5845</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1.5845</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0.478124</v>
+      </c>
+      <c r="F324" t="n">
+        <v>-1.2197</v>
+      </c>
+      <c r="H324" t="n">
+        <v>-1.2197</v>
+      </c>
+      <c r="I324" t="n">
+        <v>0.930121</v>
+      </c>
+      <c r="J324" t="n">
+        <v>-2.3199</v>
+      </c>
+      <c r="L324" t="n">
+        <v>-2.3199</v>
+      </c>
+      <c r="M324" t="n">
+        <v>1.200586</v>
       </c>
     </row>
   </sheetData>
@@ -11445,7 +11479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E323"/>
+  <dimension ref="A1:E324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17591,6 +17625,25 @@
       </c>
       <c r="E323" t="n">
         <v>1.966856</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="C324" t="n">
+        <v>-1.4941</v>
+      </c>
+      <c r="D324" t="n">
+        <v>-0.4747</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1.957521</v>
       </c>
     </row>
   </sheetData>
@@ -17604,7 +17657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E322"/>
+  <dimension ref="A1:E323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23731,6 +23784,25 @@
       </c>
       <c r="E322" t="n">
         <v>1.430263</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0.8433</v>
+      </c>
+      <c r="C323" t="n">
+        <v>-0.215</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1.0583</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1.4454</v>
       </c>
     </row>
   </sheetData>
@@ -23744,7 +23816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:G303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32513,6 +32585,35 @@
         </is>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>-0.0883</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1.7117</v>
+      </c>
+      <c r="D303" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0.833789</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M324"/>
+  <dimension ref="A1:M325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11466,6 +11466,40 @@
       </c>
       <c r="M324" t="n">
         <v>1.200586</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>1.8996</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1.8996</v>
+      </c>
+      <c r="E325" t="n">
+        <v>0.487206</v>
+      </c>
+      <c r="F325" t="n">
+        <v>-0.1037</v>
+      </c>
+      <c r="H325" t="n">
+        <v>-0.1037</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0.929156</v>
+      </c>
+      <c r="J325" t="n">
+        <v>-1.2752</v>
+      </c>
+      <c r="L325" t="n">
+        <v>-1.2752</v>
+      </c>
+      <c r="M325" t="n">
+        <v>1.185276</v>
       </c>
     </row>
   </sheetData>
@@ -11479,7 +11513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E324"/>
+  <dimension ref="A1:E325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17644,6 +17678,25 @@
       </c>
       <c r="E324" t="n">
         <v>1.957521</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="C325" t="n">
+        <v>-2.7979</v>
+      </c>
+      <c r="D325" t="n">
+        <v>-1.3654</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1.930792</v>
       </c>
     </row>
   </sheetData>
@@ -17657,7 +17710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E323"/>
+  <dimension ref="A1:E324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23803,6 +23856,25 @@
       </c>
       <c r="E323" t="n">
         <v>1.4454</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="C324" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1.6967</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1.469923</v>
       </c>
     </row>
   </sheetData>
@@ -23816,7 +23888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32614,6 +32686,35 @@
         </is>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="C304" t="n">
+        <v>-0.3983</v>
+      </c>
+      <c r="D304" t="n">
+        <v>-0.4117</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.830357</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>美容护理, 综合, 社会服务, 钢铁, 煤炭, 纺织服饰</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>电子, 电力设备, 通信, 机械设备, 有色金属, 计算机</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/size_spread/style_spread.xlsx
+++ b/size_spread/style_spread.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M332"/>
+  <dimension ref="A1:M331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11704,40 +11704,6 @@
       </c>
       <c r="M331" t="n">
         <v>1.161674</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="B332" t="n">
-        <v>4.0529</v>
-      </c>
-      <c r="D332" t="n">
-        <v>4.0529</v>
-      </c>
-      <c r="E332" t="n">
-        <v>0.539994</v>
-      </c>
-      <c r="F332" t="n">
-        <v>1.7547</v>
-      </c>
-      <c r="H332" t="n">
-        <v>1.7547</v>
-      </c>
-      <c r="I332" t="n">
-        <v>0.917184</v>
-      </c>
-      <c r="J332" t="n">
-        <v>1.914</v>
-      </c>
-      <c r="L332" t="n">
-        <v>1.914</v>
-      </c>
-      <c r="M332" t="n">
-        <v>1.183909</v>
       </c>
     </row>
   </sheetData>
@@ -11751,7 +11717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18277,25 +18243,6 @@
       </c>
       <c r="E343" t="n">
         <v>1.695853</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>-3.2026</v>
-      </c>
-      <c r="C344" t="n">
-        <v>-4.0119</v>
-      </c>
-      <c r="D344" t="n">
-        <v>-3.6072</v>
-      </c>
-      <c r="E344" t="n">
-        <v>1.700741</v>
       </c>
     </row>
   </sheetData>
